--- a/docs/downloads/2026-09-28/bursa-report-2026-09-28.xlsx
+++ b/docs/downloads/2026-09-28/bursa-report-2026-09-28.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-09-28" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-09-28'!$A$1:$M$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-09-28'!$A$1:$M$108</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -38,13 +38,13 @@
       <color rgb="000CA30C"/>
     </font>
     <font>
+      <color rgb="00898781"/>
+    </font>
+    <font>
       <color rgb="00D03B3B"/>
     </font>
-    <font>
-      <color rgb="00898781"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -54,6 +54,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="002F3E4E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EEEAF8"/>
       </patternFill>
     </fill>
   </fills>
@@ -69,22 +74,31 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -450,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -536,94 +550,110 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>表格</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>4723</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>JAKS</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>0.175</v>
-      </c>
-      <c r="E2" s="3" t="n">
-        <v>0.0294</v>
-      </c>
-      <c r="F2" s="4" t="n">
-        <v>7502000</v>
-      </c>
-      <c r="G2" s="5" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="H2" t="n">
-        <v>75</v>
-      </c>
-      <c r="I2" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="n">
-        <v>0.145</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>0.116</v>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" s="7" t="inlineStr"/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>信号</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>5291</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>HPMT</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>0.0698</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>5419600</v>
+      </c>
+      <c r="G2" s="6" t="n">
+        <v>24.55</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>74.75</v>
+      </c>
+      <c r="I2" s="7" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>0.199</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>0.186</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>🎯 EMA(5) ≥ EMA(20) + SAR &lt; 当前价格 + Supertrend(3,1.4) &lt; 当前价格 + RSI(14) 上穿 70 + 成交量 &gt; 5000000</t>
+        </is>
+      </c>
+      <c r="M2" s="8" t="inlineStr">
+        <is>
+          <t>RSI达74.75，已进入超买区；现价0.23高于50日均线0.186约24%，短期均线多头排列，信号偏强但需留意超买风险。</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>表格</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>8877</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>EKOVEST</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>0.0286</v>
-      </c>
-      <c r="F3" s="4" t="n">
-        <v>3502000</v>
-      </c>
-      <c r="G3" s="5" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="H3" t="n">
-        <v>47.52</v>
-      </c>
-      <c r="I3" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="n">
-        <v>0.179</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>0.189</v>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" s="7" t="inlineStr"/>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>信号</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>7204</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>D&amp;O</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>0.0467</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>5308000</v>
+      </c>
+      <c r="G3" s="6" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>71.27</v>
+      </c>
+      <c r="I3" s="7" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>0.475</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>0.401</v>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>🎯 EMA(5) ≥ EMA(20) + SAR &lt; 当前价格 + Supertrend(3,1.4) &lt; 当前价格 + RSI(14) 上穿 70 + 成交量 &gt; 5000000</t>
+        </is>
+      </c>
+      <c r="M3" s="8" t="inlineStr">
+        <is>
+          <t>EMA与SAR、Supertrend均偏多，但RSI达71.27已入超买区，现价高于50日均线约40%，短期偏离较大，信号可靠性需谨慎看待。</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -633,42 +663,33 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>0473</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>GIIB</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="E4" s="8" t="n">
-        <v>-0.008500000000000001</v>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>1894700</v>
-      </c>
-      <c r="G4" s="5" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="H4" t="n">
-        <v>68.72</v>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="n">
-        <v>0.547</v>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>0.493</v>
-      </c>
+          <t>Evocom Berhad</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="E4" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="11" t="n">
+        <v>37346700</v>
+      </c>
+      <c r="G4" s="12" t="n"/>
+      <c r="I4" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J4" s="9" t="n"/>
+      <c r="K4" s="9" t="n"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" s="7" t="inlineStr"/>
+      <c r="M4" s="14" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -678,42 +699,42 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="E5" s="8" t="n">
-        <v>-0.0132</v>
-      </c>
-      <c r="F5" s="4" t="n">
-        <v>1462500</v>
-      </c>
-      <c r="G5" s="5" t="n">
-        <v>0.03</v>
+          <t>JAKS</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="n">
+        <v>0.185</v>
+      </c>
+      <c r="E5" s="15" t="n">
+        <v>0.0882</v>
+      </c>
+      <c r="F5" s="11" t="n">
+        <v>34318800</v>
+      </c>
+      <c r="G5" s="12" t="n">
+        <v>0.76</v>
       </c>
       <c r="H5" t="n">
-        <v>74.89</v>
-      </c>
-      <c r="I5" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="n">
-        <v>0.318</v>
-      </c>
-      <c r="K5" s="2" t="n">
-        <v>0.184</v>
+        <v>77.83</v>
+      </c>
+      <c r="I5" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="n">
+        <v>0.146</v>
+      </c>
+      <c r="K5" s="9" t="n">
+        <v>0.116</v>
       </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" s="7" t="inlineStr"/>
+      <c r="M5" s="14" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -723,42 +744,42 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>VELESTO</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="E6" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>1455000</v>
-      </c>
-      <c r="G6" s="5" t="n">
-        <v>0.07000000000000001</v>
+          <t>INARI</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="E6" s="17" t="n">
+        <v>-0.0414</v>
+      </c>
+      <c r="F6" s="11" t="n">
+        <v>25883500</v>
+      </c>
+      <c r="G6" s="12" t="n">
+        <v>1.36</v>
       </c>
       <c r="H6" t="n">
-        <v>32.26</v>
-      </c>
-      <c r="I6" s="10" t="inlineStr">
+        <v>49.39</v>
+      </c>
+      <c r="I6" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J6" s="2" t="n">
-        <v>0.239</v>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>0.249</v>
+      <c r="J6" s="9" t="n">
+        <v>2.587</v>
+      </c>
+      <c r="K6" s="9" t="n">
+        <v>2.44</v>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" s="7" t="inlineStr"/>
+      <c r="M6" s="14" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -768,42 +789,42 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>8877</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>INARI</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="E7" s="8" t="n">
-        <v>-0.0301</v>
-      </c>
-      <c r="F7" s="4" t="n">
-        <v>978100</v>
-      </c>
-      <c r="G7" s="5" t="n">
-        <v>0.05</v>
+          <t>EKOVEST</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>0.185</v>
+      </c>
+      <c r="E7" s="15" t="n">
+        <v>0.0571</v>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>13042100</v>
+      </c>
+      <c r="G7" s="12" t="n">
+        <v>3.12</v>
       </c>
       <c r="H7" t="n">
-        <v>51.54</v>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="K7" s="2" t="n">
-        <v>2.441</v>
+        <v>55.81</v>
+      </c>
+      <c r="I7" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J7" s="9" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="K7" s="9" t="n">
+        <v>0.189</v>
       </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" s="7" t="inlineStr"/>
+      <c r="M7" s="14" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -813,42 +834,42 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>NATGATE</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="E8" s="8" t="n">
-        <v>-0.0053</v>
-      </c>
-      <c r="F8" s="4" t="n">
-        <v>681300</v>
-      </c>
-      <c r="G8" s="5" t="n">
-        <v>0.03</v>
+          <t>TOPGLOV</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="E8" s="17" t="n">
+        <v>-0.0331</v>
+      </c>
+      <c r="F8" s="11" t="n">
+        <v>12497100</v>
+      </c>
+      <c r="G8" s="12" t="n">
+        <v>0.29</v>
       </c>
       <c r="H8" t="n">
-        <v>64.91</v>
-      </c>
-      <c r="I8" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="K8" s="2" t="n">
-        <v>1.525</v>
+        <v>51.13</v>
+      </c>
+      <c r="I8" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J8" s="9" t="n">
+        <v>0.736</v>
+      </c>
+      <c r="K8" s="9" t="n">
+        <v>0.6830000000000001</v>
       </c>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" s="7" t="inlineStr"/>
+      <c r="M8" s="14" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -858,45 +879,4500 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>7106</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>SUPERMX</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="E9" s="17" t="n">
+        <v>-0.0595</v>
+      </c>
+      <c r="F9" s="11" t="n">
+        <v>9824200</v>
+      </c>
+      <c r="G9" s="12" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H9" t="n">
+        <v>56.63</v>
+      </c>
+      <c r="I9" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J9" s="9" t="n">
+        <v>0.382</v>
+      </c>
+      <c r="K9" s="9" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" s="14" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>7117</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CJCEN</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E10" s="15" t="n">
+        <v>0.08109999999999999</v>
+      </c>
+      <c r="F10" s="11" t="n">
+        <v>8867100</v>
+      </c>
+      <c r="G10" s="12" t="n">
+        <v>20.96</v>
+      </c>
+      <c r="H10" t="n">
+        <v>82.14</v>
+      </c>
+      <c r="I10" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J10" s="9" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="K10" s="9" t="n">
+        <v>0.163</v>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" s="14" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>6963</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>VS</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>0.245</v>
+      </c>
+      <c r="E11" s="15" t="n">
+        <v>0.0426</v>
+      </c>
+      <c r="F11" s="11" t="n">
+        <v>8777600</v>
+      </c>
+      <c r="G11" s="12" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="H11" t="n">
+        <v>59.1</v>
+      </c>
+      <c r="I11" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J11" s="9" t="n">
+        <v>0.232</v>
+      </c>
+      <c r="K11" s="9" t="n">
+        <v>0.233</v>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" s="14" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
           <t>0318</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>ELRIDGE</t>
         </is>
       </c>
-      <c r="D9" s="2" t="n">
+      <c r="D12" s="9" t="n">
+        <v>0.945</v>
+      </c>
+      <c r="E12" s="17" t="n">
+        <v>-0.0053</v>
+      </c>
+      <c r="F12" s="11" t="n">
+        <v>8460400</v>
+      </c>
+      <c r="G12" s="12" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="H12" t="n">
+        <v>75.98999999999999</v>
+      </c>
+      <c r="I12" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J12" s="9" t="n">
+        <v>0.884</v>
+      </c>
+      <c r="K12" s="9" t="n">
+        <v>0.851</v>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" s="14" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>0275</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>OPPSTAR</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="E13" s="15" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="F13" s="11" t="n">
+        <v>8260600</v>
+      </c>
+      <c r="G13" s="12" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="H13" t="n">
+        <v>57.43</v>
+      </c>
+      <c r="I13" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J13" s="9" t="n">
+        <v>0.6820000000000001</v>
+      </c>
+      <c r="K13" s="9" t="n">
+        <v>0.663</v>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" s="14" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>0270</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NATGATE</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="E14" s="17" t="n">
+        <v>-0.0214</v>
+      </c>
+      <c r="F14" s="11" t="n">
+        <v>7747800</v>
+      </c>
+      <c r="G14" s="12" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="H14" t="n">
+        <v>61.84</v>
+      </c>
+      <c r="I14" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J14" s="9" t="n">
+        <v>1.737</v>
+      </c>
+      <c r="K14" s="9" t="n">
+        <v>1.524</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" s="14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>7215</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NIHSIN</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="E15" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="11" t="n">
+        <v>7619500</v>
+      </c>
+      <c r="G15" s="12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H15" t="n">
+        <v>76.97</v>
+      </c>
+      <c r="I15" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J15" s="9" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="K15" s="9" t="n">
+        <v>0.184</v>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" s="14" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0259</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>SNS</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="n">
+        <v>0.545</v>
+      </c>
+      <c r="E16" s="15" t="n">
+        <v>0.0381</v>
+      </c>
+      <c r="F16" s="11" t="n">
+        <v>6933100</v>
+      </c>
+      <c r="G16" s="12" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="H16" t="n">
+        <v>60.7</v>
+      </c>
+      <c r="I16" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J16" s="9" t="n">
+        <v>0.521</v>
+      </c>
+      <c r="K16" s="9" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" s="14" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>7192</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>GIIB</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="E17" s="17" t="n">
+        <v>-0.008500000000000001</v>
+      </c>
+      <c r="F17" s="11" t="n">
+        <v>6672400</v>
+      </c>
+      <c r="G17" s="12" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H17" t="n">
+        <v>68.72</v>
+      </c>
+      <c r="I17" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J17" s="9" t="n">
+        <v>0.547</v>
+      </c>
+      <c r="K17" s="9" t="n">
+        <v>0.493</v>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" s="14" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>5218</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>VANTNRG</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="E18" s="17" t="n">
+        <v>-0.0143</v>
+      </c>
+      <c r="F18" s="11" t="n">
+        <v>5971300</v>
+      </c>
+      <c r="G18" s="12" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="H18" t="n">
+        <v>57.32</v>
+      </c>
+      <c r="I18" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J18" s="9" t="n">
+        <v>0.339</v>
+      </c>
+      <c r="K18" s="9" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" s="14" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0373</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>VERDANT</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="E19" s="15" t="n">
+        <v>0.05769999999999999</v>
+      </c>
+      <c r="F19" s="11" t="n">
+        <v>5392200</v>
+      </c>
+      <c r="G19" s="12" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="H19" t="n">
+        <v>83.03</v>
+      </c>
+      <c r="I19" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J19" s="9" t="n">
+        <v>0.224</v>
+      </c>
+      <c r="K19" s="9" t="n">
+        <v>0.209</v>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" s="14" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>5238</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>AAGB</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="E20" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="11" t="n">
+        <v>5200400</v>
+      </c>
+      <c r="G20" s="12" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H20" t="n">
+        <v>26.93</v>
+      </c>
+      <c r="I20" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J20" s="9" t="n">
+        <v>0.634</v>
+      </c>
+      <c r="K20" s="9" t="n">
+        <v>0.851</v>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" s="14" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>0248</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>YEWLEE</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="n">
+        <v>0.605</v>
+      </c>
+      <c r="E21" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="11" t="n">
+        <v>4538800</v>
+      </c>
+      <c r="G21" s="12" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="H21" t="n">
+        <v>48.07</v>
+      </c>
+      <c r="I21" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J21" s="9" t="n">
+        <v>0.608</v>
+      </c>
+      <c r="K21" s="9" t="n">
+        <v>0.604</v>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" s="14" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>3174</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>L&amp;G</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="E22" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="11" t="n">
+        <v>4456400</v>
+      </c>
+      <c r="G22" s="12" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H22" t="n">
+        <v>71.25</v>
+      </c>
+      <c r="I22" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J22" s="9" t="n">
+        <v>0.202</v>
+      </c>
+      <c r="K22" s="9" t="n">
+        <v>0.184</v>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" s="14" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>4456</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>DNEX</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="E23" s="15" t="n">
+        <v>0.0105</v>
+      </c>
+      <c r="F23" s="11" t="n">
+        <v>4405500</v>
+      </c>
+      <c r="G23" s="12" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H23" t="n">
+        <v>54.71</v>
+      </c>
+      <c r="I23" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J23" s="9" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="K23" s="9" t="n">
+        <v>0.471</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" s="14" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>0280</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>MBN</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="n">
+        <v>0.155</v>
+      </c>
+      <c r="E24" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="11" t="n">
+        <v>4377900</v>
+      </c>
+      <c r="G24" s="12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="H24" t="n">
+        <v>52.85</v>
+      </c>
+      <c r="I24" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J24" s="9" t="n">
+        <v>0.154</v>
+      </c>
+      <c r="K24" s="9" t="n">
+        <v>0.147</v>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" s="14" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>5078</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>M&amp;G</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E25" s="17" t="n">
+        <v>-0.0323</v>
+      </c>
+      <c r="F25" s="11" t="n">
+        <v>4308900</v>
+      </c>
+      <c r="G25" s="12" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H25" t="n">
+        <v>49.23</v>
+      </c>
+      <c r="I25" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J25" s="9" t="n">
+        <v>0.303</v>
+      </c>
+      <c r="K25" s="9" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" s="14" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>0175</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>HHRG</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E26" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="11" t="n">
+        <v>4050900</v>
+      </c>
+      <c r="G26" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H26" t="n">
+        <v>47.65</v>
+      </c>
+      <c r="I26" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J26" s="9" t="n">
+        <v>0.158</v>
+      </c>
+      <c r="K26" s="9" t="n">
+        <v>0.148</v>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" s="14" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2429</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>TANCO</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="E27" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="11" t="n">
+        <v>3845700</v>
+      </c>
+      <c r="G27" s="12" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H27" t="n">
+        <v>34.17</v>
+      </c>
+      <c r="I27" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J27" s="9" t="n">
+        <v>0.182</v>
+      </c>
+      <c r="K27" s="9" t="n">
+        <v>0.221</v>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" s="14" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>0138</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>ZETRIX</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="n">
+        <v>0.195</v>
+      </c>
+      <c r="E28" s="15" t="n">
+        <v>0.0263</v>
+      </c>
+      <c r="F28" s="11" t="n">
+        <v>3749600</v>
+      </c>
+      <c r="G28" s="12" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H28" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="I28" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J28" s="9" t="n">
+        <v>0.276</v>
+      </c>
+      <c r="K28" s="9" t="n">
+        <v>0.492</v>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" s="14" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>5099</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>CAPITALA</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="E29" s="17" t="n">
+        <v>-0.0204</v>
+      </c>
+      <c r="F29" s="11" t="n">
+        <v>3603200</v>
+      </c>
+      <c r="G29" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H29" t="n">
+        <v>30.78</v>
+      </c>
+      <c r="I29" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J29" s="9" t="n">
+        <v>0.276</v>
+      </c>
+      <c r="K29" s="9" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" s="14" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>0192</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>INTA</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="E30" s="15" t="n">
+        <v>0.0476</v>
+      </c>
+      <c r="F30" s="11" t="n">
+        <v>3533800</v>
+      </c>
+      <c r="G30" s="12" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="H30" t="n">
+        <v>73.38</v>
+      </c>
+      <c r="I30" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J30" s="9" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="K30" s="9" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" s="14" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>5161</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>JCY</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E31" s="15" t="n">
+        <v>0.0092</v>
+      </c>
+      <c r="F31" s="11" t="n">
+        <v>3485700</v>
+      </c>
+      <c r="G31" s="12" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H31" t="n">
+        <v>59.13</v>
+      </c>
+      <c r="I31" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J31" s="9" t="n">
+        <v>0.523</v>
+      </c>
+      <c r="K31" s="9" t="n">
+        <v>0.476</v>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" s="14" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>8052</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>CGB</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="n">
+        <v>0.865</v>
+      </c>
+      <c r="E32" s="15" t="n">
+        <v>0.0058</v>
+      </c>
+      <c r="F32" s="11" t="n">
+        <v>3473900</v>
+      </c>
+      <c r="G32" s="12" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H32" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="I32" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J32" s="9" t="n">
+        <v>0.868</v>
+      </c>
+      <c r="K32" s="9" t="n">
+        <v>0.871</v>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" s="14" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>5243</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>VELESTO</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="n">
+        <v>0.215</v>
+      </c>
+      <c r="E33" s="17" t="n">
+        <v>-0.0227</v>
+      </c>
+      <c r="F33" s="11" t="n">
+        <v>3364600</v>
+      </c>
+      <c r="G33" s="12" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H33" t="n">
+        <v>29.99</v>
+      </c>
+      <c r="I33" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J33" s="9" t="n">
+        <v>0.238</v>
+      </c>
+      <c r="K33" s="9" t="n">
+        <v>0.249</v>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" s="14" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>0111</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="E34" s="15" t="n">
+        <v>0.0313</v>
+      </c>
+      <c r="F34" s="11" t="n">
+        <v>3301000</v>
+      </c>
+      <c r="G34" s="12" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="H34" t="n">
+        <v>66.66</v>
+      </c>
+      <c r="I34" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J34" s="9" t="n">
+        <v>0.148</v>
+      </c>
+      <c r="K34" s="9" t="n">
+        <v>0.139</v>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" s="14" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>0345</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>SUNLOGY</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="E35" s="17" t="n">
+        <v>-0.0213</v>
+      </c>
+      <c r="F35" s="11" t="n">
+        <v>3264000</v>
+      </c>
+      <c r="G35" s="12" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="H35" t="n">
+        <v>55.64</v>
+      </c>
+      <c r="I35" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J35" s="9" t="n">
+        <v>0.447</v>
+      </c>
+      <c r="K35" s="9" t="n">
+        <v>0.407</v>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" s="14" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>0262</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>SUNVIEW</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="E36" s="15" t="n">
+        <v>0.0132</v>
+      </c>
+      <c r="F36" s="11" t="n">
+        <v>3259200</v>
+      </c>
+      <c r="G36" s="12" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H36" t="n">
+        <v>63.96</v>
+      </c>
+      <c r="I36" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J36" s="9" t="n">
+        <v>0.373</v>
+      </c>
+      <c r="K36" s="9" t="n">
+        <v>0.371</v>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" s="14" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>5151</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>HEXTAR</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="E37" s="17" t="n">
+        <v>-0.006500000000000001</v>
+      </c>
+      <c r="F37" s="11" t="n">
+        <v>3131000</v>
+      </c>
+      <c r="G37" s="12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H37" t="n">
+        <v>47.75</v>
+      </c>
+      <c r="I37" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J37" s="9" t="n">
+        <v>0.774</v>
+      </c>
+      <c r="K37" s="9" t="n">
+        <v>0.774</v>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" s="14" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>3336</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>IJM</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E38" s="17" t="n">
+        <v>-0.009899999999999999</v>
+      </c>
+      <c r="F38" s="11" t="n">
+        <v>3079500</v>
+      </c>
+      <c r="G38" s="12" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H38" t="n">
+        <v>67.31999999999999</v>
+      </c>
+      <c r="I38" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J38" s="9" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="K38" s="9" t="n">
+        <v>2.716</v>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" s="14" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>8893</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>MKLAND</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="E39" s="15" t="n">
+        <v>0.0286</v>
+      </c>
+      <c r="F39" s="11" t="n">
+        <v>3069700</v>
+      </c>
+      <c r="G39" s="12" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="H39" t="n">
+        <v>81.90000000000001</v>
+      </c>
+      <c r="I39" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J39" s="9" t="n">
+        <v>0.152</v>
+      </c>
+      <c r="K39" s="9" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" s="14" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>5398</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>GAMUDA</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="E40" s="17" t="n">
+        <v>-0.0061</v>
+      </c>
+      <c r="F40" s="11" t="n">
+        <v>3065600</v>
+      </c>
+      <c r="G40" s="12" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H40" t="n">
+        <v>61.73</v>
+      </c>
+      <c r="I40" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J40" s="9" t="n">
+        <v>4.739</v>
+      </c>
+      <c r="K40" s="9" t="n">
+        <v>4.509</v>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" s="14" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>9059</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>TSH</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="E41" s="17" t="n">
+        <v>-0.0365</v>
+      </c>
+      <c r="F41" s="11" t="n">
+        <v>2870200</v>
+      </c>
+      <c r="G41" s="12" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="H41" t="n">
+        <v>39.48</v>
+      </c>
+      <c r="I41" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J41" s="9" t="n">
+        <v>1.406</v>
+      </c>
+      <c r="K41" s="9" t="n">
+        <v>1.317</v>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" s="14" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>7155</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>SKPRES</t>
+        </is>
+      </c>
+      <c r="D42" s="9" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="E42" s="15" t="n">
+        <v>0.0139</v>
+      </c>
+      <c r="F42" s="11" t="n">
+        <v>2527800</v>
+      </c>
+      <c r="G42" s="12" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="H42" t="n">
+        <v>67.36</v>
+      </c>
+      <c r="I42" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J42" s="9" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="K42" s="9" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" s="14" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>0457</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>PENTECH</t>
+        </is>
+      </c>
+      <c r="D43" s="9" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="E43" s="15" t="n">
+        <v>0.0154</v>
+      </c>
+      <c r="F43" s="11" t="n">
+        <v>2345800</v>
+      </c>
+      <c r="G43" s="12" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H43" t="n">
+        <v>52.72</v>
+      </c>
+      <c r="I43" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J43" s="9" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="K43" s="9" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" s="14" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>5184</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>CYPARK</t>
+        </is>
+      </c>
+      <c r="D44" s="9" t="n">
+        <v>0.825</v>
+      </c>
+      <c r="E44" s="15" t="n">
+        <v>0.0061</v>
+      </c>
+      <c r="F44" s="11" t="n">
+        <v>2331100</v>
+      </c>
+      <c r="G44" s="12" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H44" t="n">
+        <v>70.64</v>
+      </c>
+      <c r="I44" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J44" s="9" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="K44" s="9" t="n">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" s="14" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>0193</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>KINERGY</t>
+        </is>
+      </c>
+      <c r="D45" s="9" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="E45" s="17" t="n">
+        <v>-0.0119</v>
+      </c>
+      <c r="F45" s="11" t="n">
+        <v>2288600</v>
+      </c>
+      <c r="G45" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H45" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="I45" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J45" s="9" t="n">
+        <v>0.409</v>
+      </c>
+      <c r="K45" s="9" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" s="14" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>0024</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>JAG</t>
+        </is>
+      </c>
+      <c r="D46" s="9" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="E46" s="17" t="n">
+        <v>-0.0135</v>
+      </c>
+      <c r="F46" s="11" t="n">
+        <v>2283900</v>
+      </c>
+      <c r="G46" s="12" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="H46" t="n">
+        <v>48.52</v>
+      </c>
+      <c r="I46" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J46" s="9" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="K46" s="9" t="n">
+        <v>0.366</v>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" s="14" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>5311</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>CEB</t>
+        </is>
+      </c>
+      <c r="D47" s="9" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="E47" s="15" t="n">
+        <v>0.0172</v>
+      </c>
+      <c r="F47" s="11" t="n">
+        <v>2167400</v>
+      </c>
+      <c r="G47" s="12" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H47" t="n">
+        <v>66.27</v>
+      </c>
+      <c r="I47" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J47" s="9" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="K47" s="9" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" s="14" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>0310</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>UUE</t>
+        </is>
+      </c>
+      <c r="D48" s="9" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="E48" s="17" t="n">
+        <v>-0.0333</v>
+      </c>
+      <c r="F48" s="11" t="n">
+        <v>2144500</v>
+      </c>
+      <c r="G48" s="12" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="H48" t="n">
+        <v>61.83</v>
+      </c>
+      <c r="I48" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J48" s="9" t="n">
+        <v>0.6820000000000001</v>
+      </c>
+      <c r="K48" s="9" t="n">
+        <v>0.611</v>
+      </c>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" s="14" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>0393</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>TEAMSTR</t>
+        </is>
+      </c>
+      <c r="D49" s="9" t="n">
+        <v>0.225</v>
+      </c>
+      <c r="E49" s="17" t="n">
+        <v>-0.0217</v>
+      </c>
+      <c r="F49" s="11" t="n">
+        <v>2047000</v>
+      </c>
+      <c r="G49" s="12" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="H49" t="n">
+        <v>28.13</v>
+      </c>
+      <c r="I49" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J49" s="9" t="n">
+        <v>0.243</v>
+      </c>
+      <c r="K49" s="9" t="n">
+        <v>0.243</v>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" s="14" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>4324</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>HENGYUAN</t>
+        </is>
+      </c>
+      <c r="D50" s="9" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="E50" s="15" t="n">
+        <v>0.0299</v>
+      </c>
+      <c r="F50" s="11" t="n">
+        <v>1976400</v>
+      </c>
+      <c r="G50" s="12" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H50" t="n">
+        <v>80.06</v>
+      </c>
+      <c r="I50" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J50" s="9" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="K50" s="9" t="n">
+        <v>2.356</v>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" s="14" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>7153</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>KOSSAN</t>
+        </is>
+      </c>
+      <c r="D51" s="9" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="E51" s="17" t="n">
+        <v>-0.0417</v>
+      </c>
+      <c r="F51" s="11" t="n">
+        <v>1952600</v>
+      </c>
+      <c r="G51" s="12" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H51" t="n">
+        <v>50.13</v>
+      </c>
+      <c r="I51" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J51" s="9" t="n">
+        <v>1.163</v>
+      </c>
+      <c r="K51" s="9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" s="14" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>0340</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>NORTHERN</t>
+        </is>
+      </c>
+      <c r="D52" s="9" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="E52" s="17" t="n">
+        <v>-0.007800000000000001</v>
+      </c>
+      <c r="F52" s="11" t="n">
+        <v>1821000</v>
+      </c>
+      <c r="G52" s="12" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="H52" t="n">
+        <v>93.52</v>
+      </c>
+      <c r="I52" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J52" s="9" t="n">
+        <v>0.878</v>
+      </c>
+      <c r="K52" s="9" t="n">
+        <v>0.733</v>
+      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" s="14" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>0225</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>SCGBHD</t>
+        </is>
+      </c>
+      <c r="D53" s="9" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="E53" s="17" t="n">
+        <v>-0.0382</v>
+      </c>
+      <c r="F53" s="11" t="n">
+        <v>1768700</v>
+      </c>
+      <c r="G53" s="12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H53" t="n">
+        <v>59.76</v>
+      </c>
+      <c r="I53" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J53" s="9" t="n">
+        <v>2.624</v>
+      </c>
+      <c r="K53" s="9" t="n">
+        <v>2.495</v>
+      </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" s="14" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>4197</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>SIME</t>
+        </is>
+      </c>
+      <c r="D54" s="9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E54" s="15" t="n">
+        <v>0.0121</v>
+      </c>
+      <c r="F54" s="11" t="n">
+        <v>1756900</v>
+      </c>
+      <c r="G54" s="12" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H54" t="n">
+        <v>61.94</v>
+      </c>
+      <c r="I54" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J54" s="9" t="n">
+        <v>2.439</v>
+      </c>
+      <c r="K54" s="9" t="n">
+        <v>2.276</v>
+      </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" s="14" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>0338</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>KOPI</t>
+        </is>
+      </c>
+      <c r="D55" s="9" t="n">
+        <v>0.925</v>
+      </c>
+      <c r="E55" s="15" t="n">
+        <v>0.0278</v>
+      </c>
+      <c r="F55" s="11" t="n">
+        <v>1706800</v>
+      </c>
+      <c r="G55" s="12" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="H55" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="I55" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J55" s="9" t="n">
+        <v>0.928</v>
+      </c>
+      <c r="K55" s="9" t="n">
+        <v>0.969</v>
+      </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" s="14" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>5555</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>SUNMED</t>
+        </is>
+      </c>
+      <c r="D56" s="9" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="E56" s="15" t="n">
+        <v>0.009599999999999999</v>
+      </c>
+      <c r="F56" s="11" t="n">
+        <v>1659400</v>
+      </c>
+      <c r="G56" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H56" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="I56" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J56" s="9" t="n">
+        <v>2.129</v>
+      </c>
+      <c r="K56" s="9" t="n">
+        <v>2.062</v>
+      </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" s="14" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>0369</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>JSSOLAR</t>
+        </is>
+      </c>
+      <c r="D57" s="9" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="E57" s="15" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="F57" s="11" t="n">
+        <v>1596700</v>
+      </c>
+      <c r="G57" s="12" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="H57" t="n">
+        <v>73.58</v>
+      </c>
+      <c r="I57" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J57" s="9" t="n">
+        <v>0.212</v>
+      </c>
+      <c r="K57" s="9" t="n">
+        <v>0.198</v>
+      </c>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" s="14" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>0208</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>GREATEC</t>
+        </is>
+      </c>
+      <c r="D58" s="9" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="E58" s="17" t="n">
+        <v>-0.0267</v>
+      </c>
+      <c r="F58" s="11" t="n">
+        <v>1588100</v>
+      </c>
+      <c r="G58" s="12" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H58" t="n">
+        <v>48.43</v>
+      </c>
+      <c r="I58" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J58" s="9" t="n">
+        <v>2.568</v>
+      </c>
+      <c r="K58" s="9" t="n">
+        <v>2.535</v>
+      </c>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" s="14" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>5148</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>UEMS</t>
+        </is>
+      </c>
+      <c r="D59" s="9" t="n">
+        <v>0.545</v>
+      </c>
+      <c r="E59" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" s="11" t="n">
+        <v>1531400</v>
+      </c>
+      <c r="G59" s="12" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H59" t="n">
+        <v>39.08</v>
+      </c>
+      <c r="I59" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J59" s="9" t="n">
+        <v>0.5610000000000001</v>
+      </c>
+      <c r="K59" s="9" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" s="14" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>1651</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>MRCB</t>
+        </is>
+      </c>
+      <c r="D60" s="9" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="E60" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" s="11" t="n">
+        <v>1489300</v>
+      </c>
+      <c r="G60" s="12" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H60" t="n">
+        <v>39.08</v>
+      </c>
+      <c r="I60" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J60" s="9" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="K60" s="9" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" s="14" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>6742</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>YTLPOWR</t>
+        </is>
+      </c>
+      <c r="D61" s="9" t="n">
+        <v>5.81</v>
+      </c>
+      <c r="E61" s="17" t="n">
+        <v>-0.0136</v>
+      </c>
+      <c r="F61" s="11" t="n">
+        <v>1469700</v>
+      </c>
+      <c r="G61" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H61" t="n">
+        <v>59.45</v>
+      </c>
+      <c r="I61" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J61" s="9" t="n">
+        <v>5.687</v>
+      </c>
+      <c r="K61" s="9" t="n">
+        <v>5.131</v>
+      </c>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" s="14" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>5102</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>GCB</t>
+        </is>
+      </c>
+      <c r="D62" s="9" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="E62" s="17" t="n">
+        <v>-0.0227</v>
+      </c>
+      <c r="F62" s="11" t="n">
+        <v>1450400</v>
+      </c>
+      <c r="G62" s="12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H62" t="n">
+        <v>41.16</v>
+      </c>
+      <c r="I62" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J62" s="9" t="n">
+        <v>1.372</v>
+      </c>
+      <c r="K62" s="9" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" s="14" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>0455</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>BUSCAP</t>
+        </is>
+      </c>
+      <c r="D63" s="9" t="n">
+        <v>0.545</v>
+      </c>
+      <c r="E63" s="17" t="n">
+        <v>-0.0091</v>
+      </c>
+      <c r="F63" s="11" t="n">
+        <v>1444500</v>
+      </c>
+      <c r="G63" s="12" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="H63" t="n">
+        <v>62.16</v>
+      </c>
+      <c r="I63" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J63" s="9" t="n">
+        <v>0.498</v>
+      </c>
+      <c r="K63" s="9" t="n">
+        <v>0.401</v>
+      </c>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" s="14" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>4243</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>WTK</t>
+        </is>
+      </c>
+      <c r="D64" s="9" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="E64" s="17" t="n">
+        <v>-0.0408</v>
+      </c>
+      <c r="F64" s="11" t="n">
+        <v>1440600</v>
+      </c>
+      <c r="G64" s="12" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="H64" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="I64" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J64" s="9" t="n">
+        <v>1.043</v>
+      </c>
+      <c r="K64" s="9" t="n">
+        <v>1.014</v>
+      </c>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" s="14" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>5168</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>HARTA</t>
+        </is>
+      </c>
+      <c r="D65" s="9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="E65" s="17" t="n">
+        <v>-0.0364</v>
+      </c>
+      <c r="F65" s="11" t="n">
+        <v>1440400</v>
+      </c>
+      <c r="G65" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H65" t="n">
+        <v>48.58</v>
+      </c>
+      <c r="I65" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J65" s="9" t="n">
+        <v>1.082</v>
+      </c>
+      <c r="K65" s="9" t="n">
+        <v>1.024</v>
+      </c>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" s="14" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>8907</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="D66" s="9" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="E66" s="17" t="n">
+        <v>-0.0112</v>
+      </c>
+      <c r="F66" s="11" t="n">
+        <v>1365700</v>
+      </c>
+      <c r="G66" s="12" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H66" t="n">
+        <v>47.93</v>
+      </c>
+      <c r="I66" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J66" s="9" t="n">
+        <v>1.771</v>
+      </c>
+      <c r="K66" s="9" t="n">
+        <v>1.806</v>
+      </c>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" s="14" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>4677</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>YTL</t>
+        </is>
+      </c>
+      <c r="D67" s="9" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="E67" s="17" t="n">
+        <v>-0.0167</v>
+      </c>
+      <c r="F67" s="11" t="n">
+        <v>1355400</v>
+      </c>
+      <c r="G67" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H67" t="n">
+        <v>51.33</v>
+      </c>
+      <c r="I67" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J67" s="9" t="n">
+        <v>2.348</v>
+      </c>
+      <c r="K67" s="9" t="n">
+        <v>2.239</v>
+      </c>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" s="14" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>5327</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>MEGAFB</t>
+        </is>
+      </c>
+      <c r="D68" s="9" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E68" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" s="11" t="n">
+        <v>1322500</v>
+      </c>
+      <c r="G68" s="12" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H68" t="n">
+        <v>82.34999999999999</v>
+      </c>
+      <c r="I68" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J68" s="9" t="n">
+        <v>2.461</v>
+      </c>
+      <c r="K68" s="9" t="n">
+        <v>2.119</v>
+      </c>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" s="14" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>0358</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>ICTZONE</t>
+        </is>
+      </c>
+      <c r="D69" s="9" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="E69" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" s="11" t="n">
+        <v>1289900</v>
+      </c>
+      <c r="G69" s="12" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="H69" t="n">
+        <v>50.51</v>
+      </c>
+      <c r="I69" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J69" s="9" t="n">
+        <v>0.262</v>
+      </c>
+      <c r="K69" s="9" t="n">
+        <v>0.251</v>
+      </c>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" s="14" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>1155</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>MAYBANK</t>
+        </is>
+      </c>
+      <c r="D70" s="9" t="n">
+        <v>10.18</v>
+      </c>
+      <c r="E70" s="17" t="n">
+        <v>-0.0039</v>
+      </c>
+      <c r="F70" s="11" t="n">
+        <v>1272000</v>
+      </c>
+      <c r="G70" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H70" t="n">
+        <v>47.99</v>
+      </c>
+      <c r="I70" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J70" s="9" t="n">
+        <v>10.177</v>
+      </c>
+      <c r="K70" s="9" t="n">
+        <v>10.321</v>
+      </c>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" s="14" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>7121</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="D71" s="9" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="E71" s="15" t="n">
+        <v>0.0062</v>
+      </c>
+      <c r="F71" s="11" t="n">
+        <v>1252600</v>
+      </c>
+      <c r="G71" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H71" t="n">
+        <v>52.51</v>
+      </c>
+      <c r="I71" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J71" s="9" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="K71" s="9" t="n">
+        <v>0.8080000000000001</v>
+      </c>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" s="14" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>0272</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>TTVHB</t>
+        </is>
+      </c>
+      <c r="D72" s="9" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E72" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" s="11" t="n">
+        <v>1236100</v>
+      </c>
+      <c r="G72" s="12" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="H72" t="n">
+        <v>49.72</v>
+      </c>
+      <c r="I72" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J72" s="9" t="n">
+        <v>0.249</v>
+      </c>
+      <c r="K72" s="9" t="n">
+        <v>0.253</v>
+      </c>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" s="14" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>0083</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>NOTION</t>
+        </is>
+      </c>
+      <c r="D73" s="9" t="n">
+        <v>0.665</v>
+      </c>
+      <c r="E73" s="15" t="n">
+        <v>0.0076</v>
+      </c>
+      <c r="F73" s="11" t="n">
+        <v>1232500</v>
+      </c>
+      <c r="G73" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H73" t="n">
+        <v>60.68</v>
+      </c>
+      <c r="I73" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J73" s="9" t="n">
+        <v>0.634</v>
+      </c>
+      <c r="K73" s="9" t="n">
+        <v>0.574</v>
+      </c>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" s="14" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>5296</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>MRDIY</t>
+        </is>
+      </c>
+      <c r="D74" s="9" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="E74" s="15" t="n">
+        <v>0.0155</v>
+      </c>
+      <c r="F74" s="11" t="n">
+        <v>1232000</v>
+      </c>
+      <c r="G74" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H74" t="n">
+        <v>39.66</v>
+      </c>
+      <c r="I74" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J74" s="9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="K74" s="9" t="n">
+        <v>1.445</v>
+      </c>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" s="14" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>0236</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>RAMSSOL</t>
+        </is>
+      </c>
+      <c r="D75" s="9" t="n">
+        <v>0.765</v>
+      </c>
+      <c r="E75" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" s="11" t="n">
+        <v>1119000</v>
+      </c>
+      <c r="G75" s="12" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H75" t="n">
+        <v>46.13</v>
+      </c>
+      <c r="I75" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J75" s="9" t="n">
+        <v>0.773</v>
+      </c>
+      <c r="K75" s="9" t="n">
+        <v>0.773</v>
+      </c>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" s="14" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>0112</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>MIKROMB</t>
+        </is>
+      </c>
+      <c r="D76" s="9" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E76" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" s="11" t="n">
+        <v>1117900</v>
+      </c>
+      <c r="G76" s="12" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="H76" t="n">
+        <v>70.55</v>
+      </c>
+      <c r="I76" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J76" s="9" t="n">
+        <v>0.634</v>
+      </c>
+      <c r="K76" s="9" t="n">
+        <v>0.591</v>
+      </c>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" s="14" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>5216</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>NEXG</t>
+        </is>
+      </c>
+      <c r="D77" s="9" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="E77" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" s="11" t="n">
+        <v>1102400</v>
+      </c>
+      <c r="G77" s="12" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H77" t="n">
+        <v>65.18000000000001</v>
+      </c>
+      <c r="I77" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J77" s="9" t="n">
+        <v>0.284</v>
+      </c>
+      <c r="K77" s="9" t="n">
+        <v>0.277</v>
+      </c>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" s="14" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>3379</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>INSAS</t>
+        </is>
+      </c>
+      <c r="D78" s="9" t="n">
+        <v>0.905</v>
+      </c>
+      <c r="E78" s="15" t="n">
+        <v>0.0226</v>
+      </c>
+      <c r="F78" s="11" t="n">
+        <v>1086600</v>
+      </c>
+      <c r="G78" s="12" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="H78" t="n">
+        <v>57.27</v>
+      </c>
+      <c r="I78" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J78" s="9" t="n">
+        <v>0.895</v>
+      </c>
+      <c r="K78" s="9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" s="14" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>0127</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>JHM</t>
+        </is>
+      </c>
+      <c r="D79" s="9" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="E79" s="17" t="n">
+        <v>-0.0189</v>
+      </c>
+      <c r="F79" s="11" t="n">
+        <v>1078800</v>
+      </c>
+      <c r="G79" s="12" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H79" t="n">
+        <v>55.42</v>
+      </c>
+      <c r="I79" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J79" s="9" t="n">
+        <v>0.512</v>
+      </c>
+      <c r="K79" s="9" t="n">
+        <v>0.464</v>
+      </c>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" s="14" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>0450</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>MFGROUP</t>
+        </is>
+      </c>
+      <c r="D80" s="9" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="E80" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" s="11" t="n">
+        <v>1052600</v>
+      </c>
+      <c r="G80" s="12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="H80" t="n">
+        <v>45.51</v>
+      </c>
+      <c r="I80" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J80" s="9" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="K80" s="9" t="n">
+        <v>0.266</v>
+      </c>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" s="14" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>0268</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>L&amp;PBHD</t>
+        </is>
+      </c>
+      <c r="D81" s="9" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="E81" s="15" t="n">
+        <v>0.0244</v>
+      </c>
+      <c r="F81" s="11" t="n">
+        <v>1044700</v>
+      </c>
+      <c r="G81" s="12" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="H81" t="n">
+        <v>71.81999999999999</v>
+      </c>
+      <c r="I81" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J81" s="9" t="n">
+        <v>0.187</v>
+      </c>
+      <c r="K81" s="9" t="n">
+        <v>0.156</v>
+      </c>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" s="14" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>0265</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>INFOM</t>
+        </is>
+      </c>
+      <c r="D82" s="9" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="E82" s="15" t="n">
+        <v>0.0311</v>
+      </c>
+      <c r="F82" s="11" t="n">
+        <v>1029900</v>
+      </c>
+      <c r="G82" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="H82" t="n">
+        <v>70.11</v>
+      </c>
+      <c r="I82" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J82" s="9" t="n">
+        <v>1.587</v>
+      </c>
+      <c r="K82" s="9" t="n">
+        <v>1.535</v>
+      </c>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" s="14" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>8524</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>TALIWRK</t>
+        </is>
+      </c>
+      <c r="D83" s="9" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="E83" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" s="11" t="n">
+        <v>1011300</v>
+      </c>
+      <c r="G83" s="12" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="H83" t="n">
+        <v>54.09</v>
+      </c>
+      <c r="I83" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J83" s="9" t="n">
+        <v>0.254</v>
+      </c>
+      <c r="K83" s="9" t="n">
+        <v>0.271</v>
+      </c>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" s="14" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>5210</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>ARMADA</t>
+        </is>
+      </c>
+      <c r="D84" s="9" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E84" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F84" s="11" t="n">
+        <v>1008100</v>
+      </c>
+      <c r="G84" s="12" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H84" t="n">
+        <v>47.96</v>
+      </c>
+      <c r="I84" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J84" s="9" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="K84" s="9" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" s="14" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>3182</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>GENTING</t>
+        </is>
+      </c>
+      <c r="D85" s="9" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="E85" s="15" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="F85" s="11" t="n">
+        <v>929700</v>
+      </c>
+      <c r="G85" s="12" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H85" t="n">
+        <v>39.51</v>
+      </c>
+      <c r="I85" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J85" s="9" t="n">
+        <v>1.958</v>
+      </c>
+      <c r="K85" s="9" t="n">
+        <v>2.079</v>
+      </c>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" s="14" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>0453</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>EIPOWER</t>
+        </is>
+      </c>
+      <c r="D86" s="9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="E86" s="17" t="n">
+        <v>-0.009399999999999999</v>
+      </c>
+      <c r="F86" s="11" t="n">
+        <v>888400</v>
+      </c>
+      <c r="G86" s="12" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H86" t="n">
+        <v>79.73</v>
+      </c>
+      <c r="I86" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J86" s="9" t="n">
+        <v>0.894</v>
+      </c>
+      <c r="K86" s="9" t="n">
+        <v>0.759</v>
+      </c>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" s="14" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>0215</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>SLVEST</t>
+        </is>
+      </c>
+      <c r="D87" s="9" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="E87" s="15" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="F87" s="11" t="n">
+        <v>858000</v>
+      </c>
+      <c r="G87" s="12" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H87" t="n">
+        <v>78.42</v>
+      </c>
+      <c r="I87" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J87" s="9" t="n">
+        <v>3.536</v>
+      </c>
+      <c r="K87" s="9" t="n">
+        <v>3.224</v>
+      </c>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" s="14" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>0376</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>IAB</t>
+        </is>
+      </c>
+      <c r="D88" s="9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E88" s="15" t="n">
+        <v>0.0236</v>
+      </c>
+      <c r="F88" s="11" t="n">
+        <v>845300</v>
+      </c>
+      <c r="G88" s="12" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="H88" t="n">
+        <v>50.37</v>
+      </c>
+      <c r="I88" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J88" s="9" t="n">
+        <v>1.284</v>
+      </c>
+      <c r="K88" s="9" t="n">
+        <v>1.345</v>
+      </c>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" s="14" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>0296</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>HEGROUP</t>
+        </is>
+      </c>
+      <c r="D89" s="9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="E89" s="17" t="n">
+        <v>-0.0357</v>
+      </c>
+      <c r="F89" s="11" t="n">
+        <v>840700</v>
+      </c>
+      <c r="G89" s="12" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H89" t="n">
+        <v>74.36</v>
+      </c>
+      <c r="I89" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J89" s="9" t="n">
+        <v>0.972</v>
+      </c>
+      <c r="K89" s="9" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" s="14" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>0045</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>SSB8</t>
+        </is>
+      </c>
+      <c r="D90" s="9" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="E90" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F90" s="11" t="n">
+        <v>811100</v>
+      </c>
+      <c r="G90" s="12" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H90" t="n">
+        <v>64.06999999999999</v>
+      </c>
+      <c r="I90" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J90" s="9" t="n">
+        <v>0.621</v>
+      </c>
+      <c r="K90" s="9" t="n">
+        <v>0.582</v>
+      </c>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" s="14" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>6888</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>AXIATA</t>
+        </is>
+      </c>
+      <c r="D91" s="9" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="E91" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" s="11" t="n">
+        <v>799100</v>
+      </c>
+      <c r="G91" s="12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H91" t="n">
+        <v>30.25</v>
+      </c>
+      <c r="I91" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J91" s="9" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="K91" s="9" t="n">
+        <v>1.847</v>
+      </c>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" s="14" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>0321</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>SDCG</t>
+        </is>
+      </c>
+      <c r="D92" s="9" t="n">
+        <v>0.785</v>
+      </c>
+      <c r="E92" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" s="11" t="n">
+        <v>735900</v>
+      </c>
+      <c r="G92" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H92" t="n">
+        <v>86.31</v>
+      </c>
+      <c r="I92" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J92" s="9" t="n">
+        <v>0.767</v>
+      </c>
+      <c r="K92" s="9" t="n">
+        <v>0.752</v>
+      </c>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" s="14" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>0196</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>QES</t>
+        </is>
+      </c>
+      <c r="D93" s="9" t="n">
+        <v>0.585</v>
+      </c>
+      <c r="E93" s="17" t="n">
+        <v>-0.0168</v>
+      </c>
+      <c r="F93" s="11" t="n">
+        <v>715500</v>
+      </c>
+      <c r="G93" s="12" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H93" t="n">
+        <v>54.34</v>
+      </c>
+      <c r="I93" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J93" s="9" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="K93" s="9" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" s="14" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>0271</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>WELLS</t>
+        </is>
+      </c>
+      <c r="D94" s="9" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="E94" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" s="11" t="n">
+        <v>700000</v>
+      </c>
+      <c r="G94" s="12" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="H94" t="n">
+        <v>48.02</v>
+      </c>
+      <c r="I94" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J94" s="9" t="n">
+        <v>0.631</v>
+      </c>
+      <c r="K94" s="9" t="n">
+        <v>0.637</v>
+      </c>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" s="14" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>5301</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>CTOS</t>
+        </is>
+      </c>
+      <c r="D95" s="9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E95" s="17" t="n">
+        <v>-0.0164</v>
+      </c>
+      <c r="F95" s="11" t="n">
+        <v>692700</v>
+      </c>
+      <c r="G95" s="12" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H95" t="n">
+        <v>35.76</v>
+      </c>
+      <c r="I95" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J95" s="9" t="n">
+        <v>0.637</v>
+      </c>
+      <c r="K95" s="9" t="n">
+        <v>0.657</v>
+      </c>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" s="14" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>5073</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>NAIM</t>
+        </is>
+      </c>
+      <c r="D96" s="9" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E96" s="17" t="n">
+        <v>-0.0455</v>
+      </c>
+      <c r="F96" s="11" t="n">
+        <v>689100</v>
+      </c>
+      <c r="G96" s="12" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="H96" t="n">
+        <v>59.12</v>
+      </c>
+      <c r="I96" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J96" s="9" t="n">
+        <v>0.629</v>
+      </c>
+      <c r="K96" s="9" t="n">
+        <v>0.612</v>
+      </c>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" s="14" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>0459</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>SUM</t>
+        </is>
+      </c>
+      <c r="D97" s="9" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="E97" s="15" t="n">
+        <v>0.0069</v>
+      </c>
+      <c r="F97" s="11" t="n">
+        <v>680700</v>
+      </c>
+      <c r="G97" s="12" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H97" t="n">
+        <v>70.06</v>
+      </c>
+      <c r="I97" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J97" s="9" t="n">
+        <v>0.672</v>
+      </c>
+      <c r="K97" s="9" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" s="14" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>5302</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>ATECH</t>
+        </is>
+      </c>
+      <c r="D98" s="9" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="E98" s="15" t="n">
+        <v>0.0131</v>
+      </c>
+      <c r="F98" s="11" t="n">
+        <v>664600</v>
+      </c>
+      <c r="G98" s="12" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="H98" t="n">
+        <v>53.99</v>
+      </c>
+      <c r="I98" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J98" s="9" t="n">
+        <v>0.765</v>
+      </c>
+      <c r="K98" s="9" t="n">
+        <v>0.755</v>
+      </c>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" s="14" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>5317</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>CPETECH</t>
+        </is>
+      </c>
+      <c r="D99" s="9" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="E99" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" s="11" t="n">
+        <v>662900</v>
+      </c>
+      <c r="G99" s="12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H99" t="n">
+        <v>58.59</v>
+      </c>
+      <c r="I99" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J99" s="9" t="n">
+        <v>1.241</v>
+      </c>
+      <c r="K99" s="9" t="n">
+        <v>1.138</v>
+      </c>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" s="14" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>5249</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>IOIPG</t>
+        </is>
+      </c>
+      <c r="D100" s="9" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="E100" s="17" t="n">
+        <v>-0.005699999999999999</v>
+      </c>
+      <c r="F100" s="11" t="n">
+        <v>640400</v>
+      </c>
+      <c r="G100" s="12" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H100" t="n">
+        <v>35.51</v>
+      </c>
+      <c r="I100" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J100" s="9" t="n">
+        <v>3.612</v>
+      </c>
+      <c r="K100" s="9" t="n">
+        <v>3.703</v>
+      </c>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" s="14" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>0339</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>CBHB</t>
+        </is>
+      </c>
+      <c r="D101" s="9" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="E101" s="15" t="n">
+        <v>0.0091</v>
+      </c>
+      <c r="F101" s="11" t="n">
+        <v>635600</v>
+      </c>
+      <c r="G101" s="12" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H101" t="n">
+        <v>80.17</v>
+      </c>
+      <c r="I101" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J101" s="9" t="n">
+        <v>1.007</v>
+      </c>
+      <c r="K101" s="9" t="n">
+        <v>0.845</v>
+      </c>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" s="14" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>8583</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>MAHSING</t>
+        </is>
+      </c>
+      <c r="D102" s="9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="E102" s="17" t="n">
+        <v>-0.0098</v>
+      </c>
+      <c r="F102" s="11" t="n">
+        <v>624000</v>
+      </c>
+      <c r="G102" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H102" t="n">
+        <v>36.47</v>
+      </c>
+      <c r="I102" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J102" s="9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="K102" s="9" t="n">
+        <v>1.074</v>
+      </c>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" s="14" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>0292</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>JTGROUP</t>
+        </is>
+      </c>
+      <c r="D103" s="9" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="E103" s="15" t="n">
+        <v>0.0161</v>
+      </c>
+      <c r="F103" s="11" t="n">
+        <v>611300</v>
+      </c>
+      <c r="G103" s="12" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H103" t="n">
+        <v>83.94</v>
+      </c>
+      <c r="I103" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J103" s="9" t="n">
+        <v>1.045</v>
+      </c>
+      <c r="K103" s="9" t="n">
+        <v>0.888</v>
+      </c>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" s="14" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>0217</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>PWRWELL</t>
+        </is>
+      </c>
+      <c r="D104" s="9" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="E104" s="17" t="n">
+        <v>-0.025</v>
+      </c>
+      <c r="F104" s="11" t="n">
+        <v>575500</v>
+      </c>
+      <c r="G104" s="12" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H104" t="n">
+        <v>64.58</v>
+      </c>
+      <c r="I104" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J104" s="9" t="n">
+        <v>1.107</v>
+      </c>
+      <c r="K104" s="9" t="n">
+        <v>1.007</v>
+      </c>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" s="14" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>0391</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>AMBEST</t>
+        </is>
+      </c>
+      <c r="D105" s="9" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="E105" s="17" t="n">
+        <v>-0.0143</v>
+      </c>
+      <c r="F105" s="11" t="n">
+        <v>569300</v>
+      </c>
+      <c r="G105" s="12" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H105" t="n">
+        <v>58.09</v>
+      </c>
+      <c r="I105" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J105" s="9" t="n">
+        <v>1.345</v>
+      </c>
+      <c r="K105" s="9" t="n">
+        <v>1.148</v>
+      </c>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" s="14" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>5005</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>UNISEM</t>
+        </is>
+      </c>
+      <c r="D106" s="9" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="E106" s="17" t="n">
+        <v>-0.0066</v>
+      </c>
+      <c r="F106" s="11" t="n">
+        <v>527200</v>
+      </c>
+      <c r="G106" s="12" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H106" t="n">
+        <v>55.65</v>
+      </c>
+      <c r="I106" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J106" s="9" t="n">
+        <v>4.415</v>
+      </c>
+      <c r="K106" s="9" t="n">
+        <v>4.431</v>
+      </c>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" s="14" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>4383</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>JTIASA</t>
+        </is>
+      </c>
+      <c r="D107" s="9" t="n">
         <v>0.955</v>
       </c>
-      <c r="E9" s="3" t="n">
-        <v>0.0053</v>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>523800</v>
-      </c>
-      <c r="G9" s="5" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="H9" t="n">
-        <v>79.48999999999999</v>
-      </c>
-      <c r="I9" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="n">
-        <v>0.885</v>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>0.851</v>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" s="7" t="inlineStr"/>
+      <c r="E107" s="17" t="n">
+        <v>-0.0052</v>
+      </c>
+      <c r="F107" s="11" t="n">
+        <v>505400</v>
+      </c>
+      <c r="G107" s="12" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H107" t="n">
+        <v>35.25</v>
+      </c>
+      <c r="I107" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J107" s="9" t="n">
+        <v>0.998</v>
+      </c>
+      <c r="K107" s="9" t="n">
+        <v>1.047</v>
+      </c>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" s="14" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>5199</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>HIBISCS</t>
+        </is>
+      </c>
+      <c r="D108" s="9" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="E108" s="15" t="n">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="F108" s="11" t="n">
+        <v>504200</v>
+      </c>
+      <c r="G108" s="12" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H108" t="n">
+        <v>53.76</v>
+      </c>
+      <c r="I108" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J108" s="9" t="n">
+        <v>2.226</v>
+      </c>
+      <c r="K108" s="9" t="n">
+        <v>2.104</v>
+      </c>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" s="14" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M9"/>
+  <autoFilter ref="A1:M108"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-09-28/bursa-report-2026-09-28.xlsx
+++ b/docs/downloads/2026-09-28/bursa-report-2026-09-28.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-09-28" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-09-28'!$A$1:$M$108</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-09-28'!$A$1:$M$130</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -38,10 +38,10 @@
       <color rgb="000CA30C"/>
     </font>
     <font>
-      <color rgb="00898781"/>
+      <color rgb="00D03B3B"/>
     </font>
     <font>
-      <color rgb="00D03B3B"/>
+      <color rgb="00898781"/>
     </font>
   </fonts>
   <fills count="4">
@@ -92,13 +92,13 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M108"/>
+  <dimension ref="A1:M130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -572,10 +572,10 @@
         <v>0.0698</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>5419600</v>
+        <v>5696100</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>24.55</v>
+        <v>25.81</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>74.75</v>
@@ -625,10 +625,10 @@
         <v>0.0467</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>5308000</v>
+        <v>5874800</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>0.37</v>
+        <v>0.4</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>71.27</v>
@@ -651,7 +651,7 @@
       </c>
       <c r="M3" s="8" t="inlineStr">
         <is>
-          <t>EMA与SAR、Supertrend均偏多，但RSI达71.27已入超买区，现价高于50日均线约40%，短期偏离较大，信号可靠性需谨慎看待。</t>
+          <t>现价0.56高于50日均线0.401，RSI达71.27已入超买区，EMA与Supertrend偏多，但RSI偏高，信号可靠性需谨慎看待。</t>
         </is>
       </c>
     </row>
@@ -663,31 +663,40 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0473</t>
+          <t>0138</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Evocom Berhad</t>
+          <t>ZETRIX</t>
         </is>
       </c>
       <c r="D4" s="9" t="n">
-        <v>0.13</v>
+        <v>0.185</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>0</v>
+        <v>-0.0263</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>37346700</v>
-      </c>
-      <c r="G4" s="12" t="n"/>
+        <v>45871700</v>
+      </c>
+      <c r="G4" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H4" t="n">
+        <v>22.18</v>
+      </c>
       <c r="I4" s="13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J4" s="9" t="n"/>
-      <c r="K4" s="9" t="n"/>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J4" s="9" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="K4" s="9" t="n">
+        <v>0.491</v>
+      </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" s="14" t="inlineStr"/>
     </row>
@@ -699,40 +708,31 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>0473</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>JAKS</t>
+          <t>Evocom Berhad</t>
         </is>
       </c>
       <c r="D5" s="9" t="n">
-        <v>0.185</v>
+        <v>0.135</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>0.0882</v>
+        <v>0</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>34318800</v>
-      </c>
-      <c r="G5" s="12" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="H5" t="n">
-        <v>77.83</v>
-      </c>
-      <c r="I5" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J5" s="9" t="n">
-        <v>0.146</v>
-      </c>
-      <c r="K5" s="9" t="n">
-        <v>0.116</v>
-      </c>
+        <v>44333700</v>
+      </c>
+      <c r="G5" s="12" t="n"/>
+      <c r="I5" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="n"/>
+      <c r="K5" s="9" t="n"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" s="14" t="inlineStr"/>
     </row>
@@ -744,39 +744,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D6" s="9" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="E6" s="17" t="n">
-        <v>-0.0414</v>
+        <v>0.18</v>
+      </c>
+      <c r="E6" s="16" t="n">
+        <v>0.0588</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>25883500</v>
+        <v>40917900</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>1.36</v>
+        <v>0.9</v>
       </c>
       <c r="H6" t="n">
-        <v>49.39</v>
-      </c>
-      <c r="I6" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>76.5</v>
+      </c>
+      <c r="I6" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J6" s="9" t="n">
-        <v>2.587</v>
+        <v>0.146</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>2.44</v>
+        <v>0.116</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="14" t="inlineStr"/>
@@ -789,39 +789,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>8877</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>EKOVEST</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.185</v>
-      </c>
-      <c r="E7" s="15" t="n">
-        <v>0.0571</v>
+        <v>2.55</v>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>-0.0414</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>13042100</v>
+        <v>28253900</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>3.12</v>
+        <v>1.48</v>
       </c>
       <c r="H7" t="n">
-        <v>55.81</v>
-      </c>
-      <c r="I7" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.39</v>
+      </c>
+      <c r="I7" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J7" s="9" t="n">
-        <v>0.18</v>
+        <v>2.587</v>
       </c>
       <c r="K7" s="9" t="n">
-        <v>0.189</v>
+        <v>2.44</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="14" t="inlineStr"/>
@@ -843,19 +843,19 @@
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="E8" s="17" t="n">
-        <v>-0.0331</v>
+        <v>0.72</v>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>-0.0464</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>12497100</v>
+        <v>18113200</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>0.29</v>
+        <v>0.42</v>
       </c>
       <c r="H8" t="n">
-        <v>51.13</v>
+        <v>49.15</v>
       </c>
       <c r="I8" s="13" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="J8" s="9" t="n">
-        <v>0.736</v>
+        <v>0.735</v>
       </c>
       <c r="K8" s="9" t="n">
         <v>0.6830000000000001</v>
@@ -879,39 +879,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>8877</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>EKOVEST</t>
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.395</v>
-      </c>
-      <c r="E9" s="17" t="n">
-        <v>-0.0595</v>
+        <v>0.185</v>
+      </c>
+      <c r="E9" s="16" t="n">
+        <v>0.0571</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>9824200</v>
+        <v>14113000</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>0.45</v>
+        <v>3.38</v>
       </c>
       <c r="H9" t="n">
-        <v>56.63</v>
-      </c>
-      <c r="I9" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.81</v>
+      </c>
+      <c r="I9" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J9" s="9" t="n">
-        <v>0.382</v>
+        <v>0.18</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>0.32</v>
+        <v>0.189</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="14" t="inlineStr"/>
@@ -924,39 +924,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>7117</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CJCEN</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E10" s="15" t="n">
-        <v>0.08109999999999999</v>
+        <v>0.395</v>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>-0.0595</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>8867100</v>
+        <v>10029600</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>20.96</v>
+        <v>0.46</v>
       </c>
       <c r="H10" t="n">
-        <v>82.14</v>
-      </c>
-      <c r="I10" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>56.63</v>
+      </c>
+      <c r="I10" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J10" s="9" t="n">
-        <v>0.172</v>
+        <v>0.382</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>0.163</v>
+        <v>0.32</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="14" t="inlineStr"/>
@@ -969,39 +969,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>0.245</v>
-      </c>
-      <c r="E11" s="15" t="n">
-        <v>0.0426</v>
+        <v>0.55</v>
+      </c>
+      <c r="E11" s="16" t="n">
+        <v>0.0476</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>8777600</v>
+        <v>9921000</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>0.49</v>
+        <v>1.7</v>
       </c>
       <c r="H11" t="n">
-        <v>59.1</v>
-      </c>
-      <c r="I11" s="16" t="inlineStr">
+        <v>62.28</v>
+      </c>
+      <c r="I11" s="17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J11" s="9" t="n">
-        <v>0.232</v>
+        <v>0.521</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>0.233</v>
+        <v>0.531</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="14" t="inlineStr"/>
@@ -1014,39 +1014,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>7117</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>CJCEN</t>
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>0.945</v>
-      </c>
-      <c r="E12" s="17" t="n">
-        <v>-0.0053</v>
+        <v>0.2</v>
+      </c>
+      <c r="E12" s="16" t="n">
+        <v>0.08109999999999999</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>8460400</v>
+        <v>9491200</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>2.09</v>
+        <v>22.43</v>
       </c>
       <c r="H12" t="n">
-        <v>75.98999999999999</v>
-      </c>
-      <c r="I12" s="16" t="inlineStr">
+        <v>82.14</v>
+      </c>
+      <c r="I12" s="17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J12" s="9" t="n">
-        <v>0.884</v>
+        <v>0.172</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>0.851</v>
+        <v>0.163</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="14" t="inlineStr"/>
@@ -1059,39 +1059,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="E13" s="15" t="n">
-        <v>0.036</v>
+        <v>0.24</v>
+      </c>
+      <c r="E13" s="16" t="n">
+        <v>0.0213</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>8260600</v>
+        <v>9485400</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>0.89</v>
+        <v>0.53</v>
       </c>
       <c r="H13" t="n">
-        <v>57.43</v>
-      </c>
-      <c r="I13" s="16" t="inlineStr">
+        <v>56.39</v>
+      </c>
+      <c r="I13" s="17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J13" s="9" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.232</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>0.663</v>
+        <v>0.233</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="14" t="inlineStr"/>
@@ -1104,39 +1104,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="E14" s="17" t="n">
-        <v>-0.0214</v>
+        <v>0.37</v>
+      </c>
+      <c r="E14" s="10" t="n">
+        <v>-0.0263</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>7747800</v>
+        <v>9449500</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>0.31</v>
+        <v>0.21</v>
       </c>
       <c r="H14" t="n">
-        <v>61.84</v>
-      </c>
-      <c r="I14" s="16" t="inlineStr">
+        <v>72.92</v>
+      </c>
+      <c r="I14" s="17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J14" s="9" t="n">
-        <v>1.737</v>
+        <v>0.318</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>1.524</v>
+        <v>0.183</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="14" t="inlineStr"/>
@@ -1149,39 +1149,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E15" s="10" t="n">
-        <v>0</v>
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="E15" s="16" t="n">
+        <v>0.0367</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>7619500</v>
+        <v>8919600</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>0.17</v>
+        <v>0.66</v>
       </c>
       <c r="H15" t="n">
-        <v>76.97</v>
-      </c>
-      <c r="I15" s="16" t="inlineStr">
+        <v>61.86</v>
+      </c>
+      <c r="I15" s="17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J15" s="9" t="n">
-        <v>0.319</v>
+        <v>0.525</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>0.184</v>
+        <v>0.477</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="14" t="inlineStr"/>
@@ -1194,39 +1194,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>0.545</v>
-      </c>
-      <c r="E16" s="15" t="n">
-        <v>0.0381</v>
+        <v>0.72</v>
+      </c>
+      <c r="E16" s="16" t="n">
+        <v>0.036</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>6933100</v>
+        <v>8763800</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>1.19</v>
+        <v>0.95</v>
       </c>
       <c r="H16" t="n">
-        <v>60.7</v>
-      </c>
-      <c r="I16" s="16" t="inlineStr">
+        <v>57.43</v>
+      </c>
+      <c r="I16" s="17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J16" s="9" t="n">
-        <v>0.521</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>0.531</v>
+        <v>0.663</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="14" t="inlineStr"/>
@@ -1239,39 +1239,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="E17" s="17" t="n">
-        <v>-0.008500000000000001</v>
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="E17" s="10" t="n">
+        <v>-0.0158</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>6672400</v>
+        <v>8734500</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>0.28</v>
+        <v>2.15</v>
       </c>
       <c r="H17" t="n">
-        <v>68.72</v>
-      </c>
-      <c r="I17" s="16" t="inlineStr">
+        <v>71.01000000000001</v>
+      </c>
+      <c r="I17" s="17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J17" s="9" t="n">
-        <v>0.547</v>
+        <v>0.883</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>0.493</v>
+        <v>0.851</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="14" t="inlineStr"/>
@@ -1284,39 +1284,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>5218</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>VANTNRG</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>0.345</v>
-      </c>
-      <c r="E18" s="17" t="n">
-        <v>-0.0143</v>
+        <v>1.81</v>
+      </c>
+      <c r="E18" s="10" t="n">
+        <v>-0.0321</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>5971300</v>
+        <v>8371800</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>1.49</v>
+        <v>0.34</v>
       </c>
       <c r="H18" t="n">
-        <v>57.32</v>
-      </c>
-      <c r="I18" s="16" t="inlineStr">
+        <v>59.95</v>
+      </c>
+      <c r="I18" s="17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J18" s="9" t="n">
-        <v>0.339</v>
+        <v>1.735</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>0.333</v>
+        <v>1.524</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="14" t="inlineStr"/>
@@ -1329,39 +1329,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0373</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>VERDANT</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0.275</v>
-      </c>
-      <c r="E19" s="15" t="n">
-        <v>0.05769999999999999</v>
+        <v>0.58</v>
+      </c>
+      <c r="E19" s="10" t="n">
+        <v>-0.008500000000000001</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>5392200</v>
+        <v>7286400</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>3.14</v>
+        <v>0.3</v>
       </c>
       <c r="H19" t="n">
-        <v>83.03</v>
-      </c>
-      <c r="I19" s="16" t="inlineStr">
+        <v>68.72</v>
+      </c>
+      <c r="I19" s="17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J19" s="9" t="n">
-        <v>0.224</v>
+        <v>0.547</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>0.209</v>
+        <v>0.493</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="14" t="inlineStr"/>
@@ -1374,39 +1374,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>7315</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>AHB</t>
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="E20" s="10" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="E20" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>5200400</v>
+        <v>7119000</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>0.14</v>
+        <v>0.74</v>
       </c>
       <c r="H20" t="n">
-        <v>26.93</v>
-      </c>
-      <c r="I20" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.29</v>
+      </c>
+      <c r="I20" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J20" s="9" t="n">
-        <v>0.634</v>
+        <v>0.053</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>0.851</v>
+        <v>0.043</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="14" t="inlineStr"/>
@@ -1419,39 +1419,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>5218</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>VANTNRG</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>0.605</v>
+        <v>0.345</v>
       </c>
       <c r="E21" s="10" t="n">
-        <v>0</v>
+        <v>-0.0143</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>4538800</v>
+        <v>6412500</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>0.46</v>
+        <v>1.6</v>
       </c>
       <c r="H21" t="n">
-        <v>48.07</v>
-      </c>
-      <c r="I21" s="16" t="inlineStr">
+        <v>57.32</v>
+      </c>
+      <c r="I21" s="17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J21" s="9" t="n">
-        <v>0.608</v>
+        <v>0.339</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>0.604</v>
+        <v>0.333</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="14" t="inlineStr"/>
@@ -1464,39 +1464,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="E22" s="10" t="n">
-        <v>0</v>
+        <v>0.535</v>
+      </c>
+      <c r="E22" s="16" t="n">
+        <v>0.009399999999999999</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>4456400</v>
+        <v>6403200</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>0.21</v>
+        <v>0.17</v>
       </c>
       <c r="H22" t="n">
-        <v>71.25</v>
-      </c>
-      <c r="I22" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>27.96</v>
+      </c>
+      <c r="I22" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J22" s="9" t="n">
-        <v>0.202</v>
+        <v>0.634</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>0.184</v>
+        <v>0.851</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="14" t="inlineStr"/>
@@ -1518,27 +1518,27 @@
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="E23" s="15" t="n">
-        <v>0.0105</v>
+        <v>0.47</v>
+      </c>
+      <c r="E23" s="10" t="n">
+        <v>-0.0105</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>4405500</v>
+        <v>6215800</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="H23" t="n">
-        <v>54.71</v>
-      </c>
-      <c r="I23" s="16" t="inlineStr">
+        <v>50.74</v>
+      </c>
+      <c r="I23" s="17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J23" s="9" t="n">
-        <v>0.469</v>
+        <v>0.468</v>
       </c>
       <c r="K23" s="9" t="n">
         <v>0.471</v>
@@ -1554,28 +1554,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0280</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>MBN</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.155</v>
+        <v>0.3</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>0</v>
+        <v>-0.0323</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>4377900</v>
+        <v>6082600</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>1.36</v>
+        <v>0.32</v>
       </c>
       <c r="H24" t="n">
-        <v>52.85</v>
+        <v>49.23</v>
       </c>
       <c r="I24" s="13" t="inlineStr">
         <is>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="J24" s="9" t="n">
-        <v>0.154</v>
+        <v>0.303</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>0.147</v>
+        <v>0.29</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="14" t="inlineStr"/>
@@ -1599,39 +1599,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>0175</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>HHRG</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E25" s="17" t="n">
-        <v>-0.0323</v>
+        <v>0.145</v>
+      </c>
+      <c r="E25" s="10" t="n">
+        <v>-0.0333</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>4308900</v>
+        <v>6010000</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>0.23</v>
+        <v>0.15</v>
       </c>
       <c r="H25" t="n">
-        <v>49.23</v>
-      </c>
-      <c r="I25" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>45.75</v>
+      </c>
+      <c r="I25" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J25" s="9" t="n">
-        <v>0.303</v>
+        <v>0.158</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>0.29</v>
+        <v>0.148</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="14" t="inlineStr"/>
@@ -1644,39 +1644,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0175</t>
+          <t>0373</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>HHRG</t>
+          <t>VERDANT</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="E26" s="10" t="n">
-        <v>0</v>
+        <v>0.28</v>
+      </c>
+      <c r="E26" s="16" t="n">
+        <v>0.07690000000000001</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>4050900</v>
+        <v>5904000</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>0.1</v>
+        <v>3.44</v>
       </c>
       <c r="H26" t="n">
-        <v>47.65</v>
-      </c>
-      <c r="I26" s="16" t="inlineStr">
+        <v>83.92</v>
+      </c>
+      <c r="I26" s="17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J26" s="9" t="n">
-        <v>0.158</v>
+        <v>0.225</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>0.148</v>
+        <v>0.209</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="14" t="inlineStr"/>
@@ -1689,39 +1689,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>TANCO</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>0.165</v>
-      </c>
-      <c r="E27" s="10" t="n">
-        <v>0</v>
+        <v>0.385</v>
+      </c>
+      <c r="E27" s="16" t="n">
+        <v>0.0132</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>3845700</v>
+        <v>5482100</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0.14</v>
+        <v>0.57</v>
       </c>
       <c r="H27" t="n">
-        <v>34.17</v>
-      </c>
-      <c r="I27" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.96</v>
+      </c>
+      <c r="I27" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J27" s="9" t="n">
-        <v>0.182</v>
+        <v>0.373</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>0.221</v>
+        <v>0.371</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="14" t="inlineStr"/>
@@ -1734,39 +1734,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0138</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ZETRIX</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>0.195</v>
+        <v>0.605</v>
       </c>
       <c r="E28" s="15" t="n">
-        <v>0.0263</v>
+        <v>0</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>3749600</v>
+        <v>5326900</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0.01</v>
+        <v>0.54</v>
       </c>
       <c r="H28" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="I28" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.07</v>
+      </c>
+      <c r="I28" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J28" s="9" t="n">
-        <v>0.276</v>
+        <v>0.608</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>0.492</v>
+        <v>0.604</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="14" t="inlineStr"/>
@@ -1779,40 +1779,31 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>0041</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>AIMAX</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="E29" s="17" t="n">
-        <v>-0.0204</v>
+        <v>0.005</v>
+      </c>
+      <c r="E29" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>3603200</v>
-      </c>
-      <c r="G29" s="12" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="H29" t="n">
-        <v>30.78</v>
-      </c>
-      <c r="I29" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J29" s="9" t="n">
-        <v>0.276</v>
-      </c>
-      <c r="K29" s="9" t="n">
-        <v>0.328</v>
-      </c>
+        <v>5218300</v>
+      </c>
+      <c r="G29" s="12" t="n"/>
+      <c r="I29" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J29" s="9" t="n"/>
+      <c r="K29" s="9" t="n"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="14" t="inlineStr"/>
     </row>
@@ -1824,39 +1815,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0192</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>INTA</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>0.44</v>
+        <v>0.22</v>
       </c>
       <c r="E30" s="15" t="n">
-        <v>0.0476</v>
+        <v>0</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>3533800</v>
+        <v>5019600</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>1.91</v>
+        <v>0.24</v>
       </c>
       <c r="H30" t="n">
-        <v>73.38</v>
-      </c>
-      <c r="I30" s="16" t="inlineStr">
+        <v>71.25</v>
+      </c>
+      <c r="I30" s="17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J30" s="9" t="n">
-        <v>0.395</v>
+        <v>0.202</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>0.38</v>
+        <v>0.184</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="14" t="inlineStr"/>
@@ -1869,39 +1860,39 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>0192</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>INTA</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="E31" s="15" t="n">
-        <v>0.0092</v>
+        <v>0.435</v>
+      </c>
+      <c r="E31" s="16" t="n">
+        <v>0.0357</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>3485700</v>
+        <v>4635100</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>0.26</v>
+        <v>2.5</v>
       </c>
       <c r="H31" t="n">
-        <v>59.13</v>
-      </c>
-      <c r="I31" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>72.15000000000001</v>
+      </c>
+      <c r="I31" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J31" s="9" t="n">
-        <v>0.523</v>
+        <v>0.394</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>0.476</v>
+        <v>0.38</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="14" t="inlineStr"/>
@@ -1914,39 +1905,39 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E32" s="15" t="n">
-        <v>0.0058</v>
+        <v>0.77</v>
+      </c>
+      <c r="E32" s="10" t="n">
+        <v>-0.006500000000000001</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>3473900</v>
+        <v>4541500</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>0.19</v>
+        <v>0.36</v>
       </c>
       <c r="H32" t="n">
-        <v>46.9</v>
-      </c>
-      <c r="I32" s="16" t="inlineStr">
+        <v>47.75</v>
+      </c>
+      <c r="I32" s="17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J32" s="9" t="n">
-        <v>0.868</v>
+        <v>0.774</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>0.871</v>
+        <v>0.774</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="14" t="inlineStr"/>
@@ -1959,39 +1950,39 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>VELESTO</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>0.215</v>
-      </c>
-      <c r="E33" s="17" t="n">
-        <v>-0.0227</v>
+        <v>0.865</v>
+      </c>
+      <c r="E33" s="16" t="n">
+        <v>0.0058</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>3364600</v>
+        <v>4431000</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>0.15</v>
+        <v>0.25</v>
       </c>
       <c r="H33" t="n">
-        <v>29.99</v>
-      </c>
-      <c r="I33" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.9</v>
+      </c>
+      <c r="I33" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J33" s="9" t="n">
-        <v>0.238</v>
+        <v>0.868</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>0.249</v>
+        <v>0.871</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="14" t="inlineStr"/>
@@ -2004,39 +1995,39 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0111</t>
+          <t>0280</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t>MBN</t>
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>0.165</v>
+        <v>0.155</v>
       </c>
       <c r="E34" s="15" t="n">
-        <v>0.0313</v>
+        <v>0</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>3301000</v>
+        <v>4427900</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="H34" t="n">
-        <v>66.66</v>
-      </c>
-      <c r="I34" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.85</v>
+      </c>
+      <c r="I34" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J34" s="9" t="n">
-        <v>0.148</v>
+        <v>0.154</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>0.139</v>
+        <v>0.147</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="14" t="inlineStr"/>
@@ -2049,39 +2040,39 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="E35" s="17" t="n">
-        <v>-0.0213</v>
+        <v>0.245</v>
+      </c>
+      <c r="E35" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>3264000</v>
+        <v>4364600</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0.37</v>
+        <v>0.15</v>
       </c>
       <c r="H35" t="n">
-        <v>55.64</v>
-      </c>
-      <c r="I35" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>31.98</v>
+      </c>
+      <c r="I35" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J35" s="9" t="n">
-        <v>0.447</v>
+        <v>0.276</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>0.407</v>
+        <v>0.328</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="14" t="inlineStr"/>
@@ -2094,39 +2085,39 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>MALAKOF</t>
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="E36" s="15" t="n">
-        <v>0.0132</v>
+        <v>0.795</v>
+      </c>
+      <c r="E36" s="10" t="n">
+        <v>-0.0124</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>3259200</v>
+        <v>4337100</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>0.34</v>
+        <v>1.04</v>
       </c>
       <c r="H36" t="n">
-        <v>63.96</v>
-      </c>
-      <c r="I36" s="16" t="inlineStr">
+        <v>47.1</v>
+      </c>
+      <c r="I36" s="17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J36" s="9" t="n">
-        <v>0.373</v>
+        <v>0.803</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>0.371</v>
+        <v>0.806</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="14" t="inlineStr"/>
@@ -2139,39 +2130,39 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="E37" s="17" t="n">
-        <v>-0.006500000000000001</v>
+        <v>4.87</v>
+      </c>
+      <c r="E37" s="10" t="n">
+        <v>-0.002</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>3131000</v>
+        <v>4227400</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="H37" t="n">
-        <v>47.75</v>
-      </c>
-      <c r="I37" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>63.46</v>
+      </c>
+      <c r="I37" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J37" s="9" t="n">
-        <v>0.774</v>
+        <v>4.741</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>0.774</v>
+        <v>4.509</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="14" t="inlineStr"/>
@@ -2184,39 +2175,39 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>2429</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>TANCO</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="E38" s="17" t="n">
-        <v>-0.009899999999999999</v>
+        <v>0.165</v>
+      </c>
+      <c r="E38" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>3079500</v>
+        <v>3881500</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>0.23</v>
+        <v>0.14</v>
       </c>
       <c r="H38" t="n">
-        <v>67.31999999999999</v>
-      </c>
-      <c r="I38" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.17</v>
+      </c>
+      <c r="I38" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J38" s="9" t="n">
-        <v>2.86</v>
+        <v>0.182</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>2.716</v>
+        <v>0.221</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="14" t="inlineStr"/>
@@ -2229,39 +2220,39 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>8893</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>MKLAND</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="E39" s="15" t="n">
-        <v>0.0286</v>
+        <v>0.295</v>
+      </c>
+      <c r="E39" s="16" t="n">
+        <v>0.0172</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>3069700</v>
+        <v>3749300</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>2.82</v>
+        <v>2.02</v>
       </c>
       <c r="H39" t="n">
-        <v>81.90000000000001</v>
-      </c>
-      <c r="I39" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.23</v>
+      </c>
+      <c r="I39" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J39" s="9" t="n">
-        <v>0.152</v>
+        <v>0.295</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>0.145</v>
+        <v>0.297</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="14" t="inlineStr"/>
@@ -2274,39 +2265,39 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="E40" s="17" t="n">
-        <v>-0.0061</v>
+        <v>2.98</v>
+      </c>
+      <c r="E40" s="10" t="n">
+        <v>-0.0165</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>3065600</v>
+        <v>3546100</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>0.16</v>
+        <v>0.26</v>
       </c>
       <c r="H40" t="n">
-        <v>61.73</v>
-      </c>
-      <c r="I40" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.89</v>
+      </c>
+      <c r="I40" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J40" s="9" t="n">
-        <v>4.739</v>
+        <v>2.858</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>4.509</v>
+        <v>2.716</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="14" t="inlineStr"/>
@@ -2319,39 +2310,39 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>9059</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>TSH</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="E41" s="17" t="n">
-        <v>-0.0365</v>
+        <v>0.295</v>
+      </c>
+      <c r="E41" s="16" t="n">
+        <v>0.0172</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>2870200</v>
+        <v>3541000</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>1.23</v>
+        <v>0.55</v>
       </c>
       <c r="H41" t="n">
-        <v>39.48</v>
-      </c>
-      <c r="I41" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.27</v>
+      </c>
+      <c r="I41" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J41" s="9" t="n">
-        <v>1.406</v>
+        <v>0.275</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>1.317</v>
+        <v>0.27</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="14" t="inlineStr"/>
@@ -2364,39 +2355,39 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>VELESTO</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>0.365</v>
-      </c>
-      <c r="E42" s="15" t="n">
-        <v>0.0139</v>
+        <v>0.215</v>
+      </c>
+      <c r="E42" s="10" t="n">
+        <v>-0.0227</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>2527800</v>
+        <v>3475900</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>0.36</v>
+        <v>0.16</v>
       </c>
       <c r="H42" t="n">
-        <v>67.36</v>
-      </c>
-      <c r="I42" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>29.99</v>
+      </c>
+      <c r="I42" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J42" s="9" t="n">
-        <v>0.337</v>
+        <v>0.238</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>0.319</v>
+        <v>0.249</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="14" t="inlineStr"/>
@@ -2409,39 +2400,39 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="E43" s="15" t="n">
-        <v>0.0154</v>
+        <v>0.46</v>
+      </c>
+      <c r="E43" s="10" t="n">
+        <v>-0.0213</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>2345800</v>
+        <v>3461700</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>0.29</v>
+        <v>0.39</v>
       </c>
       <c r="H43" t="n">
-        <v>52.72</v>
-      </c>
-      <c r="I43" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>55.64</v>
+      </c>
+      <c r="I43" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J43" s="9" t="n">
-        <v>0.33</v>
+        <v>0.447</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>0.311</v>
+        <v>0.407</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="14" t="inlineStr"/>
@@ -2454,39 +2445,39 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>8893</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>MKLAND</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>0.825</v>
-      </c>
-      <c r="E44" s="15" t="n">
-        <v>0.0061</v>
+        <v>0.18</v>
+      </c>
+      <c r="E44" s="16" t="n">
+        <v>0.0286</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>2331100</v>
+        <v>3407600</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0.24</v>
+        <v>3.13</v>
       </c>
       <c r="H44" t="n">
-        <v>70.64</v>
-      </c>
-      <c r="I44" s="16" t="inlineStr">
+        <v>81.90000000000001</v>
+      </c>
+      <c r="I44" s="17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J44" s="9" t="n">
-        <v>0.714</v>
+        <v>0.152</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.145</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="14" t="inlineStr"/>
@@ -2499,39 +2490,39 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>0111</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>0.415</v>
-      </c>
-      <c r="E45" s="17" t="n">
-        <v>-0.0119</v>
+        <v>0.165</v>
+      </c>
+      <c r="E45" s="16" t="n">
+        <v>0.0313</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>2288600</v>
+        <v>3335700</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>0.2</v>
+        <v>1.28</v>
       </c>
       <c r="H45" t="n">
-        <v>56.5</v>
-      </c>
-      <c r="I45" s="16" t="inlineStr">
+        <v>66.66</v>
+      </c>
+      <c r="I45" s="17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J45" s="9" t="n">
-        <v>0.409</v>
+        <v>0.148</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>0.41</v>
+        <v>0.139</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="14" t="inlineStr"/>
@@ -2544,39 +2535,39 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>9059</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>TSH</t>
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>0.365</v>
-      </c>
-      <c r="E46" s="17" t="n">
-        <v>-0.0135</v>
+        <v>1.31</v>
+      </c>
+      <c r="E46" s="10" t="n">
+        <v>-0.0438</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>2283900</v>
+        <v>3178900</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0.38</v>
+        <v>1.37</v>
       </c>
       <c r="H46" t="n">
-        <v>48.52</v>
-      </c>
-      <c r="I46" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.43</v>
+      </c>
+      <c r="I46" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J46" s="9" t="n">
-        <v>0.367</v>
+        <v>1.405</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>0.366</v>
+        <v>1.317</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="14" t="inlineStr"/>
@@ -2589,39 +2580,39 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E47" s="15" t="n">
-        <v>0.0172</v>
+        <v>0.255</v>
+      </c>
+      <c r="E47" s="10" t="n">
+        <v>-0.0192</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>2167400</v>
+        <v>2899500</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>0.34</v>
+        <v>0.24</v>
       </c>
       <c r="H47" t="n">
-        <v>66.27</v>
-      </c>
-      <c r="I47" s="16" t="inlineStr">
+        <v>37.73</v>
+      </c>
+      <c r="I47" s="17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J47" s="9" t="n">
-        <v>0.275</v>
+        <v>0.272</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>0.27</v>
+        <v>0.314</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="14" t="inlineStr"/>
@@ -2634,39 +2625,39 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>0.725</v>
-      </c>
-      <c r="E48" s="17" t="n">
-        <v>-0.0333</v>
+        <v>1.31</v>
+      </c>
+      <c r="E48" s="10" t="n">
+        <v>-0.0076</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>2144500</v>
+        <v>2833500</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>0.37</v>
+        <v>0.24</v>
       </c>
       <c r="H48" t="n">
-        <v>61.83</v>
-      </c>
-      <c r="I48" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.34</v>
+      </c>
+      <c r="I48" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J48" s="9" t="n">
-        <v>0.6820000000000001</v>
+        <v>1.374</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>0.611</v>
+        <v>1.29</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="14" t="inlineStr"/>
@@ -2679,39 +2670,39 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0393</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>TEAMSTR</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="E49" s="17" t="n">
-        <v>-0.0217</v>
+        <v>2.37</v>
+      </c>
+      <c r="E49" s="10" t="n">
+        <v>-0.008399999999999999</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>2047000</v>
+        <v>2803300</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>0.67</v>
+        <v>0.17</v>
       </c>
       <c r="H49" t="n">
-        <v>28.13</v>
-      </c>
-      <c r="I49" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.86</v>
+      </c>
+      <c r="I49" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J49" s="9" t="n">
-        <v>0.243</v>
+        <v>2.35</v>
       </c>
       <c r="K49" s="9" t="n">
-        <v>0.243</v>
+        <v>2.239</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="14" t="inlineStr"/>
@@ -2724,39 +2715,39 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>4.48</v>
-      </c>
-      <c r="E50" s="15" t="n">
-        <v>0.0299</v>
+        <v>0.335</v>
+      </c>
+      <c r="E50" s="16" t="n">
+        <v>0.0308</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>1976400</v>
+        <v>2667900</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>0.16</v>
+        <v>0.33</v>
       </c>
       <c r="H50" t="n">
-        <v>80.06</v>
-      </c>
-      <c r="I50" s="16" t="inlineStr">
+        <v>54.74</v>
+      </c>
+      <c r="I50" s="17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J50" s="9" t="n">
-        <v>3.53</v>
+        <v>0.331</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>2.356</v>
+        <v>0.311</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="14" t="inlineStr"/>
@@ -2769,39 +2760,39 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="E51" s="17" t="n">
-        <v>-0.0417</v>
+        <v>0.365</v>
+      </c>
+      <c r="E51" s="16" t="n">
+        <v>0.0139</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>1952600</v>
+        <v>2634600</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>0.21</v>
+        <v>0.38</v>
       </c>
       <c r="H51" t="n">
-        <v>50.13</v>
-      </c>
-      <c r="I51" s="16" t="inlineStr">
+        <v>67.36</v>
+      </c>
+      <c r="I51" s="17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J51" s="9" t="n">
-        <v>1.163</v>
+        <v>0.337</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>1.1</v>
+        <v>0.319</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="14" t="inlineStr"/>
@@ -2823,30 +2814,30 @@
         </is>
       </c>
       <c r="D52" s="9" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="E52" s="17" t="n">
-        <v>-0.007800000000000001</v>
+        <v>1.3</v>
+      </c>
+      <c r="E52" s="16" t="n">
+        <v>0.0156</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>1821000</v>
+        <v>2576900</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>0.33</v>
+        <v>0.47</v>
       </c>
       <c r="H52" t="n">
-        <v>93.52</v>
-      </c>
-      <c r="I52" s="16" t="inlineStr">
+        <v>95.47</v>
+      </c>
+      <c r="I52" s="17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J52" s="9" t="n">
-        <v>0.878</v>
+        <v>0.88</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>0.733</v>
+        <v>0.734</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="14" t="inlineStr"/>
@@ -2859,39 +2850,39 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="E53" s="17" t="n">
-        <v>-0.0382</v>
+        <v>0.365</v>
+      </c>
+      <c r="E53" s="10" t="n">
+        <v>-0.0135</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>1768700</v>
+        <v>2563900</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>0.25</v>
+        <v>0.43</v>
       </c>
       <c r="H53" t="n">
-        <v>59.76</v>
-      </c>
-      <c r="I53" s="16" t="inlineStr">
+        <v>48.52</v>
+      </c>
+      <c r="I53" s="17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J53" s="9" t="n">
-        <v>2.624</v>
+        <v>0.367</v>
       </c>
       <c r="K53" s="9" t="n">
-        <v>2.495</v>
+        <v>0.366</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="14" t="inlineStr"/>
@@ -2904,39 +2895,39 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>2.5</v>
+        <v>0.82</v>
       </c>
       <c r="E54" s="15" t="n">
-        <v>0.0121</v>
+        <v>0</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>1756900</v>
+        <v>2528400</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>0.11</v>
+        <v>0.26</v>
       </c>
       <c r="H54" t="n">
-        <v>61.94</v>
-      </c>
-      <c r="I54" s="16" t="inlineStr">
+        <v>70.16</v>
+      </c>
+      <c r="I54" s="17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J54" s="9" t="n">
-        <v>2.439</v>
+        <v>0.714</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>2.276</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="14" t="inlineStr"/>
@@ -2949,39 +2940,39 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>0.925</v>
-      </c>
-      <c r="E55" s="15" t="n">
-        <v>0.0278</v>
+        <v>0.72</v>
+      </c>
+      <c r="E55" s="10" t="n">
+        <v>-0.04</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>1706800</v>
+        <v>2501600</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>0.52</v>
+        <v>0.43</v>
       </c>
       <c r="H55" t="n">
-        <v>45.6</v>
-      </c>
-      <c r="I55" s="16" t="inlineStr">
+        <v>60.74</v>
+      </c>
+      <c r="I55" s="17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J55" s="9" t="n">
-        <v>0.928</v>
+        <v>0.681</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>0.969</v>
+        <v>0.611</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="14" t="inlineStr"/>
@@ -2994,39 +2985,39 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D56" s="9" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="E56" s="15" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.415</v>
+      </c>
+      <c r="E56" s="10" t="n">
+        <v>-0.0119</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>1659400</v>
+        <v>2452800</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>0.1</v>
+        <v>0.22</v>
       </c>
       <c r="H56" t="n">
-        <v>49.29</v>
-      </c>
-      <c r="I56" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.5</v>
+      </c>
+      <c r="I56" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J56" s="9" t="n">
-        <v>2.129</v>
+        <v>0.409</v>
       </c>
       <c r="K56" s="9" t="n">
-        <v>2.062</v>
+        <v>0.41</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="14" t="inlineStr"/>
@@ -3039,39 +3030,39 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0369</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>JSSOLAR</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E57" s="15" t="n">
-        <v>0.04</v>
+        <v>2.77</v>
+      </c>
+      <c r="E57" s="10" t="n">
+        <v>-0.0382</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>1596700</v>
+        <v>2435400</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>1.55</v>
+        <v>0.35</v>
       </c>
       <c r="H57" t="n">
-        <v>73.58</v>
-      </c>
-      <c r="I57" s="16" t="inlineStr">
+        <v>59.76</v>
+      </c>
+      <c r="I57" s="17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J57" s="9" t="n">
-        <v>0.212</v>
+        <v>2.624</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>0.198</v>
+        <v>2.495</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="14" t="inlineStr"/>
@@ -3084,39 +3075,39 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>0393</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>TEAMSTR</t>
         </is>
       </c>
       <c r="D58" s="9" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="E58" s="17" t="n">
-        <v>-0.0267</v>
+        <v>0.23</v>
+      </c>
+      <c r="E58" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>1588100</v>
+        <v>2276900</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>0.27</v>
+        <v>0.75</v>
       </c>
       <c r="H58" t="n">
-        <v>48.43</v>
-      </c>
-      <c r="I58" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>31.51</v>
+      </c>
+      <c r="I58" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J58" s="9" t="n">
-        <v>2.568</v>
+        <v>0.244</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>2.535</v>
+        <v>0.243</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="14" t="inlineStr"/>
@@ -3129,28 +3120,28 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>0.545</v>
-      </c>
-      <c r="E59" s="10" t="n">
-        <v>0</v>
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="E59" s="16" t="n">
+        <v>0.0062</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>1531400</v>
+        <v>2241100</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>0.24</v>
+        <v>0.17</v>
       </c>
       <c r="H59" t="n">
-        <v>39.08</v>
+        <v>52.51</v>
       </c>
       <c r="I59" s="13" t="inlineStr">
         <is>
@@ -3158,10 +3149,10 @@
         </is>
       </c>
       <c r="J59" s="9" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K59" s="9" t="n">
-        <v>0.59</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="14" t="inlineStr"/>
@@ -3174,39 +3165,39 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>MRCB</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="E60" s="10" t="n">
-        <v>0</v>
+        <v>4.45</v>
+      </c>
+      <c r="E60" s="16" t="n">
+        <v>0.023</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>1489300</v>
+        <v>2184700</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="H60" t="n">
-        <v>39.08</v>
-      </c>
-      <c r="I60" s="16" t="inlineStr">
+        <v>79.79000000000001</v>
+      </c>
+      <c r="I60" s="17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J60" s="9" t="n">
-        <v>0.298</v>
+        <v>3.527</v>
       </c>
       <c r="K60" s="9" t="n">
-        <v>0.312</v>
+        <v>2.356</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="14" t="inlineStr"/>
@@ -3219,39 +3210,39 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>IOIPG</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>5.81</v>
-      </c>
-      <c r="E61" s="17" t="n">
-        <v>-0.0136</v>
+        <v>3.56</v>
+      </c>
+      <c r="E61" s="16" t="n">
+        <v>0.0201</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>1469700</v>
+        <v>2153000</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>0.1</v>
+        <v>0.46</v>
       </c>
       <c r="H61" t="n">
-        <v>59.45</v>
-      </c>
-      <c r="I61" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.14</v>
+      </c>
+      <c r="I61" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J61" s="9" t="n">
-        <v>5.687</v>
+        <v>3.621</v>
       </c>
       <c r="K61" s="9" t="n">
-        <v>5.131</v>
+        <v>3.705</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="14" t="inlineStr"/>
@@ -3264,28 +3255,28 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D62" s="9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="E62" s="17" t="n">
-        <v>-0.0227</v>
+        <v>1.05</v>
+      </c>
+      <c r="E62" s="10" t="n">
+        <v>-0.0455</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>1450400</v>
+        <v>2120000</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>0.12</v>
+        <v>0.19</v>
       </c>
       <c r="H62" t="n">
-        <v>41.16</v>
+        <v>47.24</v>
       </c>
       <c r="I62" s="13" t="inlineStr">
         <is>
@@ -3293,10 +3284,10 @@
         </is>
       </c>
       <c r="J62" s="9" t="n">
-        <v>1.372</v>
+        <v>1.081</v>
       </c>
       <c r="K62" s="9" t="n">
-        <v>1.29</v>
+        <v>1.024</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="14" t="inlineStr"/>
@@ -3309,39 +3300,39 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>0.545</v>
-      </c>
-      <c r="E63" s="17" t="n">
-        <v>-0.0091</v>
+        <v>0.93</v>
+      </c>
+      <c r="E63" s="16" t="n">
+        <v>0.0333</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>1444500</v>
+        <v>2103400</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.64</v>
       </c>
       <c r="H63" t="n">
-        <v>62.16</v>
-      </c>
-      <c r="I63" s="16" t="inlineStr">
+        <v>47.25</v>
+      </c>
+      <c r="I63" s="17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J63" s="9" t="n">
-        <v>0.498</v>
+        <v>0.928</v>
       </c>
       <c r="K63" s="9" t="n">
-        <v>0.401</v>
+        <v>0.969</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="14" t="inlineStr"/>
@@ -3354,39 +3345,39 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>4243</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>WTK</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D64" s="9" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="E64" s="17" t="n">
-        <v>-0.0408</v>
+        <v>5.82</v>
+      </c>
+      <c r="E64" s="10" t="n">
+        <v>-0.0119</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>1440600</v>
+        <v>2089600</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>0.58</v>
+        <v>0.14</v>
       </c>
       <c r="H64" t="n">
-        <v>33.8</v>
-      </c>
-      <c r="I64" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.92</v>
+      </c>
+      <c r="I64" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J64" s="9" t="n">
-        <v>1.043</v>
+        <v>5.688</v>
       </c>
       <c r="K64" s="9" t="n">
-        <v>1.014</v>
+        <v>5.131</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="14" t="inlineStr"/>
@@ -3399,39 +3390,39 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="E65" s="17" t="n">
-        <v>-0.0364</v>
+        <v>1.15</v>
+      </c>
+      <c r="E65" s="10" t="n">
+        <v>-0.0417</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>1440400</v>
+        <v>2072900</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>0.13</v>
+        <v>0.23</v>
       </c>
       <c r="H65" t="n">
-        <v>48.58</v>
-      </c>
-      <c r="I65" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.13</v>
+      </c>
+      <c r="I65" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J65" s="9" t="n">
-        <v>1.082</v>
+        <v>1.163</v>
       </c>
       <c r="K65" s="9" t="n">
-        <v>1.024</v>
+        <v>1.1</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="14" t="inlineStr"/>
@@ -3444,39 +3435,39 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D66" s="9" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="E66" s="17" t="n">
-        <v>-0.0112</v>
+        <v>0.29</v>
+      </c>
+      <c r="E66" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>1365700</v>
+        <v>2005500</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>0.23</v>
+        <v>0.26</v>
       </c>
       <c r="H66" t="n">
-        <v>47.93</v>
-      </c>
-      <c r="I66" s="16" t="inlineStr">
+        <v>39.08</v>
+      </c>
+      <c r="I66" s="17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J66" s="9" t="n">
-        <v>1.771</v>
+        <v>0.298</v>
       </c>
       <c r="K66" s="9" t="n">
-        <v>1.806</v>
+        <v>0.312</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="14" t="inlineStr"/>
@@ -3489,39 +3480,39 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="E67" s="17" t="n">
-        <v>-0.0167</v>
+        <v>2.5</v>
+      </c>
+      <c r="E67" s="16" t="n">
+        <v>0.0121</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>1355400</v>
+        <v>2003900</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>0.08</v>
+        <v>0.13</v>
       </c>
       <c r="H67" t="n">
-        <v>51.33</v>
-      </c>
-      <c r="I67" s="16" t="inlineStr">
+        <v>61.94</v>
+      </c>
+      <c r="I67" s="17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J67" s="9" t="n">
-        <v>2.348</v>
+        <v>2.439</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>2.239</v>
+        <v>2.276</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="14" t="inlineStr"/>
@@ -3543,19 +3534,19 @@
         </is>
       </c>
       <c r="D68" s="9" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="E68" s="10" t="n">
-        <v>0</v>
+        <v>-0.0222</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>1322500</v>
+        <v>1946500</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>0.24</v>
+        <v>0.36</v>
       </c>
       <c r="H68" t="n">
-        <v>82.34999999999999</v>
+        <v>73.93000000000001</v>
       </c>
       <c r="I68" s="13" t="inlineStr">
         <is>
@@ -3563,10 +3554,10 @@
         </is>
       </c>
       <c r="J68" s="9" t="n">
-        <v>2.461</v>
+        <v>2.455</v>
       </c>
       <c r="K68" s="9" t="n">
-        <v>2.119</v>
+        <v>2.118</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="14" t="inlineStr"/>
@@ -3579,39 +3570,39 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0358</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>ICTZONE</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D69" s="9" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="E69" s="16" t="n">
+        <v>0.0086</v>
+      </c>
+      <c r="F69" s="11" t="n">
+        <v>1769000</v>
+      </c>
+      <c r="G69" s="12" t="n">
         <v>0.26</v>
       </c>
-      <c r="E69" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F69" s="11" t="n">
-        <v>1289900</v>
-      </c>
-      <c r="G69" s="12" t="n">
-        <v>0.46</v>
-      </c>
       <c r="H69" t="n">
-        <v>50.51</v>
-      </c>
-      <c r="I69" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.17</v>
+      </c>
+      <c r="I69" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J69" s="9" t="n">
-        <v>0.262</v>
+        <v>1.181</v>
       </c>
       <c r="K69" s="9" t="n">
-        <v>0.251</v>
+        <v>1.14</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="14" t="inlineStr"/>
@@ -3624,39 +3615,39 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D70" s="9" t="n">
-        <v>10.18</v>
-      </c>
-      <c r="E70" s="17" t="n">
-        <v>-0.0039</v>
+        <v>0.67</v>
+      </c>
+      <c r="E70" s="16" t="n">
+        <v>0.0152</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>1272000</v>
+        <v>1766700</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>0.08</v>
+        <v>0.19</v>
       </c>
       <c r="H70" t="n">
-        <v>47.99</v>
-      </c>
-      <c r="I70" s="16" t="inlineStr">
+        <v>61.53</v>
+      </c>
+      <c r="I70" s="17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J70" s="9" t="n">
-        <v>10.177</v>
+        <v>0.634</v>
       </c>
       <c r="K70" s="9" t="n">
-        <v>10.321</v>
+        <v>0.575</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="14" t="inlineStr"/>
@@ -3669,28 +3660,28 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>0.8149999999999999</v>
-      </c>
-      <c r="E71" s="15" t="n">
-        <v>0.0062</v>
+        <v>2.1</v>
+      </c>
+      <c r="E71" s="16" t="n">
+        <v>0.0048</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>1252600</v>
+        <v>1766500</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="H71" t="n">
-        <v>52.51</v>
+        <v>48.16</v>
       </c>
       <c r="I71" s="13" t="inlineStr">
         <is>
@@ -3698,10 +3689,10 @@
         </is>
       </c>
       <c r="J71" s="9" t="n">
-        <v>0.8100000000000001</v>
+        <v>2.128</v>
       </c>
       <c r="K71" s="9" t="n">
-        <v>0.8080000000000001</v>
+        <v>2.062</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="14" t="inlineStr"/>
@@ -3714,39 +3705,39 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0272</t>
+          <t>0369</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>TTVHB</t>
+          <t>JSSOLAR</t>
         </is>
       </c>
       <c r="D72" s="9" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E72" s="10" t="n">
-        <v>0</v>
+        <v>0.26</v>
+      </c>
+      <c r="E72" s="16" t="n">
+        <v>0.04</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>1236100</v>
+        <v>1703600</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>0.36</v>
+        <v>1.65</v>
       </c>
       <c r="H72" t="n">
-        <v>49.72</v>
-      </c>
-      <c r="I72" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>73.58</v>
+      </c>
+      <c r="I72" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J72" s="9" t="n">
-        <v>0.249</v>
+        <v>0.212</v>
       </c>
       <c r="K72" s="9" t="n">
-        <v>0.253</v>
+        <v>0.198</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="14" t="inlineStr"/>
@@ -3759,39 +3750,39 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>NEXG</t>
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>0.665</v>
+        <v>0.32</v>
       </c>
       <c r="E73" s="15" t="n">
-        <v>0.0076</v>
+        <v>0</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>1232500</v>
+        <v>1701300</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>0.13</v>
+        <v>0.1</v>
       </c>
       <c r="H73" t="n">
-        <v>60.68</v>
-      </c>
-      <c r="I73" s="16" t="inlineStr">
+        <v>65.18000000000001</v>
+      </c>
+      <c r="I73" s="17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J73" s="9" t="n">
-        <v>0.634</v>
+        <v>0.284</v>
       </c>
       <c r="K73" s="9" t="n">
-        <v>0.574</v>
+        <v>0.277</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="14" t="inlineStr"/>
@@ -3804,39 +3795,39 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D74" s="9" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="E74" s="15" t="n">
-        <v>0.0155</v>
+        <v>2.56</v>
+      </c>
+      <c r="E74" s="10" t="n">
+        <v>-0.0229</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>1232000</v>
+        <v>1669400</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>0.1</v>
+        <v>0.29</v>
       </c>
       <c r="H74" t="n">
-        <v>39.66</v>
-      </c>
-      <c r="I74" s="16" t="inlineStr">
+        <v>49.38</v>
+      </c>
+      <c r="I74" s="17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J74" s="9" t="n">
-        <v>1.33</v>
+        <v>2.569</v>
       </c>
       <c r="K74" s="9" t="n">
-        <v>1.445</v>
+        <v>2.535</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="14" t="inlineStr"/>
@@ -3849,39 +3840,39 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D75" s="9" t="n">
-        <v>0.765</v>
-      </c>
-      <c r="E75" s="10" t="n">
+        <v>0.425</v>
+      </c>
+      <c r="E75" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>1119000</v>
+        <v>1582900</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>0.18</v>
+        <v>0.27</v>
       </c>
       <c r="H75" t="n">
-        <v>46.13</v>
-      </c>
-      <c r="I75" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.85</v>
+      </c>
+      <c r="I75" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J75" s="9" t="n">
-        <v>0.773</v>
+        <v>0.402</v>
       </c>
       <c r="K75" s="9" t="n">
-        <v>0.773</v>
+        <v>0.4</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="14" t="inlineStr"/>
@@ -3894,39 +3885,39 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>4243</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>WTK</t>
         </is>
       </c>
       <c r="D76" s="9" t="n">
-        <v>0.65</v>
+        <v>0.96</v>
       </c>
       <c r="E76" s="10" t="n">
-        <v>0</v>
+        <v>-0.0204</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>1117900</v>
+        <v>1581600</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>0.33</v>
+        <v>0.63</v>
       </c>
       <c r="H76" t="n">
-        <v>70.55</v>
-      </c>
-      <c r="I76" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.93</v>
+      </c>
+      <c r="I76" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J76" s="9" t="n">
-        <v>0.634</v>
+        <v>1.045</v>
       </c>
       <c r="K76" s="9" t="n">
-        <v>0.591</v>
+        <v>1.014</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="14" t="inlineStr"/>
@@ -3939,39 +3930,39 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>NEXG</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D77" s="9" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="E77" s="10" t="n">
+        <v>0.545</v>
+      </c>
+      <c r="E77" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>1102400</v>
+        <v>1534000</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.24</v>
       </c>
       <c r="H77" t="n">
-        <v>65.18000000000001</v>
-      </c>
-      <c r="I77" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.08</v>
+      </c>
+      <c r="I77" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J77" s="9" t="n">
-        <v>0.284</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="K77" s="9" t="n">
-        <v>0.277</v>
+        <v>0.59</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="14" t="inlineStr"/>
@@ -3984,39 +3975,39 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>3379</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>INSAS</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D78" s="9" t="n">
-        <v>0.905</v>
-      </c>
-      <c r="E78" s="15" t="n">
-        <v>0.0226</v>
+        <v>0.54</v>
+      </c>
+      <c r="E78" s="10" t="n">
+        <v>-0.0182</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>1086600</v>
+        <v>1518000</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>1.87</v>
+        <v>0.85</v>
       </c>
       <c r="H78" t="n">
-        <v>57.27</v>
-      </c>
-      <c r="I78" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.11</v>
+      </c>
+      <c r="I78" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J78" s="9" t="n">
-        <v>0.895</v>
+        <v>0.497</v>
       </c>
       <c r="K78" s="9" t="n">
-        <v>0.9</v>
+        <v>0.401</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="14" t="inlineStr"/>
@@ -4029,39 +4020,39 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D79" s="9" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="E79" s="17" t="n">
-        <v>-0.0189</v>
+        <v>0.765</v>
+      </c>
+      <c r="E79" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>1078800</v>
+        <v>1466400</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>0.29</v>
+        <v>0.23</v>
       </c>
       <c r="H79" t="n">
-        <v>55.42</v>
-      </c>
-      <c r="I79" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.13</v>
+      </c>
+      <c r="I79" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J79" s="9" t="n">
-        <v>0.512</v>
+        <v>0.773</v>
       </c>
       <c r="K79" s="9" t="n">
-        <v>0.464</v>
+        <v>0.773</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="14" t="inlineStr"/>
@@ -4074,39 +4065,39 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0450</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>MFGROUP</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D80" s="9" t="n">
-        <v>0.26</v>
+        <v>10.18</v>
       </c>
       <c r="E80" s="10" t="n">
-        <v>0</v>
+        <v>-0.0039</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>1052600</v>
+        <v>1450500</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>1.33</v>
+        <v>0.09</v>
       </c>
       <c r="H80" t="n">
-        <v>45.51</v>
-      </c>
-      <c r="I80" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.99</v>
+      </c>
+      <c r="I80" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J80" s="9" t="n">
-        <v>0.261</v>
+        <v>10.177</v>
       </c>
       <c r="K80" s="9" t="n">
-        <v>0.266</v>
+        <v>10.321</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="14" t="inlineStr"/>
@@ -4119,39 +4110,39 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0268</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>L&amp;PBHD</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D81" s="9" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="E81" s="15" t="n">
-        <v>0.0244</v>
+        <v>1.76</v>
+      </c>
+      <c r="E81" s="10" t="n">
+        <v>-0.0112</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>1044700</v>
+        <v>1433400</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>0.38</v>
+        <v>0.24</v>
       </c>
       <c r="H81" t="n">
-        <v>71.81999999999999</v>
-      </c>
-      <c r="I81" s="16" t="inlineStr">
+        <v>47.93</v>
+      </c>
+      <c r="I81" s="17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J81" s="9" t="n">
-        <v>0.187</v>
+        <v>1.771</v>
       </c>
       <c r="K81" s="9" t="n">
-        <v>0.156</v>
+        <v>1.806</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="14" t="inlineStr"/>
@@ -4164,39 +4155,39 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0265</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>INFOM</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D82" s="9" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="E82" s="15" t="n">
-        <v>0.0311</v>
+        <v>0.6</v>
+      </c>
+      <c r="E82" s="10" t="n">
+        <v>-0.0164</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>1029900</v>
+        <v>1363300</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>3</v>
+        <v>0.27</v>
       </c>
       <c r="H82" t="n">
-        <v>70.11</v>
-      </c>
-      <c r="I82" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.76</v>
+      </c>
+      <c r="I82" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J82" s="9" t="n">
-        <v>1.587</v>
+        <v>0.637</v>
       </c>
       <c r="K82" s="9" t="n">
-        <v>1.535</v>
+        <v>0.657</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="14" t="inlineStr"/>
@@ -4209,39 +4200,39 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>8524</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>TALIWRK</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D83" s="9" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="E83" s="10" t="n">
-        <v>0</v>
+        <v>1.31</v>
+      </c>
+      <c r="E83" s="16" t="n">
+        <v>0.0155</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>1011300</v>
+        <v>1349700</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>0.33</v>
+        <v>0.11</v>
       </c>
       <c r="H83" t="n">
-        <v>54.09</v>
-      </c>
-      <c r="I83" s="16" t="inlineStr">
+        <v>39.66</v>
+      </c>
+      <c r="I83" s="17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J83" s="9" t="n">
-        <v>0.254</v>
+        <v>1.33</v>
       </c>
       <c r="K83" s="9" t="n">
-        <v>0.271</v>
+        <v>1.445</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="14" t="inlineStr"/>
@@ -4254,40 +4245,33 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>0468</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>UNIPAC</t>
         </is>
       </c>
       <c r="D84" s="9" t="n">
-        <v>0.35</v>
+        <v>0.245</v>
       </c>
       <c r="E84" s="10" t="n">
-        <v>0</v>
+        <v>-0.0392</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>1008100</v>
+        <v>1349400</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="H84" t="n">
-        <v>47.96</v>
+        <v>0.08</v>
       </c>
       <c r="I84" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J84" s="9" t="n">
-        <v>0.352</v>
-      </c>
-      <c r="K84" s="9" t="n">
-        <v>0.35</v>
-      </c>
+      <c r="J84" s="9" t="n"/>
+      <c r="K84" s="9" t="n"/>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="14" t="inlineStr"/>
     </row>
@@ -4299,39 +4283,39 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D85" s="9" t="n">
-        <v>1.91</v>
+        <v>0.65</v>
       </c>
       <c r="E85" s="15" t="n">
-        <v>0.016</v>
+        <v>0</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>929700</v>
+        <v>1347900</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>0.21</v>
+        <v>0.4</v>
       </c>
       <c r="H85" t="n">
-        <v>39.51</v>
-      </c>
-      <c r="I85" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>70.55</v>
+      </c>
+      <c r="I85" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J85" s="9" t="n">
-        <v>1.958</v>
+        <v>0.634</v>
       </c>
       <c r="K85" s="9" t="n">
-        <v>2.079</v>
+        <v>0.591</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="14" t="inlineStr"/>
@@ -4344,39 +4328,39 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>0358</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>ICTZONE</t>
         </is>
       </c>
       <c r="D86" s="9" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="E86" s="17" t="n">
-        <v>-0.009399999999999999</v>
+        <v>0.26</v>
+      </c>
+      <c r="E86" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>888400</v>
+        <v>1299900</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>0.11</v>
+        <v>0.47</v>
       </c>
       <c r="H86" t="n">
-        <v>79.73</v>
-      </c>
-      <c r="I86" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.51</v>
+      </c>
+      <c r="I86" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J86" s="9" t="n">
-        <v>0.894</v>
+        <v>0.262</v>
       </c>
       <c r="K86" s="9" t="n">
-        <v>0.759</v>
+        <v>0.251</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="14" t="inlineStr"/>
@@ -4389,39 +4373,39 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>0272</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>TTVHB</t>
         </is>
       </c>
       <c r="D87" s="9" t="n">
-        <v>4.07</v>
+        <v>0.25</v>
       </c>
       <c r="E87" s="15" t="n">
-        <v>0.0025</v>
+        <v>0</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>858000</v>
+        <v>1246100</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>0.18</v>
+        <v>0.36</v>
       </c>
       <c r="H87" t="n">
-        <v>78.42</v>
-      </c>
-      <c r="I87" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.72</v>
+      </c>
+      <c r="I87" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J87" s="9" t="n">
-        <v>3.536</v>
+        <v>0.249</v>
       </c>
       <c r="K87" s="9" t="n">
-        <v>3.224</v>
+        <v>0.253</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="14" t="inlineStr"/>
@@ -4434,39 +4418,39 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0376</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>IAB</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D88" s="9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="E88" s="15" t="n">
-        <v>0.0236</v>
+        <v>0.52</v>
+      </c>
+      <c r="E88" s="10" t="n">
+        <v>-0.0189</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>845300</v>
+        <v>1232100</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.33</v>
       </c>
       <c r="H88" t="n">
-        <v>50.37</v>
-      </c>
-      <c r="I88" s="16" t="inlineStr">
+        <v>55.42</v>
+      </c>
+      <c r="I88" s="17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J88" s="9" t="n">
-        <v>1.284</v>
+        <v>0.512</v>
       </c>
       <c r="K88" s="9" t="n">
-        <v>1.345</v>
+        <v>0.464</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="14" t="inlineStr"/>
@@ -4479,39 +4463,39 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D89" s="9" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="E89" s="17" t="n">
-        <v>-0.0357</v>
+        <v>1.03</v>
+      </c>
+      <c r="E89" s="10" t="n">
+        <v>-0.0283</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>840700</v>
+        <v>1220900</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>0.18</v>
+        <v>0.15</v>
       </c>
       <c r="H89" t="n">
-        <v>74.36</v>
-      </c>
-      <c r="I89" s="16" t="inlineStr">
+        <v>75.38</v>
+      </c>
+      <c r="I89" s="17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J89" s="9" t="n">
-        <v>0.972</v>
+        <v>0.892</v>
       </c>
       <c r="K89" s="9" t="n">
-        <v>0.8</v>
+        <v>0.759</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="14" t="inlineStr"/>
@@ -4524,39 +4508,39 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0045</t>
+          <t>0265</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>SSB8</t>
+          <t>INFOM</t>
         </is>
       </c>
       <c r="D90" s="9" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="E90" s="10" t="n">
-        <v>0</v>
+        <v>1.67</v>
+      </c>
+      <c r="E90" s="16" t="n">
+        <v>0.0373</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>811100</v>
+        <v>1169800</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>0.21</v>
+        <v>3.41</v>
       </c>
       <c r="H90" t="n">
-        <v>64.06999999999999</v>
-      </c>
-      <c r="I90" s="16" t="inlineStr">
+        <v>71.34999999999999</v>
+      </c>
+      <c r="I90" s="17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J90" s="9" t="n">
-        <v>0.621</v>
+        <v>1.588</v>
       </c>
       <c r="K90" s="9" t="n">
-        <v>0.582</v>
+        <v>1.536</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="14" t="inlineStr"/>
@@ -4569,39 +4553,39 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D91" s="9" t="n">
-        <v>1.63</v>
+        <v>4.04</v>
       </c>
       <c r="E91" s="10" t="n">
-        <v>0</v>
+        <v>-0.0049</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>799100</v>
+        <v>1163100</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>0.12</v>
+        <v>0.24</v>
       </c>
       <c r="H91" t="n">
-        <v>30.25</v>
-      </c>
-      <c r="I91" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I91" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J91" s="9" t="n">
-        <v>1.73</v>
+        <v>3.533</v>
       </c>
       <c r="K91" s="9" t="n">
-        <v>1.847</v>
+        <v>3.223</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="14" t="inlineStr"/>
@@ -4614,39 +4598,39 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>0376</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>IAB</t>
         </is>
       </c>
       <c r="D92" s="9" t="n">
-        <v>0.785</v>
-      </c>
-      <c r="E92" s="10" t="n">
-        <v>0</v>
+        <v>1.32</v>
+      </c>
+      <c r="E92" s="16" t="n">
+        <v>0.0394</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>735900</v>
+        <v>1158000</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>0.13</v>
+        <v>0.77</v>
       </c>
       <c r="H92" t="n">
-        <v>86.31</v>
-      </c>
-      <c r="I92" s="16" t="inlineStr">
+        <v>53.02</v>
+      </c>
+      <c r="I92" s="17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J92" s="9" t="n">
-        <v>0.767</v>
+        <v>1.286</v>
       </c>
       <c r="K92" s="9" t="n">
-        <v>0.752</v>
+        <v>1.345</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="14" t="inlineStr"/>
@@ -4659,39 +4643,39 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>0268</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>L&amp;PBHD</t>
         </is>
       </c>
       <c r="D93" s="9" t="n">
-        <v>0.585</v>
-      </c>
-      <c r="E93" s="17" t="n">
-        <v>-0.0168</v>
+        <v>0.21</v>
+      </c>
+      <c r="E93" s="16" t="n">
+        <v>0.0244</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>715500</v>
+        <v>1140100</v>
       </c>
       <c r="G93" s="12" t="n">
-        <v>0.22</v>
+        <v>0.42</v>
       </c>
       <c r="H93" t="n">
-        <v>54.34</v>
-      </c>
-      <c r="I93" s="16" t="inlineStr">
+        <v>71.81999999999999</v>
+      </c>
+      <c r="I93" s="17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J93" s="9" t="n">
-        <v>0.57</v>
+        <v>0.187</v>
       </c>
       <c r="K93" s="9" t="n">
-        <v>0.575</v>
+        <v>0.156</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="14" t="inlineStr"/>
@@ -4704,28 +4688,28 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0271</t>
+          <t>3379</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>WELLS</t>
+          <t>INSAS</t>
         </is>
       </c>
       <c r="D94" s="9" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E94" s="10" t="n">
-        <v>0</v>
+        <v>0.905</v>
+      </c>
+      <c r="E94" s="16" t="n">
+        <v>0.0226</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>700000</v>
+        <v>1134000</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>0.72</v>
+        <v>1.96</v>
       </c>
       <c r="H94" t="n">
-        <v>48.02</v>
+        <v>57.27</v>
       </c>
       <c r="I94" s="13" t="inlineStr">
         <is>
@@ -4733,10 +4717,10 @@
         </is>
       </c>
       <c r="J94" s="9" t="n">
-        <v>0.631</v>
+        <v>0.895</v>
       </c>
       <c r="K94" s="9" t="n">
-        <v>0.637</v>
+        <v>0.9</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="14" t="inlineStr"/>
@@ -4749,28 +4733,28 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>0032</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>REDTONE</t>
         </is>
       </c>
       <c r="D95" s="9" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E95" s="17" t="n">
-        <v>-0.0164</v>
+        <v>0.36</v>
+      </c>
+      <c r="E95" s="10" t="n">
+        <v>-0.0137</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>692700</v>
+        <v>1108400</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>0.14</v>
+        <v>0.65</v>
       </c>
       <c r="H95" t="n">
-        <v>35.76</v>
+        <v>59.96</v>
       </c>
       <c r="I95" s="13" t="inlineStr">
         <is>
@@ -4778,10 +4762,10 @@
         </is>
       </c>
       <c r="J95" s="9" t="n">
-        <v>0.637</v>
+        <v>0.354</v>
       </c>
       <c r="K95" s="9" t="n">
-        <v>0.657</v>
+        <v>0.319</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="14" t="inlineStr"/>
@@ -4794,39 +4778,39 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>5073</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>NAIM</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D96" s="9" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="E96" s="17" t="n">
-        <v>-0.0455</v>
+        <v>1.9</v>
+      </c>
+      <c r="E96" s="16" t="n">
+        <v>0.0106</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>689100</v>
+        <v>1108100</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.25</v>
       </c>
       <c r="H96" t="n">
-        <v>59.12</v>
-      </c>
-      <c r="I96" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.93</v>
+      </c>
+      <c r="I96" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J96" s="9" t="n">
-        <v>0.629</v>
+        <v>1.957</v>
       </c>
       <c r="K96" s="9" t="n">
-        <v>0.612</v>
+        <v>2.079</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="14" t="inlineStr"/>
@@ -4839,39 +4823,39 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>8524</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>TALIWRK</t>
         </is>
       </c>
       <c r="D97" s="9" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="E97" s="15" t="n">
-        <v>0.0069</v>
+        <v>0.26</v>
+      </c>
+      <c r="E97" s="10" t="n">
+        <v>-0.0189</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>680700</v>
+        <v>1091800</v>
       </c>
       <c r="G97" s="12" t="n">
-        <v>0.11</v>
+        <v>0.35</v>
       </c>
       <c r="H97" t="n">
-        <v>70.06</v>
-      </c>
-      <c r="I97" s="16" t="inlineStr">
+        <v>51.19</v>
+      </c>
+      <c r="I97" s="17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J97" s="9" t="n">
-        <v>0.672</v>
+        <v>0.254</v>
       </c>
       <c r="K97" s="9" t="n">
-        <v>0.615</v>
+        <v>0.271</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="14" t="inlineStr"/>
@@ -4884,39 +4868,39 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>ATECH</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D98" s="9" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E98" s="15" t="n">
-        <v>0.0131</v>
+        <v>1.09</v>
+      </c>
+      <c r="E98" s="10" t="n">
+        <v>-0.0268</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>664600</v>
+        <v>1073700</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>0.46</v>
+        <v>0.23</v>
       </c>
       <c r="H98" t="n">
-        <v>53.99</v>
-      </c>
-      <c r="I98" s="16" t="inlineStr">
+        <v>76.75</v>
+      </c>
+      <c r="I98" s="17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J98" s="9" t="n">
-        <v>0.765</v>
+        <v>0.973</v>
       </c>
       <c r="K98" s="9" t="n">
-        <v>0.755</v>
+        <v>0.8</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="14" t="inlineStr"/>
@@ -4929,39 +4913,39 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D99" s="9" t="n">
-        <v>1.29</v>
+        <v>0.315</v>
       </c>
       <c r="E99" s="10" t="n">
-        <v>0</v>
+        <v>-0.0156</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>662900</v>
+        <v>1070300</v>
       </c>
       <c r="G99" s="12" t="n">
         <v>0.17</v>
       </c>
       <c r="H99" t="n">
-        <v>58.59</v>
-      </c>
-      <c r="I99" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>44.97</v>
+      </c>
+      <c r="I99" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J99" s="9" t="n">
-        <v>1.241</v>
+        <v>0.321</v>
       </c>
       <c r="K99" s="9" t="n">
-        <v>1.138</v>
+        <v>0.339</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="14" t="inlineStr"/>
@@ -4974,28 +4958,28 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>0450</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>IOIPG</t>
+          <t>MFGROUP</t>
         </is>
       </c>
       <c r="D100" s="9" t="n">
-        <v>3.47</v>
-      </c>
-      <c r="E100" s="17" t="n">
-        <v>-0.005699999999999999</v>
+        <v>0.26</v>
+      </c>
+      <c r="E100" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>640400</v>
+        <v>1052600</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>0.14</v>
+        <v>1.33</v>
       </c>
       <c r="H100" t="n">
-        <v>35.51</v>
+        <v>45.51</v>
       </c>
       <c r="I100" s="13" t="inlineStr">
         <is>
@@ -5003,10 +4987,10 @@
         </is>
       </c>
       <c r="J100" s="9" t="n">
-        <v>3.612</v>
+        <v>0.261</v>
       </c>
       <c r="K100" s="9" t="n">
-        <v>3.703</v>
+        <v>0.266</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="14" t="inlineStr"/>
@@ -5019,39 +5003,39 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="D101" s="9" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="E101" s="15" t="n">
-        <v>0.0091</v>
+        <v>0.345</v>
+      </c>
+      <c r="E101" s="10" t="n">
+        <v>-0.0143</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>635600</v>
+        <v>1030000</v>
       </c>
       <c r="G101" s="12" t="n">
-        <v>0.05</v>
+        <v>0.15</v>
       </c>
       <c r="H101" t="n">
-        <v>80.17</v>
-      </c>
-      <c r="I101" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.18</v>
+      </c>
+      <c r="I101" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J101" s="9" t="n">
-        <v>1.007</v>
+        <v>0.352</v>
       </c>
       <c r="K101" s="9" t="n">
-        <v>0.845</v>
+        <v>0.35</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="14" t="inlineStr"/>
@@ -5064,40 +5048,33 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>0470</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>BFIELD</t>
         </is>
       </c>
       <c r="D102" s="9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="E102" s="17" t="n">
-        <v>-0.0098</v>
+        <v>0.48</v>
+      </c>
+      <c r="E102" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>624000</v>
+        <v>1022600</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="H102" t="n">
-        <v>36.47</v>
-      </c>
-      <c r="I102" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J102" s="9" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="K102" s="9" t="n">
-        <v>1.074</v>
-      </c>
+        <v>0.05</v>
+      </c>
+      <c r="I102" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J102" s="9" t="n"/>
+      <c r="K102" s="9" t="n"/>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="14" t="inlineStr"/>
     </row>
@@ -5109,40 +5086,33 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>0471</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>PIONEER</t>
         </is>
       </c>
       <c r="D103" s="9" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="E103" s="15" t="n">
-        <v>0.0161</v>
+        <v>0.295</v>
+      </c>
+      <c r="E103" s="16" t="n">
+        <v>0.0351</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>611300</v>
+        <v>1012500</v>
       </c>
       <c r="G103" s="12" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="H103" t="n">
-        <v>83.94</v>
-      </c>
-      <c r="I103" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J103" s="9" t="n">
-        <v>1.045</v>
-      </c>
-      <c r="K103" s="9" t="n">
-        <v>0.888</v>
-      </c>
+        <v>0.06</v>
+      </c>
+      <c r="I103" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J103" s="9" t="n"/>
+      <c r="K103" s="9" t="n"/>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="14" t="inlineStr"/>
     </row>
@@ -5154,39 +5124,39 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>0045</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>SSB8</t>
         </is>
       </c>
       <c r="D104" s="9" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="E104" s="17" t="n">
-        <v>-0.025</v>
+        <v>0.65</v>
+      </c>
+      <c r="E104" s="10" t="n">
+        <v>-0.0152</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>575500</v>
+        <v>1003500</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>0.16</v>
+        <v>0.26</v>
       </c>
       <c r="H104" t="n">
-        <v>64.58</v>
-      </c>
-      <c r="I104" s="16" t="inlineStr">
+        <v>60.69</v>
+      </c>
+      <c r="I104" s="17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J104" s="9" t="n">
-        <v>1.107</v>
+        <v>0.62</v>
       </c>
       <c r="K104" s="9" t="n">
-        <v>1.007</v>
+        <v>0.581</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="14" t="inlineStr"/>
@@ -5199,39 +5169,39 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>0391</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>AMBEST</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D105" s="9" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="E105" s="17" t="n">
-        <v>-0.0143</v>
+        <v>0.58</v>
+      </c>
+      <c r="E105" s="10" t="n">
+        <v>-0.0252</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>569300</v>
+        <v>976600</v>
       </c>
       <c r="G105" s="12" t="n">
-        <v>0.18</v>
+        <v>0.3</v>
       </c>
       <c r="H105" t="n">
-        <v>58.09</v>
-      </c>
-      <c r="I105" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.94</v>
+      </c>
+      <c r="I105" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J105" s="9" t="n">
-        <v>1.345</v>
+        <v>0.57</v>
       </c>
       <c r="K105" s="9" t="n">
-        <v>1.148</v>
+        <v>0.575</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="14" t="inlineStr"/>
@@ -5244,39 +5214,39 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>5005</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>UNISEM</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D106" s="9" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="E106" s="17" t="n">
-        <v>-0.0066</v>
+        <v>1.62</v>
+      </c>
+      <c r="E106" s="10" t="n">
+        <v>-0.0061</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>527200</v>
+        <v>930200</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>0.23</v>
+        <v>0.14</v>
       </c>
       <c r="H106" t="n">
-        <v>55.65</v>
-      </c>
-      <c r="I106" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>29.4</v>
+      </c>
+      <c r="I106" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J106" s="9" t="n">
-        <v>4.415</v>
+        <v>1.729</v>
       </c>
       <c r="K106" s="9" t="n">
-        <v>4.431</v>
+        <v>1.847</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="14" t="inlineStr"/>
@@ -5289,39 +5259,39 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>4383</t>
+          <t>5073</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>JTIASA</t>
+          <t>NAIM</t>
         </is>
       </c>
       <c r="D107" s="9" t="n">
-        <v>0.955</v>
-      </c>
-      <c r="E107" s="17" t="n">
-        <v>-0.0052</v>
+        <v>0.645</v>
+      </c>
+      <c r="E107" s="10" t="n">
+        <v>-0.0529</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>505400</v>
+        <v>898100</v>
       </c>
       <c r="G107" s="12" t="n">
-        <v>0.11</v>
+        <v>0.72</v>
       </c>
       <c r="H107" t="n">
-        <v>35.25</v>
-      </c>
-      <c r="I107" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.44</v>
+      </c>
+      <c r="I107" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J107" s="9" t="n">
-        <v>0.998</v>
+        <v>0.628</v>
       </c>
       <c r="K107" s="9" t="n">
-        <v>1.047</v>
+        <v>0.612</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="14" t="inlineStr"/>
@@ -5334,45 +5304,1035 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D108" s="9" t="n">
-        <v>2.25</v>
+        <v>0.785</v>
       </c>
       <c r="E108" s="15" t="n">
-        <v>0.009000000000000001</v>
+        <v>0</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>504200</v>
+        <v>841900</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.15</v>
       </c>
       <c r="H108" t="n">
-        <v>53.76</v>
-      </c>
-      <c r="I108" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>86.31</v>
+      </c>
+      <c r="I108" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J108" s="9" t="n">
-        <v>2.226</v>
+        <v>0.767</v>
       </c>
       <c r="K108" s="9" t="n">
-        <v>2.104</v>
+        <v>0.752</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="14" t="inlineStr"/>
     </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>0239</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>ECOMATE</t>
+        </is>
+      </c>
+      <c r="D109" s="9" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="E109" s="10" t="n">
+        <v>-0.0058</v>
+      </c>
+      <c r="F109" s="11" t="n">
+        <v>810000</v>
+      </c>
+      <c r="G109" s="12" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H109" t="n">
+        <v>52.56</v>
+      </c>
+      <c r="I109" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J109" s="9" t="n">
+        <v>0.859</v>
+      </c>
+      <c r="K109" s="9" t="n">
+        <v>0.856</v>
+      </c>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" s="14" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>0339</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>CBHB</t>
+        </is>
+      </c>
+      <c r="D110" s="9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E110" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F110" s="11" t="n">
+        <v>789400</v>
+      </c>
+      <c r="G110" s="12" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H110" t="n">
+        <v>79.33</v>
+      </c>
+      <c r="I110" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J110" s="9" t="n">
+        <v>1.006</v>
+      </c>
+      <c r="K110" s="9" t="n">
+        <v>0.845</v>
+      </c>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" s="14" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>5347</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>TENAGA</t>
+        </is>
+      </c>
+      <c r="D111" s="9" t="n">
+        <v>13.18</v>
+      </c>
+      <c r="E111" s="16" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="F111" s="11" t="n">
+        <v>769700</v>
+      </c>
+      <c r="G111" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H111" t="n">
+        <v>32.24</v>
+      </c>
+      <c r="I111" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J111" s="9" t="n">
+        <v>13.468</v>
+      </c>
+      <c r="K111" s="9" t="n">
+        <v>14.059</v>
+      </c>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" s="14" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>7161</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>KERJAYA</t>
+        </is>
+      </c>
+      <c r="D112" s="9" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="E112" s="10" t="n">
+        <v>-0.005500000000000001</v>
+      </c>
+      <c r="F112" s="11" t="n">
+        <v>748700</v>
+      </c>
+      <c r="G112" s="12" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H112" t="n">
+        <v>74.70999999999999</v>
+      </c>
+      <c r="I112" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J112" s="9" t="n">
+        <v>3.312</v>
+      </c>
+      <c r="K112" s="9" t="n">
+        <v>2.885</v>
+      </c>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" s="14" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>5302</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>ATECH</t>
+        </is>
+      </c>
+      <c r="D113" s="9" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="E113" s="16" t="n">
+        <v>0.006500000000000001</v>
+      </c>
+      <c r="F113" s="11" t="n">
+        <v>739200</v>
+      </c>
+      <c r="G113" s="12" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="H113" t="n">
+        <v>52.54</v>
+      </c>
+      <c r="I113" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J113" s="9" t="n">
+        <v>0.765</v>
+      </c>
+      <c r="K113" s="9" t="n">
+        <v>0.755</v>
+      </c>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" s="14" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>0459</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>SUM</t>
+        </is>
+      </c>
+      <c r="D114" s="9" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="E114" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F114" s="11" t="n">
+        <v>732500</v>
+      </c>
+      <c r="G114" s="12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H114" t="n">
+        <v>69.25</v>
+      </c>
+      <c r="I114" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J114" s="9" t="n">
+        <v>0.672</v>
+      </c>
+      <c r="K114" s="9" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" s="14" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>0271</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>WELLS</t>
+        </is>
+      </c>
+      <c r="D115" s="9" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="E115" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F115" s="11" t="n">
+        <v>700000</v>
+      </c>
+      <c r="G115" s="12" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="H115" t="n">
+        <v>48.02</v>
+      </c>
+      <c r="I115" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J115" s="9" t="n">
+        <v>0.631</v>
+      </c>
+      <c r="K115" s="9" t="n">
+        <v>0.637</v>
+      </c>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" s="14" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>5317</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>CPETECH</t>
+        </is>
+      </c>
+      <c r="D116" s="9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E116" s="16" t="n">
+        <v>0.007800000000000001</v>
+      </c>
+      <c r="F116" s="11" t="n">
+        <v>675400</v>
+      </c>
+      <c r="G116" s="12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H116" t="n">
+        <v>59.48</v>
+      </c>
+      <c r="I116" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J116" s="9" t="n">
+        <v>1.242</v>
+      </c>
+      <c r="K116" s="9" t="n">
+        <v>1.139</v>
+      </c>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" s="14" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>5199</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>HIBISCS</t>
+        </is>
+      </c>
+      <c r="D117" s="9" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="E117" s="16" t="n">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="F117" s="11" t="n">
+        <v>670900</v>
+      </c>
+      <c r="G117" s="12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H117" t="n">
+        <v>53.76</v>
+      </c>
+      <c r="I117" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J117" s="9" t="n">
+        <v>2.226</v>
+      </c>
+      <c r="K117" s="9" t="n">
+        <v>2.104</v>
+      </c>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" s="14" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>0217</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>PWRWELL</t>
+        </is>
+      </c>
+      <c r="D118" s="9" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="E118" s="10" t="n">
+        <v>-0.025</v>
+      </c>
+      <c r="F118" s="11" t="n">
+        <v>656100</v>
+      </c>
+      <c r="G118" s="12" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H118" t="n">
+        <v>64.58</v>
+      </c>
+      <c r="I118" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J118" s="9" t="n">
+        <v>1.107</v>
+      </c>
+      <c r="K118" s="9" t="n">
+        <v>1.007</v>
+      </c>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" s="14" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>5005</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>UNISEM</t>
+        </is>
+      </c>
+      <c r="D119" s="9" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="E119" s="10" t="n">
+        <v>-0.008699999999999999</v>
+      </c>
+      <c r="F119" s="11" t="n">
+        <v>649100</v>
+      </c>
+      <c r="G119" s="12" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H119" t="n">
+        <v>55.25</v>
+      </c>
+      <c r="I119" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J119" s="9" t="n">
+        <v>4.414</v>
+      </c>
+      <c r="K119" s="9" t="n">
+        <v>4.431</v>
+      </c>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" s="14" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>8583</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>MAHSING</t>
+        </is>
+      </c>
+      <c r="D120" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E120" s="10" t="n">
+        <v>-0.0196</v>
+      </c>
+      <c r="F120" s="11" t="n">
+        <v>644500</v>
+      </c>
+      <c r="G120" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H120" t="n">
+        <v>34.67</v>
+      </c>
+      <c r="I120" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J120" s="9" t="n">
+        <v>1.049</v>
+      </c>
+      <c r="K120" s="9" t="n">
+        <v>1.074</v>
+      </c>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" s="14" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>0292</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>JTGROUP</t>
+        </is>
+      </c>
+      <c r="D121" s="9" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="E121" s="16" t="n">
+        <v>0.0161</v>
+      </c>
+      <c r="F121" s="11" t="n">
+        <v>641300</v>
+      </c>
+      <c r="G121" s="12" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H121" t="n">
+        <v>83.94</v>
+      </c>
+      <c r="I121" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J121" s="9" t="n">
+        <v>1.045</v>
+      </c>
+      <c r="K121" s="9" t="n">
+        <v>0.888</v>
+      </c>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" s="14" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>0233</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>PEKAT</t>
+        </is>
+      </c>
+      <c r="D122" s="9" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="E122" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F122" s="11" t="n">
+        <v>625800</v>
+      </c>
+      <c r="G122" s="12" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H122" t="n">
+        <v>88.84999999999999</v>
+      </c>
+      <c r="I122" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J122" s="9" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="K122" s="9" t="n">
+        <v>1.951</v>
+      </c>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" s="14" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>4383</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>JTIASA</t>
+        </is>
+      </c>
+      <c r="D123" s="9" t="n">
+        <v>0.955</v>
+      </c>
+      <c r="E123" s="10" t="n">
+        <v>-0.0052</v>
+      </c>
+      <c r="F123" s="11" t="n">
+        <v>615400</v>
+      </c>
+      <c r="G123" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H123" t="n">
+        <v>35.25</v>
+      </c>
+      <c r="I123" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J123" s="9" t="n">
+        <v>0.998</v>
+      </c>
+      <c r="K123" s="9" t="n">
+        <v>1.047</v>
+      </c>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" s="14" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>0391</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>AMBEST</t>
+        </is>
+      </c>
+      <c r="D124" s="9" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="E124" s="10" t="n">
+        <v>-0.0143</v>
+      </c>
+      <c r="F124" s="11" t="n">
+        <v>611700</v>
+      </c>
+      <c r="G124" s="12" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H124" t="n">
+        <v>58.09</v>
+      </c>
+      <c r="I124" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J124" s="9" t="n">
+        <v>1.345</v>
+      </c>
+      <c r="K124" s="9" t="n">
+        <v>1.148</v>
+      </c>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" s="14" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>0223</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>SAMAIDEN</t>
+        </is>
+      </c>
+      <c r="D125" s="9" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="E125" s="10" t="n">
+        <v>-0.0035</v>
+      </c>
+      <c r="F125" s="11" t="n">
+        <v>589700</v>
+      </c>
+      <c r="G125" s="12" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H125" t="n">
+        <v>88.36</v>
+      </c>
+      <c r="I125" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J125" s="9" t="n">
+        <v>2.183</v>
+      </c>
+      <c r="K125" s="9" t="n">
+        <v>1.768</v>
+      </c>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" s="14" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>1295</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>PBBANK</t>
+        </is>
+      </c>
+      <c r="D126" s="9" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="E126" s="10" t="n">
+        <v>-0.0042</v>
+      </c>
+      <c r="F126" s="11" t="n">
+        <v>578600</v>
+      </c>
+      <c r="G126" s="12" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H126" t="n">
+        <v>38.75</v>
+      </c>
+      <c r="I126" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J126" s="9" t="n">
+        <v>4.844</v>
+      </c>
+      <c r="K126" s="9" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" s="14" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>0167</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>MCLEAN</t>
+        </is>
+      </c>
+      <c r="D127" s="9" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="E127" s="10" t="n">
+        <v>-0.0128</v>
+      </c>
+      <c r="F127" s="11" t="n">
+        <v>562800</v>
+      </c>
+      <c r="G127" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H127" t="n">
+        <v>54.35</v>
+      </c>
+      <c r="I127" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J127" s="9" t="n">
+        <v>0.756</v>
+      </c>
+      <c r="K127" s="9" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" s="14" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>1171</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>MBSB</t>
+        </is>
+      </c>
+      <c r="D128" s="9" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E128" s="16" t="n">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="F128" s="11" t="n">
+        <v>536500</v>
+      </c>
+      <c r="G128" s="12" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H128" t="n">
+        <v>42.85</v>
+      </c>
+      <c r="I128" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J128" s="9" t="n">
+        <v>0.5629999999999999</v>
+      </c>
+      <c r="K128" s="9" t="n">
+        <v>0.595</v>
+      </c>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" s="14" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>7197</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>GESHEN</t>
+        </is>
+      </c>
+      <c r="D129" s="9" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="E129" s="16" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="F129" s="11" t="n">
+        <v>529300</v>
+      </c>
+      <c r="G129" s="12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H129" t="n">
+        <v>30.61</v>
+      </c>
+      <c r="I129" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J129" s="9" t="n">
+        <v>1.182</v>
+      </c>
+      <c r="K129" s="9" t="n">
+        <v>1.285</v>
+      </c>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" s="14" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>5183</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>PCHEM</t>
+        </is>
+      </c>
+      <c r="D130" s="9" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="E130" s="10" t="n">
+        <v>-0.0134</v>
+      </c>
+      <c r="F130" s="11" t="n">
+        <v>523100</v>
+      </c>
+      <c r="G130" s="12" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H130" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="I130" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J130" s="9" t="n">
+        <v>4.583</v>
+      </c>
+      <c r="K130" s="9" t="n">
+        <v>4.538</v>
+      </c>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M108"/>
+  <autoFilter ref="A1:M130"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-09-28/bursa-report-2026-09-28.xlsx
+++ b/docs/downloads/2026-09-28/bursa-report-2026-09-28.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-09-28" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-09-28'!$A$1:$M$130</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-09-28'!$A$1:$M$153</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M130"/>
+  <dimension ref="A1:M153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -557,28 +557,28 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>5291</t>
+          <t>0192</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>HPMT</t>
+          <t>INTA</t>
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.23</v>
+        <v>0.435</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.0698</v>
+        <v>0.0357</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>5696100</v>
+        <v>5168600</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>25.81</v>
+        <v>2.79</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>74.75</v>
+        <v>72.15000000000001</v>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.199</v>
+        <v>0.394</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>0.186</v>
+        <v>0.38</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
@@ -598,7 +598,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>RSI达74.75，已进入超买区；现价0.23高于50日均线0.186约24%，短期均线多头排列，信号偏强但需留意超买风险。</t>
+          <t>现价0.435高于50日均线0.38，均线呈多头排列；但RSI达72.15已入超买区，短期动能偏强而回撤风险上升，信号可靠性中等。</t>
         </is>
       </c>
     </row>
@@ -610,95 +610,103 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
+          <t>5291</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>HPMT</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>0.225</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>0.04650000000000001</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>5817900</v>
+      </c>
+      <c r="G3" s="6" t="n">
+        <v>26.36</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="I3" s="7" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>0.198</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>0.186</v>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>🎯 EMA(5) ≥ EMA(20) + SAR &lt; 当前价格 + Supertrend(3,1.4) &lt; 当前价格 + RSI(14) 上穿 70 + 成交量 &gt; 5000000</t>
+        </is>
+      </c>
+      <c r="M3" s="8" t="inlineStr">
+        <is>
+          <t>现价0.225高于50日均线0.186，均线多头排列；但RSI达72.9已入超买区，短期动能偏热，信号可靠性需谨慎看待。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>信号</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>7204</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>D&amp;O</t>
         </is>
       </c>
-      <c r="D3" s="3" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="E3" s="4" t="n">
-        <v>0.0467</v>
-      </c>
-      <c r="F3" s="5" t="n">
-        <v>5874800</v>
-      </c>
-      <c r="G3" s="6" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>71.27</v>
-      </c>
-      <c r="I3" s="7" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="n">
+      <c r="D4" s="3" t="n">
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>0.0561</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>7249400</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>71.81999999999999</v>
+      </c>
+      <c r="I4" s="7" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="n">
         <v>0.475</v>
       </c>
-      <c r="K3" s="3" t="n">
+      <c r="K4" s="3" t="n">
         <v>0.401</v>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>🎯 EMA(5) ≥ EMA(20) + SAR &lt; 当前价格 + Supertrend(3,1.4) &lt; 当前价格 + RSI(14) 上穿 70 + 成交量 &gt; 5000000</t>
         </is>
       </c>
-      <c r="M3" s="8" t="inlineStr">
-        <is>
-          <t>现价0.56高于50日均线0.401，RSI达71.27已入超买区，EMA与Supertrend偏多，但RSI偏高，信号可靠性需谨慎看待。</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>表格</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>0138</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>ZETRIX</t>
-        </is>
-      </c>
-      <c r="D4" s="9" t="n">
-        <v>0.185</v>
-      </c>
-      <c r="E4" s="10" t="n">
-        <v>-0.0263</v>
-      </c>
-      <c r="F4" s="11" t="n">
-        <v>45871700</v>
-      </c>
-      <c r="G4" s="12" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="H4" t="n">
-        <v>22.18</v>
-      </c>
-      <c r="I4" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J4" s="9" t="n">
-        <v>0.275</v>
-      </c>
-      <c r="K4" s="9" t="n">
-        <v>0.491</v>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" s="14" t="inlineStr"/>
+      <c r="M4" s="8" t="inlineStr">
+        <is>
+          <t>RSI达71.82，已进入超买区；现价0.565远高于50日均线0.401，短期涨幅偏大，信号可靠性需谨慎看待。</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -708,31 +716,40 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0473</t>
+          <t>0138</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Evocom Berhad</t>
+          <t>ZETRIX</t>
         </is>
       </c>
       <c r="D5" s="9" t="n">
-        <v>0.135</v>
-      </c>
-      <c r="E5" s="15" t="n">
-        <v>0</v>
+        <v>0.185</v>
+      </c>
+      <c r="E5" s="10" t="n">
+        <v>-0.0263</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>44333700</v>
-      </c>
-      <c r="G5" s="12" t="n"/>
+        <v>80425100</v>
+      </c>
+      <c r="G5" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H5" t="n">
+        <v>22.18</v>
+      </c>
       <c r="I5" s="13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J5" s="9" t="n"/>
-      <c r="K5" s="9" t="n"/>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="K5" s="9" t="n">
+        <v>0.491</v>
+      </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" s="14" t="inlineStr"/>
     </row>
@@ -744,40 +761,31 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>0473</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>JAKS</t>
+          <t>Evocom Berhad</t>
         </is>
       </c>
       <c r="D6" s="9" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="E6" s="16" t="n">
-        <v>0.0588</v>
+        <v>0.135</v>
+      </c>
+      <c r="E6" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>40917900</v>
-      </c>
-      <c r="G6" s="12" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="H6" t="n">
-        <v>76.5</v>
-      </c>
-      <c r="I6" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J6" s="9" t="n">
-        <v>0.146</v>
-      </c>
-      <c r="K6" s="9" t="n">
-        <v>0.116</v>
-      </c>
+        <v>49582000</v>
+      </c>
+      <c r="G6" s="12" t="n"/>
+      <c r="I6" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J6" s="9" t="n"/>
+      <c r="K6" s="9" t="n"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="14" t="inlineStr"/>
     </row>
@@ -789,39 +797,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="E7" s="10" t="n">
-        <v>-0.0414</v>
+        <v>0.18</v>
+      </c>
+      <c r="E7" s="16" t="n">
+        <v>0.0588</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>28253900</v>
+        <v>44534600</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>1.48</v>
+        <v>0.98</v>
       </c>
       <c r="H7" t="n">
-        <v>49.39</v>
-      </c>
-      <c r="I7" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>76.5</v>
+      </c>
+      <c r="I7" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J7" s="9" t="n">
-        <v>2.587</v>
+        <v>0.146</v>
       </c>
       <c r="K7" s="9" t="n">
-        <v>2.44</v>
+        <v>0.116</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="14" t="inlineStr"/>
@@ -834,28 +842,28 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>0.72</v>
+        <v>2.55</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>-0.0464</v>
+        <v>-0.0414</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>18113200</v>
+        <v>30021300</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>0.42</v>
+        <v>1.57</v>
       </c>
       <c r="H8" t="n">
-        <v>49.15</v>
+        <v>49.39</v>
       </c>
       <c r="I8" s="13" t="inlineStr">
         <is>
@@ -863,10 +871,10 @@
         </is>
       </c>
       <c r="J8" s="9" t="n">
-        <v>0.735</v>
+        <v>2.587</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>0.6830000000000001</v>
+        <v>2.44</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="14" t="inlineStr"/>
@@ -879,39 +887,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>8877</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>EKOVEST</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.185</v>
-      </c>
-      <c r="E9" s="16" t="n">
-        <v>0.0571</v>
+        <v>0.725</v>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>-0.0397</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>14113000</v>
+        <v>22738200</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>3.38</v>
+        <v>0.52</v>
       </c>
       <c r="H9" t="n">
-        <v>55.81</v>
-      </c>
-      <c r="I9" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.12</v>
+      </c>
+      <c r="I9" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J9" s="9" t="n">
-        <v>0.18</v>
+        <v>0.736</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>0.189</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="14" t="inlineStr"/>
@@ -924,39 +932,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>0.395</v>
+        <v>0.355</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>-0.0595</v>
+        <v>-0.0658</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>10029600</v>
+        <v>17498600</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>0.46</v>
+        <v>0.39</v>
       </c>
       <c r="H10" t="n">
-        <v>56.63</v>
-      </c>
-      <c r="I10" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>67.56999999999999</v>
+      </c>
+      <c r="I10" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J10" s="9" t="n">
-        <v>0.382</v>
+        <v>0.316</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>0.32</v>
+        <v>0.183</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="14" t="inlineStr"/>
@@ -969,28 +977,28 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>8877</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>EKOVEST</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>0.55</v>
+        <v>0.19</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>0.0476</v>
+        <v>0.0857</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>9921000</v>
+        <v>14737500</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>1.7</v>
+        <v>3.53</v>
       </c>
       <c r="H11" t="n">
-        <v>62.28</v>
+        <v>61.83</v>
       </c>
       <c r="I11" s="17" t="inlineStr">
         <is>
@@ -998,10 +1006,10 @@
         </is>
       </c>
       <c r="J11" s="9" t="n">
-        <v>0.521</v>
+        <v>0.18</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>0.531</v>
+        <v>0.189</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="14" t="inlineStr"/>
@@ -1014,39 +1022,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>7117</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CJCEN</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E12" s="16" t="n">
-        <v>0.08109999999999999</v>
+        <v>0.395</v>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>-0.0595</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>9491200</v>
+        <v>13802200</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>22.43</v>
+        <v>0.63</v>
       </c>
       <c r="H12" t="n">
-        <v>82.14</v>
-      </c>
-      <c r="I12" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>56.63</v>
+      </c>
+      <c r="I12" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J12" s="9" t="n">
-        <v>0.172</v>
+        <v>0.382</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>0.163</v>
+        <v>0.32</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="14" t="inlineStr"/>
@@ -1059,28 +1067,28 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>0.24</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E13" s="16" t="n">
-        <v>0.0213</v>
+        <v>0.0275</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>9485400</v>
+        <v>11178600</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>0.53</v>
+        <v>0.83</v>
       </c>
       <c r="H13" t="n">
-        <v>56.39</v>
+        <v>60.99</v>
       </c>
       <c r="I13" s="17" t="inlineStr">
         <is>
@@ -1088,10 +1096,10 @@
         </is>
       </c>
       <c r="J13" s="9" t="n">
-        <v>0.232</v>
+        <v>0.524</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>0.233</v>
+        <v>0.477</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="14" t="inlineStr"/>
@@ -1104,28 +1112,28 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="E14" s="10" t="n">
-        <v>-0.0263</v>
+        <v>0.555</v>
+      </c>
+      <c r="E14" s="16" t="n">
+        <v>0.0571</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>9449500</v>
+        <v>10579800</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>0.21</v>
+        <v>1.81</v>
       </c>
       <c r="H14" t="n">
-        <v>72.92</v>
+        <v>63.74</v>
       </c>
       <c r="I14" s="17" t="inlineStr">
         <is>
@@ -1133,10 +1141,10 @@
         </is>
       </c>
       <c r="J14" s="9" t="n">
-        <v>0.318</v>
+        <v>0.521</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>0.183</v>
+        <v>0.531</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="14" t="inlineStr"/>
@@ -1149,39 +1157,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>0.5649999999999999</v>
-      </c>
-      <c r="E15" s="16" t="n">
-        <v>0.0367</v>
+        <v>0.53</v>
+      </c>
+      <c r="E15" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>8919600</v>
+        <v>10195600</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>0.66</v>
+        <v>0.27</v>
       </c>
       <c r="H15" t="n">
-        <v>61.86</v>
-      </c>
-      <c r="I15" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>26.93</v>
+      </c>
+      <c r="I15" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J15" s="9" t="n">
-        <v>0.525</v>
+        <v>0.634</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>0.477</v>
+        <v>0.851</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="14" t="inlineStr"/>
@@ -1194,28 +1202,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>0.72</v>
+        <v>0.245</v>
       </c>
       <c r="E16" s="16" t="n">
-        <v>0.036</v>
+        <v>0.0426</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>8763800</v>
+        <v>9868500</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>0.95</v>
+        <v>0.55</v>
       </c>
       <c r="H16" t="n">
-        <v>57.43</v>
+        <v>59.1</v>
       </c>
       <c r="I16" s="17" t="inlineStr">
         <is>
@@ -1223,10 +1231,10 @@
         </is>
       </c>
       <c r="J16" s="9" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.232</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>0.663</v>
+        <v>0.233</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="14" t="inlineStr"/>
@@ -1239,39 +1247,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.575</v>
       </c>
       <c r="E17" s="10" t="n">
-        <v>-0.0158</v>
+        <v>-0.0171</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>8734500</v>
+        <v>9810200</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>2.15</v>
+        <v>0.41</v>
       </c>
       <c r="H17" t="n">
-        <v>71.01000000000001</v>
-      </c>
-      <c r="I17" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>66.27</v>
+      </c>
+      <c r="I17" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J17" s="9" t="n">
-        <v>0.883</v>
+        <v>0.546</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>0.851</v>
+        <v>0.493</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="14" t="inlineStr"/>
@@ -1284,28 +1292,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>7117</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>CJCEN</t>
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="E18" s="10" t="n">
-        <v>-0.0321</v>
+        <v>0.2</v>
+      </c>
+      <c r="E18" s="16" t="n">
+        <v>0.08109999999999999</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>8371800</v>
+        <v>9756400</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>0.34</v>
+        <v>23.06</v>
       </c>
       <c r="H18" t="n">
-        <v>59.95</v>
+        <v>82.14</v>
       </c>
       <c r="I18" s="17" t="inlineStr">
         <is>
@@ -1313,10 +1321,10 @@
         </is>
       </c>
       <c r="J18" s="9" t="n">
-        <v>1.735</v>
+        <v>0.172</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>1.524</v>
+        <v>0.163</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="14" t="inlineStr"/>
@@ -1329,28 +1337,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0.58</v>
+        <v>1.82</v>
       </c>
       <c r="E19" s="10" t="n">
-        <v>-0.008500000000000001</v>
+        <v>-0.0267</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>7286400</v>
+        <v>9173300</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>0.3</v>
+        <v>0.37</v>
       </c>
       <c r="H19" t="n">
-        <v>68.72</v>
+        <v>60.88</v>
       </c>
       <c r="I19" s="17" t="inlineStr">
         <is>
@@ -1358,10 +1366,10 @@
         </is>
       </c>
       <c r="J19" s="9" t="n">
-        <v>0.547</v>
+        <v>1.736</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>0.493</v>
+        <v>1.524</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="14" t="inlineStr"/>
@@ -1374,28 +1382,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>7315</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AHB</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="E20" s="15" t="n">
-        <v>0</v>
+        <v>0.715</v>
+      </c>
+      <c r="E20" s="16" t="n">
+        <v>0.0288</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>7119000</v>
+        <v>9163300</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>0.74</v>
+        <v>0.99</v>
       </c>
       <c r="H20" t="n">
-        <v>56.29</v>
+        <v>56.69</v>
       </c>
       <c r="I20" s="17" t="inlineStr">
         <is>
@@ -1403,10 +1411,10 @@
         </is>
       </c>
       <c r="J20" s="9" t="n">
-        <v>0.053</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>0.043</v>
+        <v>0.663</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="14" t="inlineStr"/>
@@ -1419,28 +1427,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>5218</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>VANTNRG</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>0.345</v>
-      </c>
-      <c r="E21" s="10" t="n">
-        <v>-0.0143</v>
+        <v>0.22</v>
+      </c>
+      <c r="E21" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>6412500</v>
+        <v>9089700</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>1.6</v>
+        <v>0.43</v>
       </c>
       <c r="H21" t="n">
-        <v>57.32</v>
+        <v>71.25</v>
       </c>
       <c r="I21" s="17" t="inlineStr">
         <is>
@@ -1448,10 +1456,10 @@
         </is>
       </c>
       <c r="J21" s="9" t="n">
-        <v>0.339</v>
+        <v>0.202</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>0.333</v>
+        <v>0.184</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="14" t="inlineStr"/>
@@ -1464,36 +1472,36 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.535</v>
-      </c>
-      <c r="E22" s="16" t="n">
-        <v>0.009399999999999999</v>
+        <v>0.945</v>
+      </c>
+      <c r="E22" s="10" t="n">
+        <v>-0.0053</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>6403200</v>
+        <v>8927500</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>0.17</v>
+        <v>2.2</v>
       </c>
       <c r="H22" t="n">
-        <v>27.96</v>
-      </c>
-      <c r="I22" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>75.98999999999999</v>
+      </c>
+      <c r="I22" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J22" s="9" t="n">
-        <v>0.634</v>
+        <v>0.884</v>
       </c>
       <c r="K22" s="9" t="n">
         <v>0.851</v>
@@ -1509,40 +1517,31 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>0041</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>AIMAX</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="E23" s="10" t="n">
-        <v>-0.0105</v>
+        <v>0.005</v>
+      </c>
+      <c r="E23" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>6215800</v>
-      </c>
-      <c r="G23" s="12" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="H23" t="n">
-        <v>50.74</v>
-      </c>
-      <c r="I23" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J23" s="9" t="n">
-        <v>0.468</v>
-      </c>
-      <c r="K23" s="9" t="n">
-        <v>0.471</v>
-      </c>
+        <v>8298300</v>
+      </c>
+      <c r="G23" s="12" t="n"/>
+      <c r="I23" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J23" s="9" t="n"/>
+      <c r="K23" s="9" t="n"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="14" t="inlineStr"/>
     </row>
@@ -1554,39 +1553,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.3</v>
+        <v>0.47</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>-0.0323</v>
+        <v>-0.0105</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>6082600</v>
+        <v>7652700</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="H24" t="n">
-        <v>49.23</v>
-      </c>
-      <c r="I24" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.74</v>
+      </c>
+      <c r="I24" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J24" s="9" t="n">
-        <v>0.303</v>
+        <v>0.468</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>0.29</v>
+        <v>0.471</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="14" t="inlineStr"/>
@@ -1599,39 +1598,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0175</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>HHRG</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>0.145</v>
+        <v>0.3</v>
       </c>
       <c r="E25" s="10" t="n">
-        <v>-0.0333</v>
+        <v>-0.0323</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>6010000</v>
+        <v>7468700</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>0.15</v>
+        <v>0.4</v>
       </c>
       <c r="H25" t="n">
-        <v>45.75</v>
-      </c>
-      <c r="I25" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.23</v>
+      </c>
+      <c r="I25" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J25" s="9" t="n">
-        <v>0.158</v>
+        <v>0.303</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>0.148</v>
+        <v>0.29</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="14" t="inlineStr"/>
@@ -1644,28 +1643,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0373</t>
+          <t>7315</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>VERDANT</t>
+          <t>AHB</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="E26" s="16" t="n">
-        <v>0.07690000000000001</v>
+        <v>0.055</v>
+      </c>
+      <c r="E26" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>5904000</v>
+        <v>7119000</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>3.44</v>
+        <v>0.74</v>
       </c>
       <c r="H26" t="n">
-        <v>83.92</v>
+        <v>56.29</v>
       </c>
       <c r="I26" s="17" t="inlineStr">
         <is>
@@ -1673,10 +1672,10 @@
         </is>
       </c>
       <c r="J26" s="9" t="n">
-        <v>0.225</v>
+        <v>0.053</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>0.209</v>
+        <v>0.043</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="14" t="inlineStr"/>
@@ -1689,28 +1688,28 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>0175</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>HHRG</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="E27" s="16" t="n">
-        <v>0.0132</v>
+        <v>0.145</v>
+      </c>
+      <c r="E27" s="10" t="n">
+        <v>-0.0333</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>5482100</v>
+        <v>7029400</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0.57</v>
+        <v>0.17</v>
       </c>
       <c r="H27" t="n">
-        <v>63.96</v>
+        <v>45.75</v>
       </c>
       <c r="I27" s="17" t="inlineStr">
         <is>
@@ -1718,10 +1717,10 @@
         </is>
       </c>
       <c r="J27" s="9" t="n">
-        <v>0.373</v>
+        <v>0.158</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>0.371</v>
+        <v>0.148</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="14" t="inlineStr"/>
@@ -1734,39 +1733,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>IOIPG</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>0.605</v>
-      </c>
-      <c r="E28" s="15" t="n">
-        <v>0</v>
+        <v>3.51</v>
+      </c>
+      <c r="E28" s="16" t="n">
+        <v>0.005699999999999999</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>5326900</v>
+        <v>6960300</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0.54</v>
+        <v>1.48</v>
       </c>
       <c r="H28" t="n">
-        <v>48.07</v>
-      </c>
-      <c r="I28" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.66</v>
+      </c>
+      <c r="I28" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J28" s="9" t="n">
-        <v>0.608</v>
+        <v>3.616</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>0.604</v>
+        <v>3.704</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="14" t="inlineStr"/>
@@ -1779,31 +1778,40 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0041</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AIMAX</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>0.005</v>
+        <v>0.245</v>
       </c>
       <c r="E29" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>5218300</v>
-      </c>
-      <c r="G29" s="12" t="n"/>
-      <c r="I29" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J29" s="9" t="n"/>
-      <c r="K29" s="9" t="n"/>
+        <v>6747600</v>
+      </c>
+      <c r="G29" s="12" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H29" t="n">
+        <v>31.98</v>
+      </c>
+      <c r="I29" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J29" s="9" t="n">
+        <v>0.276</v>
+      </c>
+      <c r="K29" s="9" t="n">
+        <v>0.328</v>
+      </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="14" t="inlineStr"/>
     </row>
@@ -1815,28 +1823,28 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>0373</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>VERDANT</t>
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="E30" s="15" t="n">
-        <v>0</v>
+        <v>0.28</v>
+      </c>
+      <c r="E30" s="16" t="n">
+        <v>0.07690000000000001</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>5019600</v>
+        <v>6726600</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>0.24</v>
+        <v>3.92</v>
       </c>
       <c r="H30" t="n">
-        <v>71.25</v>
+        <v>83.92</v>
       </c>
       <c r="I30" s="17" t="inlineStr">
         <is>
@@ -1844,10 +1852,10 @@
         </is>
       </c>
       <c r="J30" s="9" t="n">
-        <v>0.202</v>
+        <v>0.225</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>0.184</v>
+        <v>0.209</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="14" t="inlineStr"/>
@@ -1860,28 +1868,28 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0192</t>
+          <t>5218</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>INTA</t>
+          <t>VANTNRG</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>0.435</v>
-      </c>
-      <c r="E31" s="16" t="n">
-        <v>0.0357</v>
+        <v>0.345</v>
+      </c>
+      <c r="E31" s="10" t="n">
+        <v>-0.0143</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>4635100</v>
+        <v>6712400</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>2.5</v>
+        <v>1.68</v>
       </c>
       <c r="H31" t="n">
-        <v>72.15000000000001</v>
+        <v>57.32</v>
       </c>
       <c r="I31" s="17" t="inlineStr">
         <is>
@@ -1889,10 +1897,10 @@
         </is>
       </c>
       <c r="J31" s="9" t="n">
-        <v>0.394</v>
+        <v>0.339</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>0.38</v>
+        <v>0.333</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="14" t="inlineStr"/>
@@ -1920,10 +1928,10 @@
         <v>-0.006500000000000001</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>4541500</v>
+        <v>6381500</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>0.36</v>
+        <v>0.51</v>
       </c>
       <c r="H32" t="n">
         <v>47.75</v>
@@ -1965,10 +1973,10 @@
         <v>0.0058</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>4431000</v>
+        <v>6013000</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="H33" t="n">
         <v>46.9</v>
@@ -1995,39 +2003,39 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0280</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>MBN</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="E34" s="15" t="n">
-        <v>0</v>
+        <v>0.385</v>
+      </c>
+      <c r="E34" s="16" t="n">
+        <v>0.0132</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>4427900</v>
+        <v>5677100</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>1.38</v>
+        <v>0.59</v>
       </c>
       <c r="H34" t="n">
-        <v>52.85</v>
-      </c>
-      <c r="I34" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.96</v>
+      </c>
+      <c r="I34" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J34" s="9" t="n">
-        <v>0.154</v>
+        <v>0.373</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>0.147</v>
+        <v>0.371</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="14" t="inlineStr"/>
@@ -2040,28 +2048,28 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>0.245</v>
+        <v>0.605</v>
       </c>
       <c r="E35" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>4364600</v>
+        <v>5350700</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0.15</v>
+        <v>0.55</v>
       </c>
       <c r="H35" t="n">
-        <v>31.98</v>
+        <v>48.07</v>
       </c>
       <c r="I35" s="17" t="inlineStr">
         <is>
@@ -2069,10 +2077,10 @@
         </is>
       </c>
       <c r="J35" s="9" t="n">
-        <v>0.276</v>
+        <v>0.608</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>0.328</v>
+        <v>0.604</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="14" t="inlineStr"/>
@@ -2085,39 +2093,39 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>MALAKOF</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>0.795</v>
+        <v>4.86</v>
       </c>
       <c r="E36" s="10" t="n">
-        <v>-0.0124</v>
+        <v>-0.004099999999999999</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>4337100</v>
+        <v>5297700</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>1.04</v>
+        <v>0.28</v>
       </c>
       <c r="H36" t="n">
-        <v>47.1</v>
-      </c>
-      <c r="I36" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>62.59</v>
+      </c>
+      <c r="I36" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J36" s="9" t="n">
-        <v>0.803</v>
+        <v>4.74</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>0.806</v>
+        <v>4.509</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="14" t="inlineStr"/>
@@ -2130,39 +2138,39 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>0095</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>4.87</v>
-      </c>
-      <c r="E37" s="10" t="n">
-        <v>-0.002</v>
+        <v>0.155</v>
+      </c>
+      <c r="E37" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>4227400</v>
+        <v>5150000</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0.22</v>
+        <v>0.24</v>
       </c>
       <c r="H37" t="n">
-        <v>63.46</v>
-      </c>
-      <c r="I37" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>44.73</v>
+      </c>
+      <c r="I37" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J37" s="9" t="n">
-        <v>4.741</v>
+        <v>0.156</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>4.509</v>
+        <v>0.159</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="14" t="inlineStr"/>
@@ -2175,28 +2183,28 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>TANCO</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>0.165</v>
+        <v>0.47</v>
       </c>
       <c r="E38" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>3881500</v>
+        <v>4446100</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>0.14</v>
+        <v>0.5</v>
       </c>
       <c r="H38" t="n">
-        <v>34.17</v>
+        <v>58.56</v>
       </c>
       <c r="I38" s="13" t="inlineStr">
         <is>
@@ -2204,10 +2212,10 @@
         </is>
       </c>
       <c r="J38" s="9" t="n">
-        <v>0.182</v>
+        <v>0.448</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>0.221</v>
+        <v>0.407</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="14" t="inlineStr"/>
@@ -2220,28 +2228,28 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>0280</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>AVANGAAD</t>
+          <t>MBN</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E39" s="16" t="n">
-        <v>0.0172</v>
+        <v>0.155</v>
+      </c>
+      <c r="E39" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>3749300</v>
+        <v>4427900</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>2.02</v>
+        <v>1.38</v>
       </c>
       <c r="H39" t="n">
-        <v>49.23</v>
+        <v>52.85</v>
       </c>
       <c r="I39" s="13" t="inlineStr">
         <is>
@@ -2249,10 +2257,10 @@
         </is>
       </c>
       <c r="J39" s="9" t="n">
-        <v>0.295</v>
+        <v>0.154</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>0.297</v>
+        <v>0.147</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="14" t="inlineStr"/>
@@ -2265,28 +2273,28 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>MALAKOF</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>2.98</v>
+        <v>0.8</v>
       </c>
       <c r="E40" s="10" t="n">
-        <v>-0.0165</v>
+        <v>-0.0062</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>3546100</v>
+        <v>4374400</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>0.26</v>
+        <v>1.05</v>
       </c>
       <c r="H40" t="n">
-        <v>64.89</v>
+        <v>48.44</v>
       </c>
       <c r="I40" s="17" t="inlineStr">
         <is>
@@ -2294,10 +2302,10 @@
         </is>
       </c>
       <c r="J40" s="9" t="n">
-        <v>2.858</v>
+        <v>0.803</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>2.716</v>
+        <v>0.806</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="14" t="inlineStr"/>
@@ -2310,28 +2318,28 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>0.295</v>
+        <v>0.83</v>
       </c>
       <c r="E41" s="16" t="n">
-        <v>0.0172</v>
+        <v>0.0122</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>3541000</v>
+        <v>4372700</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>0.55</v>
+        <v>0.45</v>
       </c>
       <c r="H41" t="n">
-        <v>66.27</v>
+        <v>71.11</v>
       </c>
       <c r="I41" s="17" t="inlineStr">
         <is>
@@ -2339,10 +2347,10 @@
         </is>
       </c>
       <c r="J41" s="9" t="n">
-        <v>0.275</v>
+        <v>0.715</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>0.27</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="14" t="inlineStr"/>
@@ -2355,39 +2363,39 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>VELESTO</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>0.215</v>
+        <v>2.98</v>
       </c>
       <c r="E42" s="10" t="n">
-        <v>-0.0227</v>
+        <v>-0.0165</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>3475900</v>
+        <v>4300200</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>0.16</v>
+        <v>0.32</v>
       </c>
       <c r="H42" t="n">
-        <v>29.99</v>
-      </c>
-      <c r="I42" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.89</v>
+      </c>
+      <c r="I42" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J42" s="9" t="n">
-        <v>0.238</v>
+        <v>2.858</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>0.249</v>
+        <v>2.716</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="14" t="inlineStr"/>
@@ -2400,39 +2408,39 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="E43" s="10" t="n">
-        <v>-0.0213</v>
+        <v>0.295</v>
+      </c>
+      <c r="E43" s="16" t="n">
+        <v>0.0172</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>3461700</v>
+        <v>4101000</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>0.39</v>
+        <v>0.64</v>
       </c>
       <c r="H43" t="n">
-        <v>55.64</v>
-      </c>
-      <c r="I43" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.27</v>
+      </c>
+      <c r="I43" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J43" s="9" t="n">
-        <v>0.447</v>
+        <v>0.275</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>0.407</v>
+        <v>0.27</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="14" t="inlineStr"/>
@@ -2445,28 +2453,28 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>8893</t>
+          <t>0340</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>MKLAND</t>
+          <t>NORTHERN</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>0.18</v>
+        <v>1.3</v>
       </c>
       <c r="E44" s="16" t="n">
-        <v>0.0286</v>
+        <v>0.0156</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>3407600</v>
+        <v>3929600</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>3.13</v>
+        <v>0.72</v>
       </c>
       <c r="H44" t="n">
-        <v>81.90000000000001</v>
+        <v>95.47</v>
       </c>
       <c r="I44" s="17" t="inlineStr">
         <is>
@@ -2474,10 +2482,10 @@
         </is>
       </c>
       <c r="J44" s="9" t="n">
-        <v>0.152</v>
+        <v>0.88</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>0.145</v>
+        <v>0.734</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="14" t="inlineStr"/>
@@ -2490,39 +2498,39 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0111</t>
+          <t>2429</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t>TANCO</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
         <v>0.165</v>
       </c>
-      <c r="E45" s="16" t="n">
-        <v>0.0313</v>
+      <c r="E45" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>3335700</v>
+        <v>3913100</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>1.28</v>
+        <v>0.14</v>
       </c>
       <c r="H45" t="n">
-        <v>66.66</v>
-      </c>
-      <c r="I45" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.17</v>
+      </c>
+      <c r="I45" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J45" s="9" t="n">
-        <v>0.148</v>
+        <v>0.182</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>0.139</v>
+        <v>0.221</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="14" t="inlineStr"/>
@@ -2535,28 +2543,28 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>9059</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>TSH</t>
+          <t>VELESTO</t>
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>1.31</v>
+        <v>0.215</v>
       </c>
       <c r="E46" s="10" t="n">
-        <v>-0.0438</v>
+        <v>-0.0227</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>3178900</v>
+        <v>3770200</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>1.37</v>
+        <v>0.17</v>
       </c>
       <c r="H46" t="n">
-        <v>38.43</v>
+        <v>29.99</v>
       </c>
       <c r="I46" s="13" t="inlineStr">
         <is>
@@ -2564,10 +2572,10 @@
         </is>
       </c>
       <c r="J46" s="9" t="n">
-        <v>1.405</v>
+        <v>0.238</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>1.317</v>
+        <v>0.249</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="14" t="inlineStr"/>
@@ -2580,39 +2588,39 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>0.255</v>
-      </c>
-      <c r="E47" s="10" t="n">
-        <v>-0.0192</v>
+        <v>0.295</v>
+      </c>
+      <c r="E47" s="16" t="n">
+        <v>0.0172</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>2899500</v>
+        <v>3749300</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>0.24</v>
+        <v>2.02</v>
       </c>
       <c r="H47" t="n">
-        <v>37.73</v>
-      </c>
-      <c r="I47" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.23</v>
+      </c>
+      <c r="I47" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J47" s="9" t="n">
-        <v>0.272</v>
+        <v>0.295</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>0.314</v>
+        <v>0.297</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="14" t="inlineStr"/>
@@ -2625,28 +2633,28 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>9059</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>TSH</t>
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="E48" s="10" t="n">
-        <v>-0.0076</v>
+        <v>-0.05110000000000001</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>2833500</v>
+        <v>3457300</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>0.24</v>
+        <v>1.49</v>
       </c>
       <c r="H48" t="n">
-        <v>43.34</v>
+        <v>37.44</v>
       </c>
       <c r="I48" s="13" t="inlineStr">
         <is>
@@ -2654,10 +2662,10 @@
         </is>
       </c>
       <c r="J48" s="9" t="n">
-        <v>1.374</v>
+        <v>1.404</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>1.29</v>
+        <v>1.317</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="14" t="inlineStr"/>
@@ -2670,28 +2678,28 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>8893</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>MKLAND</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="E49" s="10" t="n">
-        <v>-0.008399999999999999</v>
+        <v>0.175</v>
+      </c>
+      <c r="E49" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>2803300</v>
+        <v>3440600</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>0.17</v>
+        <v>3.16</v>
       </c>
       <c r="H49" t="n">
-        <v>52.86</v>
+        <v>79.92</v>
       </c>
       <c r="I49" s="17" t="inlineStr">
         <is>
@@ -2699,10 +2707,10 @@
         </is>
       </c>
       <c r="J49" s="9" t="n">
-        <v>2.35</v>
+        <v>0.151</v>
       </c>
       <c r="K49" s="9" t="n">
-        <v>2.239</v>
+        <v>0.145</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="14" t="inlineStr"/>
@@ -2715,28 +2723,28 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>0111</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>0.335</v>
+        <v>0.165</v>
       </c>
       <c r="E50" s="16" t="n">
-        <v>0.0308</v>
+        <v>0.0313</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>2667900</v>
+        <v>3355700</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>0.33</v>
+        <v>1.29</v>
       </c>
       <c r="H50" t="n">
-        <v>54.74</v>
+        <v>66.66</v>
       </c>
       <c r="I50" s="17" t="inlineStr">
         <is>
@@ -2744,10 +2752,10 @@
         </is>
       </c>
       <c r="J50" s="9" t="n">
-        <v>0.331</v>
+        <v>0.148</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>0.311</v>
+        <v>0.139</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="14" t="inlineStr"/>
@@ -2760,39 +2768,39 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>0.365</v>
-      </c>
-      <c r="E51" s="16" t="n">
-        <v>0.0139</v>
+        <v>1.05</v>
+      </c>
+      <c r="E51" s="10" t="n">
+        <v>-0.0455</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>2634600</v>
+        <v>3298500</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>0.38</v>
+        <v>0.3</v>
       </c>
       <c r="H51" t="n">
-        <v>67.36</v>
-      </c>
-      <c r="I51" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.24</v>
+      </c>
+      <c r="I51" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J51" s="9" t="n">
-        <v>0.337</v>
+        <v>1.081</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>0.319</v>
+        <v>1.024</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="14" t="inlineStr"/>
@@ -2805,28 +2813,28 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D52" s="9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="E52" s="16" t="n">
-        <v>0.0156</v>
+        <v>2.79</v>
+      </c>
+      <c r="E52" s="10" t="n">
+        <v>-0.0312</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>2576900</v>
+        <v>3205000</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>0.47</v>
+        <v>0.46</v>
       </c>
       <c r="H52" t="n">
-        <v>95.47</v>
+        <v>61.02</v>
       </c>
       <c r="I52" s="17" t="inlineStr">
         <is>
@@ -2834,10 +2842,10 @@
         </is>
       </c>
       <c r="J52" s="9" t="n">
-        <v>0.88</v>
+        <v>2.626</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>0.734</v>
+        <v>2.495</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="14" t="inlineStr"/>
@@ -2850,28 +2858,28 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>NEXG</t>
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>0.365</v>
-      </c>
-      <c r="E53" s="10" t="n">
-        <v>-0.0135</v>
+        <v>0.325</v>
+      </c>
+      <c r="E53" s="16" t="n">
+        <v>0.0156</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>2563900</v>
+        <v>3162500</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>0.43</v>
+        <v>0.19</v>
       </c>
       <c r="H53" t="n">
-        <v>48.52</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="I53" s="17" t="inlineStr">
         <is>
@@ -2879,10 +2887,10 @@
         </is>
       </c>
       <c r="J53" s="9" t="n">
-        <v>0.367</v>
+        <v>0.285</v>
       </c>
       <c r="K53" s="9" t="n">
-        <v>0.366</v>
+        <v>0.277</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="14" t="inlineStr"/>
@@ -2895,39 +2903,39 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="E54" s="15" t="n">
-        <v>0</v>
+        <v>1.31</v>
+      </c>
+      <c r="E54" s="10" t="n">
+        <v>-0.0076</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>2528400</v>
+        <v>3157000</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="H54" t="n">
-        <v>70.16</v>
-      </c>
-      <c r="I54" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.34</v>
+      </c>
+      <c r="I54" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J54" s="9" t="n">
-        <v>0.714</v>
+        <v>1.374</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>0.6870000000000001</v>
+        <v>1.29</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="14" t="inlineStr"/>
@@ -2940,28 +2948,28 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>0.72</v>
+        <v>0.255</v>
       </c>
       <c r="E55" s="10" t="n">
-        <v>-0.04</v>
+        <v>-0.0192</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>2501600</v>
+        <v>2954600</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>0.43</v>
+        <v>0.25</v>
       </c>
       <c r="H55" t="n">
-        <v>60.74</v>
+        <v>37.73</v>
       </c>
       <c r="I55" s="17" t="inlineStr">
         <is>
@@ -2969,10 +2977,10 @@
         </is>
       </c>
       <c r="J55" s="9" t="n">
-        <v>0.681</v>
+        <v>0.272</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>0.611</v>
+        <v>0.314</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="14" t="inlineStr"/>
@@ -2985,28 +2993,28 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D56" s="9" t="n">
-        <v>0.415</v>
-      </c>
-      <c r="E56" s="10" t="n">
-        <v>-0.0119</v>
+        <v>0.33</v>
+      </c>
+      <c r="E56" s="16" t="n">
+        <v>0.0154</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>2452800</v>
+        <v>2856200</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>0.22</v>
+        <v>0.36</v>
       </c>
       <c r="H56" t="n">
-        <v>56.5</v>
+        <v>52.72</v>
       </c>
       <c r="I56" s="17" t="inlineStr">
         <is>
@@ -3014,10 +3022,10 @@
         </is>
       </c>
       <c r="J56" s="9" t="n">
-        <v>0.409</v>
+        <v>0.33</v>
       </c>
       <c r="K56" s="9" t="n">
-        <v>0.41</v>
+        <v>0.311</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="14" t="inlineStr"/>
@@ -3030,39 +3038,39 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>2.77</v>
+        <v>2.08</v>
       </c>
       <c r="E57" s="10" t="n">
-        <v>-0.0382</v>
+        <v>-0.0048</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>2435400</v>
+        <v>2838900</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>0.35</v>
+        <v>0.17</v>
       </c>
       <c r="H57" t="n">
-        <v>59.76</v>
-      </c>
-      <c r="I57" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.92</v>
+      </c>
+      <c r="I57" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J57" s="9" t="n">
-        <v>2.624</v>
+        <v>2.126</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>2.495</v>
+        <v>2.062</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="14" t="inlineStr"/>
@@ -3075,39 +3083,39 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0393</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>TEAMSTR</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D58" s="9" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="E58" s="15" t="n">
-        <v>0</v>
+        <v>0.72</v>
+      </c>
+      <c r="E58" s="10" t="n">
+        <v>-0.04</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>2276900</v>
+        <v>2829000</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>0.75</v>
+        <v>0.49</v>
       </c>
       <c r="H58" t="n">
-        <v>31.51</v>
-      </c>
-      <c r="I58" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.74</v>
+      </c>
+      <c r="I58" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J58" s="9" t="n">
-        <v>0.244</v>
+        <v>0.681</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>0.243</v>
+        <v>0.611</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="14" t="inlineStr"/>
@@ -3120,39 +3128,39 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>0.8149999999999999</v>
-      </c>
-      <c r="E59" s="16" t="n">
-        <v>0.0062</v>
+        <v>2.37</v>
+      </c>
+      <c r="E59" s="10" t="n">
+        <v>-0.008399999999999999</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>2241100</v>
+        <v>2806700</v>
       </c>
       <c r="G59" s="12" t="n">
         <v>0.17</v>
       </c>
       <c r="H59" t="n">
-        <v>52.51</v>
-      </c>
-      <c r="I59" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.86</v>
+      </c>
+      <c r="I59" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J59" s="9" t="n">
-        <v>0.8100000000000001</v>
+        <v>2.35</v>
       </c>
       <c r="K59" s="9" t="n">
-        <v>0.8080000000000001</v>
+        <v>2.239</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="14" t="inlineStr"/>
@@ -3165,28 +3173,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="E60" s="16" t="n">
-        <v>0.023</v>
+        <v>0.365</v>
+      </c>
+      <c r="E60" s="10" t="n">
+        <v>-0.0135</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>2184700</v>
+        <v>2774000</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>0.18</v>
+        <v>0.46</v>
       </c>
       <c r="H60" t="n">
-        <v>79.79000000000001</v>
+        <v>48.52</v>
       </c>
       <c r="I60" s="17" t="inlineStr">
         <is>
@@ -3194,10 +3202,10 @@
         </is>
       </c>
       <c r="J60" s="9" t="n">
-        <v>3.527</v>
+        <v>0.367</v>
       </c>
       <c r="K60" s="9" t="n">
-        <v>2.356</v>
+        <v>0.366</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="14" t="inlineStr"/>
@@ -3210,39 +3218,39 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>IOIPG</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="E61" s="16" t="n">
-        <v>0.0201</v>
+        <v>0.36</v>
+      </c>
+      <c r="E61" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>2153000</v>
+        <v>2696600</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>0.46</v>
+        <v>0.38</v>
       </c>
       <c r="H61" t="n">
-        <v>43.14</v>
-      </c>
-      <c r="I61" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>65.70999999999999</v>
+      </c>
+      <c r="I61" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J61" s="9" t="n">
-        <v>3.621</v>
+        <v>0.337</v>
       </c>
       <c r="K61" s="9" t="n">
-        <v>3.705</v>
+        <v>0.319</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="14" t="inlineStr"/>
@@ -3255,39 +3263,39 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D62" s="9" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="E62" s="10" t="n">
-        <v>-0.0455</v>
+        <v>2.5</v>
+      </c>
+      <c r="E62" s="16" t="n">
+        <v>0.0121</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>2120000</v>
+        <v>2630600</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="H62" t="n">
-        <v>47.24</v>
-      </c>
-      <c r="I62" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.94</v>
+      </c>
+      <c r="I62" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J62" s="9" t="n">
-        <v>1.081</v>
+        <v>2.439</v>
       </c>
       <c r="K62" s="9" t="n">
-        <v>1.024</v>
+        <v>2.276</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="14" t="inlineStr"/>
@@ -3300,28 +3308,28 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="E63" s="16" t="n">
-        <v>0.0333</v>
+        <v>0.41</v>
+      </c>
+      <c r="E63" s="10" t="n">
+        <v>-0.0238</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>2103400</v>
+        <v>2472800</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>0.64</v>
+        <v>0.22</v>
       </c>
       <c r="H63" t="n">
-        <v>47.25</v>
+        <v>51.48</v>
       </c>
       <c r="I63" s="17" t="inlineStr">
         <is>
@@ -3329,10 +3337,10 @@
         </is>
       </c>
       <c r="J63" s="9" t="n">
-        <v>0.928</v>
+        <v>0.409</v>
       </c>
       <c r="K63" s="9" t="n">
-        <v>0.969</v>
+        <v>0.41</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="14" t="inlineStr"/>
@@ -3345,28 +3353,28 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D64" s="9" t="n">
-        <v>5.82</v>
-      </c>
-      <c r="E64" s="10" t="n">
-        <v>-0.0119</v>
+        <v>4.44</v>
+      </c>
+      <c r="E64" s="16" t="n">
+        <v>0.0207</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>2089600</v>
+        <v>2383700</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="H64" t="n">
-        <v>59.92</v>
+        <v>79.69</v>
       </c>
       <c r="I64" s="17" t="inlineStr">
         <is>
@@ -3374,10 +3382,10 @@
         </is>
       </c>
       <c r="J64" s="9" t="n">
-        <v>5.688</v>
+        <v>3.526</v>
       </c>
       <c r="K64" s="9" t="n">
-        <v>5.131</v>
+        <v>2.355</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="14" t="inlineStr"/>
@@ -3390,28 +3398,28 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="E65" s="10" t="n">
-        <v>-0.0417</v>
+        <v>1.3</v>
+      </c>
+      <c r="E65" s="16" t="n">
+        <v>0.007800000000000001</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>2072900</v>
+        <v>2361300</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>0.23</v>
+        <v>0.2</v>
       </c>
       <c r="H65" t="n">
-        <v>50.13</v>
+        <v>36.84</v>
       </c>
       <c r="I65" s="17" t="inlineStr">
         <is>
@@ -3419,10 +3427,10 @@
         </is>
       </c>
       <c r="J65" s="9" t="n">
-        <v>1.163</v>
+        <v>1.329</v>
       </c>
       <c r="K65" s="9" t="n">
-        <v>1.1</v>
+        <v>1.444</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="14" t="inlineStr"/>
@@ -3435,28 +3443,28 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>MRCB</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D66" s="9" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="E66" s="15" t="n">
-        <v>0</v>
+        <v>5.81</v>
+      </c>
+      <c r="E66" s="10" t="n">
+        <v>-0.0136</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>2005500</v>
+        <v>2352700</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>0.26</v>
+        <v>0.16</v>
       </c>
       <c r="H66" t="n">
-        <v>39.08</v>
+        <v>59.45</v>
       </c>
       <c r="I66" s="17" t="inlineStr">
         <is>
@@ -3464,10 +3472,10 @@
         </is>
       </c>
       <c r="J66" s="9" t="n">
-        <v>0.298</v>
+        <v>5.687</v>
       </c>
       <c r="K66" s="9" t="n">
-        <v>0.312</v>
+        <v>5.131</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="14" t="inlineStr"/>
@@ -3480,39 +3488,39 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E67" s="16" t="n">
-        <v>0.0121</v>
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="E67" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>2003900</v>
+        <v>2312100</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>0.13</v>
+        <v>0.18</v>
       </c>
       <c r="H67" t="n">
-        <v>61.94</v>
-      </c>
-      <c r="I67" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.19</v>
+      </c>
+      <c r="I67" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J67" s="9" t="n">
-        <v>2.439</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>2.276</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="14" t="inlineStr"/>
@@ -3525,39 +3533,39 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>0369</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>JSSOLAR</t>
         </is>
       </c>
       <c r="D68" s="9" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="E68" s="10" t="n">
-        <v>-0.0222</v>
+        <v>0.26</v>
+      </c>
+      <c r="E68" s="16" t="n">
+        <v>0.04</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>1946500</v>
+        <v>2304300</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>0.36</v>
+        <v>2.24</v>
       </c>
       <c r="H68" t="n">
-        <v>73.93000000000001</v>
-      </c>
-      <c r="I68" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>73.58</v>
+      </c>
+      <c r="I68" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J68" s="9" t="n">
-        <v>2.455</v>
+        <v>0.212</v>
       </c>
       <c r="K68" s="9" t="n">
-        <v>2.118</v>
+        <v>0.198</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="14" t="inlineStr"/>
@@ -3570,39 +3578,39 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>0393</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>TEAMSTR</t>
         </is>
       </c>
       <c r="D69" s="9" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="E69" s="16" t="n">
-        <v>0.0086</v>
+        <v>0.23</v>
+      </c>
+      <c r="E69" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>1769000</v>
+        <v>2276900</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>0.26</v>
+        <v>0.75</v>
       </c>
       <c r="H69" t="n">
-        <v>49.17</v>
-      </c>
-      <c r="I69" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>31.51</v>
+      </c>
+      <c r="I69" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J69" s="9" t="n">
-        <v>1.181</v>
+        <v>0.244</v>
       </c>
       <c r="K69" s="9" t="n">
-        <v>1.14</v>
+        <v>0.243</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="14" t="inlineStr"/>
@@ -3615,28 +3623,28 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D70" s="9" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="E70" s="16" t="n">
-        <v>0.0152</v>
+        <v>0.29</v>
+      </c>
+      <c r="E70" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>1766700</v>
+        <v>2261100</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>0.19</v>
+        <v>0.3</v>
       </c>
       <c r="H70" t="n">
-        <v>61.53</v>
+        <v>39.08</v>
       </c>
       <c r="I70" s="17" t="inlineStr">
         <is>
@@ -3644,10 +3652,10 @@
         </is>
       </c>
       <c r="J70" s="9" t="n">
-        <v>0.634</v>
+        <v>0.298</v>
       </c>
       <c r="K70" s="9" t="n">
-        <v>0.575</v>
+        <v>0.312</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="14" t="inlineStr"/>
@@ -3660,39 +3668,39 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>2.1</v>
+        <v>0.93</v>
       </c>
       <c r="E71" s="16" t="n">
-        <v>0.0048</v>
+        <v>0.0333</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>1766500</v>
+        <v>2234000</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>0.11</v>
+        <v>0.68</v>
       </c>
       <c r="H71" t="n">
-        <v>48.16</v>
-      </c>
-      <c r="I71" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.25</v>
+      </c>
+      <c r="I71" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J71" s="9" t="n">
-        <v>2.128</v>
+        <v>0.928</v>
       </c>
       <c r="K71" s="9" t="n">
-        <v>2.062</v>
+        <v>0.969</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="14" t="inlineStr"/>
@@ -3705,28 +3713,28 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0369</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>JSSOLAR</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D72" s="9" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E72" s="16" t="n">
-        <v>0.04</v>
+        <v>1.15</v>
+      </c>
+      <c r="E72" s="10" t="n">
+        <v>-0.0417</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>1703600</v>
+        <v>2207200</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>1.65</v>
+        <v>0.24</v>
       </c>
       <c r="H72" t="n">
-        <v>73.58</v>
+        <v>50.13</v>
       </c>
       <c r="I72" s="17" t="inlineStr">
         <is>
@@ -3734,10 +3742,10 @@
         </is>
       </c>
       <c r="J72" s="9" t="n">
-        <v>0.212</v>
+        <v>1.163</v>
       </c>
       <c r="K72" s="9" t="n">
-        <v>0.198</v>
+        <v>1.1</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="14" t="inlineStr"/>
@@ -3750,39 +3758,39 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>NEXG</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>0.32</v>
+        <v>0.765</v>
       </c>
       <c r="E73" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>1701300</v>
+        <v>2156200</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>0.1</v>
+        <v>0.34</v>
       </c>
       <c r="H73" t="n">
-        <v>65.18000000000001</v>
-      </c>
-      <c r="I73" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.13</v>
+      </c>
+      <c r="I73" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J73" s="9" t="n">
-        <v>0.284</v>
+        <v>0.773</v>
       </c>
       <c r="K73" s="9" t="n">
-        <v>0.277</v>
+        <v>0.773</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="14" t="inlineStr"/>
@@ -3795,28 +3803,28 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D74" s="9" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="E74" s="10" t="n">
-        <v>-0.0229</v>
+        <v>0.67</v>
+      </c>
+      <c r="E74" s="16" t="n">
+        <v>0.0152</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>1669400</v>
+        <v>2097100</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>0.29</v>
+        <v>0.22</v>
       </c>
       <c r="H74" t="n">
-        <v>49.38</v>
+        <v>61.53</v>
       </c>
       <c r="I74" s="17" t="inlineStr">
         <is>
@@ -3824,10 +3832,10 @@
         </is>
       </c>
       <c r="J74" s="9" t="n">
-        <v>2.569</v>
+        <v>0.634</v>
       </c>
       <c r="K74" s="9" t="n">
-        <v>2.535</v>
+        <v>0.575</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="14" t="inlineStr"/>
@@ -3840,39 +3848,39 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D75" s="9" t="n">
-        <v>0.425</v>
-      </c>
-      <c r="E75" s="15" t="n">
-        <v>0</v>
+        <v>2.66</v>
+      </c>
+      <c r="E75" s="10" t="n">
+        <v>-0.0148</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>1582900</v>
+        <v>2046900</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>0.27</v>
+        <v>0.38</v>
       </c>
       <c r="H75" t="n">
-        <v>57.85</v>
-      </c>
-      <c r="I75" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>76.54000000000001</v>
+      </c>
+      <c r="I75" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J75" s="9" t="n">
-        <v>0.402</v>
+        <v>2.457</v>
       </c>
       <c r="K75" s="9" t="n">
-        <v>0.4</v>
+        <v>2.118</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="14" t="inlineStr"/>
@@ -3885,39 +3893,39 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>4243</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>WTK</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D76" s="9" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="E76" s="10" t="n">
-        <v>-0.0204</v>
+        <v>0.425</v>
+      </c>
+      <c r="E76" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>1581600</v>
+        <v>1930800</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>0.63</v>
+        <v>0.33</v>
       </c>
       <c r="H76" t="n">
-        <v>35.93</v>
-      </c>
-      <c r="I76" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.85</v>
+      </c>
+      <c r="I76" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J76" s="9" t="n">
-        <v>1.045</v>
+        <v>0.402</v>
       </c>
       <c r="K76" s="9" t="n">
-        <v>1.014</v>
+        <v>0.4</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="14" t="inlineStr"/>
@@ -3930,39 +3938,39 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D77" s="9" t="n">
-        <v>0.545</v>
-      </c>
-      <c r="E77" s="15" t="n">
-        <v>0</v>
+        <v>1.17</v>
+      </c>
+      <c r="E77" s="16" t="n">
+        <v>0.0086</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>1534000</v>
+        <v>1795100</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>0.24</v>
+        <v>0.27</v>
       </c>
       <c r="H77" t="n">
-        <v>39.08</v>
-      </c>
-      <c r="I77" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.17</v>
+      </c>
+      <c r="I77" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J77" s="9" t="n">
-        <v>0.5610000000000001</v>
+        <v>1.181</v>
       </c>
       <c r="K77" s="9" t="n">
-        <v>0.59</v>
+        <v>1.14</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="14" t="inlineStr"/>
@@ -3975,28 +3983,28 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D78" s="9" t="n">
-        <v>0.54</v>
+        <v>2.55</v>
       </c>
       <c r="E78" s="10" t="n">
-        <v>-0.0182</v>
+        <v>-0.0267</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>1518000</v>
+        <v>1723500</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>0.85</v>
+        <v>0.3</v>
       </c>
       <c r="H78" t="n">
-        <v>61.11</v>
+        <v>48.43</v>
       </c>
       <c r="I78" s="17" t="inlineStr">
         <is>
@@ -4004,10 +4012,10 @@
         </is>
       </c>
       <c r="J78" s="9" t="n">
-        <v>0.497</v>
+        <v>2.568</v>
       </c>
       <c r="K78" s="9" t="n">
-        <v>0.401</v>
+        <v>2.535</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="14" t="inlineStr"/>
@@ -4020,39 +4028,39 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D79" s="9" t="n">
-        <v>0.765</v>
-      </c>
-      <c r="E79" s="15" t="n">
-        <v>0</v>
+        <v>4.11</v>
+      </c>
+      <c r="E79" s="16" t="n">
+        <v>0.0123</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>1466400</v>
+        <v>1690200</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>0.23</v>
+        <v>0.35</v>
       </c>
       <c r="H79" t="n">
-        <v>46.13</v>
-      </c>
-      <c r="I79" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>79.13</v>
+      </c>
+      <c r="I79" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J79" s="9" t="n">
-        <v>0.773</v>
+        <v>3.54</v>
       </c>
       <c r="K79" s="9" t="n">
-        <v>0.773</v>
+        <v>3.224</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="14" t="inlineStr"/>
@@ -4080,10 +4088,10 @@
         <v>-0.0039</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>1450500</v>
+        <v>1666500</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="H80" t="n">
         <v>47.99</v>
@@ -4110,39 +4118,39 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D81" s="9" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="E81" s="10" t="n">
-        <v>-0.0112</v>
+        <v>0.545</v>
+      </c>
+      <c r="E81" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>1433400</v>
+        <v>1659000</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>0.24</v>
+        <v>0.26</v>
       </c>
       <c r="H81" t="n">
-        <v>47.93</v>
-      </c>
-      <c r="I81" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.08</v>
+      </c>
+      <c r="I81" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J81" s="9" t="n">
-        <v>1.771</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="K81" s="9" t="n">
-        <v>1.806</v>
+        <v>0.59</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="14" t="inlineStr"/>
@@ -4155,28 +4163,28 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>4243</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>WTK</t>
         </is>
       </c>
       <c r="D82" s="9" t="n">
-        <v>0.6</v>
+        <v>0.96</v>
       </c>
       <c r="E82" s="10" t="n">
-        <v>-0.0164</v>
+        <v>-0.0204</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>1363300</v>
+        <v>1620900</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>0.27</v>
+        <v>0.65</v>
       </c>
       <c r="H82" t="n">
-        <v>35.76</v>
+        <v>35.93</v>
       </c>
       <c r="I82" s="13" t="inlineStr">
         <is>
@@ -4184,10 +4192,10 @@
         </is>
       </c>
       <c r="J82" s="9" t="n">
-        <v>0.637</v>
+        <v>1.045</v>
       </c>
       <c r="K82" s="9" t="n">
-        <v>0.657</v>
+        <v>1.014</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="14" t="inlineStr"/>
@@ -4200,39 +4208,39 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>0358</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>ICTZONE</t>
         </is>
       </c>
       <c r="D83" s="9" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="E83" s="16" t="n">
-        <v>0.0155</v>
+        <v>0.26</v>
+      </c>
+      <c r="E83" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>1349700</v>
+        <v>1602800</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>0.11</v>
+        <v>0.58</v>
       </c>
       <c r="H83" t="n">
-        <v>39.66</v>
-      </c>
-      <c r="I83" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.51</v>
+      </c>
+      <c r="I83" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J83" s="9" t="n">
-        <v>1.33</v>
+        <v>0.262</v>
       </c>
       <c r="K83" s="9" t="n">
-        <v>1.445</v>
+        <v>0.251</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="14" t="inlineStr"/>
@@ -4245,33 +4253,40 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0468</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>UNIPAC</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D84" s="9" t="n">
-        <v>0.245</v>
+        <v>1.04</v>
       </c>
       <c r="E84" s="10" t="n">
-        <v>-0.0392</v>
+        <v>-0.0189</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>1349400</v>
+        <v>1588700</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="I84" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J84" s="9" t="n"/>
-      <c r="K84" s="9" t="n"/>
+        <v>0.19</v>
+      </c>
+      <c r="H84" t="n">
+        <v>77.48999999999999</v>
+      </c>
+      <c r="I84" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J84" s="9" t="n">
+        <v>0.893</v>
+      </c>
+      <c r="K84" s="9" t="n">
+        <v>0.759</v>
+      </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="14" t="inlineStr"/>
     </row>
@@ -4283,28 +4298,28 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D85" s="9" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="E85" s="15" t="n">
-        <v>0</v>
+        <v>0.535</v>
+      </c>
+      <c r="E85" s="10" t="n">
+        <v>-0.0273</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>1347900</v>
+        <v>1538800</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>0.4</v>
+        <v>0.86</v>
       </c>
       <c r="H85" t="n">
-        <v>70.55</v>
+        <v>60.09</v>
       </c>
       <c r="I85" s="17" t="inlineStr">
         <is>
@@ -4312,10 +4327,10 @@
         </is>
       </c>
       <c r="J85" s="9" t="n">
-        <v>0.634</v>
+        <v>0.497</v>
       </c>
       <c r="K85" s="9" t="n">
-        <v>0.591</v>
+        <v>0.401</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="14" t="inlineStr"/>
@@ -4328,28 +4343,28 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0358</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>ICTZONE</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D86" s="9" t="n">
-        <v>0.26</v>
+        <v>0.61</v>
       </c>
       <c r="E86" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>1299900</v>
+        <v>1534900</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>0.47</v>
+        <v>0.31</v>
       </c>
       <c r="H86" t="n">
-        <v>50.51</v>
+        <v>38.17</v>
       </c>
       <c r="I86" s="13" t="inlineStr">
         <is>
@@ -4357,10 +4372,10 @@
         </is>
       </c>
       <c r="J86" s="9" t="n">
-        <v>0.262</v>
+        <v>0.638</v>
       </c>
       <c r="K86" s="9" t="n">
-        <v>0.251</v>
+        <v>0.658</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="14" t="inlineStr"/>
@@ -4373,28 +4388,28 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0272</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>TTVHB</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D87" s="9" t="n">
-        <v>0.25</v>
+        <v>0.865</v>
       </c>
       <c r="E87" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>1246100</v>
+        <v>1529100</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>0.36</v>
+        <v>0.52</v>
       </c>
       <c r="H87" t="n">
-        <v>49.72</v>
+        <v>59.03</v>
       </c>
       <c r="I87" s="13" t="inlineStr">
         <is>
@@ -4402,10 +4417,10 @@
         </is>
       </c>
       <c r="J87" s="9" t="n">
-        <v>0.249</v>
+        <v>0.859</v>
       </c>
       <c r="K87" s="9" t="n">
-        <v>0.253</v>
+        <v>0.856</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="14" t="inlineStr"/>
@@ -4418,39 +4433,39 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D88" s="9" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="E88" s="10" t="n">
-        <v>-0.0189</v>
+        <v>1.63</v>
+      </c>
+      <c r="E88" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>1232100</v>
+        <v>1519800</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>0.33</v>
+        <v>0.23</v>
       </c>
       <c r="H88" t="n">
-        <v>55.42</v>
-      </c>
-      <c r="I88" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>30.25</v>
+      </c>
+      <c r="I88" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J88" s="9" t="n">
-        <v>0.512</v>
+        <v>1.73</v>
       </c>
       <c r="K88" s="9" t="n">
-        <v>0.464</v>
+        <v>1.847</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="14" t="inlineStr"/>
@@ -4463,28 +4478,28 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D89" s="9" t="n">
-        <v>1.03</v>
+        <v>1.76</v>
       </c>
       <c r="E89" s="10" t="n">
-        <v>-0.0283</v>
+        <v>-0.0112</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>1220900</v>
+        <v>1460200</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>0.15</v>
+        <v>0.24</v>
       </c>
       <c r="H89" t="n">
-        <v>75.38</v>
+        <v>47.93</v>
       </c>
       <c r="I89" s="17" t="inlineStr">
         <is>
@@ -4492,10 +4507,10 @@
         </is>
       </c>
       <c r="J89" s="9" t="n">
-        <v>0.892</v>
+        <v>1.771</v>
       </c>
       <c r="K89" s="9" t="n">
-        <v>0.759</v>
+        <v>1.806</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="14" t="inlineStr"/>
@@ -4508,28 +4523,28 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0265</t>
+          <t>0268</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>INFOM</t>
+          <t>L&amp;PBHD</t>
         </is>
       </c>
       <c r="D90" s="9" t="n">
-        <v>1.67</v>
+        <v>0.21</v>
       </c>
       <c r="E90" s="16" t="n">
-        <v>0.0373</v>
+        <v>0.0244</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>1169800</v>
+        <v>1428600</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>3.41</v>
+        <v>0.52</v>
       </c>
       <c r="H90" t="n">
-        <v>71.34999999999999</v>
+        <v>71.81999999999999</v>
       </c>
       <c r="I90" s="17" t="inlineStr">
         <is>
@@ -4537,10 +4552,10 @@
         </is>
       </c>
       <c r="J90" s="9" t="n">
-        <v>1.588</v>
+        <v>0.187</v>
       </c>
       <c r="K90" s="9" t="n">
-        <v>1.536</v>
+        <v>0.156</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="14" t="inlineStr"/>
@@ -4553,39 +4568,39 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D91" s="9" t="n">
-        <v>4.04</v>
-      </c>
-      <c r="E91" s="10" t="n">
-        <v>-0.0049</v>
+        <v>1.89</v>
+      </c>
+      <c r="E91" s="16" t="n">
+        <v>0.0053</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>1163100</v>
+        <v>1418800</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>0.24</v>
+        <v>0.31</v>
       </c>
       <c r="H91" t="n">
-        <v>76.90000000000001</v>
-      </c>
-      <c r="I91" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.25</v>
+      </c>
+      <c r="I91" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J91" s="9" t="n">
-        <v>3.533</v>
+        <v>1.956</v>
       </c>
       <c r="K91" s="9" t="n">
-        <v>3.223</v>
+        <v>2.078</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="14" t="inlineStr"/>
@@ -4598,39 +4613,39 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0376</t>
+          <t>0032</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>IAB</t>
+          <t>REDTONE</t>
         </is>
       </c>
       <c r="D92" s="9" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="E92" s="16" t="n">
-        <v>0.0394</v>
+        <v>0.36</v>
+      </c>
+      <c r="E92" s="10" t="n">
+        <v>-0.0137</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>1158000</v>
+        <v>1408400</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>0.77</v>
+        <v>0.83</v>
       </c>
       <c r="H92" t="n">
-        <v>53.02</v>
-      </c>
-      <c r="I92" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>59.96</v>
+      </c>
+      <c r="I92" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J92" s="9" t="n">
-        <v>1.286</v>
+        <v>0.354</v>
       </c>
       <c r="K92" s="9" t="n">
-        <v>1.345</v>
+        <v>0.319</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="14" t="inlineStr"/>
@@ -4643,28 +4658,28 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0268</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>L&amp;PBHD</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D93" s="9" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="E93" s="16" t="n">
-        <v>0.0244</v>
+        <v>0.65</v>
+      </c>
+      <c r="E93" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>1140100</v>
+        <v>1383100</v>
       </c>
       <c r="G93" s="12" t="n">
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="H93" t="n">
-        <v>71.81999999999999</v>
+        <v>70.55</v>
       </c>
       <c r="I93" s="17" t="inlineStr">
         <is>
@@ -4672,10 +4687,10 @@
         </is>
       </c>
       <c r="J93" s="9" t="n">
-        <v>0.187</v>
+        <v>0.634</v>
       </c>
       <c r="K93" s="9" t="n">
-        <v>0.156</v>
+        <v>0.591</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="14" t="inlineStr"/>
@@ -4688,39 +4703,39 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>3379</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>INSAS</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D94" s="9" t="n">
-        <v>0.905</v>
-      </c>
-      <c r="E94" s="16" t="n">
-        <v>0.0226</v>
+        <v>0.52</v>
+      </c>
+      <c r="E94" s="10" t="n">
+        <v>-0.0189</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>1134000</v>
+        <v>1367700</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>1.96</v>
+        <v>0.37</v>
       </c>
       <c r="H94" t="n">
-        <v>57.27</v>
-      </c>
-      <c r="I94" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.42</v>
+      </c>
+      <c r="I94" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J94" s="9" t="n">
-        <v>0.895</v>
+        <v>0.512</v>
       </c>
       <c r="K94" s="9" t="n">
-        <v>0.9</v>
+        <v>0.464</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="14" t="inlineStr"/>
@@ -4733,40 +4748,33 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0032</t>
+          <t>0468</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>REDTONE</t>
+          <t>UNIPAC</t>
         </is>
       </c>
       <c r="D95" s="9" t="n">
-        <v>0.36</v>
+        <v>0.25</v>
       </c>
       <c r="E95" s="10" t="n">
-        <v>-0.0137</v>
+        <v>-0.0196</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>1108400</v>
+        <v>1364400</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="H95" t="n">
-        <v>59.96</v>
+        <v>0.08</v>
       </c>
       <c r="I95" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J95" s="9" t="n">
-        <v>0.354</v>
-      </c>
-      <c r="K95" s="9" t="n">
-        <v>0.319</v>
-      </c>
+      <c r="J95" s="9" t="n"/>
+      <c r="K95" s="9" t="n"/>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="14" t="inlineStr"/>
     </row>
@@ -4778,39 +4786,39 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>MBSB</t>
         </is>
       </c>
       <c r="D96" s="9" t="n">
-        <v>1.9</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="E96" s="16" t="n">
-        <v>0.0106</v>
+        <v>0.018</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>1108100</v>
+        <v>1363300</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>0.25</v>
+        <v>0.36</v>
       </c>
       <c r="H96" t="n">
-        <v>37.93</v>
-      </c>
-      <c r="I96" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.24</v>
+      </c>
+      <c r="I96" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J96" s="9" t="n">
-        <v>1.957</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="K96" s="9" t="n">
-        <v>2.079</v>
+        <v>0.595</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="14" t="inlineStr"/>
@@ -4823,28 +4831,28 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>8524</t>
+          <t>0376</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>TALIWRK</t>
+          <t>IAB</t>
         </is>
       </c>
       <c r="D97" s="9" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E97" s="10" t="n">
-        <v>-0.0189</v>
+        <v>1.32</v>
+      </c>
+      <c r="E97" s="16" t="n">
+        <v>0.0394</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>1091800</v>
+        <v>1344400</v>
       </c>
       <c r="G97" s="12" t="n">
-        <v>0.35</v>
+        <v>0.9</v>
       </c>
       <c r="H97" t="n">
-        <v>51.19</v>
+        <v>53.02</v>
       </c>
       <c r="I97" s="17" t="inlineStr">
         <is>
@@ -4852,10 +4860,10 @@
         </is>
       </c>
       <c r="J97" s="9" t="n">
-        <v>0.254</v>
+        <v>1.286</v>
       </c>
       <c r="K97" s="9" t="n">
-        <v>0.271</v>
+        <v>1.345</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="14" t="inlineStr"/>
@@ -4868,28 +4876,28 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>0265</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>INFOM</t>
         </is>
       </c>
       <c r="D98" s="9" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="E98" s="10" t="n">
-        <v>-0.0268</v>
+        <v>1.68</v>
+      </c>
+      <c r="E98" s="16" t="n">
+        <v>0.0435</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>1073700</v>
+        <v>1301500</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>0.23</v>
+        <v>3.79</v>
       </c>
       <c r="H98" t="n">
-        <v>76.75</v>
+        <v>72.48</v>
       </c>
       <c r="I98" s="17" t="inlineStr">
         <is>
@@ -4897,10 +4905,10 @@
         </is>
       </c>
       <c r="J98" s="9" t="n">
-        <v>0.973</v>
+        <v>1.589</v>
       </c>
       <c r="K98" s="9" t="n">
-        <v>0.8</v>
+        <v>1.536</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="14" t="inlineStr"/>
@@ -4913,39 +4921,39 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0104</t>
+          <t>0272</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>GENETEC</t>
+          <t>TTVHB</t>
         </is>
       </c>
       <c r="D99" s="9" t="n">
-        <v>0.315</v>
-      </c>
-      <c r="E99" s="10" t="n">
-        <v>-0.0156</v>
+        <v>0.25</v>
+      </c>
+      <c r="E99" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>1070300</v>
+        <v>1257000</v>
       </c>
       <c r="G99" s="12" t="n">
-        <v>0.17</v>
+        <v>0.37</v>
       </c>
       <c r="H99" t="n">
-        <v>44.97</v>
-      </c>
-      <c r="I99" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.72</v>
+      </c>
+      <c r="I99" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J99" s="9" t="n">
-        <v>0.321</v>
+        <v>0.249</v>
       </c>
       <c r="K99" s="9" t="n">
-        <v>0.339</v>
+        <v>0.253</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="14" t="inlineStr"/>
@@ -4958,39 +4966,39 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0450</t>
+          <t>0045</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>MFGROUP</t>
+          <t>SSB8</t>
         </is>
       </c>
       <c r="D100" s="9" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E100" s="15" t="n">
-        <v>0</v>
+        <v>0.65</v>
+      </c>
+      <c r="E100" s="10" t="n">
+        <v>-0.0152</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>1052600</v>
+        <v>1213200</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>1.33</v>
+        <v>0.32</v>
       </c>
       <c r="H100" t="n">
-        <v>45.51</v>
-      </c>
-      <c r="I100" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.69</v>
+      </c>
+      <c r="I100" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J100" s="9" t="n">
-        <v>0.261</v>
+        <v>0.62</v>
       </c>
       <c r="K100" s="9" t="n">
-        <v>0.266</v>
+        <v>0.581</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="14" t="inlineStr"/>
@@ -5003,39 +5011,39 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D101" s="9" t="n">
-        <v>0.345</v>
+        <v>0.315</v>
       </c>
       <c r="E101" s="10" t="n">
-        <v>-0.0143</v>
+        <v>-0.0156</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>1030000</v>
+        <v>1201700</v>
       </c>
       <c r="G101" s="12" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="H101" t="n">
-        <v>43.18</v>
-      </c>
-      <c r="I101" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>44.97</v>
+      </c>
+      <c r="I101" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J101" s="9" t="n">
-        <v>0.352</v>
+        <v>0.321</v>
       </c>
       <c r="K101" s="9" t="n">
-        <v>0.35</v>
+        <v>0.339</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="14" t="inlineStr"/>
@@ -5048,33 +5056,40 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0470</t>
+          <t>3379</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>BFIELD</t>
+          <t>INSAS</t>
         </is>
       </c>
       <c r="D102" s="9" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="E102" s="15" t="n">
-        <v>0</v>
+        <v>0.905</v>
+      </c>
+      <c r="E102" s="16" t="n">
+        <v>0.0226</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>1022600</v>
+        <v>1191000</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I102" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J102" s="9" t="n"/>
-      <c r="K102" s="9" t="n"/>
+        <v>2.05</v>
+      </c>
+      <c r="H102" t="n">
+        <v>57.27</v>
+      </c>
+      <c r="I102" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J102" s="9" t="n">
+        <v>0.895</v>
+      </c>
+      <c r="K102" s="9" t="n">
+        <v>0.9</v>
+      </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="14" t="inlineStr"/>
     </row>
@@ -5086,33 +5101,40 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0471</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>PIONEER</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D103" s="9" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E103" s="16" t="n">
-        <v>0.0351</v>
+        <v>0.785</v>
+      </c>
+      <c r="E103" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>1012500</v>
+        <v>1183900</v>
       </c>
       <c r="G103" s="12" t="n">
-        <v>0.06</v>
+        <v>0.2</v>
+      </c>
+      <c r="H103" t="n">
+        <v>86.31</v>
       </c>
       <c r="I103" s="17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J103" s="9" t="n"/>
-      <c r="K103" s="9" t="n"/>
+      <c r="J103" s="9" t="n">
+        <v>0.767</v>
+      </c>
+      <c r="K103" s="9" t="n">
+        <v>0.752</v>
+      </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="14" t="inlineStr"/>
     </row>
@@ -5124,28 +5146,28 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>0045</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>SSB8</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D104" s="9" t="n">
-        <v>0.65</v>
+        <v>1.09</v>
       </c>
       <c r="E104" s="10" t="n">
-        <v>-0.0152</v>
+        <v>-0.0268</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>1003500</v>
+        <v>1141900</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="H104" t="n">
-        <v>60.69</v>
+        <v>76.75</v>
       </c>
       <c r="I104" s="17" t="inlineStr">
         <is>
@@ -5153,10 +5175,10 @@
         </is>
       </c>
       <c r="J104" s="9" t="n">
-        <v>0.62</v>
+        <v>0.973</v>
       </c>
       <c r="K104" s="9" t="n">
-        <v>0.581</v>
+        <v>0.8</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="14" t="inlineStr"/>
@@ -5184,10 +5206,10 @@
         <v>-0.0252</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>976600</v>
+        <v>1127700</v>
       </c>
       <c r="G105" s="12" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="H105" t="n">
         <v>52.94</v>
@@ -5214,40 +5236,33 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>0470</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>BFIELD</t>
         </is>
       </c>
       <c r="D106" s="9" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="E106" s="10" t="n">
-        <v>-0.0061</v>
+        <v>0.48</v>
+      </c>
+      <c r="E106" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>930200</v>
+        <v>1125100</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="H106" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="I106" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J106" s="9" t="n">
-        <v>1.729</v>
-      </c>
-      <c r="K106" s="9" t="n">
-        <v>1.847</v>
-      </c>
+        <v>0.05</v>
+      </c>
+      <c r="I106" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J106" s="9" t="n"/>
+      <c r="K106" s="9" t="n"/>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="14" t="inlineStr"/>
     </row>
@@ -5259,28 +5274,28 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>5073</t>
+          <t>8524</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>NAIM</t>
+          <t>TALIWRK</t>
         </is>
       </c>
       <c r="D107" s="9" t="n">
-        <v>0.645</v>
+        <v>0.26</v>
       </c>
       <c r="E107" s="10" t="n">
-        <v>-0.0529</v>
+        <v>-0.0189</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>898100</v>
+        <v>1093800</v>
       </c>
       <c r="G107" s="12" t="n">
-        <v>0.72</v>
+        <v>0.35</v>
       </c>
       <c r="H107" t="n">
-        <v>57.44</v>
+        <v>51.19</v>
       </c>
       <c r="I107" s="17" t="inlineStr">
         <is>
@@ -5288,10 +5303,10 @@
         </is>
       </c>
       <c r="J107" s="9" t="n">
-        <v>0.628</v>
+        <v>0.254</v>
       </c>
       <c r="K107" s="9" t="n">
-        <v>0.612</v>
+        <v>0.271</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="14" t="inlineStr"/>
@@ -5304,28 +5319,28 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>1589</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>IWCITY</t>
         </is>
       </c>
       <c r="D108" s="9" t="n">
-        <v>0.785</v>
-      </c>
-      <c r="E108" s="15" t="n">
-        <v>0</v>
+        <v>0.215</v>
+      </c>
+      <c r="E108" s="16" t="n">
+        <v>0.0238</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>841900</v>
+        <v>1065000</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>0.15</v>
+        <v>2.18</v>
       </c>
       <c r="H108" t="n">
-        <v>86.31</v>
+        <v>48.08</v>
       </c>
       <c r="I108" s="17" t="inlineStr">
         <is>
@@ -5333,10 +5348,10 @@
         </is>
       </c>
       <c r="J108" s="9" t="n">
-        <v>0.767</v>
+        <v>0.215</v>
       </c>
       <c r="K108" s="9" t="n">
-        <v>0.752</v>
+        <v>0.225</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="14" t="inlineStr"/>
@@ -5349,40 +5364,33 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>0239</t>
+          <t>0471</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>ECOMATE</t>
+          <t>PIONEER</t>
         </is>
       </c>
       <c r="D109" s="9" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="E109" s="10" t="n">
-        <v>-0.0058</v>
+        <v>0.29</v>
+      </c>
+      <c r="E109" s="16" t="n">
+        <v>0.0175</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>810000</v>
+        <v>1063500</v>
       </c>
       <c r="G109" s="12" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="H109" t="n">
-        <v>52.56</v>
-      </c>
-      <c r="I109" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J109" s="9" t="n">
-        <v>0.859</v>
-      </c>
-      <c r="K109" s="9" t="n">
-        <v>0.856</v>
-      </c>
+        <v>0.06</v>
+      </c>
+      <c r="I109" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J109" s="9" t="n"/>
+      <c r="K109" s="9" t="n"/>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="14" t="inlineStr"/>
     </row>
@@ -5394,28 +5402,28 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>0172</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>OCK</t>
         </is>
       </c>
       <c r="D110" s="9" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="E110" s="15" t="n">
-        <v>0</v>
+        <v>0.48</v>
+      </c>
+      <c r="E110" s="10" t="n">
+        <v>-0.0204</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>789400</v>
+        <v>1059900</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.32</v>
       </c>
       <c r="H110" t="n">
-        <v>79.33</v>
+        <v>68.65000000000001</v>
       </c>
       <c r="I110" s="17" t="inlineStr">
         <is>
@@ -5423,10 +5431,10 @@
         </is>
       </c>
       <c r="J110" s="9" t="n">
-        <v>1.006</v>
+        <v>0.446</v>
       </c>
       <c r="K110" s="9" t="n">
-        <v>0.845</v>
+        <v>0.404</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="14" t="inlineStr"/>
@@ -5439,39 +5447,39 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>0450</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>TENAGA</t>
+          <t>MFGROUP</t>
         </is>
       </c>
       <c r="D111" s="9" t="n">
-        <v>13.18</v>
-      </c>
-      <c r="E111" s="16" t="n">
-        <v>0.003</v>
+        <v>0.26</v>
+      </c>
+      <c r="E111" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>769700</v>
+        <v>1052600</v>
       </c>
       <c r="G111" s="12" t="n">
-        <v>0.08</v>
+        <v>1.33</v>
       </c>
       <c r="H111" t="n">
-        <v>32.24</v>
-      </c>
-      <c r="I111" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.51</v>
+      </c>
+      <c r="I111" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J111" s="9" t="n">
-        <v>13.468</v>
+        <v>0.261</v>
       </c>
       <c r="K111" s="9" t="n">
-        <v>14.059</v>
+        <v>0.266</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="14" t="inlineStr"/>
@@ -5484,39 +5492,39 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>7161</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>KERJAYA</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="D112" s="9" t="n">
-        <v>3.61</v>
+        <v>0.345</v>
       </c>
       <c r="E112" s="10" t="n">
-        <v>-0.005500000000000001</v>
+        <v>-0.0143</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>748700</v>
+        <v>1031200</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>0.23</v>
+        <v>0.15</v>
       </c>
       <c r="H112" t="n">
-        <v>74.70999999999999</v>
-      </c>
-      <c r="I112" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.18</v>
+      </c>
+      <c r="I112" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J112" s="9" t="n">
-        <v>3.312</v>
+        <v>0.352</v>
       </c>
       <c r="K112" s="9" t="n">
-        <v>2.885</v>
+        <v>0.35</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="14" t="inlineStr"/>
@@ -5529,28 +5537,28 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>ATECH</t>
+          <t>TENAGA</t>
         </is>
       </c>
       <c r="D113" s="9" t="n">
-        <v>0.77</v>
+        <v>13.22</v>
       </c>
       <c r="E113" s="16" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.0061</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>739200</v>
+        <v>999000</v>
       </c>
       <c r="G113" s="12" t="n">
-        <v>0.51</v>
+        <v>0.1</v>
       </c>
       <c r="H113" t="n">
-        <v>52.54</v>
+        <v>34.32</v>
       </c>
       <c r="I113" s="17" t="inlineStr">
         <is>
@@ -5558,10 +5566,10 @@
         </is>
       </c>
       <c r="J113" s="9" t="n">
-        <v>0.765</v>
+        <v>13.472</v>
       </c>
       <c r="K113" s="9" t="n">
-        <v>0.755</v>
+        <v>14.06</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="14" t="inlineStr"/>
@@ -5574,28 +5582,28 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D114" s="9" t="n">
-        <v>0.725</v>
-      </c>
-      <c r="E114" s="15" t="n">
-        <v>0</v>
+        <v>1.11</v>
+      </c>
+      <c r="E114" s="16" t="n">
+        <v>0.0091</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>732500</v>
+        <v>990300</v>
       </c>
       <c r="G114" s="12" t="n">
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
       <c r="H114" t="n">
-        <v>69.25</v>
+        <v>80.17</v>
       </c>
       <c r="I114" s="17" t="inlineStr">
         <is>
@@ -5603,10 +5611,10 @@
         </is>
       </c>
       <c r="J114" s="9" t="n">
-        <v>0.672</v>
+        <v>1.007</v>
       </c>
       <c r="K114" s="9" t="n">
-        <v>0.615</v>
+        <v>0.845</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="14" t="inlineStr"/>
@@ -5619,28 +5627,28 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>0271</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>WELLS</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D115" s="9" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E115" s="15" t="n">
-        <v>0</v>
+        <v>4.39</v>
+      </c>
+      <c r="E115" s="10" t="n">
+        <v>-0.0223</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>700000</v>
+        <v>970500</v>
       </c>
       <c r="G115" s="12" t="n">
-        <v>0.72</v>
+        <v>0.13</v>
       </c>
       <c r="H115" t="n">
-        <v>48.02</v>
+        <v>44.19</v>
       </c>
       <c r="I115" s="13" t="inlineStr">
         <is>
@@ -5648,10 +5656,10 @@
         </is>
       </c>
       <c r="J115" s="9" t="n">
-        <v>0.631</v>
+        <v>4.579</v>
       </c>
       <c r="K115" s="9" t="n">
-        <v>0.637</v>
+        <v>4.537</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="14" t="inlineStr"/>
@@ -5664,39 +5672,39 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>5073</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>NAIM</t>
         </is>
       </c>
       <c r="D116" s="9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="E116" s="16" t="n">
-        <v>0.007800000000000001</v>
+        <v>0.65</v>
+      </c>
+      <c r="E116" s="10" t="n">
+        <v>-0.0455</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>675400</v>
+        <v>938400</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>0.17</v>
+        <v>0.76</v>
       </c>
       <c r="H116" t="n">
-        <v>59.48</v>
-      </c>
-      <c r="I116" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.12</v>
+      </c>
+      <c r="I116" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J116" s="9" t="n">
-        <v>1.242</v>
+        <v>0.629</v>
       </c>
       <c r="K116" s="9" t="n">
-        <v>1.139</v>
+        <v>0.612</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="14" t="inlineStr"/>
@@ -5709,28 +5717,28 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D117" s="9" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="E117" s="16" t="n">
-        <v>0.009000000000000001</v>
+        <v>4.78</v>
+      </c>
+      <c r="E117" s="10" t="n">
+        <v>-0.0042</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>670900</v>
+        <v>918400</v>
       </c>
       <c r="G117" s="12" t="n">
-        <v>0.09</v>
+        <v>0.05</v>
       </c>
       <c r="H117" t="n">
-        <v>53.76</v>
+        <v>38.75</v>
       </c>
       <c r="I117" s="13" t="inlineStr">
         <is>
@@ -5738,10 +5746,10 @@
         </is>
       </c>
       <c r="J117" s="9" t="n">
-        <v>2.226</v>
+        <v>4.844</v>
       </c>
       <c r="K117" s="9" t="n">
-        <v>2.104</v>
+        <v>4.96</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="14" t="inlineStr"/>
@@ -5754,28 +5762,28 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>7161</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>KERJAYA</t>
         </is>
       </c>
       <c r="D118" s="9" t="n">
-        <v>1.17</v>
+        <v>3.59</v>
       </c>
       <c r="E118" s="10" t="n">
-        <v>-0.025</v>
+        <v>-0.011</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>656100</v>
+        <v>853900</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>0.18</v>
+        <v>0.27</v>
       </c>
       <c r="H118" t="n">
-        <v>64.58</v>
+        <v>73</v>
       </c>
       <c r="I118" s="17" t="inlineStr">
         <is>
@@ -5783,10 +5791,10 @@
         </is>
       </c>
       <c r="J118" s="9" t="n">
-        <v>1.107</v>
+        <v>3.31</v>
       </c>
       <c r="K118" s="9" t="n">
-        <v>1.007</v>
+        <v>2.884</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="14" t="inlineStr"/>
@@ -5799,39 +5807,39 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>5005</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>UNISEM</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D119" s="9" t="n">
-        <v>4.54</v>
-      </c>
-      <c r="E119" s="10" t="n">
-        <v>-0.008699999999999999</v>
+        <v>2.23</v>
+      </c>
+      <c r="E119" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>649100</v>
+        <v>820300</v>
       </c>
       <c r="G119" s="12" t="n">
-        <v>0.28</v>
+        <v>0.11</v>
       </c>
       <c r="H119" t="n">
-        <v>55.25</v>
-      </c>
-      <c r="I119" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.41</v>
+      </c>
+      <c r="I119" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J119" s="9" t="n">
-        <v>4.414</v>
+        <v>2.224</v>
       </c>
       <c r="K119" s="9" t="n">
-        <v>4.431</v>
+        <v>2.104</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="14" t="inlineStr"/>
@@ -5844,28 +5852,28 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D120" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E120" s="10" t="n">
-        <v>-0.0196</v>
+        <v>0.98</v>
+      </c>
+      <c r="E120" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>644500</v>
+        <v>817000</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>0.13</v>
+        <v>0.43</v>
       </c>
       <c r="H120" t="n">
-        <v>34.67</v>
+        <v>43.55</v>
       </c>
       <c r="I120" s="13" t="inlineStr">
         <is>
@@ -5873,10 +5881,10 @@
         </is>
       </c>
       <c r="J120" s="9" t="n">
-        <v>1.049</v>
+        <v>0.996</v>
       </c>
       <c r="K120" s="9" t="n">
-        <v>1.074</v>
+        <v>1.012</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="14" t="inlineStr"/>
@@ -5889,28 +5897,28 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>5005</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>UNISEM</t>
         </is>
       </c>
       <c r="D121" s="9" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="E121" s="16" t="n">
-        <v>0.0161</v>
+        <v>4.54</v>
+      </c>
+      <c r="E121" s="10" t="n">
+        <v>-0.008699999999999999</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>641300</v>
+        <v>806000</v>
       </c>
       <c r="G121" s="12" t="n">
-        <v>0.24</v>
+        <v>0.35</v>
       </c>
       <c r="H121" t="n">
-        <v>83.94</v>
+        <v>55.25</v>
       </c>
       <c r="I121" s="17" t="inlineStr">
         <is>
@@ -5918,10 +5926,10 @@
         </is>
       </c>
       <c r="J121" s="9" t="n">
-        <v>1.045</v>
+        <v>4.414</v>
       </c>
       <c r="K121" s="9" t="n">
-        <v>0.888</v>
+        <v>4.431</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="14" t="inlineStr"/>
@@ -5934,28 +5942,28 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>0233</t>
+          <t>0223</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>PEKAT</t>
+          <t>SAMAIDEN</t>
         </is>
       </c>
       <c r="D122" s="9" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="E122" s="15" t="n">
-        <v>0</v>
+        <v>2.87</v>
+      </c>
+      <c r="E122" s="16" t="n">
+        <v>0.0035</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>625800</v>
+        <v>799400</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>0.29</v>
+        <v>0.32</v>
       </c>
       <c r="H122" t="n">
-        <v>88.84999999999999</v>
+        <v>89.28</v>
       </c>
       <c r="I122" s="17" t="inlineStr">
         <is>
@@ -5963,10 +5971,10 @@
         </is>
       </c>
       <c r="J122" s="9" t="n">
-        <v>2.247</v>
+        <v>2.185</v>
       </c>
       <c r="K122" s="9" t="n">
-        <v>1.951</v>
+        <v>1.768</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="14" t="inlineStr"/>
@@ -5988,19 +5996,19 @@
         </is>
       </c>
       <c r="D123" s="9" t="n">
-        <v>0.955</v>
-      </c>
-      <c r="E123" s="10" t="n">
-        <v>-0.0052</v>
+        <v>0.965</v>
+      </c>
+      <c r="E123" s="16" t="n">
+        <v>0.0052</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>615400</v>
+        <v>788400</v>
       </c>
       <c r="G123" s="12" t="n">
-        <v>0.13</v>
+        <v>0.17</v>
       </c>
       <c r="H123" t="n">
-        <v>35.25</v>
+        <v>37.8</v>
       </c>
       <c r="I123" s="13" t="inlineStr">
         <is>
@@ -6008,7 +6016,7 @@
         </is>
       </c>
       <c r="J123" s="9" t="n">
-        <v>0.998</v>
+        <v>0.999</v>
       </c>
       <c r="K123" s="9" t="n">
         <v>1.047</v>
@@ -6024,39 +6032,39 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>0391</t>
+          <t>5302</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>AMBEST</t>
+          <t>ATECH</t>
         </is>
       </c>
       <c r="D124" s="9" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="E124" s="10" t="n">
-        <v>-0.0143</v>
+        <v>0.77</v>
+      </c>
+      <c r="E124" s="16" t="n">
+        <v>0.006500000000000001</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>611700</v>
+        <v>764300</v>
       </c>
       <c r="G124" s="12" t="n">
-        <v>0.19</v>
+        <v>0.52</v>
       </c>
       <c r="H124" t="n">
-        <v>58.09</v>
-      </c>
-      <c r="I124" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.54</v>
+      </c>
+      <c r="I124" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J124" s="9" t="n">
-        <v>1.345</v>
+        <v>0.765</v>
       </c>
       <c r="K124" s="9" t="n">
-        <v>1.148</v>
+        <v>0.755</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="14" t="inlineStr"/>
@@ -6069,28 +6077,28 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D125" s="9" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="E125" s="10" t="n">
-        <v>-0.0035</v>
+        <v>7.93</v>
+      </c>
+      <c r="E125" s="16" t="n">
+        <v>0.0038</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>589700</v>
+        <v>755900</v>
       </c>
       <c r="G125" s="12" t="n">
-        <v>0.24</v>
+        <v>0.06</v>
       </c>
       <c r="H125" t="n">
-        <v>88.36</v>
+        <v>59.27</v>
       </c>
       <c r="I125" s="17" t="inlineStr">
         <is>
@@ -6098,10 +6106,10 @@
         </is>
       </c>
       <c r="J125" s="9" t="n">
-        <v>2.183</v>
+        <v>7.8</v>
       </c>
       <c r="K125" s="9" t="n">
-        <v>1.768</v>
+        <v>7.73</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="14" t="inlineStr"/>
@@ -6114,39 +6122,39 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>0233</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>PEKAT</t>
         </is>
       </c>
       <c r="D126" s="9" t="n">
-        <v>4.78</v>
-      </c>
-      <c r="E126" s="10" t="n">
-        <v>-0.0042</v>
+        <v>2.84</v>
+      </c>
+      <c r="E126" s="16" t="n">
+        <v>0.0071</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>578600</v>
+        <v>755300</v>
       </c>
       <c r="G126" s="12" t="n">
-        <v>0.03</v>
+        <v>0.35</v>
       </c>
       <c r="H126" t="n">
-        <v>38.75</v>
-      </c>
-      <c r="I126" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>89.09</v>
+      </c>
+      <c r="I126" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J126" s="9" t="n">
-        <v>4.844</v>
+        <v>2.249</v>
       </c>
       <c r="K126" s="9" t="n">
-        <v>4.96</v>
+        <v>1.951</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="14" t="inlineStr"/>
@@ -6159,28 +6167,28 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>0240</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>CORAZA</t>
         </is>
       </c>
       <c r="D127" s="9" t="n">
-        <v>0.77</v>
+        <v>1.05</v>
       </c>
       <c r="E127" s="10" t="n">
-        <v>-0.0128</v>
+        <v>-0.0367</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>562800</v>
+        <v>740700</v>
       </c>
       <c r="G127" s="12" t="n">
-        <v>0.2</v>
+        <v>0.29</v>
       </c>
       <c r="H127" t="n">
-        <v>54.35</v>
+        <v>39.35</v>
       </c>
       <c r="I127" s="17" t="inlineStr">
         <is>
@@ -6188,10 +6196,10 @@
         </is>
       </c>
       <c r="J127" s="9" t="n">
-        <v>0.756</v>
+        <v>1.098</v>
       </c>
       <c r="K127" s="9" t="n">
-        <v>0.74</v>
+        <v>1.119</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="14" t="inlineStr"/>
@@ -6204,28 +6212,28 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>MBSB</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D128" s="9" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="E128" s="16" t="n">
-        <v>0.009000000000000001</v>
+        <v>0.725</v>
+      </c>
+      <c r="E128" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>536500</v>
+        <v>734500</v>
       </c>
       <c r="G128" s="12" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="H128" t="n">
-        <v>42.85</v>
+        <v>69.25</v>
       </c>
       <c r="I128" s="17" t="inlineStr">
         <is>
@@ -6233,10 +6241,10 @@
         </is>
       </c>
       <c r="J128" s="9" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.672</v>
       </c>
       <c r="K128" s="9" t="n">
-        <v>0.595</v>
+        <v>0.615</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="14" t="inlineStr"/>
@@ -6249,39 +6257,39 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>7197</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>GESHEN</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D129" s="9" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="E129" s="16" t="n">
-        <v>0.023</v>
+        <v>0.77</v>
+      </c>
+      <c r="E129" s="10" t="n">
+        <v>-0.0128</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>529300</v>
+        <v>732200</v>
       </c>
       <c r="G129" s="12" t="n">
-        <v>1.4</v>
+        <v>0.26</v>
       </c>
       <c r="H129" t="n">
-        <v>30.61</v>
-      </c>
-      <c r="I129" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.35</v>
+      </c>
+      <c r="I129" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J129" s="9" t="n">
-        <v>1.182</v>
+        <v>0.756</v>
       </c>
       <c r="K129" s="9" t="n">
-        <v>1.285</v>
+        <v>0.74</v>
       </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="14" t="inlineStr"/>
@@ -6294,45 +6302,1080 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D130" s="9" t="n">
-        <v>4.43</v>
-      </c>
-      <c r="E130" s="10" t="n">
-        <v>-0.0134</v>
+        <v>1.27</v>
+      </c>
+      <c r="E130" s="16" t="n">
+        <v>0.0242</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>523100</v>
+        <v>715200</v>
       </c>
       <c r="G130" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.27</v>
       </c>
       <c r="H130" t="n">
-        <v>45.3</v>
-      </c>
-      <c r="I130" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>84.34</v>
+      </c>
+      <c r="I130" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J130" s="9" t="n">
-        <v>4.583</v>
+        <v>1.046</v>
       </c>
       <c r="K130" s="9" t="n">
-        <v>4.538</v>
+        <v>0.888</v>
       </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" s="14" t="inlineStr"/>
     </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>8583</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>MAHSING</t>
+        </is>
+      </c>
+      <c r="D131" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E131" s="10" t="n">
+        <v>-0.0196</v>
+      </c>
+      <c r="F131" s="11" t="n">
+        <v>705700</v>
+      </c>
+      <c r="G131" s="12" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H131" t="n">
+        <v>34.67</v>
+      </c>
+      <c r="I131" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J131" s="9" t="n">
+        <v>1.049</v>
+      </c>
+      <c r="K131" s="9" t="n">
+        <v>1.074</v>
+      </c>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" s="14" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>0271</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>WELLS</t>
+        </is>
+      </c>
+      <c r="D132" s="9" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="E132" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F132" s="11" t="n">
+        <v>700000</v>
+      </c>
+      <c r="G132" s="12" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="H132" t="n">
+        <v>48.02</v>
+      </c>
+      <c r="I132" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J132" s="9" t="n">
+        <v>0.631</v>
+      </c>
+      <c r="K132" s="9" t="n">
+        <v>0.637</v>
+      </c>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" s="14" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>5162</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>VSTECS</t>
+        </is>
+      </c>
+      <c r="D133" s="9" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="E133" s="16" t="n">
+        <v>0.0242</v>
+      </c>
+      <c r="F133" s="11" t="n">
+        <v>679600</v>
+      </c>
+      <c r="G133" s="12" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="H133" t="n">
+        <v>54.81</v>
+      </c>
+      <c r="I133" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J133" s="9" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="K133" s="9" t="n">
+        <v>1.693</v>
+      </c>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" s="14" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>5317</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>CPETECH</t>
+        </is>
+      </c>
+      <c r="D134" s="9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E134" s="16" t="n">
+        <v>0.007800000000000001</v>
+      </c>
+      <c r="F134" s="11" t="n">
+        <v>679200</v>
+      </c>
+      <c r="G134" s="12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H134" t="n">
+        <v>59.48</v>
+      </c>
+      <c r="I134" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J134" s="9" t="n">
+        <v>1.242</v>
+      </c>
+      <c r="K134" s="9" t="n">
+        <v>1.139</v>
+      </c>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" s="14" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>0217</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>PWRWELL</t>
+        </is>
+      </c>
+      <c r="D135" s="9" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="E135" s="10" t="n">
+        <v>-0.025</v>
+      </c>
+      <c r="F135" s="11" t="n">
+        <v>676100</v>
+      </c>
+      <c r="G135" s="12" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H135" t="n">
+        <v>64.58</v>
+      </c>
+      <c r="I135" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J135" s="9" t="n">
+        <v>1.107</v>
+      </c>
+      <c r="K135" s="9" t="n">
+        <v>1.007</v>
+      </c>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" s="14" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>5323</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>JPG</t>
+        </is>
+      </c>
+      <c r="D136" s="9" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="E136" s="16" t="n">
+        <v>0.005600000000000001</v>
+      </c>
+      <c r="F136" s="11" t="n">
+        <v>649600</v>
+      </c>
+      <c r="G136" s="12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H136" t="n">
+        <v>37.04</v>
+      </c>
+      <c r="I136" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J136" s="9" t="n">
+        <v>1.903</v>
+      </c>
+      <c r="K136" s="9" t="n">
+        <v>1.966</v>
+      </c>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" s="14" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>5878</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>KPJ</t>
+        </is>
+      </c>
+      <c r="D137" s="9" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="E137" s="10" t="n">
+        <v>-0.015</v>
+      </c>
+      <c r="F137" s="11" t="n">
+        <v>644200</v>
+      </c>
+      <c r="G137" s="12" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H137" t="n">
+        <v>41.54</v>
+      </c>
+      <c r="I137" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J137" s="9" t="n">
+        <v>2.674</v>
+      </c>
+      <c r="K137" s="9" t="n">
+        <v>2.872</v>
+      </c>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" s="14" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>1066</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>RHBBANK</t>
+        </is>
+      </c>
+      <c r="D138" s="9" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="E138" s="16" t="n">
+        <v>0.0051</v>
+      </c>
+      <c r="F138" s="11" t="n">
+        <v>635300</v>
+      </c>
+      <c r="G138" s="12" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H138" t="n">
+        <v>36.58</v>
+      </c>
+      <c r="I138" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J138" s="9" t="n">
+        <v>7.975</v>
+      </c>
+      <c r="K138" s="9" t="n">
+        <v>8.260999999999999</v>
+      </c>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" s="14" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>0390</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>ISF</t>
+        </is>
+      </c>
+      <c r="D139" s="9" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="E139" s="10" t="n">
+        <v>-0.0059</v>
+      </c>
+      <c r="F139" s="11" t="n">
+        <v>635100</v>
+      </c>
+      <c r="G139" s="12" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H139" t="n">
+        <v>64.11</v>
+      </c>
+      <c r="I139" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J139" s="9" t="n">
+        <v>0.801</v>
+      </c>
+      <c r="K139" s="9" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" s="14" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>0391</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>AMBEST</t>
+        </is>
+      </c>
+      <c r="D140" s="9" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="E140" s="10" t="n">
+        <v>-0.0143</v>
+      </c>
+      <c r="F140" s="11" t="n">
+        <v>629600</v>
+      </c>
+      <c r="G140" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H140" t="n">
+        <v>58.09</v>
+      </c>
+      <c r="I140" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J140" s="9" t="n">
+        <v>1.345</v>
+      </c>
+      <c r="K140" s="9" t="n">
+        <v>1.148</v>
+      </c>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" s="14" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>7277</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>DIALOG</t>
+        </is>
+      </c>
+      <c r="D141" s="9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="E141" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F141" s="11" t="n">
+        <v>626600</v>
+      </c>
+      <c r="G141" s="12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H141" t="n">
+        <v>45.43</v>
+      </c>
+      <c r="I141" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J141" s="9" t="n">
+        <v>1.983</v>
+      </c>
+      <c r="K141" s="9" t="n">
+        <v>1.974</v>
+      </c>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" s="14" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>0326</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>SORENTO</t>
+        </is>
+      </c>
+      <c r="D142" s="9" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="E142" s="10" t="n">
+        <v>-0.0074</v>
+      </c>
+      <c r="F142" s="11" t="n">
+        <v>617700</v>
+      </c>
+      <c r="G142" s="12" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="H142" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="I142" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J142" s="9" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="K142" s="9" t="n">
+        <v>0.647</v>
+      </c>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" s="14" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>0128</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>FRONTKN</t>
+        </is>
+      </c>
+      <c r="D143" s="9" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="E143" s="10" t="n">
+        <v>-0.0178</v>
+      </c>
+      <c r="F143" s="11" t="n">
+        <v>613300</v>
+      </c>
+      <c r="G143" s="12" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H143" t="n">
+        <v>48.52</v>
+      </c>
+      <c r="I143" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J143" s="9" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="K143" s="9" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" s="14" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>5225</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>IHH</t>
+        </is>
+      </c>
+      <c r="D144" s="9" t="n">
+        <v>8.029999999999999</v>
+      </c>
+      <c r="E144" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F144" s="11" t="n">
+        <v>600300</v>
+      </c>
+      <c r="G144" s="12" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H144" t="n">
+        <v>52.14</v>
+      </c>
+      <c r="I144" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J144" s="9" t="n">
+        <v>7.951</v>
+      </c>
+      <c r="K144" s="9" t="n">
+        <v>8.151999999999999</v>
+      </c>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" s="14" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>7160</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>PENTA</t>
+        </is>
+      </c>
+      <c r="D145" s="9" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="E145" s="10" t="n">
+        <v>-0.0132</v>
+      </c>
+      <c r="F145" s="11" t="n">
+        <v>592600</v>
+      </c>
+      <c r="G145" s="12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H145" t="n">
+        <v>48.96</v>
+      </c>
+      <c r="I145" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J145" s="9" t="n">
+        <v>5.282</v>
+      </c>
+      <c r="K145" s="9" t="n">
+        <v>5.276</v>
+      </c>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" s="14" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>5286</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="D146" s="9" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="E146" s="10" t="n">
+        <v>-0.0155</v>
+      </c>
+      <c r="F146" s="11" t="n">
+        <v>570500</v>
+      </c>
+      <c r="G146" s="12" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H146" t="n">
+        <v>47.82</v>
+      </c>
+      <c r="I146" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J146" s="9" t="n">
+        <v>5.803</v>
+      </c>
+      <c r="K146" s="9" t="n">
+        <v>5.754</v>
+      </c>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" s="14" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>5357</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>SKYECHIP</t>
+        </is>
+      </c>
+      <c r="D147" s="9" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="E147" s="10" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="F147" s="11" t="n">
+        <v>558000</v>
+      </c>
+      <c r="G147" s="12" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H147" t="n">
+        <v>46.71</v>
+      </c>
+      <c r="I147" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J147" s="9" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="K147" s="9" t="n">
+        <v>3.041</v>
+      </c>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" s="14" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>5271</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>PECCA</t>
+        </is>
+      </c>
+      <c r="D148" s="9" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="E148" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F148" s="11" t="n">
+        <v>538700</v>
+      </c>
+      <c r="G148" s="12" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H148" t="n">
+        <v>68.31</v>
+      </c>
+      <c r="I148" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J148" s="9" t="n">
+        <v>1.355</v>
+      </c>
+      <c r="K148" s="9" t="n">
+        <v>1.325</v>
+      </c>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" s="14" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>0056</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>NCT</t>
+        </is>
+      </c>
+      <c r="D149" s="9" t="n">
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="E149" s="16" t="n">
+        <v>0.0089</v>
+      </c>
+      <c r="F149" s="11" t="n">
+        <v>535500</v>
+      </c>
+      <c r="G149" s="12" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H149" t="n">
+        <v>51.06</v>
+      </c>
+      <c r="I149" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J149" s="9" t="n">
+        <v>0.5629999999999999</v>
+      </c>
+      <c r="K149" s="9" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" s="14" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>7197</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>GESHEN</t>
+        </is>
+      </c>
+      <c r="D150" s="9" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="E150" s="16" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="F150" s="11" t="n">
+        <v>529300</v>
+      </c>
+      <c r="G150" s="12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H150" t="n">
+        <v>30.61</v>
+      </c>
+      <c r="I150" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J150" s="9" t="n">
+        <v>1.182</v>
+      </c>
+      <c r="K150" s="9" t="n">
+        <v>1.285</v>
+      </c>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" s="14" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>6139</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>TAKAFUL</t>
+        </is>
+      </c>
+      <c r="D151" s="9" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="E151" s="10" t="n">
+        <v>-0.0067</v>
+      </c>
+      <c r="F151" s="11" t="n">
+        <v>522500</v>
+      </c>
+      <c r="G151" s="12" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="H151" t="n">
+        <v>33.69</v>
+      </c>
+      <c r="I151" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J151" s="9" t="n">
+        <v>3.071</v>
+      </c>
+      <c r="K151" s="9" t="n">
+        <v>3.152</v>
+      </c>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" s="14" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>5292</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>UWC</t>
+        </is>
+      </c>
+      <c r="D152" s="9" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E152" s="10" t="n">
+        <v>-0.0262</v>
+      </c>
+      <c r="F152" s="11" t="n">
+        <v>512200</v>
+      </c>
+      <c r="G152" s="12" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H152" t="n">
+        <v>53.59</v>
+      </c>
+      <c r="I152" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J152" s="9" t="n">
+        <v>6.571</v>
+      </c>
+      <c r="K152" s="9" t="n">
+        <v>6.496</v>
+      </c>
+      <c r="L152" t="inlineStr"/>
+      <c r="M152" s="14" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>5328</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>LWSABAH</t>
+        </is>
+      </c>
+      <c r="D153" s="9" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="E153" s="10" t="n">
+        <v>-0.0289</v>
+      </c>
+      <c r="F153" s="11" t="n">
+        <v>505400</v>
+      </c>
+      <c r="G153" s="12" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="H153" t="n">
+        <v>49.53</v>
+      </c>
+      <c r="I153" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J153" s="9" t="n">
+        <v>1.701</v>
+      </c>
+      <c r="K153" s="9" t="n">
+        <v>1.614</v>
+      </c>
+      <c r="L153" t="inlineStr"/>
+      <c r="M153" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M130"/>
+  <autoFilter ref="A1:M153"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-09-28/bursa-report-2026-09-28.xlsx
+++ b/docs/downloads/2026-09-28/bursa-report-2026-09-28.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-09-28" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-09-28'!$A$1:$M$153</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-09-28'!$A$1:$M$192</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -38,10 +38,10 @@
       <color rgb="000CA30C"/>
     </font>
     <font>
-      <color rgb="00D03B3B"/>
+      <color rgb="00898781"/>
     </font>
     <font>
-      <color rgb="00898781"/>
+      <color rgb="00D03B3B"/>
     </font>
   </fonts>
   <fills count="4">
@@ -92,13 +92,13 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M153"/>
+  <dimension ref="A1:M192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -572,10 +572,10 @@
         <v>0.0357</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>5168600</v>
+        <v>5476300</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>2.79</v>
+        <v>2.96</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>72.15000000000001</v>
@@ -598,7 +598,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>现价0.435高于50日均线0.38，均线呈多头排列；但RSI达72.15已入超买区，短期动能偏强而回撤风险上升，信号可靠性中等。</t>
+          <t>现价0.435高于50日均线0.38，均线多头排列；但RSI达72.15已入超买区，短期动能偏强而追高风险上升，信号可靠性中等。</t>
         </is>
       </c>
     </row>
@@ -625,10 +625,10 @@
         <v>0.04650000000000001</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>5817900</v>
+        <v>5841900</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>26.36</v>
+        <v>26.47</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>72.90000000000001</v>
@@ -678,10 +678,10 @@
         <v>0.0561</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>7249400</v>
+        <v>8549600</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.5</v>
+        <v>0.59</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>71.81999999999999</v>
@@ -704,7 +704,7 @@
       </c>
       <c r="M4" s="8" t="inlineStr">
         <is>
-          <t>RSI达71.82，已进入超买区；现价0.565远高于50日均线0.401，短期涨幅偏大，信号可靠性需谨慎看待。</t>
+          <t>RSI达71.82，已进入超买区；现价0.565远高于50日均线0.401，短期偏离较大，信号偏热。</t>
         </is>
       </c>
     </row>
@@ -725,19 +725,19 @@
         </is>
       </c>
       <c r="D5" s="9" t="n">
-        <v>0.185</v>
+        <v>0.19</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>-0.0263</v>
+        <v>0</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>80425100</v>
+        <v>91053300</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>0.13</v>
+        <v>0.15</v>
       </c>
       <c r="H5" t="n">
-        <v>22.18</v>
+        <v>22.61</v>
       </c>
       <c r="I5" s="13" t="inlineStr">
         <is>
@@ -761,22 +761,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0473</t>
+          <t>0041</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Evocom Berhad</t>
+          <t>AIMAX</t>
         </is>
       </c>
       <c r="D6" s="9" t="n">
-        <v>0.135</v>
-      </c>
-      <c r="E6" s="15" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="E6" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>49582000</v>
+        <v>58888600</v>
       </c>
       <c r="G6" s="12" t="n"/>
       <c r="I6" s="13" t="inlineStr">
@@ -806,21 +806,21 @@
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="E7" s="16" t="n">
-        <v>0.0588</v>
+        <v>0.185</v>
+      </c>
+      <c r="E7" s="15" t="n">
+        <v>0.0882</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>44534600</v>
+        <v>56178800</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>0.98</v>
+        <v>1.24</v>
       </c>
       <c r="H7" t="n">
-        <v>76.5</v>
-      </c>
-      <c r="I7" s="17" t="inlineStr">
+        <v>77.83</v>
+      </c>
+      <c r="I7" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -842,40 +842,31 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>0473</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>Evocom Berhad</t>
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>2.55</v>
+        <v>0.13</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>-0.0414</v>
+        <v>0</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>30021300</v>
-      </c>
-      <c r="G8" s="12" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="H8" t="n">
-        <v>49.39</v>
-      </c>
+        <v>55808400</v>
+      </c>
+      <c r="G8" s="12" t="n"/>
       <c r="I8" s="13" t="inlineStr">
         <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J8" s="9" t="n">
-        <v>2.587</v>
-      </c>
-      <c r="K8" s="9" t="n">
-        <v>2.44</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J8" s="9" t="n"/>
+      <c r="K8" s="9" t="n"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="14" t="inlineStr"/>
     </row>
@@ -887,28 +878,28 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.725</v>
-      </c>
-      <c r="E9" s="10" t="n">
-        <v>-0.0397</v>
+        <v>2.52</v>
+      </c>
+      <c r="E9" s="17" t="n">
+        <v>-0.0526</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>22738200</v>
+        <v>34398200</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>0.52</v>
+        <v>1.8</v>
       </c>
       <c r="H9" t="n">
-        <v>50.12</v>
+        <v>47.42</v>
       </c>
       <c r="I9" s="13" t="inlineStr">
         <is>
@@ -916,10 +907,10 @@
         </is>
       </c>
       <c r="J9" s="9" t="n">
-        <v>0.736</v>
+        <v>2.584</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>0.6830000000000001</v>
+        <v>2.44</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="14" t="inlineStr"/>
@@ -941,27 +932,27 @@
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>0.355</v>
-      </c>
-      <c r="E10" s="10" t="n">
-        <v>-0.0658</v>
+        <v>0.36</v>
+      </c>
+      <c r="E10" s="17" t="n">
+        <v>-0.0526</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>17498600</v>
+        <v>26428800</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>0.39</v>
+        <v>0.58</v>
       </c>
       <c r="H10" t="n">
-        <v>67.56999999999999</v>
-      </c>
-      <c r="I10" s="17" t="inlineStr">
+        <v>69.26000000000001</v>
+      </c>
+      <c r="I10" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J10" s="9" t="n">
-        <v>0.316</v>
+        <v>0.317</v>
       </c>
       <c r="K10" s="9" t="n">
         <v>0.183</v>
@@ -988,19 +979,19 @@
       <c r="D11" s="9" t="n">
         <v>0.19</v>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="E11" s="15" t="n">
         <v>0.0857</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>14737500</v>
+        <v>24687800</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>3.53</v>
+        <v>5.91</v>
       </c>
       <c r="H11" t="n">
         <v>61.83</v>
       </c>
-      <c r="I11" s="17" t="inlineStr">
+      <c r="I11" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -1022,28 +1013,28 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>0.395</v>
-      </c>
-      <c r="E12" s="10" t="n">
-        <v>-0.0595</v>
+        <v>0.73</v>
+      </c>
+      <c r="E12" s="17" t="n">
+        <v>-0.0331</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>13802200</v>
+        <v>23598000</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>0.63</v>
+        <v>0.54</v>
       </c>
       <c r="H12" t="n">
-        <v>56.63</v>
+        <v>51.13</v>
       </c>
       <c r="I12" s="13" t="inlineStr">
         <is>
@@ -1051,10 +1042,10 @@
         </is>
       </c>
       <c r="J12" s="9" t="n">
-        <v>0.382</v>
+        <v>0.736</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>0.32</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="14" t="inlineStr"/>
@@ -1067,39 +1058,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="E13" s="16" t="n">
-        <v>0.0275</v>
+        <v>0.57</v>
+      </c>
+      <c r="E13" s="17" t="n">
+        <v>-0.0256</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>11178600</v>
+        <v>16462100</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>0.83</v>
+        <v>0.68</v>
       </c>
       <c r="H13" t="n">
-        <v>60.99</v>
-      </c>
-      <c r="I13" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>64</v>
+      </c>
+      <c r="I13" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J13" s="9" t="n">
-        <v>0.524</v>
+        <v>0.546</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>0.477</v>
+        <v>0.492</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="14" t="inlineStr"/>
@@ -1112,39 +1103,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>0.555</v>
-      </c>
-      <c r="E14" s="16" t="n">
-        <v>0.0571</v>
+        <v>0.24</v>
+      </c>
+      <c r="E14" s="15" t="n">
+        <v>0.0213</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>10579800</v>
+        <v>14737800</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>1.81</v>
+        <v>0.82</v>
       </c>
       <c r="H14" t="n">
-        <v>63.74</v>
-      </c>
-      <c r="I14" s="17" t="inlineStr">
+        <v>56.39</v>
+      </c>
+      <c r="I14" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J14" s="9" t="n">
-        <v>0.521</v>
+        <v>0.232</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>0.531</v>
+        <v>0.233</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="14" t="inlineStr"/>
@@ -1157,28 +1148,28 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="E15" s="15" t="n">
-        <v>0</v>
+        <v>0.395</v>
+      </c>
+      <c r="E15" s="17" t="n">
+        <v>-0.0595</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>10195600</v>
+        <v>14699000</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>0.27</v>
+        <v>0.67</v>
       </c>
       <c r="H15" t="n">
-        <v>26.93</v>
+        <v>56.63</v>
       </c>
       <c r="I15" s="13" t="inlineStr">
         <is>
@@ -1186,10 +1177,10 @@
         </is>
       </c>
       <c r="J15" s="9" t="n">
-        <v>0.634</v>
+        <v>0.382</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>0.851</v>
+        <v>0.32</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="14" t="inlineStr"/>
@@ -1202,39 +1193,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>0.245</v>
-      </c>
-      <c r="E16" s="16" t="n">
-        <v>0.0426</v>
+        <v>1.81</v>
+      </c>
+      <c r="E16" s="17" t="n">
+        <v>-0.0321</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>9868500</v>
+        <v>13579600</v>
       </c>
       <c r="G16" s="12" t="n">
         <v>0.55</v>
       </c>
       <c r="H16" t="n">
-        <v>59.1</v>
-      </c>
-      <c r="I16" s="17" t="inlineStr">
+        <v>59.95</v>
+      </c>
+      <c r="I16" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J16" s="9" t="n">
-        <v>0.232</v>
+        <v>1.735</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>0.233</v>
+        <v>1.524</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="14" t="inlineStr"/>
@@ -1247,39 +1238,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>0.575</v>
-      </c>
-      <c r="E17" s="10" t="n">
-        <v>-0.0171</v>
+        <v>0.555</v>
+      </c>
+      <c r="E17" s="15" t="n">
+        <v>0.0183</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>9810200</v>
+        <v>13065400</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>0.41</v>
+        <v>0.97</v>
       </c>
       <c r="H17" t="n">
-        <v>66.27</v>
-      </c>
-      <c r="I17" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.08</v>
+      </c>
+      <c r="I17" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J17" s="9" t="n">
-        <v>0.546</v>
+        <v>0.524</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>0.493</v>
+        <v>0.476</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="14" t="inlineStr"/>
@@ -1292,39 +1283,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>7117</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CJCEN</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E18" s="16" t="n">
-        <v>0.08109999999999999</v>
+        <v>0.3</v>
+      </c>
+      <c r="E18" s="17" t="n">
+        <v>-0.0323</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>9756400</v>
+        <v>11864400</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>23.06</v>
+        <v>0.63</v>
       </c>
       <c r="H18" t="n">
-        <v>82.14</v>
-      </c>
-      <c r="I18" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.23</v>
+      </c>
+      <c r="I18" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J18" s="9" t="n">
-        <v>0.172</v>
+        <v>0.303</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>0.163</v>
+        <v>0.29</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="14" t="inlineStr"/>
@@ -1337,39 +1328,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>VELESTO</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="E19" s="10" t="n">
-        <v>-0.0267</v>
+        <v>0.215</v>
+      </c>
+      <c r="E19" s="17" t="n">
+        <v>-0.0227</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>9173300</v>
+        <v>11210200</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>0.37</v>
+        <v>0.51</v>
       </c>
       <c r="H19" t="n">
-        <v>60.88</v>
-      </c>
-      <c r="I19" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>29.99</v>
+      </c>
+      <c r="I19" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J19" s="9" t="n">
-        <v>1.736</v>
+        <v>0.238</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>1.524</v>
+        <v>0.249</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="14" t="inlineStr"/>
@@ -1382,39 +1373,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>0.715</v>
-      </c>
-      <c r="E20" s="16" t="n">
-        <v>0.0288</v>
+        <v>0.55</v>
+      </c>
+      <c r="E20" s="15" t="n">
+        <v>0.0476</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>9163300</v>
+        <v>11139800</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>0.99</v>
+        <v>1.91</v>
       </c>
       <c r="H20" t="n">
-        <v>56.69</v>
-      </c>
-      <c r="I20" s="17" t="inlineStr">
+        <v>62.28</v>
+      </c>
+      <c r="I20" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J20" s="9" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.521</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>0.663</v>
+        <v>0.531</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="14" t="inlineStr"/>
@@ -1427,39 +1418,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>0.22</v>
+        <v>0.535</v>
       </c>
       <c r="E21" s="15" t="n">
-        <v>0</v>
+        <v>0.009399999999999999</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>9089700</v>
+        <v>10892600</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>0.43</v>
+        <v>0.29</v>
       </c>
       <c r="H21" t="n">
-        <v>71.25</v>
-      </c>
-      <c r="I21" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>27.96</v>
+      </c>
+      <c r="I21" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J21" s="9" t="n">
-        <v>0.202</v>
+        <v>0.634</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>0.184</v>
+        <v>0.851</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="14" t="inlineStr"/>
@@ -1472,39 +1463,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.945</v>
-      </c>
-      <c r="E22" s="10" t="n">
-        <v>-0.0053</v>
+        <v>0.77</v>
+      </c>
+      <c r="E22" s="17" t="n">
+        <v>-0.006500000000000001</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>8927500</v>
+        <v>10249000</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>2.2</v>
+        <v>0.82</v>
       </c>
       <c r="H22" t="n">
-        <v>75.98999999999999</v>
-      </c>
-      <c r="I22" s="17" t="inlineStr">
+        <v>47.75</v>
+      </c>
+      <c r="I22" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J22" s="9" t="n">
-        <v>0.884</v>
+        <v>0.774</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>0.851</v>
+        <v>0.774</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="14" t="inlineStr"/>
@@ -1517,31 +1508,40 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0041</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AIMAX</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="E23" s="15" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="E23" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>8298300</v>
-      </c>
-      <c r="G23" s="12" t="n"/>
-      <c r="I23" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J23" s="9" t="n"/>
-      <c r="K23" s="9" t="n"/>
+        <v>10116000</v>
+      </c>
+      <c r="G23" s="12" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="H23" t="n">
+        <v>78.75</v>
+      </c>
+      <c r="I23" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J23" s="9" t="n">
+        <v>0.885</v>
+      </c>
+      <c r="K23" s="9" t="n">
+        <v>0.851</v>
+      </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="14" t="inlineStr"/>
     </row>
@@ -1553,39 +1553,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>7117</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>CJCEN</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="E24" s="10" t="n">
-        <v>-0.0105</v>
+        <v>0.2</v>
+      </c>
+      <c r="E24" s="15" t="n">
+        <v>0.08109999999999999</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>7652700</v>
+        <v>10020500</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>0.31</v>
+        <v>23.69</v>
       </c>
       <c r="H24" t="n">
-        <v>50.74</v>
-      </c>
-      <c r="I24" s="17" t="inlineStr">
+        <v>82.14</v>
+      </c>
+      <c r="I24" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J24" s="9" t="n">
-        <v>0.468</v>
+        <v>0.172</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>0.471</v>
+        <v>0.163</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="14" t="inlineStr"/>
@@ -1598,39 +1598,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E25" s="10" t="n">
-        <v>-0.0323</v>
+        <v>0.715</v>
+      </c>
+      <c r="E25" s="15" t="n">
+        <v>0.0288</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>7468700</v>
+        <v>9908400</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>0.4</v>
+        <v>1.07</v>
       </c>
       <c r="H25" t="n">
-        <v>49.23</v>
-      </c>
-      <c r="I25" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.69</v>
+      </c>
+      <c r="I25" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J25" s="9" t="n">
-        <v>0.303</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>0.29</v>
+        <v>0.663</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="14" t="inlineStr"/>
@@ -1643,39 +1643,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>7315</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AHB</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="E26" s="15" t="n">
-        <v>0</v>
+        <v>0.215</v>
+      </c>
+      <c r="E26" s="17" t="n">
+        <v>-0.0227</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>7119000</v>
+        <v>9901600</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>0.74</v>
+        <v>0.47</v>
       </c>
       <c r="H26" t="n">
-        <v>56.29</v>
-      </c>
-      <c r="I26" s="17" t="inlineStr">
+        <v>65.40000000000001</v>
+      </c>
+      <c r="I26" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J26" s="9" t="n">
-        <v>0.053</v>
+        <v>0.202</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>0.043</v>
+        <v>0.184</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="14" t="inlineStr"/>
@@ -1688,39 +1688,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0175</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>HHRG</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>0.145</v>
-      </c>
-      <c r="E27" s="10" t="n">
-        <v>-0.0333</v>
+        <v>0.865</v>
+      </c>
+      <c r="E27" s="15" t="n">
+        <v>0.0058</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>7029400</v>
+        <v>9515100</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0.17</v>
+        <v>0.53</v>
       </c>
       <c r="H27" t="n">
-        <v>45.75</v>
-      </c>
-      <c r="I27" s="17" t="inlineStr">
+        <v>46.9</v>
+      </c>
+      <c r="I27" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J27" s="9" t="n">
-        <v>0.158</v>
+        <v>0.868</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>0.148</v>
+        <v>0.871</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="14" t="inlineStr"/>
@@ -1733,39 +1733,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>IOIPG</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="E28" s="16" t="n">
-        <v>0.005699999999999999</v>
+        <v>0.245</v>
+      </c>
+      <c r="E28" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>6960300</v>
+        <v>8989000</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>1.48</v>
+        <v>0.32</v>
       </c>
       <c r="H28" t="n">
-        <v>38.66</v>
-      </c>
-      <c r="I28" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>31.98</v>
+      </c>
+      <c r="I28" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J28" s="9" t="n">
-        <v>3.616</v>
+        <v>0.276</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>3.704</v>
+        <v>0.328</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="14" t="inlineStr"/>
@@ -1778,39 +1778,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>0.245</v>
-      </c>
-      <c r="E29" s="15" t="n">
-        <v>0</v>
+        <v>0.465</v>
+      </c>
+      <c r="E29" s="17" t="n">
+        <v>-0.0211</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>6747600</v>
+        <v>8557100</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0.24</v>
+        <v>0.35</v>
       </c>
       <c r="H29" t="n">
-        <v>31.98</v>
-      </c>
-      <c r="I29" s="17" t="inlineStr">
+        <v>48.8</v>
+      </c>
+      <c r="I29" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J29" s="9" t="n">
-        <v>0.276</v>
+        <v>0.468</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>0.328</v>
+        <v>0.471</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="14" t="inlineStr"/>
@@ -1823,39 +1823,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0373</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>VERDANT</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="E30" s="16" t="n">
-        <v>0.07690000000000001</v>
+        <v>2.09</v>
+      </c>
+      <c r="E30" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>6726600</v>
+        <v>8469100</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>3.92</v>
+        <v>0.52</v>
       </c>
       <c r="H30" t="n">
-        <v>83.92</v>
-      </c>
-      <c r="I30" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.97</v>
+      </c>
+      <c r="I30" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J30" s="9" t="n">
-        <v>0.225</v>
+        <v>2.127</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>0.209</v>
+        <v>2.062</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="14" t="inlineStr"/>
@@ -1868,39 +1868,39 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>5218</t>
+          <t>0373</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>VANTNRG</t>
+          <t>VERDANT</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>0.345</v>
-      </c>
-      <c r="E31" s="10" t="n">
-        <v>-0.0143</v>
+        <v>0.275</v>
+      </c>
+      <c r="E31" s="15" t="n">
+        <v>0.05769999999999999</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>6712400</v>
+        <v>8134600</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>1.68</v>
+        <v>4.74</v>
       </c>
       <c r="H31" t="n">
-        <v>57.32</v>
-      </c>
-      <c r="I31" s="17" t="inlineStr">
+        <v>83.03</v>
+      </c>
+      <c r="I31" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J31" s="9" t="n">
-        <v>0.339</v>
+        <v>0.224</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>0.333</v>
+        <v>0.209</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="14" t="inlineStr"/>
@@ -1913,39 +1913,39 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>0.77</v>
+        <v>0.47</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>-0.006500000000000001</v>
+        <v>0</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>6381500</v>
+        <v>8056600</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>0.51</v>
+        <v>0.9</v>
       </c>
       <c r="H32" t="n">
-        <v>47.75</v>
-      </c>
-      <c r="I32" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>58.56</v>
+      </c>
+      <c r="I32" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J32" s="9" t="n">
-        <v>0.774</v>
+        <v>0.448</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>0.774</v>
+        <v>0.407</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="14" t="inlineStr"/>
@@ -1958,39 +1958,39 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>IOIPG</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E33" s="16" t="n">
-        <v>0.0058</v>
+        <v>3.49</v>
+      </c>
+      <c r="E33" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>6013000</v>
+        <v>7781200</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>0.33</v>
+        <v>1.66</v>
       </c>
       <c r="H33" t="n">
-        <v>46.9</v>
-      </c>
-      <c r="I33" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.67</v>
+      </c>
+      <c r="I33" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J33" s="9" t="n">
-        <v>0.868</v>
+        <v>3.614</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>0.871</v>
+        <v>3.703</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="14" t="inlineStr"/>
@@ -2003,39 +2003,39 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>9377</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>FSBM</t>
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="E34" s="16" t="n">
-        <v>0.0132</v>
+        <v>0.095</v>
+      </c>
+      <c r="E34" s="17" t="n">
+        <v>-0.09519999999999999</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>5677100</v>
+        <v>7764200</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>0.59</v>
+        <v>0.3</v>
       </c>
       <c r="H34" t="n">
-        <v>63.96</v>
-      </c>
-      <c r="I34" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33</v>
+      </c>
+      <c r="I34" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J34" s="9" t="n">
-        <v>0.373</v>
+        <v>0.133</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>0.371</v>
+        <v>0.162</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="14" t="inlineStr"/>
@@ -2048,39 +2048,39 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>0.605</v>
-      </c>
-      <c r="E35" s="15" t="n">
-        <v>0</v>
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="E35" s="17" t="n">
+        <v>-0.0061</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>5350700</v>
+        <v>7759800</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0.55</v>
+        <v>0.8</v>
       </c>
       <c r="H35" t="n">
-        <v>48.07</v>
-      </c>
-      <c r="I35" s="17" t="inlineStr">
+        <v>69.03</v>
+      </c>
+      <c r="I35" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J35" s="9" t="n">
-        <v>0.608</v>
+        <v>0.713</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>0.604</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="14" t="inlineStr"/>
@@ -2093,39 +2093,39 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>5218</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>VANTNRG</t>
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>4.86</v>
-      </c>
-      <c r="E36" s="10" t="n">
-        <v>-0.004099999999999999</v>
+        <v>0.345</v>
+      </c>
+      <c r="E36" s="17" t="n">
+        <v>-0.0143</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>5297700</v>
+        <v>7608100</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>0.28</v>
+        <v>1.9</v>
       </c>
       <c r="H36" t="n">
-        <v>62.59</v>
-      </c>
-      <c r="I36" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.32</v>
+      </c>
+      <c r="I36" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J36" s="9" t="n">
-        <v>4.74</v>
+        <v>0.339</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>4.509</v>
+        <v>0.333</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="14" t="inlineStr"/>
@@ -2138,39 +2138,39 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0095</t>
+          <t>0175</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>MAG</t>
+          <t>HHRG</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="E37" s="15" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E37" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>5150000</v>
+        <v>7406400</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0.24</v>
+        <v>0.18</v>
       </c>
       <c r="H37" t="n">
-        <v>44.73</v>
-      </c>
-      <c r="I37" s="17" t="inlineStr">
+        <v>47.65</v>
+      </c>
+      <c r="I37" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J37" s="9" t="n">
-        <v>0.156</v>
+        <v>0.158</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>0.159</v>
+        <v>0.148</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="14" t="inlineStr"/>
@@ -2183,39 +2183,39 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>7315</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>AHB</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="E38" s="15" t="n">
-        <v>0</v>
+        <v>0.05</v>
+      </c>
+      <c r="E38" s="17" t="n">
+        <v>-0.09089999999999999</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>4446100</v>
+        <v>7184000</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="H38" t="n">
-        <v>58.56</v>
-      </c>
-      <c r="I38" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.92</v>
+      </c>
+      <c r="I38" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J38" s="9" t="n">
-        <v>0.448</v>
+        <v>0.053</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>0.407</v>
+        <v>0.043</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="14" t="inlineStr"/>
@@ -2228,39 +2228,39 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0280</t>
+          <t>0095</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>MBN</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
         <v>0.155</v>
       </c>
-      <c r="E39" s="15" t="n">
+      <c r="E39" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>4427900</v>
+        <v>7160000</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>1.38</v>
+        <v>0.34</v>
       </c>
       <c r="H39" t="n">
-        <v>52.85</v>
-      </c>
-      <c r="I39" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>44.73</v>
+      </c>
+      <c r="I39" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J39" s="9" t="n">
-        <v>0.154</v>
+        <v>0.156</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>0.147</v>
+        <v>0.159</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="14" t="inlineStr"/>
@@ -2273,39 +2273,39 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>MALAKOF</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E40" s="10" t="n">
-        <v>-0.0062</v>
+        <v>2.81</v>
+      </c>
+      <c r="E40" s="17" t="n">
+        <v>-0.0243</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>4374400</v>
+        <v>6945000</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="H40" t="n">
-        <v>48.44</v>
-      </c>
-      <c r="I40" s="17" t="inlineStr">
+        <v>62.35</v>
+      </c>
+      <c r="I40" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J40" s="9" t="n">
-        <v>0.803</v>
+        <v>2.628</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>0.806</v>
+        <v>2.495</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="14" t="inlineStr"/>
@@ -2318,39 +2318,39 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="E41" s="16" t="n">
-        <v>0.0122</v>
+        <v>2.5</v>
+      </c>
+      <c r="E41" s="15" t="n">
+        <v>0.0121</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>4372700</v>
+        <v>6841200</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="H41" t="n">
-        <v>71.11</v>
-      </c>
-      <c r="I41" s="17" t="inlineStr">
+        <v>61.94</v>
+      </c>
+      <c r="I41" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J41" s="9" t="n">
-        <v>0.715</v>
+        <v>2.439</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>0.6870000000000001</v>
+        <v>2.276</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="14" t="inlineStr"/>
@@ -2363,39 +2363,39 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>2.98</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E42" s="10" t="n">
-        <v>-0.0165</v>
+        <v>0</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>4300200</v>
+        <v>6580500</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>0.32</v>
+        <v>0.51</v>
       </c>
       <c r="H42" t="n">
-        <v>64.89</v>
-      </c>
-      <c r="I42" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.19</v>
+      </c>
+      <c r="I42" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J42" s="9" t="n">
-        <v>2.858</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>2.716</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="14" t="inlineStr"/>
@@ -2408,39 +2408,39 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E43" s="16" t="n">
-        <v>0.0172</v>
+        <v>4.86</v>
+      </c>
+      <c r="E43" s="17" t="n">
+        <v>-0.004099999999999999</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>4101000</v>
+        <v>6527300</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>0.64</v>
+        <v>0.34</v>
       </c>
       <c r="H43" t="n">
-        <v>66.27</v>
-      </c>
-      <c r="I43" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>62.59</v>
+      </c>
+      <c r="I43" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J43" s="9" t="n">
-        <v>0.275</v>
+        <v>4.74</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>0.27</v>
+        <v>4.509</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="14" t="inlineStr"/>
@@ -2453,39 +2453,39 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="E44" s="16" t="n">
-        <v>0.0156</v>
+        <v>0.385</v>
+      </c>
+      <c r="E44" s="15" t="n">
+        <v>0.0132</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>3929600</v>
+        <v>6238100</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0.72</v>
+        <v>0.65</v>
       </c>
       <c r="H44" t="n">
-        <v>95.47</v>
-      </c>
-      <c r="I44" s="17" t="inlineStr">
+        <v>63.96</v>
+      </c>
+      <c r="I44" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J44" s="9" t="n">
-        <v>0.88</v>
+        <v>0.373</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>0.734</v>
+        <v>0.371</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="14" t="inlineStr"/>
@@ -2498,39 +2498,39 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>TANCO</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>0.165</v>
-      </c>
-      <c r="E45" s="15" t="n">
-        <v>0</v>
+        <v>0.6</v>
+      </c>
+      <c r="E45" s="17" t="n">
+        <v>-0.0083</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>3913100</v>
+        <v>5966500</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>0.14</v>
+        <v>0.61</v>
       </c>
       <c r="H45" t="n">
-        <v>34.17</v>
-      </c>
-      <c r="I45" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>45.5</v>
+      </c>
+      <c r="I45" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J45" s="9" t="n">
-        <v>0.182</v>
+        <v>0.607</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>0.221</v>
+        <v>0.604</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="14" t="inlineStr"/>
@@ -2543,39 +2543,39 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>VELESTO</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>0.215</v>
-      </c>
-      <c r="E46" s="10" t="n">
-        <v>-0.0227</v>
+        <v>2.99</v>
+      </c>
+      <c r="E46" s="17" t="n">
+        <v>-0.0132</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>3770200</v>
+        <v>5820500</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0.17</v>
+        <v>0.43</v>
       </c>
       <c r="H46" t="n">
-        <v>29.99</v>
-      </c>
-      <c r="I46" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.08</v>
+      </c>
+      <c r="I46" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J46" s="9" t="n">
-        <v>0.238</v>
+        <v>2.859</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>0.249</v>
+        <v>2.716</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="14" t="inlineStr"/>
@@ -2588,39 +2588,39 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>1589</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>AVANGAAD</t>
+          <t>IWCITY</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E47" s="16" t="n">
-        <v>0.0172</v>
+        <v>0.23</v>
+      </c>
+      <c r="E47" s="15" t="n">
+        <v>0.09519999999999999</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>3749300</v>
+        <v>5525200</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>2.02</v>
+        <v>11.29</v>
       </c>
       <c r="H47" t="n">
-        <v>49.23</v>
-      </c>
-      <c r="I47" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.72</v>
+      </c>
+      <c r="I47" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J47" s="9" t="n">
-        <v>0.295</v>
+        <v>0.217</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>0.297</v>
+        <v>0.225</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="14" t="inlineStr"/>
@@ -2633,39 +2633,39 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>9059</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>TSH</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>1.3</v>
+        <v>0.29</v>
       </c>
       <c r="E48" s="10" t="n">
-        <v>-0.05110000000000001</v>
+        <v>0</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>3457300</v>
+        <v>5242500</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>1.49</v>
+        <v>0.82</v>
       </c>
       <c r="H48" t="n">
-        <v>37.44</v>
-      </c>
-      <c r="I48" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.82</v>
+      </c>
+      <c r="I48" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J48" s="9" t="n">
-        <v>1.404</v>
+        <v>0.274</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>1.317</v>
+        <v>0.269</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="14" t="inlineStr"/>
@@ -2678,39 +2678,39 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>8893</t>
+          <t>0340</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>MKLAND</t>
+          <t>NORTHERN</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>0.175</v>
+        <v>1.3</v>
       </c>
       <c r="E49" s="15" t="n">
-        <v>0</v>
+        <v>0.0156</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>3440600</v>
+        <v>4942000</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>3.16</v>
+        <v>0.9</v>
       </c>
       <c r="H49" t="n">
-        <v>79.92</v>
-      </c>
-      <c r="I49" s="17" t="inlineStr">
+        <v>95.47</v>
+      </c>
+      <c r="I49" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J49" s="9" t="n">
-        <v>0.151</v>
+        <v>0.88</v>
       </c>
       <c r="K49" s="9" t="n">
-        <v>0.145</v>
+        <v>0.734</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="14" t="inlineStr"/>
@@ -2723,39 +2723,39 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0111</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>0.165</v>
-      </c>
-      <c r="E50" s="16" t="n">
-        <v>0.0313</v>
+        <v>2.36</v>
+      </c>
+      <c r="E50" s="17" t="n">
+        <v>-0.0126</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>3355700</v>
+        <v>4866600</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>1.29</v>
+        <v>0.29</v>
       </c>
       <c r="H50" t="n">
-        <v>66.66</v>
-      </c>
-      <c r="I50" s="17" t="inlineStr">
+        <v>52.09</v>
+      </c>
+      <c r="I50" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J50" s="9" t="n">
-        <v>0.148</v>
+        <v>2.349</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>0.139</v>
+        <v>2.239</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="14" t="inlineStr"/>
@@ -2768,39 +2768,39 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="E51" s="10" t="n">
-        <v>-0.0455</v>
+        <v>0.365</v>
+      </c>
+      <c r="E51" s="17" t="n">
+        <v>-0.0135</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>3298500</v>
+        <v>4594900</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>0.3</v>
+        <v>0.77</v>
       </c>
       <c r="H51" t="n">
-        <v>47.24</v>
-      </c>
-      <c r="I51" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.52</v>
+      </c>
+      <c r="I51" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J51" s="9" t="n">
-        <v>1.081</v>
+        <v>0.367</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>1.024</v>
+        <v>0.366</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="14" t="inlineStr"/>
@@ -2813,39 +2813,39 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>0280</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>MBN</t>
         </is>
       </c>
       <c r="D52" s="9" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="E52" s="10" t="n">
-        <v>-0.0312</v>
+        <v>0.16</v>
+      </c>
+      <c r="E52" s="15" t="n">
+        <v>0.0323</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>3205000</v>
+        <v>4522900</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>0.46</v>
+        <v>1.41</v>
       </c>
       <c r="H52" t="n">
-        <v>61.02</v>
-      </c>
-      <c r="I52" s="17" t="inlineStr">
+        <v>56.74</v>
+      </c>
+      <c r="I52" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J52" s="9" t="n">
-        <v>2.626</v>
+        <v>0.154</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>2.495</v>
+        <v>0.147</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="14" t="inlineStr"/>
@@ -2858,39 +2858,39 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>NEXG</t>
+          <t>MALAKOF</t>
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>0.325</v>
-      </c>
-      <c r="E53" s="16" t="n">
-        <v>0.0156</v>
+        <v>0.805</v>
+      </c>
+      <c r="E53" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>3162500</v>
+        <v>4507000</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>0.19</v>
+        <v>1.08</v>
       </c>
       <c r="H53" t="n">
-        <v>66.40000000000001</v>
-      </c>
-      <c r="I53" s="17" t="inlineStr">
+        <v>49.87</v>
+      </c>
+      <c r="I53" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J53" s="9" t="n">
-        <v>0.285</v>
+        <v>0.804</v>
       </c>
       <c r="K53" s="9" t="n">
-        <v>0.277</v>
+        <v>0.806</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="14" t="inlineStr"/>
@@ -2903,39 +2903,39 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="E54" s="10" t="n">
-        <v>-0.0076</v>
+        <v>0.25</v>
+      </c>
+      <c r="E54" s="17" t="n">
+        <v>-0.0385</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>3157000</v>
+        <v>4314100</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>0.27</v>
+        <v>0.36</v>
       </c>
       <c r="H54" t="n">
-        <v>43.34</v>
-      </c>
-      <c r="I54" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>36.09</v>
+      </c>
+      <c r="I54" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J54" s="9" t="n">
-        <v>1.374</v>
+        <v>0.272</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>1.29</v>
+        <v>0.314</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="14" t="inlineStr"/>
@@ -2948,39 +2948,39 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>0.255</v>
-      </c>
-      <c r="E55" s="10" t="n">
-        <v>-0.0192</v>
+        <v>1.05</v>
+      </c>
+      <c r="E55" s="17" t="n">
+        <v>-0.0455</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>2954600</v>
+        <v>4214400</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>0.25</v>
+        <v>0.38</v>
       </c>
       <c r="H55" t="n">
-        <v>37.73</v>
-      </c>
-      <c r="I55" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.24</v>
+      </c>
+      <c r="I55" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J55" s="9" t="n">
-        <v>0.272</v>
+        <v>1.081</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>0.314</v>
+        <v>1.024</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="14" t="inlineStr"/>
@@ -2993,39 +2993,39 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>2429</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>TANCO</t>
         </is>
       </c>
       <c r="D56" s="9" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="E56" s="16" t="n">
-        <v>0.0154</v>
+        <v>0.17</v>
+      </c>
+      <c r="E56" s="15" t="n">
+        <v>0.0303</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>2856200</v>
+        <v>4141100</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>0.36</v>
+        <v>0.15</v>
       </c>
       <c r="H56" t="n">
-        <v>52.72</v>
-      </c>
-      <c r="I56" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.52</v>
+      </c>
+      <c r="I56" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J56" s="9" t="n">
-        <v>0.33</v>
+        <v>0.182</v>
       </c>
       <c r="K56" s="9" t="n">
-        <v>0.311</v>
+        <v>0.221</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="14" t="inlineStr"/>
@@ -3038,39 +3038,39 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="E57" s="10" t="n">
-        <v>-0.0048</v>
+        <v>4.13</v>
+      </c>
+      <c r="E57" s="15" t="n">
+        <v>0.0172</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>2838900</v>
+        <v>4136600</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>0.17</v>
+        <v>0.86</v>
       </c>
       <c r="H57" t="n">
-        <v>45.92</v>
-      </c>
-      <c r="I57" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>79.47</v>
+      </c>
+      <c r="I57" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J57" s="9" t="n">
-        <v>2.126</v>
+        <v>3.542</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>2.062</v>
+        <v>3.225</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="14" t="inlineStr"/>
@@ -3083,39 +3083,39 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>8893</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>MKLAND</t>
         </is>
       </c>
       <c r="D58" s="9" t="n">
-        <v>0.72</v>
+        <v>0.175</v>
       </c>
       <c r="E58" s="10" t="n">
-        <v>-0.04</v>
+        <v>0</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>2829000</v>
+        <v>3871200</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>0.49</v>
+        <v>3.55</v>
       </c>
       <c r="H58" t="n">
-        <v>60.74</v>
-      </c>
-      <c r="I58" s="17" t="inlineStr">
+        <v>79.92</v>
+      </c>
+      <c r="I58" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J58" s="9" t="n">
-        <v>0.681</v>
+        <v>0.151</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>0.611</v>
+        <v>0.145</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="14" t="inlineStr"/>
@@ -3128,39 +3128,39 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>2.37</v>
+        <v>1.32</v>
       </c>
       <c r="E59" s="10" t="n">
-        <v>-0.008399999999999999</v>
+        <v>0</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>2806700</v>
+        <v>3844300</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>0.17</v>
+        <v>0.33</v>
       </c>
       <c r="H59" t="n">
-        <v>52.86</v>
-      </c>
-      <c r="I59" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.52</v>
+      </c>
+      <c r="I59" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J59" s="9" t="n">
-        <v>2.35</v>
+        <v>1.375</v>
       </c>
       <c r="K59" s="9" t="n">
-        <v>2.239</v>
+        <v>1.29</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="14" t="inlineStr"/>
@@ -3173,39 +3173,39 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>0.365</v>
-      </c>
-      <c r="E60" s="10" t="n">
-        <v>-0.0135</v>
+        <v>5.79</v>
+      </c>
+      <c r="E60" s="17" t="n">
+        <v>-0.017</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>2774000</v>
+        <v>3835100</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>0.46</v>
+        <v>0.26</v>
       </c>
       <c r="H60" t="n">
-        <v>48.52</v>
-      </c>
-      <c r="I60" s="17" t="inlineStr">
+        <v>58.54</v>
+      </c>
+      <c r="I60" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J60" s="9" t="n">
-        <v>0.367</v>
+        <v>5.685</v>
       </c>
       <c r="K60" s="9" t="n">
-        <v>0.366</v>
+        <v>5.131</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="14" t="inlineStr"/>
@@ -3218,39 +3218,39 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>0.36</v>
+        <v>0.295</v>
       </c>
       <c r="E61" s="15" t="n">
-        <v>0</v>
+        <v>0.0172</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>2696600</v>
+        <v>3749300</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>0.38</v>
+        <v>2.02</v>
       </c>
       <c r="H61" t="n">
-        <v>65.70999999999999</v>
-      </c>
-      <c r="I61" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.23</v>
+      </c>
+      <c r="I61" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J61" s="9" t="n">
-        <v>0.337</v>
+        <v>0.295</v>
       </c>
       <c r="K61" s="9" t="n">
-        <v>0.319</v>
+        <v>0.297</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="14" t="inlineStr"/>
@@ -3263,39 +3263,39 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>9059</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>TSH</t>
         </is>
       </c>
       <c r="D62" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E62" s="16" t="n">
-        <v>0.0121</v>
+        <v>1.28</v>
+      </c>
+      <c r="E62" s="17" t="n">
+        <v>-0.06570000000000001</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>2630600</v>
+        <v>3748400</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>0.17</v>
+        <v>1.61</v>
       </c>
       <c r="H62" t="n">
-        <v>61.94</v>
-      </c>
-      <c r="I62" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.61</v>
+      </c>
+      <c r="I62" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J62" s="9" t="n">
-        <v>2.439</v>
+        <v>1.402</v>
       </c>
       <c r="K62" s="9" t="n">
-        <v>2.276</v>
+        <v>1.317</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="14" t="inlineStr"/>
@@ -3308,39 +3308,39 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="E63" s="10" t="n">
-        <v>-0.0238</v>
+        <v>0.55</v>
+      </c>
+      <c r="E63" s="15" t="n">
+        <v>0.0092</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>2472800</v>
+        <v>3675400</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>0.22</v>
+        <v>0.58</v>
       </c>
       <c r="H63" t="n">
-        <v>51.48</v>
-      </c>
-      <c r="I63" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.68</v>
+      </c>
+      <c r="I63" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J63" s="9" t="n">
-        <v>0.409</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="K63" s="9" t="n">
-        <v>0.41</v>
+        <v>0.59</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="14" t="inlineStr"/>
@@ -3353,39 +3353,39 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>NEXG</t>
         </is>
       </c>
       <c r="D64" s="9" t="n">
-        <v>4.44</v>
-      </c>
-      <c r="E64" s="16" t="n">
-        <v>0.0207</v>
+        <v>0.32</v>
+      </c>
+      <c r="E64" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>2383700</v>
+        <v>3536700</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>0.2</v>
+        <v>0.22</v>
       </c>
       <c r="H64" t="n">
-        <v>79.69</v>
-      </c>
-      <c r="I64" s="17" t="inlineStr">
+        <v>65.18000000000001</v>
+      </c>
+      <c r="I64" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J64" s="9" t="n">
-        <v>3.526</v>
+        <v>0.284</v>
       </c>
       <c r="K64" s="9" t="n">
-        <v>2.355</v>
+        <v>0.277</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="14" t="inlineStr"/>
@@ -3398,39 +3398,39 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="E65" s="16" t="n">
-        <v>0.007800000000000001</v>
+        <v>2.55</v>
+      </c>
+      <c r="E65" s="17" t="n">
+        <v>-0.0267</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>2361300</v>
+        <v>3399100</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>0.2</v>
+        <v>0.58</v>
       </c>
       <c r="H65" t="n">
-        <v>36.84</v>
-      </c>
-      <c r="I65" s="17" t="inlineStr">
+        <v>48.43</v>
+      </c>
+      <c r="I65" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J65" s="9" t="n">
-        <v>1.329</v>
+        <v>2.568</v>
       </c>
       <c r="K65" s="9" t="n">
-        <v>1.444</v>
+        <v>2.535</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="14" t="inlineStr"/>
@@ -3443,39 +3443,39 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D66" s="9" t="n">
-        <v>5.81</v>
-      </c>
-      <c r="E66" s="10" t="n">
-        <v>-0.0136</v>
+        <v>1.18</v>
+      </c>
+      <c r="E66" s="15" t="n">
+        <v>0.0172</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>2352700</v>
+        <v>3364000</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>0.16</v>
+        <v>0.5</v>
       </c>
       <c r="H66" t="n">
-        <v>59.45</v>
-      </c>
-      <c r="I66" s="17" t="inlineStr">
+        <v>50.53</v>
+      </c>
+      <c r="I66" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J66" s="9" t="n">
-        <v>5.687</v>
+        <v>1.181</v>
       </c>
       <c r="K66" s="9" t="n">
-        <v>5.131</v>
+        <v>1.14</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="14" t="inlineStr"/>
@@ -3488,39 +3488,39 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>0111</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.165</v>
       </c>
       <c r="E67" s="15" t="n">
-        <v>0</v>
+        <v>0.0313</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>2312100</v>
+        <v>3362700</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>0.18</v>
+        <v>1.29</v>
       </c>
       <c r="H67" t="n">
-        <v>50.19</v>
-      </c>
-      <c r="I67" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.66</v>
+      </c>
+      <c r="I67" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J67" s="9" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.148</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.139</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="14" t="inlineStr"/>
@@ -3533,39 +3533,39 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0369</t>
+          <t>0050</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>JSSOLAR</t>
+          <t>SYSTECH</t>
         </is>
       </c>
       <c r="D68" s="9" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E68" s="16" t="n">
-        <v>0.04</v>
+        <v>0.18</v>
+      </c>
+      <c r="E68" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>2304300</v>
+        <v>3320800</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>2.24</v>
+        <v>0.64</v>
       </c>
       <c r="H68" t="n">
-        <v>73.58</v>
-      </c>
-      <c r="I68" s="17" t="inlineStr">
+        <v>63.42</v>
+      </c>
+      <c r="I68" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J68" s="9" t="n">
-        <v>0.212</v>
+        <v>0.163</v>
       </c>
       <c r="K68" s="9" t="n">
-        <v>0.198</v>
+        <v>0.165</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="14" t="inlineStr"/>
@@ -3578,39 +3578,39 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0393</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>TEAMSTR</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D69" s="9" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="E69" s="15" t="n">
-        <v>0</v>
+        <v>0.715</v>
+      </c>
+      <c r="E69" s="17" t="n">
+        <v>-0.0467</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>2276900</v>
+        <v>3267800</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>0.75</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H69" t="n">
-        <v>31.51</v>
-      </c>
-      <c r="I69" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.69</v>
+      </c>
+      <c r="I69" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J69" s="9" t="n">
-        <v>0.244</v>
+        <v>0.681</v>
       </c>
       <c r="K69" s="9" t="n">
-        <v>0.243</v>
+        <v>0.611</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="14" t="inlineStr"/>
@@ -3623,39 +3623,39 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>MRCB</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D70" s="9" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="E70" s="15" t="n">
+        <v>0.865</v>
+      </c>
+      <c r="E70" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>2261100</v>
+        <v>3210700</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>0.3</v>
+        <v>1.09</v>
       </c>
       <c r="H70" t="n">
-        <v>39.08</v>
-      </c>
-      <c r="I70" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>59.03</v>
+      </c>
+      <c r="I70" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J70" s="9" t="n">
-        <v>0.298</v>
+        <v>0.859</v>
       </c>
       <c r="K70" s="9" t="n">
-        <v>0.312</v>
+        <v>0.856</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="14" t="inlineStr"/>
@@ -3677,27 +3677,27 @@
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="E71" s="16" t="n">
-        <v>0.0333</v>
+        <v>0.92</v>
+      </c>
+      <c r="E71" s="15" t="n">
+        <v>0.0222</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>2234000</v>
+        <v>3209200</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>0.68</v>
+        <v>0.98</v>
       </c>
       <c r="H71" t="n">
-        <v>47.25</v>
-      </c>
-      <c r="I71" s="17" t="inlineStr">
+        <v>43.85</v>
+      </c>
+      <c r="I71" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J71" s="9" t="n">
-        <v>0.928</v>
+        <v>0.927</v>
       </c>
       <c r="K71" s="9" t="n">
         <v>0.969</v>
@@ -3713,39 +3713,39 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D72" s="9" t="n">
-        <v>1.15</v>
+        <v>0.325</v>
       </c>
       <c r="E72" s="10" t="n">
-        <v>-0.0417</v>
+        <v>0</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>2207200</v>
+        <v>3055800</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>0.24</v>
+        <v>0.38</v>
       </c>
       <c r="H72" t="n">
-        <v>50.13</v>
-      </c>
-      <c r="I72" s="17" t="inlineStr">
+        <v>50.52</v>
+      </c>
+      <c r="I72" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J72" s="9" t="n">
-        <v>1.163</v>
+        <v>0.33</v>
       </c>
       <c r="K72" s="9" t="n">
-        <v>1.1</v>
+        <v>0.311</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="14" t="inlineStr"/>
@@ -3769,14 +3769,14 @@
       <c r="D73" s="9" t="n">
         <v>0.765</v>
       </c>
-      <c r="E73" s="15" t="n">
+      <c r="E73" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>2156200</v>
+        <v>2986200</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>0.34</v>
+        <v>0.48</v>
       </c>
       <c r="H73" t="n">
         <v>46.13</v>
@@ -3803,39 +3803,39 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D74" s="9" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="E74" s="16" t="n">
-        <v>0.0152</v>
+        <v>10.2</v>
+      </c>
+      <c r="E74" s="17" t="n">
+        <v>-0.002</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>2097100</v>
+        <v>2971400</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>0.22</v>
+        <v>0.18</v>
       </c>
       <c r="H74" t="n">
-        <v>61.53</v>
-      </c>
-      <c r="I74" s="17" t="inlineStr">
+        <v>49.44</v>
+      </c>
+      <c r="I74" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J74" s="9" t="n">
-        <v>0.634</v>
+        <v>10.179</v>
       </c>
       <c r="K74" s="9" t="n">
-        <v>0.575</v>
+        <v>10.321</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="14" t="inlineStr"/>
@@ -3848,39 +3848,39 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D75" s="9" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="E75" s="10" t="n">
-        <v>-0.0148</v>
+        <v>1.32</v>
+      </c>
+      <c r="E75" s="15" t="n">
+        <v>0.0233</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>2046900</v>
+        <v>2811700</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>0.38</v>
+        <v>0.23</v>
       </c>
       <c r="H75" t="n">
-        <v>76.54000000000001</v>
-      </c>
-      <c r="I75" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>42.24</v>
+      </c>
+      <c r="I75" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J75" s="9" t="n">
-        <v>2.457</v>
+        <v>1.331</v>
       </c>
       <c r="K75" s="9" t="n">
-        <v>2.118</v>
+        <v>1.445</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="14" t="inlineStr"/>
@@ -3893,39 +3893,39 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D76" s="9" t="n">
-        <v>0.425</v>
+        <v>4.41</v>
       </c>
       <c r="E76" s="15" t="n">
-        <v>0</v>
+        <v>0.0138</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>1930800</v>
+        <v>2806600</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>0.33</v>
+        <v>0.23</v>
       </c>
       <c r="H76" t="n">
-        <v>57.85</v>
-      </c>
-      <c r="I76" s="17" t="inlineStr">
+        <v>79.41</v>
+      </c>
+      <c r="I76" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J76" s="9" t="n">
-        <v>0.402</v>
+        <v>3.523</v>
       </c>
       <c r="K76" s="9" t="n">
-        <v>0.4</v>
+        <v>2.355</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="14" t="inlineStr"/>
@@ -3938,39 +3938,39 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D77" s="9" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="E77" s="16" t="n">
-        <v>0.0086</v>
+        <v>0.36</v>
+      </c>
+      <c r="E77" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>1795100</v>
+        <v>2721500</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>0.27</v>
+        <v>0.39</v>
       </c>
       <c r="H77" t="n">
-        <v>49.17</v>
-      </c>
-      <c r="I77" s="17" t="inlineStr">
+        <v>65.70999999999999</v>
+      </c>
+      <c r="I77" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J77" s="9" t="n">
-        <v>1.181</v>
+        <v>0.337</v>
       </c>
       <c r="K77" s="9" t="n">
-        <v>1.14</v>
+        <v>0.319</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="14" t="inlineStr"/>
@@ -3983,39 +3983,39 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D78" s="9" t="n">
-        <v>2.55</v>
+        <v>0.29</v>
       </c>
       <c r="E78" s="10" t="n">
-        <v>-0.0267</v>
+        <v>0</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>1723500</v>
+        <v>2653800</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="H78" t="n">
-        <v>48.43</v>
-      </c>
-      <c r="I78" s="17" t="inlineStr">
+        <v>39.08</v>
+      </c>
+      <c r="I78" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J78" s="9" t="n">
-        <v>2.568</v>
+        <v>0.298</v>
       </c>
       <c r="K78" s="9" t="n">
-        <v>2.535</v>
+        <v>0.312</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="14" t="inlineStr"/>
@@ -4028,39 +4028,39 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D79" s="9" t="n">
-        <v>4.11</v>
-      </c>
-      <c r="E79" s="16" t="n">
-        <v>0.0123</v>
+        <v>0.415</v>
+      </c>
+      <c r="E79" s="17" t="n">
+        <v>-0.0119</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>1690200</v>
+        <v>2627100</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>0.35</v>
+        <v>0.23</v>
       </c>
       <c r="H79" t="n">
-        <v>79.13</v>
-      </c>
-      <c r="I79" s="17" t="inlineStr">
+        <v>56.5</v>
+      </c>
+      <c r="I79" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J79" s="9" t="n">
-        <v>3.54</v>
+        <v>0.409</v>
       </c>
       <c r="K79" s="9" t="n">
-        <v>3.224</v>
+        <v>0.41</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="14" t="inlineStr"/>
@@ -4073,39 +4073,39 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>0369</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>JSSOLAR</t>
         </is>
       </c>
       <c r="D80" s="9" t="n">
-        <v>10.18</v>
-      </c>
-      <c r="E80" s="10" t="n">
-        <v>-0.0039</v>
+        <v>0.255</v>
+      </c>
+      <c r="E80" s="15" t="n">
+        <v>0.02</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>1666500</v>
+        <v>2586000</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>0.1</v>
+        <v>2.51</v>
       </c>
       <c r="H80" t="n">
-        <v>47.99</v>
-      </c>
-      <c r="I80" s="17" t="inlineStr">
+        <v>72.41</v>
+      </c>
+      <c r="I80" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J80" s="9" t="n">
-        <v>10.177</v>
+        <v>0.212</v>
       </c>
       <c r="K80" s="9" t="n">
-        <v>10.321</v>
+        <v>0.198</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="14" t="inlineStr"/>
@@ -4118,39 +4118,39 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D81" s="9" t="n">
-        <v>0.545</v>
+        <v>0.665</v>
       </c>
       <c r="E81" s="15" t="n">
-        <v>0</v>
+        <v>0.0076</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>1659000</v>
+        <v>2555800</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="H81" t="n">
-        <v>39.08</v>
-      </c>
-      <c r="I81" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.68</v>
+      </c>
+      <c r="I81" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J81" s="9" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.634</v>
       </c>
       <c r="K81" s="9" t="n">
-        <v>0.59</v>
+        <v>0.574</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="14" t="inlineStr"/>
@@ -4163,39 +4163,39 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>4243</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>WTK</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D82" s="9" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="E82" s="10" t="n">
-        <v>-0.0204</v>
+        <v>1.15</v>
+      </c>
+      <c r="E82" s="17" t="n">
+        <v>-0.0417</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>1620900</v>
+        <v>2283600</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>0.65</v>
+        <v>0.25</v>
       </c>
       <c r="H82" t="n">
-        <v>35.93</v>
-      </c>
-      <c r="I82" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.13</v>
+      </c>
+      <c r="I82" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J82" s="9" t="n">
-        <v>1.045</v>
+        <v>1.163</v>
       </c>
       <c r="K82" s="9" t="n">
-        <v>1.014</v>
+        <v>1.1</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="14" t="inlineStr"/>
@@ -4208,28 +4208,28 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0358</t>
+          <t>0393</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>ICTZONE</t>
+          <t>TEAMSTR</t>
         </is>
       </c>
       <c r="D83" s="9" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E83" s="15" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="E83" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>1602800</v>
+        <v>2276900</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>0.58</v>
+        <v>0.75</v>
       </c>
       <c r="H83" t="n">
-        <v>50.51</v>
+        <v>31.51</v>
       </c>
       <c r="I83" s="13" t="inlineStr">
         <is>
@@ -4237,10 +4237,10 @@
         </is>
       </c>
       <c r="J83" s="9" t="n">
-        <v>0.262</v>
+        <v>0.244</v>
       </c>
       <c r="K83" s="9" t="n">
-        <v>0.251</v>
+        <v>0.243</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="14" t="inlineStr"/>
@@ -4253,39 +4253,39 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D84" s="9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="E84" s="10" t="n">
-        <v>-0.0189</v>
+        <v>0.42</v>
+      </c>
+      <c r="E84" s="17" t="n">
+        <v>-0.0118</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>1588700</v>
+        <v>2230900</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>0.19</v>
+        <v>0.38</v>
       </c>
       <c r="H84" t="n">
-        <v>77.48999999999999</v>
-      </c>
-      <c r="I84" s="17" t="inlineStr">
+        <v>56.23</v>
+      </c>
+      <c r="I84" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J84" s="9" t="n">
-        <v>0.893</v>
+        <v>0.402</v>
       </c>
       <c r="K84" s="9" t="n">
-        <v>0.759</v>
+        <v>0.4</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="14" t="inlineStr"/>
@@ -4298,39 +4298,39 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D85" s="9" t="n">
-        <v>0.535</v>
-      </c>
-      <c r="E85" s="10" t="n">
-        <v>-0.0273</v>
+        <v>0.78</v>
+      </c>
+      <c r="E85" s="17" t="n">
+        <v>-0.0064</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>1538800</v>
+        <v>2225100</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>0.86</v>
+        <v>0.38</v>
       </c>
       <c r="H85" t="n">
-        <v>60.09</v>
-      </c>
-      <c r="I85" s="17" t="inlineStr">
+        <v>74.67</v>
+      </c>
+      <c r="I85" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J85" s="9" t="n">
-        <v>0.497</v>
+        <v>0.767</v>
       </c>
       <c r="K85" s="9" t="n">
-        <v>0.401</v>
+        <v>0.752</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="14" t="inlineStr"/>
@@ -4343,28 +4343,28 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D86" s="9" t="n">
-        <v>0.61</v>
+        <v>1.65</v>
       </c>
       <c r="E86" s="15" t="n">
-        <v>0</v>
+        <v>0.0123</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>1534900</v>
+        <v>2222700</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>0.31</v>
+        <v>0.34</v>
       </c>
       <c r="H86" t="n">
-        <v>38.17</v>
+        <v>34.08</v>
       </c>
       <c r="I86" s="13" t="inlineStr">
         <is>
@@ -4372,10 +4372,10 @@
         </is>
       </c>
       <c r="J86" s="9" t="n">
-        <v>0.638</v>
+        <v>1.732</v>
       </c>
       <c r="K86" s="9" t="n">
-        <v>0.658</v>
+        <v>1.847</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="14" t="inlineStr"/>
@@ -4388,28 +4388,28 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0239</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>ECOMATE</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D87" s="9" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E87" s="15" t="n">
-        <v>0</v>
+        <v>2.63</v>
+      </c>
+      <c r="E87" s="17" t="n">
+        <v>-0.0259</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>1529100</v>
+        <v>2221900</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>0.52</v>
+        <v>0.41</v>
       </c>
       <c r="H87" t="n">
-        <v>59.03</v>
+        <v>72.69</v>
       </c>
       <c r="I87" s="13" t="inlineStr">
         <is>
@@ -4417,10 +4417,10 @@
         </is>
       </c>
       <c r="J87" s="9" t="n">
-        <v>0.859</v>
+        <v>2.454</v>
       </c>
       <c r="K87" s="9" t="n">
-        <v>0.856</v>
+        <v>2.118</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="14" t="inlineStr"/>
@@ -4433,39 +4433,39 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D88" s="9" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="E88" s="15" t="n">
-        <v>0</v>
+        <v>0.51</v>
+      </c>
+      <c r="E88" s="17" t="n">
+        <v>-0.0377</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>1519800</v>
+        <v>2207700</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>0.23</v>
+        <v>0.59</v>
       </c>
       <c r="H88" t="n">
-        <v>30.25</v>
-      </c>
-      <c r="I88" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.34</v>
+      </c>
+      <c r="I88" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J88" s="9" t="n">
-        <v>1.73</v>
+        <v>0.512</v>
       </c>
       <c r="K88" s="9" t="n">
-        <v>1.847</v>
+        <v>0.464</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="14" t="inlineStr"/>
@@ -4478,39 +4478,39 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D89" s="9" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="E89" s="10" t="n">
-        <v>-0.0112</v>
+        <v>1.09</v>
+      </c>
+      <c r="E89" s="17" t="n">
+        <v>-0.0268</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>1460200</v>
+        <v>2206500</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>0.24</v>
+        <v>0.46</v>
       </c>
       <c r="H89" t="n">
-        <v>47.93</v>
-      </c>
-      <c r="I89" s="17" t="inlineStr">
+        <v>76.75</v>
+      </c>
+      <c r="I89" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J89" s="9" t="n">
-        <v>1.771</v>
+        <v>0.973</v>
       </c>
       <c r="K89" s="9" t="n">
-        <v>1.806</v>
+        <v>0.8</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="14" t="inlineStr"/>
@@ -4523,39 +4523,39 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0268</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>L&amp;PBHD</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D90" s="9" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="E90" s="16" t="n">
-        <v>0.0244</v>
+        <v>1.76</v>
+      </c>
+      <c r="E90" s="17" t="n">
+        <v>-0.0112</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>1428600</v>
+        <v>2176500</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>0.52</v>
+        <v>0.36</v>
       </c>
       <c r="H90" t="n">
-        <v>71.81999999999999</v>
-      </c>
-      <c r="I90" s="17" t="inlineStr">
+        <v>47.93</v>
+      </c>
+      <c r="I90" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J90" s="9" t="n">
-        <v>0.187</v>
+        <v>1.771</v>
       </c>
       <c r="K90" s="9" t="n">
-        <v>0.156</v>
+        <v>1.806</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="14" t="inlineStr"/>
@@ -4568,39 +4568,39 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>MBSB</t>
         </is>
       </c>
       <c r="D91" s="9" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="E91" s="16" t="n">
-        <v>0.0053</v>
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="E91" s="15" t="n">
+        <v>0.018</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>1418800</v>
+        <v>2123100</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>0.31</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H91" t="n">
-        <v>36.25</v>
-      </c>
-      <c r="I91" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.24</v>
+      </c>
+      <c r="I91" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J91" s="9" t="n">
-        <v>1.956</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="K91" s="9" t="n">
-        <v>2.078</v>
+        <v>0.595</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="14" t="inlineStr"/>
@@ -4613,39 +4613,39 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0032</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>REDTONE</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D92" s="9" t="n">
-        <v>0.36</v>
+        <v>1.1</v>
       </c>
       <c r="E92" s="10" t="n">
-        <v>-0.0137</v>
+        <v>0</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>1408400</v>
+        <v>2002000</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>0.83</v>
+        <v>0.16</v>
       </c>
       <c r="H92" t="n">
-        <v>59.96</v>
-      </c>
-      <c r="I92" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>79.33</v>
+      </c>
+      <c r="I92" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J92" s="9" t="n">
-        <v>0.354</v>
+        <v>1.006</v>
       </c>
       <c r="K92" s="9" t="n">
-        <v>0.319</v>
+        <v>0.845</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="14" t="inlineStr"/>
@@ -4658,39 +4658,39 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>0265</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>INFOM</t>
         </is>
       </c>
       <c r="D93" s="9" t="n">
-        <v>0.65</v>
+        <v>1.69</v>
       </c>
       <c r="E93" s="15" t="n">
-        <v>0</v>
+        <v>0.04969999999999999</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>1383100</v>
+        <v>1950100</v>
       </c>
       <c r="G93" s="12" t="n">
-        <v>0.41</v>
+        <v>5.68</v>
       </c>
       <c r="H93" t="n">
-        <v>70.55</v>
-      </c>
-      <c r="I93" s="17" t="inlineStr">
+        <v>73.53</v>
+      </c>
+      <c r="I93" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J93" s="9" t="n">
-        <v>0.634</v>
+        <v>1.59</v>
       </c>
       <c r="K93" s="9" t="n">
-        <v>0.591</v>
+        <v>1.536</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="14" t="inlineStr"/>
@@ -4703,39 +4703,39 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D94" s="9" t="n">
-        <v>0.52</v>
+        <v>0.55</v>
       </c>
       <c r="E94" s="10" t="n">
-        <v>-0.0189</v>
+        <v>0</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>1367700</v>
+        <v>1862600</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>0.37</v>
+        <v>1.04</v>
       </c>
       <c r="H94" t="n">
-        <v>55.42</v>
-      </c>
-      <c r="I94" s="17" t="inlineStr">
+        <v>63.26</v>
+      </c>
+      <c r="I94" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J94" s="9" t="n">
-        <v>0.512</v>
+        <v>0.498</v>
       </c>
       <c r="K94" s="9" t="n">
-        <v>0.464</v>
+        <v>0.401</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="14" t="inlineStr"/>
@@ -4748,33 +4748,40 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0468</t>
+          <t>5162</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>UNIPAC</t>
+          <t>VSTECS</t>
         </is>
       </c>
       <c r="D95" s="9" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E95" s="10" t="n">
-        <v>-0.0196</v>
+        <v>1.66</v>
+      </c>
+      <c r="E95" s="15" t="n">
+        <v>0.0061</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>1364400</v>
+        <v>1846400</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="I95" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J95" s="9" t="n"/>
-      <c r="K95" s="9" t="n"/>
+        <v>1.24</v>
+      </c>
+      <c r="H95" t="n">
+        <v>51.42</v>
+      </c>
+      <c r="I95" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J95" s="9" t="n">
+        <v>1.637</v>
+      </c>
+      <c r="K95" s="9" t="n">
+        <v>1.693</v>
+      </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="14" t="inlineStr"/>
     </row>
@@ -4786,39 +4793,39 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>MBSB</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D96" s="9" t="n">
-        <v>0.5649999999999999</v>
-      </c>
-      <c r="E96" s="16" t="n">
-        <v>0.018</v>
+        <v>1.04</v>
+      </c>
+      <c r="E96" s="17" t="n">
+        <v>-0.0189</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>1363300</v>
+        <v>1838700</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>0.36</v>
+        <v>0.22</v>
       </c>
       <c r="H96" t="n">
-        <v>46.24</v>
-      </c>
-      <c r="I96" s="17" t="inlineStr">
+        <v>77.48999999999999</v>
+      </c>
+      <c r="I96" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J96" s="9" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.893</v>
       </c>
       <c r="K96" s="9" t="n">
-        <v>0.595</v>
+        <v>0.759</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="14" t="inlineStr"/>
@@ -4831,39 +4838,39 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0376</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>IAB</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D97" s="9" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="E97" s="16" t="n">
-        <v>0.0394</v>
+        <v>1.91</v>
+      </c>
+      <c r="E97" s="15" t="n">
+        <v>0.016</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>1344400</v>
+        <v>1814400</v>
       </c>
       <c r="G97" s="12" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="H97" t="n">
-        <v>53.02</v>
-      </c>
-      <c r="I97" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.51</v>
+      </c>
+      <c r="I97" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J97" s="9" t="n">
-        <v>1.286</v>
+        <v>1.958</v>
       </c>
       <c r="K97" s="9" t="n">
-        <v>1.345</v>
+        <v>2.079</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="14" t="inlineStr"/>
@@ -4876,39 +4883,39 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>0265</t>
+          <t>4243</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>INFOM</t>
+          <t>WTK</t>
         </is>
       </c>
       <c r="D98" s="9" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="E98" s="16" t="n">
-        <v>0.0435</v>
+        <v>0.96</v>
+      </c>
+      <c r="E98" s="17" t="n">
+        <v>-0.0204</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>1301500</v>
+        <v>1724900</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>3.79</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H98" t="n">
-        <v>72.48</v>
-      </c>
-      <c r="I98" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.93</v>
+      </c>
+      <c r="I98" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J98" s="9" t="n">
-        <v>1.589</v>
+        <v>1.045</v>
       </c>
       <c r="K98" s="9" t="n">
-        <v>1.536</v>
+        <v>1.014</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="14" t="inlineStr"/>
@@ -4921,28 +4928,28 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0272</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>TTVHB</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D99" s="9" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E99" s="15" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="E99" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>1257000</v>
+        <v>1671600</v>
       </c>
       <c r="G99" s="12" t="n">
-        <v>0.37</v>
+        <v>0.33</v>
       </c>
       <c r="H99" t="n">
-        <v>49.72</v>
+        <v>38.17</v>
       </c>
       <c r="I99" s="13" t="inlineStr">
         <is>
@@ -4950,10 +4957,10 @@
         </is>
       </c>
       <c r="J99" s="9" t="n">
-        <v>0.249</v>
+        <v>0.638</v>
       </c>
       <c r="K99" s="9" t="n">
-        <v>0.253</v>
+        <v>0.658</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="14" t="inlineStr"/>
@@ -4966,39 +4973,39 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0045</t>
+          <t>0376</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>SSB8</t>
+          <t>IAB</t>
         </is>
       </c>
       <c r="D100" s="9" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="E100" s="10" t="n">
-        <v>-0.0152</v>
+        <v>1.3</v>
+      </c>
+      <c r="E100" s="15" t="n">
+        <v>0.0236</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>1213200</v>
+        <v>1604500</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>0.32</v>
+        <v>1.07</v>
       </c>
       <c r="H100" t="n">
-        <v>60.69</v>
-      </c>
-      <c r="I100" s="17" t="inlineStr">
+        <v>50.37</v>
+      </c>
+      <c r="I100" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J100" s="9" t="n">
-        <v>0.62</v>
+        <v>1.284</v>
       </c>
       <c r="K100" s="9" t="n">
-        <v>0.581</v>
+        <v>1.345</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="14" t="inlineStr"/>
@@ -5011,39 +5018,39 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0104</t>
+          <t>0358</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>GENETEC</t>
+          <t>ICTZONE</t>
         </is>
       </c>
       <c r="D101" s="9" t="n">
-        <v>0.315</v>
+        <v>0.26</v>
       </c>
       <c r="E101" s="10" t="n">
-        <v>-0.0156</v>
+        <v>0</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>1201700</v>
+        <v>1602800</v>
       </c>
       <c r="G101" s="12" t="n">
-        <v>0.19</v>
+        <v>0.58</v>
       </c>
       <c r="H101" t="n">
-        <v>44.97</v>
-      </c>
-      <c r="I101" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.51</v>
+      </c>
+      <c r="I101" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J101" s="9" t="n">
-        <v>0.321</v>
+        <v>0.262</v>
       </c>
       <c r="K101" s="9" t="n">
-        <v>0.339</v>
+        <v>0.251</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="14" t="inlineStr"/>
@@ -5056,28 +5063,28 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>3379</t>
+          <t>0272</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>INSAS</t>
+          <t>TTVHB</t>
         </is>
       </c>
       <c r="D102" s="9" t="n">
-        <v>0.905</v>
-      </c>
-      <c r="E102" s="16" t="n">
-        <v>0.0226</v>
+        <v>0.24</v>
+      </c>
+      <c r="E102" s="17" t="n">
+        <v>-0.04</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>1191000</v>
+        <v>1597000</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>2.05</v>
+        <v>0.47</v>
       </c>
       <c r="H102" t="n">
-        <v>57.27</v>
+        <v>46.04</v>
       </c>
       <c r="I102" s="13" t="inlineStr">
         <is>
@@ -5085,10 +5092,10 @@
         </is>
       </c>
       <c r="J102" s="9" t="n">
-        <v>0.895</v>
+        <v>0.248</v>
       </c>
       <c r="K102" s="9" t="n">
-        <v>0.9</v>
+        <v>0.253</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="14" t="inlineStr"/>
@@ -5101,39 +5108,39 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>0233</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>PEKAT</t>
         </is>
       </c>
       <c r="D103" s="9" t="n">
-        <v>0.785</v>
+        <v>2.88</v>
       </c>
       <c r="E103" s="15" t="n">
-        <v>0</v>
+        <v>0.0213</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>1183900</v>
+        <v>1590300</v>
       </c>
       <c r="G103" s="12" t="n">
-        <v>0.2</v>
+        <v>0.73</v>
       </c>
       <c r="H103" t="n">
-        <v>86.31</v>
-      </c>
-      <c r="I103" s="17" t="inlineStr">
+        <v>89.54000000000001</v>
+      </c>
+      <c r="I103" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J103" s="9" t="n">
-        <v>0.767</v>
+        <v>2.253</v>
       </c>
       <c r="K103" s="9" t="n">
-        <v>0.752</v>
+        <v>1.952</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="14" t="inlineStr"/>
@@ -5146,39 +5153,39 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>0032</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>REDTONE</t>
         </is>
       </c>
       <c r="D104" s="9" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="E104" s="10" t="n">
-        <v>-0.0268</v>
+        <v>0.36</v>
+      </c>
+      <c r="E104" s="17" t="n">
+        <v>-0.0137</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>1141900</v>
+        <v>1561400</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>0.24</v>
+        <v>0.92</v>
       </c>
       <c r="H104" t="n">
-        <v>76.75</v>
-      </c>
-      <c r="I104" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>59.96</v>
+      </c>
+      <c r="I104" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J104" s="9" t="n">
-        <v>0.973</v>
+        <v>0.354</v>
       </c>
       <c r="K104" s="9" t="n">
-        <v>0.8</v>
+        <v>0.319</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="14" t="inlineStr"/>
@@ -5191,40 +5198,33 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>0470</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>BFIELD</t>
         </is>
       </c>
       <c r="D105" s="9" t="n">
-        <v>0.58</v>
+        <v>0.48</v>
       </c>
       <c r="E105" s="10" t="n">
-        <v>-0.0252</v>
+        <v>0</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>1127700</v>
+        <v>1543100</v>
       </c>
       <c r="G105" s="12" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="H105" t="n">
-        <v>52.94</v>
-      </c>
-      <c r="I105" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J105" s="9" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="K105" s="9" t="n">
-        <v>0.575</v>
-      </c>
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I105" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J105" s="9" t="n"/>
+      <c r="K105" s="9" t="n"/>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="14" t="inlineStr"/>
     </row>
@@ -5236,33 +5236,40 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0470</t>
+          <t>5212</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>BFIELD</t>
+          <t>PAVREIT</t>
         </is>
       </c>
       <c r="D106" s="9" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="E106" s="15" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="E106" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>1125100</v>
+        <v>1534600</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I106" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J106" s="9" t="n"/>
-      <c r="K106" s="9" t="n"/>
+        <v>0.54</v>
+      </c>
+      <c r="H106" t="n">
+        <v>41.51</v>
+      </c>
+      <c r="I106" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J106" s="9" t="n">
+        <v>1.584</v>
+      </c>
+      <c r="K106" s="9" t="n">
+        <v>1.647</v>
+      </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="14" t="inlineStr"/>
     </row>
@@ -5274,39 +5281,39 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>8524</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>TALIWRK</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D107" s="9" t="n">
-        <v>0.26</v>
+        <v>0.37</v>
       </c>
       <c r="E107" s="10" t="n">
-        <v>-0.0189</v>
+        <v>0</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>1093800</v>
+        <v>1532400</v>
       </c>
       <c r="G107" s="12" t="n">
         <v>0.35</v>
       </c>
       <c r="H107" t="n">
-        <v>51.19</v>
-      </c>
-      <c r="I107" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.29</v>
+      </c>
+      <c r="I107" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J107" s="9" t="n">
-        <v>0.254</v>
+        <v>0.377</v>
       </c>
       <c r="K107" s="9" t="n">
-        <v>0.271</v>
+        <v>0.391</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="14" t="inlineStr"/>
@@ -5319,39 +5326,39 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>1589</t>
+          <t>0268</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>IWCITY</t>
+          <t>L&amp;PBHD</t>
         </is>
       </c>
       <c r="D108" s="9" t="n">
-        <v>0.215</v>
-      </c>
-      <c r="E108" s="16" t="n">
-        <v>0.0238</v>
+        <v>0.21</v>
+      </c>
+      <c r="E108" s="15" t="n">
+        <v>0.0244</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>1065000</v>
+        <v>1528600</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>2.18</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H108" t="n">
-        <v>48.08</v>
-      </c>
-      <c r="I108" s="17" t="inlineStr">
+        <v>71.81999999999999</v>
+      </c>
+      <c r="I108" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J108" s="9" t="n">
-        <v>0.215</v>
+        <v>0.187</v>
       </c>
       <c r="K108" s="9" t="n">
-        <v>0.225</v>
+        <v>0.156</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="14" t="inlineStr"/>
@@ -5364,33 +5371,40 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>0471</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>PIONEER</t>
+          <t>TENAGA</t>
         </is>
       </c>
       <c r="D109" s="9" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="E109" s="16" t="n">
-        <v>0.0175</v>
+        <v>13.2</v>
+      </c>
+      <c r="E109" s="15" t="n">
+        <v>0.0046</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>1063500</v>
+        <v>1500500</v>
       </c>
       <c r="G109" s="12" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="I109" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J109" s="9" t="n"/>
-      <c r="K109" s="9" t="n"/>
+        <v>0.15</v>
+      </c>
+      <c r="H109" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="I109" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J109" s="9" t="n">
+        <v>13.47</v>
+      </c>
+      <c r="K109" s="9" t="n">
+        <v>14.059</v>
+      </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="14" t="inlineStr"/>
     </row>
@@ -5402,39 +5416,39 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>0172</t>
+          <t>0223</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>OCK</t>
+          <t>SAMAIDEN</t>
         </is>
       </c>
       <c r="D110" s="9" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="E110" s="10" t="n">
-        <v>-0.0204</v>
+        <v>2.9</v>
+      </c>
+      <c r="E110" s="15" t="n">
+        <v>0.014</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>1059900</v>
+        <v>1491100</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>0.32</v>
+        <v>0.6</v>
       </c>
       <c r="H110" t="n">
-        <v>68.65000000000001</v>
-      </c>
-      <c r="I110" s="17" t="inlineStr">
+        <v>89.56999999999999</v>
+      </c>
+      <c r="I110" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J110" s="9" t="n">
-        <v>0.446</v>
+        <v>2.188</v>
       </c>
       <c r="K110" s="9" t="n">
-        <v>0.404</v>
+        <v>1.769</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="14" t="inlineStr"/>
@@ -5447,40 +5461,33 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>0450</t>
+          <t>0468</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>MFGROUP</t>
+          <t>UNIPAC</t>
         </is>
       </c>
       <c r="D111" s="9" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E111" s="15" t="n">
-        <v>0</v>
+        <v>0.245</v>
+      </c>
+      <c r="E111" s="17" t="n">
+        <v>-0.0392</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>1052600</v>
+        <v>1480600</v>
       </c>
       <c r="G111" s="12" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="H111" t="n">
-        <v>45.51</v>
+        <v>0.09</v>
       </c>
       <c r="I111" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J111" s="9" t="n">
-        <v>0.261</v>
-      </c>
-      <c r="K111" s="9" t="n">
-        <v>0.266</v>
-      </c>
+      <c r="J111" s="9" t="n"/>
+      <c r="K111" s="9" t="n"/>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="14" t="inlineStr"/>
     </row>
@@ -5492,28 +5499,28 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D112" s="9" t="n">
-        <v>0.345</v>
+        <v>4.8</v>
       </c>
       <c r="E112" s="10" t="n">
-        <v>-0.0143</v>
+        <v>0</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>1031200</v>
+        <v>1476100</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>0.15</v>
+        <v>0.08</v>
       </c>
       <c r="H112" t="n">
-        <v>43.18</v>
+        <v>40.81</v>
       </c>
       <c r="I112" s="13" t="inlineStr">
         <is>
@@ -5521,10 +5528,10 @@
         </is>
       </c>
       <c r="J112" s="9" t="n">
-        <v>0.352</v>
+        <v>4.846</v>
       </c>
       <c r="K112" s="9" t="n">
-        <v>0.35</v>
+        <v>4.96</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="14" t="inlineStr"/>
@@ -5537,39 +5544,39 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>0045</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>TENAGA</t>
+          <t>SSB8</t>
         </is>
       </c>
       <c r="D113" s="9" t="n">
-        <v>13.22</v>
-      </c>
-      <c r="E113" s="16" t="n">
-        <v>0.0061</v>
+        <v>0.645</v>
+      </c>
+      <c r="E113" s="17" t="n">
+        <v>-0.0227</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>999000</v>
+        <v>1435200</v>
       </c>
       <c r="G113" s="12" t="n">
-        <v>0.1</v>
+        <v>0.38</v>
       </c>
       <c r="H113" t="n">
-        <v>34.32</v>
-      </c>
-      <c r="I113" s="17" t="inlineStr">
+        <v>59.13</v>
+      </c>
+      <c r="I113" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J113" s="9" t="n">
-        <v>13.472</v>
+        <v>0.619</v>
       </c>
       <c r="K113" s="9" t="n">
-        <v>14.06</v>
+        <v>0.581</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="14" t="inlineStr"/>
@@ -5582,39 +5589,39 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>5323</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>JPG</t>
         </is>
       </c>
       <c r="D114" s="9" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="E114" s="16" t="n">
-        <v>0.0091</v>
+        <v>1.79</v>
+      </c>
+      <c r="E114" s="17" t="n">
+        <v>-0.005600000000000001</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>990300</v>
+        <v>1435200</v>
       </c>
       <c r="G114" s="12" t="n">
-        <v>0.08</v>
+        <v>0.2</v>
       </c>
       <c r="H114" t="n">
-        <v>80.17</v>
-      </c>
-      <c r="I114" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.72</v>
+      </c>
+      <c r="I114" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J114" s="9" t="n">
-        <v>1.007</v>
+        <v>1.901</v>
       </c>
       <c r="K114" s="9" t="n">
-        <v>0.845</v>
+        <v>1.966</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="14" t="inlineStr"/>
@@ -5627,39 +5634,39 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>0128</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>FRONTKN</t>
         </is>
       </c>
       <c r="D115" s="9" t="n">
-        <v>4.39</v>
-      </c>
-      <c r="E115" s="10" t="n">
-        <v>-0.0223</v>
+        <v>4.96</v>
+      </c>
+      <c r="E115" s="17" t="n">
+        <v>-0.0178</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>970500</v>
+        <v>1386900</v>
       </c>
       <c r="G115" s="12" t="n">
-        <v>0.13</v>
+        <v>0.25</v>
       </c>
       <c r="H115" t="n">
-        <v>44.19</v>
-      </c>
-      <c r="I115" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.52</v>
+      </c>
+      <c r="I115" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J115" s="9" t="n">
-        <v>4.579</v>
+        <v>4.98</v>
       </c>
       <c r="K115" s="9" t="n">
-        <v>4.537</v>
+        <v>5.04</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="14" t="inlineStr"/>
@@ -5672,39 +5679,39 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>5073</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>NAIM</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D116" s="9" t="n">
         <v>0.65</v>
       </c>
       <c r="E116" s="10" t="n">
-        <v>-0.0455</v>
+        <v>0</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>938400</v>
+        <v>1385100</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>0.76</v>
+        <v>0.41</v>
       </c>
       <c r="H116" t="n">
-        <v>59.12</v>
-      </c>
-      <c r="I116" s="17" t="inlineStr">
+        <v>70.55</v>
+      </c>
+      <c r="I116" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J116" s="9" t="n">
-        <v>0.629</v>
+        <v>0.634</v>
       </c>
       <c r="K116" s="9" t="n">
-        <v>0.612</v>
+        <v>0.591</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="14" t="inlineStr"/>
@@ -5717,39 +5724,39 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D117" s="9" t="n">
-        <v>4.78</v>
-      </c>
-      <c r="E117" s="10" t="n">
-        <v>-0.0042</v>
+        <v>0.425</v>
+      </c>
+      <c r="E117" s="17" t="n">
+        <v>-0.0449</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>918400</v>
+        <v>1325500</v>
       </c>
       <c r="G117" s="12" t="n">
-        <v>0.05</v>
+        <v>0.41</v>
       </c>
       <c r="H117" t="n">
-        <v>38.75</v>
-      </c>
-      <c r="I117" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>45.13</v>
+      </c>
+      <c r="I117" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J117" s="9" t="n">
-        <v>4.844</v>
+        <v>0.439</v>
       </c>
       <c r="K117" s="9" t="n">
-        <v>4.96</v>
+        <v>0.432</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="14" t="inlineStr"/>
@@ -5762,39 +5769,39 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>7161</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>KERJAYA</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="D118" s="9" t="n">
-        <v>3.59</v>
-      </c>
-      <c r="E118" s="10" t="n">
-        <v>-0.011</v>
+        <v>0.345</v>
+      </c>
+      <c r="E118" s="17" t="n">
+        <v>-0.0143</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>853900</v>
+        <v>1313500</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>0.27</v>
+        <v>0.19</v>
       </c>
       <c r="H118" t="n">
-        <v>73</v>
-      </c>
-      <c r="I118" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.18</v>
+      </c>
+      <c r="I118" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J118" s="9" t="n">
-        <v>3.31</v>
+        <v>0.352</v>
       </c>
       <c r="K118" s="9" t="n">
-        <v>2.884</v>
+        <v>0.35</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="14" t="inlineStr"/>
@@ -5807,39 +5814,39 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>7161</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>KERJAYA</t>
         </is>
       </c>
       <c r="D119" s="9" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="E119" s="15" t="n">
-        <v>0</v>
+        <v>3.6</v>
+      </c>
+      <c r="E119" s="17" t="n">
+        <v>-0.0083</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>820300</v>
+        <v>1312400</v>
       </c>
       <c r="G119" s="12" t="n">
-        <v>0.11</v>
+        <v>0.41</v>
       </c>
       <c r="H119" t="n">
-        <v>52.41</v>
-      </c>
-      <c r="I119" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>73.84</v>
+      </c>
+      <c r="I119" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J119" s="9" t="n">
-        <v>2.224</v>
+        <v>3.311</v>
       </c>
       <c r="K119" s="9" t="n">
-        <v>2.104</v>
+        <v>2.885</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="14" t="inlineStr"/>
@@ -5852,39 +5859,39 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>7225</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="D120" s="9" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="E120" s="15" t="n">
-        <v>0</v>
+        <v>0.215</v>
+      </c>
+      <c r="E120" s="17" t="n">
+        <v>-0.0227</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>817000</v>
+        <v>1297500</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>0.43</v>
+        <v>0.22</v>
       </c>
       <c r="H120" t="n">
-        <v>43.55</v>
-      </c>
-      <c r="I120" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51</v>
+      </c>
+      <c r="I120" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J120" s="9" t="n">
-        <v>0.996</v>
+        <v>0.214</v>
       </c>
       <c r="K120" s="9" t="n">
-        <v>1.012</v>
+        <v>0.212</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="14" t="inlineStr"/>
@@ -5897,39 +5904,39 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>5005</t>
+          <t>0172</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>UNISEM</t>
+          <t>OCK</t>
         </is>
       </c>
       <c r="D121" s="9" t="n">
-        <v>4.54</v>
-      </c>
-      <c r="E121" s="10" t="n">
-        <v>-0.008699999999999999</v>
+        <v>0.48</v>
+      </c>
+      <c r="E121" s="17" t="n">
+        <v>-0.0204</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>806000</v>
+        <v>1292800</v>
       </c>
       <c r="G121" s="12" t="n">
-        <v>0.35</v>
+        <v>0.39</v>
       </c>
       <c r="H121" t="n">
-        <v>55.25</v>
-      </c>
-      <c r="I121" s="17" t="inlineStr">
+        <v>68.65000000000001</v>
+      </c>
+      <c r="I121" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J121" s="9" t="n">
-        <v>4.414</v>
+        <v>0.446</v>
       </c>
       <c r="K121" s="9" t="n">
-        <v>4.431</v>
+        <v>0.404</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="14" t="inlineStr"/>
@@ -5942,39 +5949,39 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D122" s="9" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="E122" s="16" t="n">
-        <v>0.0035</v>
+        <v>1.96</v>
+      </c>
+      <c r="E122" s="15" t="n">
+        <v>0.0051</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>799400</v>
+        <v>1284800</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>0.32</v>
+        <v>0.18</v>
       </c>
       <c r="H122" t="n">
-        <v>89.28</v>
-      </c>
-      <c r="I122" s="17" t="inlineStr">
+        <v>46.89</v>
+      </c>
+      <c r="I122" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J122" s="9" t="n">
-        <v>2.185</v>
+        <v>1.984</v>
       </c>
       <c r="K122" s="9" t="n">
-        <v>1.768</v>
+        <v>1.974</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="14" t="inlineStr"/>
@@ -5987,39 +5994,39 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>4383</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>JTIASA</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D123" s="9" t="n">
-        <v>0.965</v>
-      </c>
-      <c r="E123" s="16" t="n">
-        <v>0.0052</v>
+        <v>0.315</v>
+      </c>
+      <c r="E123" s="17" t="n">
+        <v>-0.0156</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>788400</v>
+        <v>1253200</v>
       </c>
       <c r="G123" s="12" t="n">
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
       <c r="H123" t="n">
-        <v>37.8</v>
-      </c>
-      <c r="I123" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>44.97</v>
+      </c>
+      <c r="I123" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J123" s="9" t="n">
-        <v>0.999</v>
+        <v>0.321</v>
       </c>
       <c r="K123" s="9" t="n">
-        <v>1.047</v>
+        <v>0.339</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" s="14" t="inlineStr"/>
@@ -6032,39 +6039,39 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>3379</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>ATECH</t>
+          <t>INSAS</t>
         </is>
       </c>
       <c r="D124" s="9" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="E124" s="16" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.9</v>
+      </c>
+      <c r="E124" s="15" t="n">
+        <v>0.0169</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>764300</v>
+        <v>1246800</v>
       </c>
       <c r="G124" s="12" t="n">
-        <v>0.52</v>
+        <v>2.15</v>
       </c>
       <c r="H124" t="n">
-        <v>52.54</v>
-      </c>
-      <c r="I124" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.79</v>
+      </c>
+      <c r="I124" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J124" s="9" t="n">
-        <v>0.765</v>
+        <v>0.895</v>
       </c>
       <c r="K124" s="9" t="n">
-        <v>0.755</v>
+        <v>0.9</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="14" t="inlineStr"/>
@@ -6077,39 +6084,39 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D125" s="9" t="n">
-        <v>7.93</v>
-      </c>
-      <c r="E125" s="16" t="n">
-        <v>0.0038</v>
+        <v>7.48</v>
+      </c>
+      <c r="E125" s="15" t="n">
+        <v>0.0027</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>755900</v>
+        <v>1207600</v>
       </c>
       <c r="G125" s="12" t="n">
-        <v>0.06</v>
+        <v>0.16</v>
       </c>
       <c r="H125" t="n">
-        <v>59.27</v>
-      </c>
-      <c r="I125" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.06</v>
+      </c>
+      <c r="I125" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J125" s="9" t="n">
-        <v>7.8</v>
+        <v>7.686</v>
       </c>
       <c r="K125" s="9" t="n">
-        <v>7.73</v>
+        <v>7.843</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="14" t="inlineStr"/>
@@ -6122,39 +6129,39 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>0233</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>PEKAT</t>
+          <t>ALPHA</t>
         </is>
       </c>
       <c r="D126" s="9" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="E126" s="16" t="n">
-        <v>0.0071</v>
+        <v>0.255</v>
+      </c>
+      <c r="E126" s="15" t="n">
+        <v>0.0408</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>755300</v>
+        <v>1198300</v>
       </c>
       <c r="G126" s="12" t="n">
-        <v>0.35</v>
+        <v>0.58</v>
       </c>
       <c r="H126" t="n">
-        <v>89.09</v>
-      </c>
-      <c r="I126" s="17" t="inlineStr">
+        <v>53.99</v>
+      </c>
+      <c r="I126" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J126" s="9" t="n">
-        <v>2.249</v>
+        <v>0.248</v>
       </c>
       <c r="K126" s="9" t="n">
-        <v>1.951</v>
+        <v>0.261</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="14" t="inlineStr"/>
@@ -6167,39 +6174,39 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>0307</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>KENERGY</t>
         </is>
       </c>
       <c r="D127" s="9" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="E127" s="10" t="n">
-        <v>-0.0367</v>
+        <v>0.355</v>
+      </c>
+      <c r="E127" s="17" t="n">
+        <v>-0.0274</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>740700</v>
+        <v>1194800</v>
       </c>
       <c r="G127" s="12" t="n">
-        <v>0.29</v>
+        <v>2.25</v>
       </c>
       <c r="H127" t="n">
-        <v>39.35</v>
-      </c>
-      <c r="I127" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.74</v>
+      </c>
+      <c r="I127" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J127" s="9" t="n">
-        <v>1.098</v>
+        <v>0.383</v>
       </c>
       <c r="K127" s="9" t="n">
-        <v>1.119</v>
+        <v>0.385</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="14" t="inlineStr"/>
@@ -6212,39 +6219,39 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>5005</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>UNISEM</t>
         </is>
       </c>
       <c r="D128" s="9" t="n">
-        <v>0.725</v>
-      </c>
-      <c r="E128" s="15" t="n">
-        <v>0</v>
+        <v>4.46</v>
+      </c>
+      <c r="E128" s="17" t="n">
+        <v>-0.0262</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>734500</v>
+        <v>1182700</v>
       </c>
       <c r="G128" s="12" t="n">
-        <v>0.12</v>
+        <v>0.51</v>
       </c>
       <c r="H128" t="n">
-        <v>69.25</v>
-      </c>
-      <c r="I128" s="17" t="inlineStr">
+        <v>52.25</v>
+      </c>
+      <c r="I128" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J128" s="9" t="n">
-        <v>0.672</v>
+        <v>4.407</v>
       </c>
       <c r="K128" s="9" t="n">
-        <v>0.615</v>
+        <v>4.429</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="14" t="inlineStr"/>
@@ -6257,40 +6264,33 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>0471</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>PIONEER</t>
         </is>
       </c>
       <c r="D129" s="9" t="n">
-        <v>0.77</v>
+        <v>0.285</v>
       </c>
       <c r="E129" s="10" t="n">
-        <v>-0.0128</v>
+        <v>0</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>732200</v>
+        <v>1164200</v>
       </c>
       <c r="G129" s="12" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="H129" t="n">
-        <v>54.35</v>
-      </c>
-      <c r="I129" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J129" s="9" t="n">
-        <v>0.756</v>
-      </c>
-      <c r="K129" s="9" t="n">
-        <v>0.74</v>
-      </c>
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I129" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J129" s="9" t="n"/>
+      <c r="K129" s="9" t="n"/>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="14" t="inlineStr"/>
     </row>
@@ -6302,39 +6302,39 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>SKYECHIP</t>
         </is>
       </c>
       <c r="D130" s="9" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="E130" s="16" t="n">
-        <v>0.0242</v>
+        <v>2.96</v>
+      </c>
+      <c r="E130" s="17" t="n">
+        <v>-0.0166</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>715200</v>
+        <v>1156900</v>
       </c>
       <c r="G130" s="12" t="n">
-        <v>0.27</v>
+        <v>0.37</v>
       </c>
       <c r="H130" t="n">
-        <v>84.34</v>
-      </c>
-      <c r="I130" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.05</v>
+      </c>
+      <c r="I130" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J130" s="9" t="n">
-        <v>1.046</v>
+        <v>3.008</v>
       </c>
       <c r="K130" s="9" t="n">
-        <v>0.888</v>
+        <v>3.04</v>
       </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" s="14" t="inlineStr"/>
@@ -6347,28 +6347,28 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D131" s="9" t="n">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="E131" s="10" t="n">
-        <v>-0.0196</v>
+        <v>0</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>705700</v>
+        <v>1155700</v>
       </c>
       <c r="G131" s="12" t="n">
-        <v>0.15</v>
+        <v>0.61</v>
       </c>
       <c r="H131" t="n">
-        <v>34.67</v>
+        <v>43.55</v>
       </c>
       <c r="I131" s="13" t="inlineStr">
         <is>
@@ -6376,10 +6376,10 @@
         </is>
       </c>
       <c r="J131" s="9" t="n">
-        <v>1.049</v>
+        <v>0.996</v>
       </c>
       <c r="K131" s="9" t="n">
-        <v>1.074</v>
+        <v>1.012</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="14" t="inlineStr"/>
@@ -6392,39 +6392,39 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>0271</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>WELLS</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D132" s="9" t="n">
-        <v>0.63</v>
+        <v>7.95</v>
       </c>
       <c r="E132" s="15" t="n">
-        <v>0</v>
+        <v>0.0063</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>700000</v>
+        <v>1153800</v>
       </c>
       <c r="G132" s="12" t="n">
-        <v>0.72</v>
+        <v>0.09</v>
       </c>
       <c r="H132" t="n">
-        <v>48.02</v>
-      </c>
-      <c r="I132" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.18</v>
+      </c>
+      <c r="I132" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J132" s="9" t="n">
-        <v>0.631</v>
+        <v>7.802</v>
       </c>
       <c r="K132" s="9" t="n">
-        <v>0.637</v>
+        <v>7.73</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="14" t="inlineStr"/>
@@ -6437,39 +6437,39 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>5162</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>VSTECS</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D133" s="9" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="E133" s="16" t="n">
-        <v>0.0242</v>
+        <v>0.58</v>
+      </c>
+      <c r="E133" s="17" t="n">
+        <v>-0.0252</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>679600</v>
+        <v>1127700</v>
       </c>
       <c r="G133" s="12" t="n">
-        <v>0.46</v>
+        <v>0.35</v>
       </c>
       <c r="H133" t="n">
-        <v>54.81</v>
-      </c>
-      <c r="I133" s="17" t="inlineStr">
+        <v>52.94</v>
+      </c>
+      <c r="I133" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J133" s="9" t="n">
-        <v>1.64</v>
+        <v>0.57</v>
       </c>
       <c r="K133" s="9" t="n">
-        <v>1.693</v>
+        <v>0.575</v>
       </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" s="14" t="inlineStr"/>
@@ -6482,39 +6482,39 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>7160</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>PENTA</t>
         </is>
       </c>
       <c r="D134" s="9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="E134" s="16" t="n">
-        <v>0.007800000000000001</v>
+        <v>5.2</v>
+      </c>
+      <c r="E134" s="17" t="n">
+        <v>-0.0207</v>
       </c>
       <c r="F134" s="11" t="n">
-        <v>679200</v>
+        <v>1117700</v>
       </c>
       <c r="G134" s="12" t="n">
-        <v>0.17</v>
+        <v>0.46</v>
       </c>
       <c r="H134" t="n">
-        <v>59.48</v>
-      </c>
-      <c r="I134" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.73</v>
+      </c>
+      <c r="I134" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J134" s="9" t="n">
-        <v>1.242</v>
+        <v>5.279</v>
       </c>
       <c r="K134" s="9" t="n">
-        <v>1.139</v>
+        <v>5.275</v>
       </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" s="14" t="inlineStr"/>
@@ -6527,39 +6527,39 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D135" s="9" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="E135" s="10" t="n">
-        <v>-0.025</v>
+        <v>4.4</v>
+      </c>
+      <c r="E135" s="17" t="n">
+        <v>-0.02</v>
       </c>
       <c r="F135" s="11" t="n">
-        <v>676100</v>
+        <v>1094700</v>
       </c>
       <c r="G135" s="12" t="n">
-        <v>0.19</v>
+        <v>0.14</v>
       </c>
       <c r="H135" t="n">
-        <v>64.58</v>
-      </c>
-      <c r="I135" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.46</v>
+      </c>
+      <c r="I135" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J135" s="9" t="n">
-        <v>1.107</v>
+        <v>4.58</v>
       </c>
       <c r="K135" s="9" t="n">
-        <v>1.007</v>
+        <v>4.537</v>
       </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" s="14" t="inlineStr"/>
@@ -6572,39 +6572,39 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>JPG</t>
+          <t>KPJ</t>
         </is>
       </c>
       <c r="D136" s="9" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="E136" s="16" t="n">
-        <v>0.005600000000000001</v>
+        <v>2.63</v>
+      </c>
+      <c r="E136" s="17" t="n">
+        <v>-0.015</v>
       </c>
       <c r="F136" s="11" t="n">
-        <v>649600</v>
+        <v>1094100</v>
       </c>
       <c r="G136" s="12" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="H136" t="n">
-        <v>37.04</v>
-      </c>
-      <c r="I136" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>41.54</v>
+      </c>
+      <c r="I136" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J136" s="9" t="n">
-        <v>1.903</v>
+        <v>2.674</v>
       </c>
       <c r="K136" s="9" t="n">
-        <v>1.966</v>
+        <v>2.872</v>
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" s="14" t="inlineStr"/>
@@ -6617,39 +6617,39 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>8524</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>KPJ</t>
+          <t>TALIWRK</t>
         </is>
       </c>
       <c r="D137" s="9" t="n">
-        <v>2.63</v>
+        <v>0.265</v>
       </c>
       <c r="E137" s="10" t="n">
-        <v>-0.015</v>
+        <v>0</v>
       </c>
       <c r="F137" s="11" t="n">
-        <v>644200</v>
+        <v>1093900</v>
       </c>
       <c r="G137" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.35</v>
       </c>
       <c r="H137" t="n">
-        <v>41.54</v>
-      </c>
-      <c r="I137" s="17" t="inlineStr">
+        <v>54.09</v>
+      </c>
+      <c r="I137" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J137" s="9" t="n">
-        <v>2.674</v>
+        <v>0.254</v>
       </c>
       <c r="K137" s="9" t="n">
-        <v>2.872</v>
+        <v>0.271</v>
       </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" s="14" t="inlineStr"/>
@@ -6662,39 +6662,39 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D138" s="9" t="n">
-        <v>7.83</v>
-      </c>
-      <c r="E138" s="16" t="n">
-        <v>0.0051</v>
+        <v>0.78</v>
+      </c>
+      <c r="E138" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F138" s="11" t="n">
-        <v>635300</v>
+        <v>1085900</v>
       </c>
       <c r="G138" s="12" t="n">
-        <v>0.06</v>
+        <v>0.39</v>
       </c>
       <c r="H138" t="n">
-        <v>36.58</v>
-      </c>
-      <c r="I138" s="17" t="inlineStr">
+        <v>57.08</v>
+      </c>
+      <c r="I138" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J138" s="9" t="n">
-        <v>7.975</v>
+        <v>0.757</v>
       </c>
       <c r="K138" s="9" t="n">
-        <v>8.260999999999999</v>
+        <v>0.74</v>
       </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" s="14" t="inlineStr"/>
@@ -6707,39 +6707,39 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D139" s="9" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="E139" s="10" t="n">
-        <v>-0.0059</v>
+        <v>5.62</v>
+      </c>
+      <c r="E139" s="17" t="n">
+        <v>-0.031</v>
       </c>
       <c r="F139" s="11" t="n">
-        <v>635100</v>
+        <v>1062900</v>
       </c>
       <c r="G139" s="12" t="n">
-        <v>0.21</v>
+        <v>0.34</v>
       </c>
       <c r="H139" t="n">
-        <v>64.11</v>
-      </c>
-      <c r="I139" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.53</v>
+      </c>
+      <c r="I139" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J139" s="9" t="n">
-        <v>0.801</v>
+        <v>5.794</v>
       </c>
       <c r="K139" s="9" t="n">
-        <v>0.72</v>
+        <v>5.752</v>
       </c>
       <c r="L139" t="inlineStr"/>
       <c r="M139" s="14" t="inlineStr"/>
@@ -6752,39 +6752,39 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>0391</t>
+          <t>0395</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>AMBEST</t>
+          <t>OGX</t>
         </is>
       </c>
       <c r="D140" s="9" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="E140" s="10" t="n">
-        <v>-0.0143</v>
+        <v>0.43</v>
+      </c>
+      <c r="E140" s="17" t="n">
+        <v>-0.0227</v>
       </c>
       <c r="F140" s="11" t="n">
-        <v>629600</v>
+        <v>1055100</v>
       </c>
       <c r="G140" s="12" t="n">
-        <v>0.2</v>
+        <v>0.34</v>
       </c>
       <c r="H140" t="n">
-        <v>58.09</v>
-      </c>
-      <c r="I140" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.37</v>
+      </c>
+      <c r="I140" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J140" s="9" t="n">
-        <v>1.345</v>
+        <v>0.434</v>
       </c>
       <c r="K140" s="9" t="n">
-        <v>1.148</v>
+        <v>0.452</v>
       </c>
       <c r="L140" t="inlineStr"/>
       <c r="M140" s="14" t="inlineStr"/>
@@ -6797,39 +6797,39 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>0450</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>MFGROUP</t>
         </is>
       </c>
       <c r="D141" s="9" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="E141" s="15" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="E141" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F141" s="11" t="n">
-        <v>626600</v>
+        <v>1052600</v>
       </c>
       <c r="G141" s="12" t="n">
-        <v>0.09</v>
+        <v>1.33</v>
       </c>
       <c r="H141" t="n">
-        <v>45.43</v>
-      </c>
-      <c r="I141" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.51</v>
+      </c>
+      <c r="I141" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J141" s="9" t="n">
-        <v>1.983</v>
+        <v>0.261</v>
       </c>
       <c r="K141" s="9" t="n">
-        <v>1.974</v>
+        <v>0.266</v>
       </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" s="14" t="inlineStr"/>
@@ -6842,39 +6842,39 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>0326</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>SORENTO</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D142" s="9" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="E142" s="10" t="n">
-        <v>-0.0074</v>
+        <v>2.24</v>
+      </c>
+      <c r="E142" s="15" t="n">
+        <v>0.004500000000000001</v>
       </c>
       <c r="F142" s="11" t="n">
-        <v>617700</v>
+        <v>1034700</v>
       </c>
       <c r="G142" s="12" t="n">
-        <v>1.48</v>
+        <v>0.14</v>
       </c>
       <c r="H142" t="n">
-        <v>57.6</v>
-      </c>
-      <c r="I142" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.1</v>
+      </c>
+      <c r="I142" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J142" s="9" t="n">
-        <v>0.655</v>
+        <v>2.225</v>
       </c>
       <c r="K142" s="9" t="n">
-        <v>0.647</v>
+        <v>2.104</v>
       </c>
       <c r="L142" t="inlineStr"/>
       <c r="M142" s="14" t="inlineStr"/>
@@ -6887,39 +6887,39 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>0128</t>
+          <t>5073</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>FRONTKN</t>
+          <t>NAIM</t>
         </is>
       </c>
       <c r="D143" s="9" t="n">
-        <v>4.96</v>
-      </c>
-      <c r="E143" s="10" t="n">
-        <v>-0.0178</v>
+        <v>0.65</v>
+      </c>
+      <c r="E143" s="17" t="n">
+        <v>-0.0455</v>
       </c>
       <c r="F143" s="11" t="n">
-        <v>613300</v>
+        <v>1030800</v>
       </c>
       <c r="G143" s="12" t="n">
-        <v>0.11</v>
+        <v>0.83</v>
       </c>
       <c r="H143" t="n">
-        <v>48.52</v>
-      </c>
-      <c r="I143" s="17" t="inlineStr">
+        <v>59.12</v>
+      </c>
+      <c r="I143" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J143" s="9" t="n">
-        <v>4.98</v>
+        <v>0.629</v>
       </c>
       <c r="K143" s="9" t="n">
-        <v>5.04</v>
+        <v>0.612</v>
       </c>
       <c r="L143" t="inlineStr"/>
       <c r="M143" s="14" t="inlineStr"/>
@@ -6932,39 +6932,39 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>0267</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>IHH</t>
+          <t>ECA</t>
         </is>
       </c>
       <c r="D144" s="9" t="n">
-        <v>8.029999999999999</v>
-      </c>
-      <c r="E144" s="15" t="n">
-        <v>0</v>
+        <v>0.365</v>
+      </c>
+      <c r="E144" s="17" t="n">
+        <v>-0.0267</v>
       </c>
       <c r="F144" s="11" t="n">
-        <v>600300</v>
+        <v>1016700</v>
       </c>
       <c r="G144" s="12" t="n">
-        <v>0.15</v>
+        <v>0.3</v>
       </c>
       <c r="H144" t="n">
-        <v>52.14</v>
-      </c>
-      <c r="I144" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.31</v>
+      </c>
+      <c r="I144" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J144" s="9" t="n">
-        <v>7.951</v>
+        <v>0.394</v>
       </c>
       <c r="K144" s="9" t="n">
-        <v>8.151999999999999</v>
+        <v>0.372</v>
       </c>
       <c r="L144" t="inlineStr"/>
       <c r="M144" s="14" t="inlineStr"/>
@@ -6977,39 +6977,39 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>7160</t>
+          <t>0240</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>PENTA</t>
+          <t>CORAZA</t>
         </is>
       </c>
       <c r="D145" s="9" t="n">
-        <v>5.24</v>
-      </c>
-      <c r="E145" s="10" t="n">
-        <v>-0.0132</v>
+        <v>1.05</v>
+      </c>
+      <c r="E145" s="17" t="n">
+        <v>-0.0367</v>
       </c>
       <c r="F145" s="11" t="n">
-        <v>592600</v>
+        <v>956800</v>
       </c>
       <c r="G145" s="12" t="n">
-        <v>0.25</v>
+        <v>0.38</v>
       </c>
       <c r="H145" t="n">
-        <v>48.96</v>
-      </c>
-      <c r="I145" s="17" t="inlineStr">
+        <v>39.35</v>
+      </c>
+      <c r="I145" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J145" s="9" t="n">
-        <v>5.282</v>
+        <v>1.098</v>
       </c>
       <c r="K145" s="9" t="n">
-        <v>5.276</v>
+        <v>1.119</v>
       </c>
       <c r="L145" t="inlineStr"/>
       <c r="M145" s="14" t="inlineStr"/>
@@ -7022,39 +7022,39 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>0372</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>CHEEDING</t>
         </is>
       </c>
       <c r="D146" s="9" t="n">
-        <v>5.71</v>
-      </c>
-      <c r="E146" s="10" t="n">
-        <v>-0.0155</v>
+        <v>0.595</v>
+      </c>
+      <c r="E146" s="17" t="n">
+        <v>-0.0083</v>
       </c>
       <c r="F146" s="11" t="n">
-        <v>570500</v>
+        <v>954000</v>
       </c>
       <c r="G146" s="12" t="n">
-        <v>0.18</v>
+        <v>0.36</v>
       </c>
       <c r="H146" t="n">
-        <v>47.82</v>
-      </c>
-      <c r="I146" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.07</v>
+      </c>
+      <c r="I146" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J146" s="9" t="n">
-        <v>5.803</v>
+        <v>0.593</v>
       </c>
       <c r="K146" s="9" t="n">
-        <v>5.754</v>
+        <v>0.61</v>
       </c>
       <c r="L146" t="inlineStr"/>
       <c r="M146" s="14" t="inlineStr"/>
@@ -7067,39 +7067,39 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>DUFU</t>
         </is>
       </c>
       <c r="D147" s="9" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="E147" s="10" t="n">
-        <v>-0.01</v>
+        <v>2.85</v>
+      </c>
+      <c r="E147" s="17" t="n">
+        <v>-0.024</v>
       </c>
       <c r="F147" s="11" t="n">
-        <v>558000</v>
+        <v>947800</v>
       </c>
       <c r="G147" s="12" t="n">
-        <v>0.18</v>
+        <v>0.32</v>
       </c>
       <c r="H147" t="n">
-        <v>46.71</v>
-      </c>
-      <c r="I147" s="17" t="inlineStr">
+        <v>55.28</v>
+      </c>
+      <c r="I147" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J147" s="9" t="n">
-        <v>3.01</v>
+        <v>2.787</v>
       </c>
       <c r="K147" s="9" t="n">
-        <v>3.041</v>
+        <v>2.685</v>
       </c>
       <c r="L147" t="inlineStr"/>
       <c r="M147" s="14" t="inlineStr"/>
@@ -7112,39 +7112,39 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>5271</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>PECCA</t>
+          <t>IHH</t>
         </is>
       </c>
       <c r="D148" s="9" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="E148" s="15" t="n">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="E148" s="17" t="n">
+        <v>-0.0037</v>
       </c>
       <c r="F148" s="11" t="n">
-        <v>538700</v>
+        <v>947000</v>
       </c>
       <c r="G148" s="12" t="n">
-        <v>0.28</v>
+        <v>0.23</v>
       </c>
       <c r="H148" t="n">
-        <v>68.31</v>
-      </c>
-      <c r="I148" s="17" t="inlineStr">
+        <v>50.63</v>
+      </c>
+      <c r="I148" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J148" s="9" t="n">
-        <v>1.355</v>
+        <v>7.949</v>
       </c>
       <c r="K148" s="9" t="n">
-        <v>1.325</v>
+        <v>8.151</v>
       </c>
       <c r="L148" t="inlineStr"/>
       <c r="M148" s="14" t="inlineStr"/>
@@ -7157,39 +7157,39 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>0056</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>NCT</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D149" s="9" t="n">
-        <v>0.5649999999999999</v>
-      </c>
-      <c r="E149" s="16" t="n">
-        <v>0.0089</v>
+        <v>0.84</v>
+      </c>
+      <c r="E149" s="17" t="n">
+        <v>-0.0059</v>
       </c>
       <c r="F149" s="11" t="n">
-        <v>535500</v>
+        <v>925100</v>
       </c>
       <c r="G149" s="12" t="n">
-        <v>0.22</v>
+        <v>0.31</v>
       </c>
       <c r="H149" t="n">
-        <v>51.06</v>
-      </c>
-      <c r="I149" s="17" t="inlineStr">
+        <v>64.11</v>
+      </c>
+      <c r="I149" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J149" s="9" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.801</v>
       </c>
       <c r="K149" s="9" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.72</v>
       </c>
       <c r="L149" t="inlineStr"/>
       <c r="M149" s="14" t="inlineStr"/>
@@ -7202,28 +7202,28 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>7197</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>GESHEN</t>
+          <t>SPSETIA</t>
         </is>
       </c>
       <c r="D150" s="9" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="E150" s="16" t="n">
-        <v>0.023</v>
+        <v>0.765</v>
+      </c>
+      <c r="E150" s="17" t="n">
+        <v>-0.0192</v>
       </c>
       <c r="F150" s="11" t="n">
-        <v>529300</v>
+        <v>918800</v>
       </c>
       <c r="G150" s="12" t="n">
-        <v>1.4</v>
+        <v>0.22</v>
       </c>
       <c r="H150" t="n">
-        <v>30.61</v>
+        <v>37.15</v>
       </c>
       <c r="I150" s="13" t="inlineStr">
         <is>
@@ -7231,10 +7231,10 @@
         </is>
       </c>
       <c r="J150" s="9" t="n">
-        <v>1.182</v>
+        <v>0.796</v>
       </c>
       <c r="K150" s="9" t="n">
-        <v>1.285</v>
+        <v>0.849</v>
       </c>
       <c r="L150" t="inlineStr"/>
       <c r="M150" s="14" t="inlineStr"/>
@@ -7247,28 +7247,28 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>TAKAFUL</t>
+          <t>IOICORP</t>
         </is>
       </c>
       <c r="D151" s="9" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="E151" s="10" t="n">
-        <v>-0.0067</v>
+        <v>4.77</v>
+      </c>
+      <c r="E151" s="15" t="n">
+        <v>0.0021</v>
       </c>
       <c r="F151" s="11" t="n">
-        <v>522500</v>
+        <v>916200</v>
       </c>
       <c r="G151" s="12" t="n">
-        <v>0.49</v>
+        <v>0.11</v>
       </c>
       <c r="H151" t="n">
-        <v>33.69</v>
+        <v>55.58</v>
       </c>
       <c r="I151" s="13" t="inlineStr">
         <is>
@@ -7276,10 +7276,10 @@
         </is>
       </c>
       <c r="J151" s="9" t="n">
-        <v>3.071</v>
+        <v>4.747</v>
       </c>
       <c r="K151" s="9" t="n">
-        <v>3.152</v>
+        <v>4.589</v>
       </c>
       <c r="L151" t="inlineStr"/>
       <c r="M151" s="14" t="inlineStr"/>
@@ -7292,39 +7292,39 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>UWC</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D152" s="9" t="n">
-        <v>6.7</v>
+        <v>0.615</v>
       </c>
       <c r="E152" s="10" t="n">
-        <v>-0.0262</v>
+        <v>0</v>
       </c>
       <c r="F152" s="11" t="n">
-        <v>512200</v>
+        <v>910200</v>
       </c>
       <c r="G152" s="12" t="n">
-        <v>0.15</v>
+        <v>0.3</v>
       </c>
       <c r="H152" t="n">
-        <v>53.59</v>
-      </c>
-      <c r="I152" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>65.06</v>
+      </c>
+      <c r="I152" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J152" s="9" t="n">
-        <v>6.571</v>
+        <v>0.609</v>
       </c>
       <c r="K152" s="9" t="n">
-        <v>6.496</v>
+        <v>0.589</v>
       </c>
       <c r="L152" t="inlineStr"/>
       <c r="M152" s="14" t="inlineStr"/>
@@ -7337,28 +7337,28 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>5328</t>
+          <t>3069</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>LWSABAH</t>
+          <t>MFCB</t>
         </is>
       </c>
       <c r="D153" s="9" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="E153" s="10" t="n">
-        <v>-0.0289</v>
+        <v>3.01</v>
+      </c>
+      <c r="E153" s="17" t="n">
+        <v>-0.0227</v>
       </c>
       <c r="F153" s="11" t="n">
-        <v>505400</v>
+        <v>905700</v>
       </c>
       <c r="G153" s="12" t="n">
-        <v>0.39</v>
+        <v>1.01</v>
       </c>
       <c r="H153" t="n">
-        <v>49.53</v>
+        <v>57.2</v>
       </c>
       <c r="I153" s="13" t="inlineStr">
         <is>
@@ -7366,16 +7366,1769 @@
         </is>
       </c>
       <c r="J153" s="9" t="n">
-        <v>1.701</v>
+        <v>2.944</v>
       </c>
       <c r="K153" s="9" t="n">
-        <v>1.614</v>
+        <v>2.902</v>
       </c>
       <c r="L153" t="inlineStr"/>
       <c r="M153" s="14" t="inlineStr"/>
     </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>5317</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>CPETECH</t>
+        </is>
+      </c>
+      <c r="D154" s="9" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="E154" s="17" t="n">
+        <v>-0.007800000000000001</v>
+      </c>
+      <c r="F154" s="11" t="n">
+        <v>897100</v>
+      </c>
+      <c r="G154" s="12" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H154" t="n">
+        <v>57.33</v>
+      </c>
+      <c r="I154" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J154" s="9" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="K154" s="9" t="n">
+        <v>1.138</v>
+      </c>
+      <c r="L154" t="inlineStr"/>
+      <c r="M154" s="14" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>5211</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>SUNWAY</t>
+        </is>
+      </c>
+      <c r="D155" s="9" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="E155" s="17" t="n">
+        <v>-0.013</v>
+      </c>
+      <c r="F155" s="11" t="n">
+        <v>881700</v>
+      </c>
+      <c r="G155" s="12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H155" t="n">
+        <v>35.27</v>
+      </c>
+      <c r="I155" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J155" s="9" t="n">
+        <v>4.724</v>
+      </c>
+      <c r="K155" s="9" t="n">
+        <v>4.993</v>
+      </c>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" s="14" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>7241</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>NGGB</t>
+        </is>
+      </c>
+      <c r="D156" s="9" t="n">
+        <v>0.715</v>
+      </c>
+      <c r="E156" s="17" t="n">
+        <v>-0.0069</v>
+      </c>
+      <c r="F156" s="11" t="n">
+        <v>879800</v>
+      </c>
+      <c r="G156" s="12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H156" t="n">
+        <v>53.25</v>
+      </c>
+      <c r="I156" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J156" s="9" t="n">
+        <v>0.708</v>
+      </c>
+      <c r="K156" s="9" t="n">
+        <v>0.713</v>
+      </c>
+      <c r="L156" t="inlineStr"/>
+      <c r="M156" s="14" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>0217</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>PWRWELL</t>
+        </is>
+      </c>
+      <c r="D157" s="9" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="E157" s="17" t="n">
+        <v>-0.0167</v>
+      </c>
+      <c r="F157" s="11" t="n">
+        <v>877600</v>
+      </c>
+      <c r="G157" s="12" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H157" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="I157" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J157" s="9" t="n">
+        <v>1.108</v>
+      </c>
+      <c r="K157" s="9" t="n">
+        <v>1.007</v>
+      </c>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" s="14" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>0466</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>SRKKAI</t>
+        </is>
+      </c>
+      <c r="D158" s="9" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="E158" s="17" t="n">
+        <v>-0.0286</v>
+      </c>
+      <c r="F158" s="11" t="n">
+        <v>867800</v>
+      </c>
+      <c r="G158" s="12" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="H158" t="n">
+        <v>42.12</v>
+      </c>
+      <c r="I158" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J158" s="9" t="n">
+        <v>0.524</v>
+      </c>
+      <c r="K158" s="9" t="n">
+        <v>0.532</v>
+      </c>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" s="14" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>0273</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>VLB</t>
+        </is>
+      </c>
+      <c r="D159" s="9" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="E159" s="17" t="n">
+        <v>-0.0408</v>
+      </c>
+      <c r="F159" s="11" t="n">
+        <v>865800</v>
+      </c>
+      <c r="G159" s="12" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H159" t="n">
+        <v>60.04</v>
+      </c>
+      <c r="I159" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J159" s="9" t="n">
+        <v>0.895</v>
+      </c>
+      <c r="K159" s="9" t="n">
+        <v>0.8070000000000001</v>
+      </c>
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" s="14" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>8583</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>MAHSING</t>
+        </is>
+      </c>
+      <c r="D160" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E160" s="17" t="n">
+        <v>-0.0196</v>
+      </c>
+      <c r="F160" s="11" t="n">
+        <v>860700</v>
+      </c>
+      <c r="G160" s="12" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H160" t="n">
+        <v>34.67</v>
+      </c>
+      <c r="I160" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J160" s="9" t="n">
+        <v>1.049</v>
+      </c>
+      <c r="K160" s="9" t="n">
+        <v>1.074</v>
+      </c>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" s="14" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>5356</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>STRATUS</t>
+        </is>
+      </c>
+      <c r="D161" s="9" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="E161" s="17" t="n">
+        <v>-0.0135</v>
+      </c>
+      <c r="F161" s="11" t="n">
+        <v>859700</v>
+      </c>
+      <c r="G161" s="12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H161" t="n">
+        <v>53.82</v>
+      </c>
+      <c r="I161" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J161" s="9" t="n">
+        <v>2.863</v>
+      </c>
+      <c r="K161" s="9" t="n"/>
+      <c r="L161" t="inlineStr"/>
+      <c r="M161" s="14" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>4383</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>JTIASA</t>
+        </is>
+      </c>
+      <c r="D162" s="9" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="E162" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F162" s="11" t="n">
+        <v>852900</v>
+      </c>
+      <c r="G162" s="12" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H162" t="n">
+        <v>36.18</v>
+      </c>
+      <c r="I162" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J162" s="9" t="n">
+        <v>0.998</v>
+      </c>
+      <c r="K162" s="9" t="n">
+        <v>1.047</v>
+      </c>
+      <c r="L162" t="inlineStr"/>
+      <c r="M162" s="14" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>0292</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>JTGROUP</t>
+        </is>
+      </c>
+      <c r="D163" s="9" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="E163" s="15" t="n">
+        <v>0.0161</v>
+      </c>
+      <c r="F163" s="11" t="n">
+        <v>832100</v>
+      </c>
+      <c r="G163" s="12" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="H163" t="n">
+        <v>83.94</v>
+      </c>
+      <c r="I163" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J163" s="9" t="n">
+        <v>1.045</v>
+      </c>
+      <c r="K163" s="9" t="n">
+        <v>0.888</v>
+      </c>
+      <c r="L163" t="inlineStr"/>
+      <c r="M163" s="14" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>0459</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>SUM</t>
+        </is>
+      </c>
+      <c r="D164" s="9" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="E164" s="17" t="n">
+        <v>-0.0069</v>
+      </c>
+      <c r="F164" s="11" t="n">
+        <v>825500</v>
+      </c>
+      <c r="G164" s="12" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H164" t="n">
+        <v>67.44</v>
+      </c>
+      <c r="I164" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J164" s="9" t="n">
+        <v>0.671</v>
+      </c>
+      <c r="K164" s="9" t="n">
+        <v>0.614</v>
+      </c>
+      <c r="L164" t="inlineStr"/>
+      <c r="M164" s="14" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>5271</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>PECCA</t>
+        </is>
+      </c>
+      <c r="D165" s="9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E165" s="15" t="n">
+        <v>0.0072</v>
+      </c>
+      <c r="F165" s="11" t="n">
+        <v>813400</v>
+      </c>
+      <c r="G165" s="12" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="H165" t="n">
+        <v>70.67</v>
+      </c>
+      <c r="I165" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J165" s="9" t="n">
+        <v>1.356</v>
+      </c>
+      <c r="K165" s="9" t="n">
+        <v>1.325</v>
+      </c>
+      <c r="L165" t="inlineStr"/>
+      <c r="M165" s="14" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>6139</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>TAKAFUL</t>
+        </is>
+      </c>
+      <c r="D166" s="9" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="E166" s="17" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="F166" s="11" t="n">
+        <v>807900</v>
+      </c>
+      <c r="G166" s="12" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H166" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="I166" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J166" s="9" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="K166" s="9" t="n">
+        <v>3.152</v>
+      </c>
+      <c r="L166" t="inlineStr"/>
+      <c r="M166" s="14" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>5302</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>ATECH</t>
+        </is>
+      </c>
+      <c r="D167" s="9" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="E167" s="15" t="n">
+        <v>0.006500000000000001</v>
+      </c>
+      <c r="F167" s="11" t="n">
+        <v>795100</v>
+      </c>
+      <c r="G167" s="12" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="H167" t="n">
+        <v>52.54</v>
+      </c>
+      <c r="I167" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J167" s="9" t="n">
+        <v>0.765</v>
+      </c>
+      <c r="K167" s="9" t="n">
+        <v>0.755</v>
+      </c>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" s="14" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>1066</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>RHBBANK</t>
+        </is>
+      </c>
+      <c r="D168" s="9" t="n">
+        <v>7.82</v>
+      </c>
+      <c r="E168" s="15" t="n">
+        <v>0.0039</v>
+      </c>
+      <c r="F168" s="11" t="n">
+        <v>766000</v>
+      </c>
+      <c r="G168" s="12" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H168" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="I168" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J168" s="9" t="n">
+        <v>7.974</v>
+      </c>
+      <c r="K168" s="9" t="n">
+        <v>8.26</v>
+      </c>
+      <c r="L168" t="inlineStr"/>
+      <c r="M168" s="14" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>5292</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>UWC</t>
+        </is>
+      </c>
+      <c r="D169" s="9" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="E169" s="17" t="n">
+        <v>-0.0305</v>
+      </c>
+      <c r="F169" s="11" t="n">
+        <v>757700</v>
+      </c>
+      <c r="G169" s="12" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H169" t="n">
+        <v>52.86</v>
+      </c>
+      <c r="I169" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J169" s="9" t="n">
+        <v>6.569</v>
+      </c>
+      <c r="K169" s="9" t="n">
+        <v>6.495</v>
+      </c>
+      <c r="L169" t="inlineStr"/>
+      <c r="M169" s="14" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>0391</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>AMBEST</t>
+        </is>
+      </c>
+      <c r="D170" s="9" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="E170" s="17" t="n">
+        <v>-0.0143</v>
+      </c>
+      <c r="F170" s="11" t="n">
+        <v>743000</v>
+      </c>
+      <c r="G170" s="12" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H170" t="n">
+        <v>58.09</v>
+      </c>
+      <c r="I170" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J170" s="9" t="n">
+        <v>1.345</v>
+      </c>
+      <c r="K170" s="9" t="n">
+        <v>1.148</v>
+      </c>
+      <c r="L170" t="inlineStr"/>
+      <c r="M170" s="14" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>0097</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>VITROX</t>
+        </is>
+      </c>
+      <c r="D171" s="9" t="n">
+        <v>9.82</v>
+      </c>
+      <c r="E171" s="17" t="n">
+        <v>-0.0091</v>
+      </c>
+      <c r="F171" s="11" t="n">
+        <v>718700</v>
+      </c>
+      <c r="G171" s="12" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H171" t="n">
+        <v>62.34</v>
+      </c>
+      <c r="I171" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J171" s="9" t="n">
+        <v>9.529999999999999</v>
+      </c>
+      <c r="K171" s="9" t="n">
+        <v>9.061</v>
+      </c>
+      <c r="L171" t="inlineStr"/>
+      <c r="M171" s="14" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>0271</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>WELLS</t>
+        </is>
+      </c>
+      <c r="D172" s="9" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="E172" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F172" s="11" t="n">
+        <v>700000</v>
+      </c>
+      <c r="G172" s="12" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="H172" t="n">
+        <v>48.02</v>
+      </c>
+      <c r="I172" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J172" s="9" t="n">
+        <v>0.631</v>
+      </c>
+      <c r="K172" s="9" t="n">
+        <v>0.637</v>
+      </c>
+      <c r="L172" t="inlineStr"/>
+      <c r="M172" s="14" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>5328</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>LWSABAH</t>
+        </is>
+      </c>
+      <c r="D173" s="9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="E173" s="17" t="n">
+        <v>-0.0173</v>
+      </c>
+      <c r="F173" s="11" t="n">
+        <v>692300</v>
+      </c>
+      <c r="G173" s="12" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="H173" t="n">
+        <v>52.1</v>
+      </c>
+      <c r="I173" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J173" s="9" t="n">
+        <v>1.703</v>
+      </c>
+      <c r="K173" s="9" t="n">
+        <v>1.614</v>
+      </c>
+      <c r="L173" t="inlineStr"/>
+      <c r="M173" s="14" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>7197</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>GESHEN</t>
+        </is>
+      </c>
+      <c r="D174" s="9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="E174" s="17" t="n">
+        <v>-0.0046</v>
+      </c>
+      <c r="F174" s="11" t="n">
+        <v>657200</v>
+      </c>
+      <c r="G174" s="12" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="H174" t="n">
+        <v>22.96</v>
+      </c>
+      <c r="I174" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J174" s="9" t="n">
+        <v>1.179</v>
+      </c>
+      <c r="K174" s="9" t="n">
+        <v>1.285</v>
+      </c>
+      <c r="L174" t="inlineStr"/>
+      <c r="M174" s="14" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>5272</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>RANHILL</t>
+        </is>
+      </c>
+      <c r="D175" s="9" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="E175" s="17" t="n">
+        <v>-0.0423</v>
+      </c>
+      <c r="F175" s="11" t="n">
+        <v>650000</v>
+      </c>
+      <c r="G175" s="12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H175" t="n">
+        <v>67.34999999999999</v>
+      </c>
+      <c r="I175" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J175" s="9" t="n">
+        <v>2.931</v>
+      </c>
+      <c r="K175" s="9" t="n">
+        <v>2.521</v>
+      </c>
+      <c r="L175" t="inlineStr"/>
+      <c r="M175" s="14" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>5285</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>SDG</t>
+        </is>
+      </c>
+      <c r="D176" s="9" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="E176" s="17" t="n">
+        <v>-0.0048</v>
+      </c>
+      <c r="F176" s="11" t="n">
+        <v>644900</v>
+      </c>
+      <c r="G176" s="12" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H176" t="n">
+        <v>40.13</v>
+      </c>
+      <c r="I176" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J176" s="9" t="n">
+        <v>6.308</v>
+      </c>
+      <c r="K176" s="9" t="n">
+        <v>6.496</v>
+      </c>
+      <c r="L176" t="inlineStr"/>
+      <c r="M176" s="14" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>5288</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>SIMEPROP</t>
+        </is>
+      </c>
+      <c r="D177" s="9" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="E177" s="17" t="n">
+        <v>-0.007800000000000001</v>
+      </c>
+      <c r="F177" s="11" t="n">
+        <v>638800</v>
+      </c>
+      <c r="G177" s="12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H177" t="n">
+        <v>42.22</v>
+      </c>
+      <c r="I177" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J177" s="9" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="K177" s="9" t="n">
+        <v>1.322</v>
+      </c>
+      <c r="L177" t="inlineStr"/>
+      <c r="M177" s="14" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>9792</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>SEG</t>
+        </is>
+      </c>
+      <c r="D178" s="9" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="E178" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F178" s="11" t="n">
+        <v>631100</v>
+      </c>
+      <c r="G178" s="12" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="H178" t="n">
+        <v>54.14</v>
+      </c>
+      <c r="I178" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J178" s="9" t="n">
+        <v>0.633</v>
+      </c>
+      <c r="K178" s="9" t="n">
+        <v>0.629</v>
+      </c>
+      <c r="L178" t="inlineStr"/>
+      <c r="M178" s="14" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>0245</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>MNHLDG</t>
+        </is>
+      </c>
+      <c r="D179" s="9" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="E179" s="17" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="F179" s="11" t="n">
+        <v>622000</v>
+      </c>
+      <c r="G179" s="12" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H179" t="n">
+        <v>62.75</v>
+      </c>
+      <c r="I179" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J179" s="9" t="n">
+        <v>3.743</v>
+      </c>
+      <c r="K179" s="9" t="n">
+        <v>3.395</v>
+      </c>
+      <c r="L179" t="inlineStr"/>
+      <c r="M179" s="14" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>0326</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>SORENTO</t>
+        </is>
+      </c>
+      <c r="D180" s="9" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="E180" s="17" t="n">
+        <v>-0.0074</v>
+      </c>
+      <c r="F180" s="11" t="n">
+        <v>617700</v>
+      </c>
+      <c r="G180" s="12" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="H180" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="I180" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J180" s="9" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="K180" s="9" t="n">
+        <v>0.647</v>
+      </c>
+      <c r="L180" t="inlineStr"/>
+      <c r="M180" s="14" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>5141</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>DAYANG</t>
+        </is>
+      </c>
+      <c r="D181" s="9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E181" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F181" s="11" t="n">
+        <v>593500</v>
+      </c>
+      <c r="G181" s="12" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H181" t="n">
+        <v>52.85</v>
+      </c>
+      <c r="I181" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J181" s="9" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="K181" s="9" t="n">
+        <v>1.532</v>
+      </c>
+      <c r="L181" t="inlineStr"/>
+      <c r="M181" s="14" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>5916</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>MSC</t>
+        </is>
+      </c>
+      <c r="D182" s="9" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="E182" s="17" t="n">
+        <v>-0.0172</v>
+      </c>
+      <c r="F182" s="11" t="n">
+        <v>588400</v>
+      </c>
+      <c r="G182" s="12" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H182" t="n">
+        <v>40.98</v>
+      </c>
+      <c r="I182" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J182" s="9" t="n">
+        <v>1.757</v>
+      </c>
+      <c r="K182" s="9" t="n">
+        <v>1.857</v>
+      </c>
+      <c r="L182" t="inlineStr"/>
+      <c r="M182" s="14" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>0056</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>NCT</t>
+        </is>
+      </c>
+      <c r="D183" s="9" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E183" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F183" s="11" t="n">
+        <v>585500</v>
+      </c>
+      <c r="G183" s="12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H183" t="n">
+        <v>48.38</v>
+      </c>
+      <c r="I183" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J183" s="9" t="n">
+        <v>0.5629999999999999</v>
+      </c>
+      <c r="K183" s="9" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="L183" t="inlineStr"/>
+      <c r="M183" s="14" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>5326</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>99SMART</t>
+        </is>
+      </c>
+      <c r="D184" s="9" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="E184" s="15" t="n">
+        <v>0.0031</v>
+      </c>
+      <c r="F184" s="11" t="n">
+        <v>575500</v>
+      </c>
+      <c r="G184" s="12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H184" t="n">
+        <v>36.09</v>
+      </c>
+      <c r="I184" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J184" s="9" t="n">
+        <v>3.301</v>
+      </c>
+      <c r="K184" s="9" t="n">
+        <v>3.487</v>
+      </c>
+      <c r="L184" t="inlineStr"/>
+      <c r="M184" s="14" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>7579</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>AWC</t>
+        </is>
+      </c>
+      <c r="D185" s="9" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="E185" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F185" s="11" t="n">
+        <v>573500</v>
+      </c>
+      <c r="G185" s="12" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="H185" t="n">
+        <v>78.42</v>
+      </c>
+      <c r="I185" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J185" s="9" t="n">
+        <v>0.5610000000000001</v>
+      </c>
+      <c r="K185" s="9" t="n">
+        <v>0.492</v>
+      </c>
+      <c r="L185" t="inlineStr"/>
+      <c r="M185" s="14" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>3794</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>MCEMENT</t>
+        </is>
+      </c>
+      <c r="D186" s="9" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="E186" s="17" t="n">
+        <v>-0.0054</v>
+      </c>
+      <c r="F186" s="11" t="n">
+        <v>570200</v>
+      </c>
+      <c r="G186" s="12" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H186" t="n">
+        <v>36.48</v>
+      </c>
+      <c r="I186" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J186" s="9" t="n">
+        <v>5.697</v>
+      </c>
+      <c r="K186" s="9" t="n">
+        <v>6.083</v>
+      </c>
+      <c r="L186" t="inlineStr"/>
+      <c r="M186" s="14" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>7103</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>SPRITZER</t>
+        </is>
+      </c>
+      <c r="D187" s="9" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E187" s="17" t="n">
+        <v>-0.0451</v>
+      </c>
+      <c r="F187" s="11" t="n">
+        <v>560400</v>
+      </c>
+      <c r="G187" s="12" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="H187" t="n">
+        <v>50.54</v>
+      </c>
+      <c r="I187" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J187" s="9" t="n">
+        <v>3.655</v>
+      </c>
+      <c r="K187" s="9" t="n">
+        <v>3.324</v>
+      </c>
+      <c r="L187" t="inlineStr"/>
+      <c r="M187" s="14" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>5330</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>TMK</t>
+        </is>
+      </c>
+      <c r="D188" s="9" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="E188" s="17" t="n">
+        <v>-0.0336</v>
+      </c>
+      <c r="F188" s="11" t="n">
+        <v>550700</v>
+      </c>
+      <c r="G188" s="12" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="H188" t="n">
+        <v>45.7</v>
+      </c>
+      <c r="I188" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J188" s="9" t="n">
+        <v>2.974</v>
+      </c>
+      <c r="K188" s="9" t="n">
+        <v>2.798</v>
+      </c>
+      <c r="L188" t="inlineStr"/>
+      <c r="M188" s="14" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>7174</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>CAB</t>
+        </is>
+      </c>
+      <c r="D189" s="9" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="E189" s="15" t="n">
+        <v>0.0189</v>
+      </c>
+      <c r="F189" s="11" t="n">
+        <v>549600</v>
+      </c>
+      <c r="G189" s="12" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="H189" t="n">
+        <v>60.7</v>
+      </c>
+      <c r="I189" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J189" s="9" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="K189" s="9" t="n">
+        <v>0.527</v>
+      </c>
+      <c r="L189" t="inlineStr"/>
+      <c r="M189" s="14" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>5180</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>CLMT</t>
+        </is>
+      </c>
+      <c r="D190" s="9" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="E190" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F190" s="11" t="n">
+        <v>541300</v>
+      </c>
+      <c r="G190" s="12" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H190" t="n">
+        <v>43.06</v>
+      </c>
+      <c r="I190" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J190" s="9" t="n">
+        <v>0.587</v>
+      </c>
+      <c r="K190" s="9" t="n">
+        <v>0.587</v>
+      </c>
+      <c r="L190" t="inlineStr"/>
+      <c r="M190" s="14" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>7498</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>RALCO</t>
+        </is>
+      </c>
+      <c r="D191" s="9" t="n">
+        <v>0.985</v>
+      </c>
+      <c r="E191" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F191" s="11" t="n">
+        <v>523900</v>
+      </c>
+      <c r="G191" s="12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="H191" t="n">
+        <v>53.67</v>
+      </c>
+      <c r="I191" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J191" s="9" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="K191" s="9" t="n">
+        <v>0.974</v>
+      </c>
+      <c r="L191" t="inlineStr"/>
+      <c r="M191" s="14" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>5309</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>ITMAX</t>
+        </is>
+      </c>
+      <c r="D192" s="9" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="E192" s="15" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="F192" s="11" t="n">
+        <v>523800</v>
+      </c>
+      <c r="G192" s="12" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H192" t="n">
+        <v>58.67</v>
+      </c>
+      <c r="I192" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J192" s="9" t="n">
+        <v>4.439</v>
+      </c>
+      <c r="K192" s="9" t="n">
+        <v>4.489</v>
+      </c>
+      <c r="L192" t="inlineStr"/>
+      <c r="M192" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M153"/>
+  <autoFilter ref="A1:M192"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-09-28/bursa-report-2026-09-28.xlsx
+++ b/docs/downloads/2026-09-28/bursa-report-2026-09-28.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-09-28" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-09-28'!$A$1:$M$192</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-09-28'!$A$1:$M$205</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M192"/>
+  <dimension ref="A1:M205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -572,10 +572,10 @@
         <v>0.0357</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>5476300</v>
+        <v>5775900</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>2.96</v>
+        <v>3.12</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>72.15000000000001</v>
@@ -598,7 +598,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>现价0.435高于50日均线0.38，均线多头排列；但RSI达72.15已入超买区，短期动能偏强而追高风险上升，信号可靠性中等。</t>
+          <t>现价0.435高于50日均线0.38，均线结构偏多；但RSI达72.15已入超买区，短期动能偏热，信号可靠性需谨慎看待。</t>
         </is>
       </c>
     </row>
@@ -625,10 +625,10 @@
         <v>0.04650000000000001</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>5841900</v>
+        <v>5983700</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>26.47</v>
+        <v>27.11</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>72.90000000000001</v>
@@ -651,7 +651,7 @@
       </c>
       <c r="M3" s="8" t="inlineStr">
         <is>
-          <t>现价0.225高于50日均线0.186，均线多头排列；但RSI达72.9已入超买区，短期动能偏热，信号可靠性需谨慎看待。</t>
+          <t>RSI 72.9已超买，现价高于50日均线约21%，EMA与SAR、Supertrend均偏多，但量能信号需确认。</t>
         </is>
       </c>
     </row>
@@ -678,10 +678,10 @@
         <v>0.0561</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>8549600</v>
+        <v>9059000</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.59</v>
+        <v>0.62</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>71.81999999999999</v>
@@ -731,10 +731,10 @@
         <v>0</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>91053300</v>
+        <v>99140200</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>0.15</v>
+        <v>0.17</v>
       </c>
       <c r="H5" t="n">
         <v>22.61</v>
@@ -776,7 +776,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>58888600</v>
+        <v>63159800</v>
       </c>
       <c r="G6" s="12" t="n"/>
       <c r="I6" s="13" t="inlineStr">
@@ -806,19 +806,19 @@
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.185</v>
+        <v>0.18</v>
       </c>
       <c r="E7" s="15" t="n">
-        <v>0.0882</v>
+        <v>0.0588</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>56178800</v>
+        <v>56847800</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="H7" t="n">
-        <v>77.83</v>
+        <v>76.5</v>
       </c>
       <c r="I7" s="16" t="inlineStr">
         <is>
@@ -851,13 +851,13 @@
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>0.13</v>
+        <v>0.135</v>
       </c>
       <c r="E8" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>55808400</v>
+        <v>56519500</v>
       </c>
       <c r="G8" s="12" t="n"/>
       <c r="I8" s="13" t="inlineStr">
@@ -887,19 +887,19 @@
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="E9" s="17" t="n">
-        <v>-0.0526</v>
+        <v>-0.0451</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>34398200</v>
+        <v>36587700</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="H9" t="n">
-        <v>47.42</v>
+        <v>48.72</v>
       </c>
       <c r="I9" s="13" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         </is>
       </c>
       <c r="J9" s="9" t="n">
-        <v>2.584</v>
+        <v>2.586</v>
       </c>
       <c r="K9" s="9" t="n">
         <v>2.44</v>
@@ -932,19 +932,19 @@
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>0.36</v>
+        <v>0.365</v>
       </c>
       <c r="E10" s="17" t="n">
-        <v>-0.0526</v>
+        <v>-0.0395</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>26428800</v>
+        <v>26751800</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="H10" t="n">
-        <v>69.26000000000001</v>
+        <v>71.04000000000001</v>
       </c>
       <c r="I10" s="16" t="inlineStr">
         <is>
@@ -968,39 +968,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>8877</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>EKOVEST</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="E11" s="15" t="n">
-        <v>0.0857</v>
+        <v>0.72</v>
+      </c>
+      <c r="E11" s="17" t="n">
+        <v>-0.0464</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>24687800</v>
+        <v>26587500</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>5.91</v>
+        <v>0.61</v>
       </c>
       <c r="H11" t="n">
-        <v>61.83</v>
-      </c>
-      <c r="I11" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.15</v>
+      </c>
+      <c r="I11" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J11" s="9" t="n">
-        <v>0.18</v>
+        <v>0.735</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>0.189</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="14" t="inlineStr"/>
@@ -1013,39 +1013,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>8877</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>EKOVEST</t>
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="E12" s="17" t="n">
-        <v>-0.0331</v>
+        <v>0.185</v>
+      </c>
+      <c r="E12" s="15" t="n">
+        <v>0.0571</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>23598000</v>
+        <v>25339900</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>0.54</v>
+        <v>6.07</v>
       </c>
       <c r="H12" t="n">
-        <v>51.13</v>
-      </c>
-      <c r="I12" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.81</v>
+      </c>
+      <c r="I12" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J12" s="9" t="n">
-        <v>0.736</v>
+        <v>0.18</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.189</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="14" t="inlineStr"/>
@@ -1073,10 +1073,10 @@
         <v>-0.0256</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>16462100</v>
+        <v>17463200</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>0.68</v>
+        <v>0.73</v>
       </c>
       <c r="H13" t="n">
         <v>64</v>
@@ -1103,39 +1103,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="E14" s="15" t="n">
-        <v>0.0213</v>
+        <v>0.395</v>
+      </c>
+      <c r="E14" s="17" t="n">
+        <v>-0.0595</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>14737800</v>
+        <v>15401300</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>0.82</v>
+        <v>0.71</v>
       </c>
       <c r="H14" t="n">
-        <v>56.39</v>
-      </c>
-      <c r="I14" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>56.63</v>
+      </c>
+      <c r="I14" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J14" s="9" t="n">
-        <v>0.232</v>
+        <v>0.382</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>0.233</v>
+        <v>0.32</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="14" t="inlineStr"/>
@@ -1148,39 +1148,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>0.395</v>
-      </c>
-      <c r="E15" s="17" t="n">
-        <v>-0.0595</v>
+        <v>0.24</v>
+      </c>
+      <c r="E15" s="15" t="n">
+        <v>0.0213</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>14699000</v>
+        <v>15304800</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="H15" t="n">
-        <v>56.63</v>
-      </c>
-      <c r="I15" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.39</v>
+      </c>
+      <c r="I15" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J15" s="9" t="n">
-        <v>0.382</v>
+        <v>0.232</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>0.32</v>
+        <v>0.233</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="14" t="inlineStr"/>
@@ -1202,19 +1202,19 @@
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="E16" s="17" t="n">
-        <v>-0.0321</v>
+        <v>-0.0267</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>13579600</v>
+        <v>13999300</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>59.95</v>
+        <v>60.88</v>
       </c>
       <c r="I16" s="16" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         </is>
       </c>
       <c r="J16" s="9" t="n">
-        <v>1.735</v>
+        <v>1.736</v>
       </c>
       <c r="K16" s="9" t="n">
         <v>1.524</v>
@@ -1247,19 +1247,19 @@
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>0.555</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>0.0183</v>
+        <v>0.0275</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>13065400</v>
+        <v>13868100</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>0.97</v>
+        <v>1.03</v>
       </c>
       <c r="H17" t="n">
-        <v>60.08</v>
+        <v>60.99</v>
       </c>
       <c r="I17" s="16" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>0.524</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>0.476</v>
+        <v>0.477</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="14" t="inlineStr"/>
@@ -1298,10 +1298,10 @@
         <v>-0.0323</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>11864400</v>
+        <v>12967800</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>0.63</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H18" t="n">
         <v>49.23</v>
@@ -1328,39 +1328,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>VELESTO</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0.215</v>
-      </c>
-      <c r="E19" s="17" t="n">
-        <v>-0.0227</v>
+        <v>0.865</v>
+      </c>
+      <c r="E19" s="15" t="n">
+        <v>0.0058</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>11210200</v>
+        <v>12954400</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>0.51</v>
+        <v>0.72</v>
       </c>
       <c r="H19" t="n">
-        <v>29.99</v>
-      </c>
-      <c r="I19" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.9</v>
+      </c>
+      <c r="I19" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J19" s="9" t="n">
-        <v>0.238</v>
+        <v>0.868</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>0.249</v>
+        <v>0.871</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="14" t="inlineStr"/>
@@ -1373,28 +1373,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="E20" s="15" t="n">
-        <v>0.0476</v>
+        <v>0.77</v>
+      </c>
+      <c r="E20" s="17" t="n">
+        <v>-0.006500000000000001</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>11139800</v>
+        <v>11948700</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>1.91</v>
+        <v>0.96</v>
       </c>
       <c r="H20" t="n">
-        <v>62.28</v>
+        <v>47.75</v>
       </c>
       <c r="I20" s="16" t="inlineStr">
         <is>
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="J20" s="9" t="n">
-        <v>0.521</v>
+        <v>0.774</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>0.531</v>
+        <v>0.774</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="14" t="inlineStr"/>
@@ -1418,28 +1418,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>VELESTO</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>0.535</v>
-      </c>
-      <c r="E21" s="15" t="n">
-        <v>0.009399999999999999</v>
+        <v>0.21</v>
+      </c>
+      <c r="E21" s="17" t="n">
+        <v>-0.0455</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>10892600</v>
+        <v>11699400</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>0.29</v>
+        <v>0.54</v>
       </c>
       <c r="H21" t="n">
-        <v>27.96</v>
+        <v>28.01</v>
       </c>
       <c r="I21" s="13" t="inlineStr">
         <is>
@@ -1447,10 +1447,10 @@
         </is>
       </c>
       <c r="J21" s="9" t="n">
-        <v>0.634</v>
+        <v>0.238</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>0.851</v>
+        <v>0.249</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="14" t="inlineStr"/>
@@ -1463,28 +1463,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="E22" s="17" t="n">
-        <v>-0.006500000000000001</v>
+        <v>0.55</v>
+      </c>
+      <c r="E22" s="15" t="n">
+        <v>0.0476</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>10249000</v>
+        <v>11630100</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>0.82</v>
+        <v>1.99</v>
       </c>
       <c r="H22" t="n">
-        <v>47.75</v>
+        <v>62.28</v>
       </c>
       <c r="I22" s="16" t="inlineStr">
         <is>
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="J22" s="9" t="n">
-        <v>0.774</v>
+        <v>0.521</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>0.774</v>
+        <v>0.531</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="14" t="inlineStr"/>
@@ -1508,36 +1508,36 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>0.95</v>
+        <v>0.53</v>
       </c>
       <c r="E23" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>10116000</v>
+        <v>11518300</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>2.49</v>
+        <v>0.3</v>
       </c>
       <c r="H23" t="n">
-        <v>78.75</v>
-      </c>
-      <c r="I23" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>26.93</v>
+      </c>
+      <c r="I23" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J23" s="9" t="n">
-        <v>0.885</v>
+        <v>0.634</v>
       </c>
       <c r="K23" s="9" t="n">
         <v>0.851</v>
@@ -1553,28 +1553,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>7117</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CJCEN</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.2</v>
+        <v>0.705</v>
       </c>
       <c r="E24" s="15" t="n">
-        <v>0.08109999999999999</v>
+        <v>0.0144</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>10020500</v>
+        <v>10877000</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>23.69</v>
+        <v>1.18</v>
       </c>
       <c r="H24" t="n">
-        <v>82.14</v>
+        <v>55.12</v>
       </c>
       <c r="I24" s="16" t="inlineStr">
         <is>
@@ -1582,10 +1582,10 @@
         </is>
       </c>
       <c r="J24" s="9" t="n">
-        <v>0.172</v>
+        <v>0.681</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>0.163</v>
+        <v>0.662</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="14" t="inlineStr"/>
@@ -1598,28 +1598,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>7117</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>CJCEN</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>0.715</v>
+        <v>0.195</v>
       </c>
       <c r="E25" s="15" t="n">
-        <v>0.0288</v>
+        <v>0.0541</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>9908400</v>
+        <v>10571000</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>1.07</v>
+        <v>24.99</v>
       </c>
       <c r="H25" t="n">
-        <v>56.69</v>
+        <v>80.20999999999999</v>
       </c>
       <c r="I25" s="16" t="inlineStr">
         <is>
@@ -1627,10 +1627,10 @@
         </is>
       </c>
       <c r="J25" s="9" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.171</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>0.663</v>
+        <v>0.163</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="14" t="inlineStr"/>
@@ -1643,28 +1643,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>0.215</v>
+        <v>0.945</v>
       </c>
       <c r="E26" s="17" t="n">
-        <v>-0.0227</v>
+        <v>-0.0053</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>9901600</v>
+        <v>10122900</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>0.47</v>
+        <v>2.49</v>
       </c>
       <c r="H26" t="n">
-        <v>65.40000000000001</v>
+        <v>75.98999999999999</v>
       </c>
       <c r="I26" s="16" t="inlineStr">
         <is>
@@ -1672,10 +1672,10 @@
         </is>
       </c>
       <c r="J26" s="9" t="n">
-        <v>0.202</v>
+        <v>0.884</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>0.184</v>
+        <v>0.851</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="14" t="inlineStr"/>
@@ -1688,28 +1688,28 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E27" s="15" t="n">
-        <v>0.0058</v>
+        <v>0.22</v>
+      </c>
+      <c r="E27" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>9515100</v>
+        <v>9946400</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0.53</v>
+        <v>0.47</v>
       </c>
       <c r="H27" t="n">
-        <v>46.9</v>
+        <v>71.25</v>
       </c>
       <c r="I27" s="16" t="inlineStr">
         <is>
@@ -1717,10 +1717,10 @@
         </is>
       </c>
       <c r="J27" s="9" t="n">
-        <v>0.868</v>
+        <v>0.202</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>0.871</v>
+        <v>0.184</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="14" t="inlineStr"/>
@@ -1748,10 +1748,10 @@
         <v>0</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>8989000</v>
+        <v>9382200</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="H28" t="n">
         <v>31.98</v>
@@ -1778,39 +1778,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>0.465</v>
-      </c>
-      <c r="E29" s="17" t="n">
-        <v>-0.0211</v>
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="E29" s="15" t="n">
+        <v>0.0062</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>8557100</v>
+        <v>8802000</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0.35</v>
+        <v>0.68</v>
       </c>
       <c r="H29" t="n">
-        <v>48.8</v>
-      </c>
-      <c r="I29" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.51</v>
+      </c>
+      <c r="I29" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J29" s="9" t="n">
-        <v>0.468</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>0.471</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="14" t="inlineStr"/>
@@ -1832,19 +1832,19 @@
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="E30" s="10" t="n">
-        <v>0</v>
+        <v>2.08</v>
+      </c>
+      <c r="E30" s="17" t="n">
+        <v>-0.0048</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>8469100</v>
+        <v>8686100</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="H30" t="n">
-        <v>46.97</v>
+        <v>45.92</v>
       </c>
       <c r="I30" s="13" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         </is>
       </c>
       <c r="J30" s="9" t="n">
-        <v>2.127</v>
+        <v>2.126</v>
       </c>
       <c r="K30" s="9" t="n">
         <v>2.062</v>
@@ -1868,28 +1868,28 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0373</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>VERDANT</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>0.275</v>
-      </c>
-      <c r="E31" s="15" t="n">
-        <v>0.05769999999999999</v>
+        <v>0.465</v>
+      </c>
+      <c r="E31" s="17" t="n">
+        <v>-0.0211</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>8134600</v>
+        <v>8668500</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>4.74</v>
+        <v>0.36</v>
       </c>
       <c r="H31" t="n">
-        <v>83.03</v>
+        <v>48.8</v>
       </c>
       <c r="I31" s="16" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="J31" s="9" t="n">
-        <v>0.224</v>
+        <v>0.468</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>0.209</v>
+        <v>0.471</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="14" t="inlineStr"/>
@@ -1913,39 +1913,39 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="E32" s="10" t="n">
-        <v>0</v>
+        <v>2.5</v>
+      </c>
+      <c r="E32" s="15" t="n">
+        <v>0.0121</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>8056600</v>
+        <v>8403900</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>0.9</v>
+        <v>0.54</v>
       </c>
       <c r="H32" t="n">
-        <v>58.56</v>
-      </c>
-      <c r="I32" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.94</v>
+      </c>
+      <c r="I32" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J32" s="9" t="n">
-        <v>0.448</v>
+        <v>2.439</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>0.407</v>
+        <v>2.276</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="14" t="inlineStr"/>
@@ -1958,28 +1958,28 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>IOIPG</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>3.49</v>
+        <v>0.47</v>
       </c>
       <c r="E33" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>7781200</v>
+        <v>8370000</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>1.66</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H33" t="n">
-        <v>36.67</v>
+        <v>58.56</v>
       </c>
       <c r="I33" s="13" t="inlineStr">
         <is>
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="J33" s="9" t="n">
-        <v>3.614</v>
+        <v>0.448</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>3.703</v>
+        <v>0.407</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="14" t="inlineStr"/>
@@ -2003,39 +2003,39 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>9377</t>
+          <t>0373</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>FSBM</t>
+          <t>VERDANT</t>
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>0.095</v>
-      </c>
-      <c r="E34" s="17" t="n">
-        <v>-0.09519999999999999</v>
+        <v>0.28</v>
+      </c>
+      <c r="E34" s="15" t="n">
+        <v>0.07690000000000001</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>7764200</v>
+        <v>8254400</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>0.3</v>
+        <v>4.81</v>
       </c>
       <c r="H34" t="n">
-        <v>33</v>
-      </c>
-      <c r="I34" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>83.92</v>
+      </c>
+      <c r="I34" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J34" s="9" t="n">
-        <v>0.133</v>
+        <v>0.225</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>0.162</v>
+        <v>0.209</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="14" t="inlineStr"/>
@@ -2057,19 +2057,19 @@
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>0.8149999999999999</v>
-      </c>
-      <c r="E35" s="17" t="n">
-        <v>-0.0061</v>
+        <v>0.82</v>
+      </c>
+      <c r="E35" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>7759800</v>
+        <v>8183100</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0.8</v>
+        <v>0.84</v>
       </c>
       <c r="H35" t="n">
-        <v>69.03</v>
+        <v>70.16</v>
       </c>
       <c r="I35" s="16" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="J35" s="9" t="n">
-        <v>0.713</v>
+        <v>0.714</v>
       </c>
       <c r="K35" s="9" t="n">
         <v>0.6870000000000001</v>
@@ -2093,39 +2093,39 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>5218</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>VANTNRG</t>
+          <t>IOIPG</t>
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>0.345</v>
-      </c>
-      <c r="E36" s="17" t="n">
-        <v>-0.0143</v>
+        <v>3.5</v>
+      </c>
+      <c r="E36" s="15" t="n">
+        <v>0.0029</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>7608100</v>
+        <v>8092100</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="H36" t="n">
-        <v>57.32</v>
-      </c>
-      <c r="I36" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.68</v>
+      </c>
+      <c r="I36" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J36" s="9" t="n">
-        <v>0.339</v>
+        <v>3.615</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>0.333</v>
+        <v>3.704</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="14" t="inlineStr"/>
@@ -2138,28 +2138,28 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0175</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>HHRG</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="E37" s="10" t="n">
-        <v>0</v>
+        <v>2.78</v>
+      </c>
+      <c r="E37" s="17" t="n">
+        <v>-0.0347</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>7406400</v>
+        <v>7904000</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0.18</v>
+        <v>1.13</v>
       </c>
       <c r="H37" t="n">
-        <v>47.65</v>
+        <v>60.38</v>
       </c>
       <c r="I37" s="16" t="inlineStr">
         <is>
@@ -2167,10 +2167,10 @@
         </is>
       </c>
       <c r="J37" s="9" t="n">
-        <v>0.158</v>
+        <v>2.625</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>0.148</v>
+        <v>2.495</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="14" t="inlineStr"/>
@@ -2183,39 +2183,39 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>7315</t>
+          <t>9377</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>AHB</t>
+          <t>FSBM</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>0.05</v>
+        <v>0.095</v>
       </c>
       <c r="E38" s="17" t="n">
-        <v>-0.09089999999999999</v>
+        <v>-0.09519999999999999</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>7184000</v>
+        <v>7857600</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>0.75</v>
+        <v>0.3</v>
       </c>
       <c r="H38" t="n">
-        <v>48.92</v>
-      </c>
-      <c r="I38" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33</v>
+      </c>
+      <c r="I38" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J38" s="9" t="n">
-        <v>0.053</v>
+        <v>0.133</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>0.043</v>
+        <v>0.162</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="14" t="inlineStr"/>
@@ -2228,28 +2228,28 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0095</t>
+          <t>5218</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>MAG</t>
+          <t>VANTNRG</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="E39" s="10" t="n">
-        <v>0</v>
+        <v>0.34</v>
+      </c>
+      <c r="E39" s="17" t="n">
+        <v>-0.0286</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>7160000</v>
+        <v>7695400</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>0.34</v>
+        <v>1.93</v>
       </c>
       <c r="H39" t="n">
-        <v>44.73</v>
+        <v>52.59</v>
       </c>
       <c r="I39" s="16" t="inlineStr">
         <is>
@@ -2257,10 +2257,10 @@
         </is>
       </c>
       <c r="J39" s="9" t="n">
-        <v>0.156</v>
+        <v>0.338</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>0.159</v>
+        <v>0.332</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="14" t="inlineStr"/>
@@ -2273,28 +2273,28 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>0175</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>HHRG</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="E40" s="17" t="n">
-        <v>-0.0243</v>
+        <v>0.15</v>
+      </c>
+      <c r="E40" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>6945000</v>
+        <v>7534000</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>1</v>
+        <v>0.18</v>
       </c>
       <c r="H40" t="n">
-        <v>62.35</v>
+        <v>47.65</v>
       </c>
       <c r="I40" s="16" t="inlineStr">
         <is>
@@ -2302,10 +2302,10 @@
         </is>
       </c>
       <c r="J40" s="9" t="n">
-        <v>2.628</v>
+        <v>0.158</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>2.495</v>
+        <v>0.148</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="14" t="inlineStr"/>
@@ -2318,28 +2318,28 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>7315</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>AHB</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E41" s="15" t="n">
-        <v>0.0121</v>
+        <v>0.05</v>
+      </c>
+      <c r="E41" s="17" t="n">
+        <v>-0.09089999999999999</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>6841200</v>
+        <v>7184200</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>0.44</v>
+        <v>0.75</v>
       </c>
       <c r="H41" t="n">
-        <v>61.94</v>
+        <v>48.92</v>
       </c>
       <c r="I41" s="16" t="inlineStr">
         <is>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="J41" s="9" t="n">
-        <v>2.439</v>
+        <v>0.053</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>2.276</v>
+        <v>0.043</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="14" t="inlineStr"/>
@@ -2363,39 +2363,39 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>0095</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.155</v>
       </c>
       <c r="E42" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>6580500</v>
+        <v>7160000</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>0.51</v>
+        <v>0.34</v>
       </c>
       <c r="H42" t="n">
-        <v>50.19</v>
-      </c>
-      <c r="I42" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>44.73</v>
+      </c>
+      <c r="I42" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J42" s="9" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.156</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.159</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="14" t="inlineStr"/>
@@ -2408,39 +2408,39 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>4.86</v>
-      </c>
-      <c r="E43" s="17" t="n">
-        <v>-0.004099999999999999</v>
+        <v>0.39</v>
+      </c>
+      <c r="E43" s="15" t="n">
+        <v>0.0263</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>6527300</v>
+        <v>7059800</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>0.34</v>
+        <v>0.73</v>
       </c>
       <c r="H43" t="n">
-        <v>62.59</v>
-      </c>
-      <c r="I43" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>67.3</v>
+      </c>
+      <c r="I43" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J43" s="9" t="n">
-        <v>4.74</v>
+        <v>0.374</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>4.509</v>
+        <v>0.371</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="14" t="inlineStr"/>
@@ -2453,28 +2453,28 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="E44" s="15" t="n">
-        <v>0.0132</v>
+        <v>2.98</v>
+      </c>
+      <c r="E44" s="17" t="n">
+        <v>-0.0165</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>6238100</v>
+        <v>6756200</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0.65</v>
+        <v>0.5</v>
       </c>
       <c r="H44" t="n">
-        <v>63.96</v>
+        <v>64.89</v>
       </c>
       <c r="I44" s="16" t="inlineStr">
         <is>
@@ -2482,10 +2482,10 @@
         </is>
       </c>
       <c r="J44" s="9" t="n">
-        <v>0.373</v>
+        <v>2.858</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>0.371</v>
+        <v>2.716</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="14" t="inlineStr"/>
@@ -2498,39 +2498,39 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E45" s="17" t="n">
-        <v>-0.0083</v>
+        <v>4.88</v>
+      </c>
+      <c r="E45" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>5966500</v>
+        <v>6727600</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>0.61</v>
+        <v>0.35</v>
       </c>
       <c r="H45" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="I45" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>64.36</v>
+      </c>
+      <c r="I45" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J45" s="9" t="n">
-        <v>0.607</v>
+        <v>4.742</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>0.604</v>
+        <v>4.509</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="14" t="inlineStr"/>
@@ -2543,28 +2543,28 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>2.99</v>
+        <v>0.6</v>
       </c>
       <c r="E46" s="17" t="n">
-        <v>-0.0132</v>
+        <v>-0.0083</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>5820500</v>
+        <v>5996900</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0.43</v>
+        <v>0.61</v>
       </c>
       <c r="H46" t="n">
-        <v>66.08</v>
+        <v>45.5</v>
       </c>
       <c r="I46" s="16" t="inlineStr">
         <is>
@@ -2572,10 +2572,10 @@
         </is>
       </c>
       <c r="J46" s="9" t="n">
-        <v>2.859</v>
+        <v>0.607</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>2.716</v>
+        <v>0.604</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="14" t="inlineStr"/>
@@ -2603,10 +2603,10 @@
         <v>0.09519999999999999</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>5525200</v>
+        <v>5789100</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>11.29</v>
+        <v>11.83</v>
       </c>
       <c r="H47" t="n">
         <v>58.72</v>
@@ -2633,28 +2633,28 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="E48" s="10" t="n">
-        <v>0</v>
+        <v>0.36</v>
+      </c>
+      <c r="E48" s="17" t="n">
+        <v>-0.027</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>5242500</v>
+        <v>5524500</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>0.82</v>
+        <v>0.92</v>
       </c>
       <c r="H48" t="n">
-        <v>63.82</v>
+        <v>45.16</v>
       </c>
       <c r="I48" s="16" t="inlineStr">
         <is>
@@ -2662,10 +2662,10 @@
         </is>
       </c>
       <c r="J48" s="9" t="n">
-        <v>0.274</v>
+        <v>0.366</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>0.269</v>
+        <v>0.366</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="14" t="inlineStr"/>
@@ -2693,10 +2693,10 @@
         <v>0.0156</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>4942000</v>
+        <v>5439000</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H49" t="n">
         <v>95.47</v>
@@ -2723,28 +2723,28 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="E50" s="17" t="n">
-        <v>-0.0126</v>
+        <v>0.29</v>
+      </c>
+      <c r="E50" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>4866600</v>
+        <v>5342500</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>0.29</v>
+        <v>0.84</v>
       </c>
       <c r="H50" t="n">
-        <v>52.09</v>
+        <v>63.82</v>
       </c>
       <c r="I50" s="16" t="inlineStr">
         <is>
@@ -2752,10 +2752,10 @@
         </is>
       </c>
       <c r="J50" s="9" t="n">
-        <v>2.349</v>
+        <v>0.274</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>2.239</v>
+        <v>0.269</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="14" t="inlineStr"/>
@@ -2768,28 +2768,28 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>0.365</v>
-      </c>
-      <c r="E51" s="17" t="n">
-        <v>-0.0135</v>
+        <v>4.19</v>
+      </c>
+      <c r="E51" s="15" t="n">
+        <v>0.032</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>4594900</v>
+        <v>5314800</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>0.77</v>
+        <v>1.11</v>
       </c>
       <c r="H51" t="n">
-        <v>48.52</v>
+        <v>80.43000000000001</v>
       </c>
       <c r="I51" s="16" t="inlineStr">
         <is>
@@ -2797,10 +2797,10 @@
         </is>
       </c>
       <c r="J51" s="9" t="n">
-        <v>0.367</v>
+        <v>3.547</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>0.366</v>
+        <v>3.226</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="14" t="inlineStr"/>
@@ -2813,28 +2813,28 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0280</t>
+          <t>8893</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>MBN</t>
+          <t>MKLAND</t>
         </is>
       </c>
       <c r="D52" s="9" t="n">
-        <v>0.16</v>
+        <v>0.18</v>
       </c>
       <c r="E52" s="15" t="n">
-        <v>0.0323</v>
+        <v>0.0286</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>4522900</v>
+        <v>5033700</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>1.41</v>
+        <v>4.62</v>
       </c>
       <c r="H52" t="n">
-        <v>56.74</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="I52" s="16" t="inlineStr">
         <is>
@@ -2842,10 +2842,10 @@
         </is>
       </c>
       <c r="J52" s="9" t="n">
-        <v>0.154</v>
+        <v>0.152</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>0.147</v>
+        <v>0.145</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="14" t="inlineStr"/>
@@ -2858,28 +2858,28 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>MALAKOF</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>0.805</v>
-      </c>
-      <c r="E53" s="10" t="n">
-        <v>0</v>
+        <v>2.35</v>
+      </c>
+      <c r="E53" s="17" t="n">
+        <v>-0.0167</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>4507000</v>
+        <v>4922100</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>1.08</v>
+        <v>0.3</v>
       </c>
       <c r="H53" t="n">
-        <v>49.87</v>
+        <v>51.33</v>
       </c>
       <c r="I53" s="16" t="inlineStr">
         <is>
@@ -2887,10 +2887,10 @@
         </is>
       </c>
       <c r="J53" s="9" t="n">
-        <v>0.804</v>
+        <v>2.348</v>
       </c>
       <c r="K53" s="9" t="n">
-        <v>0.806</v>
+        <v>2.239</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="14" t="inlineStr"/>
@@ -2903,28 +2903,28 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>0280</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>MBN</t>
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E54" s="17" t="n">
-        <v>-0.0385</v>
+        <v>0.16</v>
+      </c>
+      <c r="E54" s="15" t="n">
+        <v>0.0323</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>4314100</v>
+        <v>4522900</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>0.36</v>
+        <v>1.41</v>
       </c>
       <c r="H54" t="n">
-        <v>36.09</v>
+        <v>56.74</v>
       </c>
       <c r="I54" s="16" t="inlineStr">
         <is>
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="J54" s="9" t="n">
-        <v>0.272</v>
+        <v>0.154</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>0.314</v>
+        <v>0.147</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="14" t="inlineStr"/>
@@ -2948,39 +2948,39 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>MALAKOF</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="E55" s="17" t="n">
-        <v>-0.0455</v>
+        <v>0.805</v>
+      </c>
+      <c r="E55" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>4214400</v>
+        <v>4507000</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>0.38</v>
+        <v>1.08</v>
       </c>
       <c r="H55" t="n">
-        <v>47.24</v>
-      </c>
-      <c r="I55" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.87</v>
+      </c>
+      <c r="I55" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J55" s="9" t="n">
-        <v>1.081</v>
+        <v>0.804</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>1.024</v>
+        <v>0.806</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="14" t="inlineStr"/>
@@ -2993,28 +2993,28 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>TANCO</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D56" s="9" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="E56" s="15" t="n">
-        <v>0.0303</v>
+        <v>1.05</v>
+      </c>
+      <c r="E56" s="17" t="n">
+        <v>-0.0455</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>4141100</v>
+        <v>4469200</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>0.15</v>
+        <v>0.4</v>
       </c>
       <c r="H56" t="n">
-        <v>37.52</v>
+        <v>47.24</v>
       </c>
       <c r="I56" s="13" t="inlineStr">
         <is>
@@ -3022,10 +3022,10 @@
         </is>
       </c>
       <c r="J56" s="9" t="n">
-        <v>0.182</v>
+        <v>1.081</v>
       </c>
       <c r="K56" s="9" t="n">
-        <v>0.221</v>
+        <v>1.024</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="14" t="inlineStr"/>
@@ -3038,39 +3038,39 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>4.13</v>
-      </c>
-      <c r="E57" s="15" t="n">
-        <v>0.0172</v>
+        <v>0.545</v>
+      </c>
+      <c r="E57" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>4136600</v>
+        <v>4360600</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>0.86</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H57" t="n">
-        <v>79.47</v>
-      </c>
-      <c r="I57" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.08</v>
+      </c>
+      <c r="I57" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J57" s="9" t="n">
-        <v>3.542</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>3.225</v>
+        <v>0.59</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="14" t="inlineStr"/>
@@ -3083,28 +3083,28 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>8893</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>MKLAND</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D58" s="9" t="n">
-        <v>0.175</v>
-      </c>
-      <c r="E58" s="10" t="n">
-        <v>0</v>
+        <v>0.25</v>
+      </c>
+      <c r="E58" s="17" t="n">
+        <v>-0.0385</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>3871200</v>
+        <v>4350200</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>3.55</v>
+        <v>0.37</v>
       </c>
       <c r="H58" t="n">
-        <v>79.92</v>
+        <v>36.09</v>
       </c>
       <c r="I58" s="16" t="inlineStr">
         <is>
@@ -3112,10 +3112,10 @@
         </is>
       </c>
       <c r="J58" s="9" t="n">
-        <v>0.151</v>
+        <v>0.272</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>0.145</v>
+        <v>0.314</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="14" t="inlineStr"/>
@@ -3128,39 +3128,39 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="E59" s="10" t="n">
-        <v>0</v>
+        <v>5.8</v>
+      </c>
+      <c r="E59" s="17" t="n">
+        <v>-0.0153</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>3844300</v>
+        <v>4314000</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="H59" t="n">
-        <v>44.52</v>
-      </c>
-      <c r="I59" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.99</v>
+      </c>
+      <c r="I59" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J59" s="9" t="n">
-        <v>1.375</v>
+        <v>5.686</v>
       </c>
       <c r="K59" s="9" t="n">
-        <v>1.29</v>
+        <v>5.131</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="14" t="inlineStr"/>
@@ -3173,39 +3173,39 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>2429</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>TANCO</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>5.79</v>
-      </c>
-      <c r="E60" s="17" t="n">
-        <v>-0.017</v>
+        <v>0.17</v>
+      </c>
+      <c r="E60" s="15" t="n">
+        <v>0.0303</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>3835100</v>
+        <v>4158300</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>0.26</v>
+        <v>0.15</v>
       </c>
       <c r="H60" t="n">
-        <v>58.54</v>
-      </c>
-      <c r="I60" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.52</v>
+      </c>
+      <c r="I60" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J60" s="9" t="n">
-        <v>5.685</v>
+        <v>0.182</v>
       </c>
       <c r="K60" s="9" t="n">
-        <v>5.131</v>
+        <v>0.221</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="14" t="inlineStr"/>
@@ -3218,28 +3218,28 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>AVANGAAD</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E61" s="15" t="n">
-        <v>0.0172</v>
+        <v>1.31</v>
+      </c>
+      <c r="E61" s="17" t="n">
+        <v>-0.0076</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>3749300</v>
+        <v>4013800</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>2.02</v>
+        <v>0.35</v>
       </c>
       <c r="H61" t="n">
-        <v>49.23</v>
+        <v>43.34</v>
       </c>
       <c r="I61" s="13" t="inlineStr">
         <is>
@@ -3247,10 +3247,10 @@
         </is>
       </c>
       <c r="J61" s="9" t="n">
-        <v>0.295</v>
+        <v>1.374</v>
       </c>
       <c r="K61" s="9" t="n">
-        <v>0.297</v>
+        <v>1.29</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="14" t="inlineStr"/>
@@ -3272,19 +3272,19 @@
         </is>
       </c>
       <c r="D62" s="9" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="E62" s="17" t="n">
-        <v>-0.06570000000000001</v>
+        <v>-0.0584</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>3748400</v>
+        <v>3802100</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="H62" t="n">
-        <v>35.61</v>
+        <v>36.5</v>
       </c>
       <c r="I62" s="13" t="inlineStr">
         <is>
@@ -3292,7 +3292,7 @@
         </is>
       </c>
       <c r="J62" s="9" t="n">
-        <v>1.402</v>
+        <v>1.403</v>
       </c>
       <c r="K62" s="9" t="n">
         <v>1.317</v>
@@ -3308,28 +3308,28 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>0.55</v>
+        <v>0.295</v>
       </c>
       <c r="E63" s="15" t="n">
-        <v>0.0092</v>
+        <v>0.0172</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>3675400</v>
+        <v>3749300</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>0.58</v>
+        <v>2.02</v>
       </c>
       <c r="H63" t="n">
-        <v>41.68</v>
+        <v>49.23</v>
       </c>
       <c r="I63" s="13" t="inlineStr">
         <is>
@@ -3337,10 +3337,10 @@
         </is>
       </c>
       <c r="J63" s="9" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.295</v>
       </c>
       <c r="K63" s="9" t="n">
-        <v>0.59</v>
+        <v>0.297</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="14" t="inlineStr"/>
@@ -3353,39 +3353,39 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>NEXG</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D64" s="9" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="E64" s="10" t="n">
-        <v>0</v>
+        <v>0.86</v>
+      </c>
+      <c r="E64" s="17" t="n">
+        <v>-0.0058</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>3536700</v>
+        <v>3719700</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>0.22</v>
+        <v>1.26</v>
       </c>
       <c r="H64" t="n">
-        <v>65.18000000000001</v>
-      </c>
-      <c r="I64" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.56</v>
+      </c>
+      <c r="I64" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J64" s="9" t="n">
-        <v>0.284</v>
+        <v>0.859</v>
       </c>
       <c r="K64" s="9" t="n">
-        <v>0.277</v>
+        <v>0.856</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="14" t="inlineStr"/>
@@ -3398,28 +3398,28 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>2.55</v>
+        <v>10.2</v>
       </c>
       <c r="E65" s="17" t="n">
-        <v>-0.0267</v>
+        <v>-0.002</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>3399100</v>
+        <v>3660400</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>0.58</v>
+        <v>0.22</v>
       </c>
       <c r="H65" t="n">
-        <v>48.43</v>
+        <v>49.44</v>
       </c>
       <c r="I65" s="16" t="inlineStr">
         <is>
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="J65" s="9" t="n">
-        <v>2.568</v>
+        <v>10.179</v>
       </c>
       <c r="K65" s="9" t="n">
-        <v>2.535</v>
+        <v>10.321</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="14" t="inlineStr"/>
@@ -3443,28 +3443,28 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>0369</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>JSSOLAR</t>
         </is>
       </c>
       <c r="D66" s="9" t="n">
-        <v>1.18</v>
+        <v>0.255</v>
       </c>
       <c r="E66" s="15" t="n">
-        <v>0.0172</v>
+        <v>0.02</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>3364000</v>
+        <v>3619900</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>0.5</v>
+        <v>3.51</v>
       </c>
       <c r="H66" t="n">
-        <v>50.53</v>
+        <v>72.41</v>
       </c>
       <c r="I66" s="16" t="inlineStr">
         <is>
@@ -3472,10 +3472,10 @@
         </is>
       </c>
       <c r="J66" s="9" t="n">
-        <v>1.181</v>
+        <v>0.212</v>
       </c>
       <c r="K66" s="9" t="n">
-        <v>1.14</v>
+        <v>0.198</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="14" t="inlineStr"/>
@@ -3488,28 +3488,28 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0111</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>0.165</v>
+        <v>1.18</v>
       </c>
       <c r="E67" s="15" t="n">
-        <v>0.0313</v>
+        <v>0.0172</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>3362700</v>
+        <v>3614700</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>1.29</v>
+        <v>0.54</v>
       </c>
       <c r="H67" t="n">
-        <v>66.66</v>
+        <v>50.53</v>
       </c>
       <c r="I67" s="16" t="inlineStr">
         <is>
@@ -3517,10 +3517,10 @@
         </is>
       </c>
       <c r="J67" s="9" t="n">
-        <v>0.148</v>
+        <v>1.181</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>0.139</v>
+        <v>1.14</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="14" t="inlineStr"/>
@@ -3533,28 +3533,28 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0050</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>SYSTECH</t>
+          <t>NEXG</t>
         </is>
       </c>
       <c r="D68" s="9" t="n">
-        <v>0.18</v>
+        <v>0.32</v>
       </c>
       <c r="E68" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>3320800</v>
+        <v>3611700</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>0.64</v>
+        <v>0.22</v>
       </c>
       <c r="H68" t="n">
-        <v>63.42</v>
+        <v>65.18000000000001</v>
       </c>
       <c r="I68" s="16" t="inlineStr">
         <is>
@@ -3562,10 +3562,10 @@
         </is>
       </c>
       <c r="J68" s="9" t="n">
-        <v>0.163</v>
+        <v>0.284</v>
       </c>
       <c r="K68" s="9" t="n">
-        <v>0.165</v>
+        <v>0.277</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="14" t="inlineStr"/>
@@ -3578,28 +3578,28 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D69" s="9" t="n">
-        <v>0.715</v>
-      </c>
-      <c r="E69" s="17" t="n">
-        <v>-0.0467</v>
+        <v>0.91</v>
+      </c>
+      <c r="E69" s="15" t="n">
+        <v>0.0111</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>3267800</v>
+        <v>3597700</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.1</v>
       </c>
       <c r="H69" t="n">
-        <v>59.69</v>
+        <v>39.98</v>
       </c>
       <c r="I69" s="16" t="inlineStr">
         <is>
@@ -3607,10 +3607,10 @@
         </is>
       </c>
       <c r="J69" s="9" t="n">
-        <v>0.681</v>
+        <v>0.926</v>
       </c>
       <c r="K69" s="9" t="n">
-        <v>0.611</v>
+        <v>0.969</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="14" t="inlineStr"/>
@@ -3623,39 +3623,39 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0239</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>ECOMATE</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D70" s="9" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E70" s="10" t="n">
-        <v>0</v>
+        <v>2.55</v>
+      </c>
+      <c r="E70" s="17" t="n">
+        <v>-0.0267</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>3210700</v>
+        <v>3526100</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>1.09</v>
+        <v>0.61</v>
       </c>
       <c r="H70" t="n">
-        <v>59.03</v>
-      </c>
-      <c r="I70" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.43</v>
+      </c>
+      <c r="I70" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J70" s="9" t="n">
-        <v>0.859</v>
+        <v>2.568</v>
       </c>
       <c r="K70" s="9" t="n">
-        <v>0.856</v>
+        <v>2.535</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="14" t="inlineStr"/>
@@ -3668,28 +3668,28 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="E71" s="15" t="n">
-        <v>0.0222</v>
+        <v>0.715</v>
+      </c>
+      <c r="E71" s="17" t="n">
+        <v>-0.0467</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>3209200</v>
+        <v>3464500</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>0.98</v>
+        <v>0.6</v>
       </c>
       <c r="H71" t="n">
-        <v>43.85</v>
+        <v>59.69</v>
       </c>
       <c r="I71" s="16" t="inlineStr">
         <is>
@@ -3697,10 +3697,10 @@
         </is>
       </c>
       <c r="J71" s="9" t="n">
-        <v>0.927</v>
+        <v>0.681</v>
       </c>
       <c r="K71" s="9" t="n">
-        <v>0.969</v>
+        <v>0.611</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="14" t="inlineStr"/>
@@ -3713,28 +3713,28 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>0111</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="D72" s="9" t="n">
-        <v>0.325</v>
-      </c>
-      <c r="E72" s="10" t="n">
-        <v>0</v>
+        <v>0.165</v>
+      </c>
+      <c r="E72" s="15" t="n">
+        <v>0.0313</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>3055800</v>
+        <v>3383500</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>0.38</v>
+        <v>1.3</v>
       </c>
       <c r="H72" t="n">
-        <v>50.52</v>
+        <v>66.66</v>
       </c>
       <c r="I72" s="16" t="inlineStr">
         <is>
@@ -3742,10 +3742,10 @@
         </is>
       </c>
       <c r="J72" s="9" t="n">
-        <v>0.33</v>
+        <v>0.148</v>
       </c>
       <c r="K72" s="9" t="n">
-        <v>0.311</v>
+        <v>0.139</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="14" t="inlineStr"/>
@@ -3767,19 +3767,19 @@
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>0.765</v>
-      </c>
-      <c r="E73" s="10" t="n">
-        <v>0</v>
+        <v>0.77</v>
+      </c>
+      <c r="E73" s="15" t="n">
+        <v>0.006500000000000001</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>2986200</v>
+        <v>3347200</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>0.48</v>
+        <v>0.53</v>
       </c>
       <c r="H73" t="n">
-        <v>46.13</v>
+        <v>48.8</v>
       </c>
       <c r="I73" s="13" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         </is>
       </c>
       <c r="J73" s="9" t="n">
-        <v>0.773</v>
+        <v>0.774</v>
       </c>
       <c r="K73" s="9" t="n">
         <v>0.773</v>
@@ -3803,28 +3803,28 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>0050</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>SYSTECH</t>
         </is>
       </c>
       <c r="D74" s="9" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="E74" s="17" t="n">
-        <v>-0.002</v>
+        <v>0.18</v>
+      </c>
+      <c r="E74" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>2971400</v>
+        <v>3320800</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>0.18</v>
+        <v>0.64</v>
       </c>
       <c r="H74" t="n">
-        <v>49.44</v>
+        <v>63.42</v>
       </c>
       <c r="I74" s="16" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="J74" s="9" t="n">
-        <v>10.179</v>
+        <v>0.163</v>
       </c>
       <c r="K74" s="9" t="n">
-        <v>10.321</v>
+        <v>0.165</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="14" t="inlineStr"/>
@@ -3848,28 +3848,28 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D75" s="9" t="n">
-        <v>1.32</v>
+        <v>4.39</v>
       </c>
       <c r="E75" s="15" t="n">
-        <v>0.0233</v>
+        <v>0.0092</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>2811700</v>
+        <v>3116800</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>0.23</v>
+        <v>0.26</v>
       </c>
       <c r="H75" t="n">
-        <v>42.24</v>
+        <v>79.20999999999999</v>
       </c>
       <c r="I75" s="16" t="inlineStr">
         <is>
@@ -3877,10 +3877,10 @@
         </is>
       </c>
       <c r="J75" s="9" t="n">
-        <v>1.331</v>
+        <v>3.521</v>
       </c>
       <c r="K75" s="9" t="n">
-        <v>1.445</v>
+        <v>2.354</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="14" t="inlineStr"/>
@@ -3893,28 +3893,28 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D76" s="9" t="n">
-        <v>4.41</v>
+        <v>0.33</v>
       </c>
       <c r="E76" s="15" t="n">
-        <v>0.0138</v>
+        <v>0.0154</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>2806600</v>
+        <v>3067900</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>0.23</v>
+        <v>0.38</v>
       </c>
       <c r="H76" t="n">
-        <v>79.41</v>
+        <v>52.72</v>
       </c>
       <c r="I76" s="16" t="inlineStr">
         <is>
@@ -3922,10 +3922,10 @@
         </is>
       </c>
       <c r="J76" s="9" t="n">
-        <v>3.523</v>
+        <v>0.33</v>
       </c>
       <c r="K76" s="9" t="n">
-        <v>2.355</v>
+        <v>0.311</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="14" t="inlineStr"/>
@@ -3938,28 +3938,28 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D77" s="9" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="E77" s="10" t="n">
-        <v>0</v>
+        <v>1.32</v>
+      </c>
+      <c r="E77" s="15" t="n">
+        <v>0.0233</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>2721500</v>
+        <v>2962400</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>0.39</v>
+        <v>0.24</v>
       </c>
       <c r="H77" t="n">
-        <v>65.70999999999999</v>
+        <v>42.24</v>
       </c>
       <c r="I77" s="16" t="inlineStr">
         <is>
@@ -3967,10 +3967,10 @@
         </is>
       </c>
       <c r="J77" s="9" t="n">
-        <v>0.337</v>
+        <v>1.331</v>
       </c>
       <c r="K77" s="9" t="n">
-        <v>0.319</v>
+        <v>1.445</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="14" t="inlineStr"/>
@@ -3983,39 +3983,39 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>MRCB</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D78" s="9" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="E78" s="10" t="n">
-        <v>0</v>
+        <v>0.765</v>
+      </c>
+      <c r="E78" s="17" t="n">
+        <v>-0.0255</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>2653800</v>
+        <v>2918500</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>0.35</v>
+        <v>0.5</v>
       </c>
       <c r="H78" t="n">
-        <v>39.08</v>
-      </c>
-      <c r="I78" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.15</v>
+      </c>
+      <c r="I78" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J78" s="9" t="n">
-        <v>0.298</v>
+        <v>0.766</v>
       </c>
       <c r="K78" s="9" t="n">
-        <v>0.312</v>
+        <v>0.752</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="14" t="inlineStr"/>
@@ -4028,28 +4028,28 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D79" s="9" t="n">
-        <v>0.415</v>
-      </c>
-      <c r="E79" s="17" t="n">
-        <v>-0.0119</v>
+        <v>0.29</v>
+      </c>
+      <c r="E79" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>2627100</v>
+        <v>2866800</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>0.23</v>
+        <v>0.38</v>
       </c>
       <c r="H79" t="n">
-        <v>56.5</v>
+        <v>39.08</v>
       </c>
       <c r="I79" s="16" t="inlineStr">
         <is>
@@ -4057,10 +4057,10 @@
         </is>
       </c>
       <c r="J79" s="9" t="n">
-        <v>0.409</v>
+        <v>0.298</v>
       </c>
       <c r="K79" s="9" t="n">
-        <v>0.41</v>
+        <v>0.312</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="14" t="inlineStr"/>
@@ -4073,28 +4073,28 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0369</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>JSSOLAR</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D80" s="9" t="n">
-        <v>0.255</v>
-      </c>
-      <c r="E80" s="15" t="n">
-        <v>0.02</v>
+        <v>0.66</v>
+      </c>
+      <c r="E80" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>2586000</v>
+        <v>2819600</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>2.51</v>
+        <v>0.3</v>
       </c>
       <c r="H80" t="n">
-        <v>72.41</v>
+        <v>59.78</v>
       </c>
       <c r="I80" s="16" t="inlineStr">
         <is>
@@ -4102,10 +4102,10 @@
         </is>
       </c>
       <c r="J80" s="9" t="n">
-        <v>0.212</v>
+        <v>0.633</v>
       </c>
       <c r="K80" s="9" t="n">
-        <v>0.198</v>
+        <v>0.574</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="14" t="inlineStr"/>
@@ -4118,28 +4118,28 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D81" s="9" t="n">
-        <v>0.665</v>
-      </c>
-      <c r="E81" s="15" t="n">
-        <v>0.0076</v>
+        <v>0.36</v>
+      </c>
+      <c r="E81" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>2555800</v>
+        <v>2796500</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>0.27</v>
+        <v>0.4</v>
       </c>
       <c r="H81" t="n">
-        <v>60.68</v>
+        <v>65.70999999999999</v>
       </c>
       <c r="I81" s="16" t="inlineStr">
         <is>
@@ -4147,10 +4147,10 @@
         </is>
       </c>
       <c r="J81" s="9" t="n">
-        <v>0.634</v>
+        <v>0.337</v>
       </c>
       <c r="K81" s="9" t="n">
-        <v>0.574</v>
+        <v>0.319</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="14" t="inlineStr"/>
@@ -4163,28 +4163,28 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D82" s="9" t="n">
-        <v>1.15</v>
+        <v>0.415</v>
       </c>
       <c r="E82" s="17" t="n">
-        <v>-0.0417</v>
+        <v>-0.0119</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>2283600</v>
+        <v>2680400</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="H82" t="n">
-        <v>50.13</v>
+        <v>56.5</v>
       </c>
       <c r="I82" s="16" t="inlineStr">
         <is>
@@ -4192,10 +4192,10 @@
         </is>
       </c>
       <c r="J82" s="9" t="n">
-        <v>1.163</v>
+        <v>0.409</v>
       </c>
       <c r="K82" s="9" t="n">
-        <v>1.1</v>
+        <v>0.41</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="14" t="inlineStr"/>
@@ -4208,28 +4208,28 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0393</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>TEAMSTR</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D83" s="9" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="E83" s="10" t="n">
-        <v>0</v>
+        <v>1.65</v>
+      </c>
+      <c r="E83" s="15" t="n">
+        <v>0.0123</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>2276900</v>
+        <v>2563300</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>0.75</v>
+        <v>0.4</v>
       </c>
       <c r="H83" t="n">
-        <v>31.51</v>
+        <v>34.08</v>
       </c>
       <c r="I83" s="13" t="inlineStr">
         <is>
@@ -4237,10 +4237,10 @@
         </is>
       </c>
       <c r="J83" s="9" t="n">
-        <v>0.244</v>
+        <v>1.732</v>
       </c>
       <c r="K83" s="9" t="n">
-        <v>0.243</v>
+        <v>1.847</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="14" t="inlineStr"/>
@@ -4253,28 +4253,28 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D84" s="9" t="n">
-        <v>0.42</v>
+        <v>1.09</v>
       </c>
       <c r="E84" s="17" t="n">
-        <v>-0.0118</v>
+        <v>-0.0268</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>2230900</v>
+        <v>2472700</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>0.38</v>
+        <v>0.52</v>
       </c>
       <c r="H84" t="n">
-        <v>56.23</v>
+        <v>76.75</v>
       </c>
       <c r="I84" s="16" t="inlineStr">
         <is>
@@ -4282,10 +4282,10 @@
         </is>
       </c>
       <c r="J84" s="9" t="n">
-        <v>0.402</v>
+        <v>0.973</v>
       </c>
       <c r="K84" s="9" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="14" t="inlineStr"/>
@@ -4298,28 +4298,28 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D85" s="9" t="n">
-        <v>0.78</v>
+        <v>0.42</v>
       </c>
       <c r="E85" s="17" t="n">
-        <v>-0.0064</v>
+        <v>-0.0118</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>2225100</v>
+        <v>2390000</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>0.38</v>
+        <v>0.41</v>
       </c>
       <c r="H85" t="n">
-        <v>74.67</v>
+        <v>56.23</v>
       </c>
       <c r="I85" s="16" t="inlineStr">
         <is>
@@ -4327,10 +4327,10 @@
         </is>
       </c>
       <c r="J85" s="9" t="n">
-        <v>0.767</v>
+        <v>0.402</v>
       </c>
       <c r="K85" s="9" t="n">
-        <v>0.752</v>
+        <v>0.4</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="14" t="inlineStr"/>
@@ -4343,39 +4343,39 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D86" s="9" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="E86" s="15" t="n">
-        <v>0.0123</v>
+        <v>0.51</v>
+      </c>
+      <c r="E86" s="17" t="n">
+        <v>-0.0377</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>2222700</v>
+        <v>2382200</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>0.34</v>
+        <v>0.64</v>
       </c>
       <c r="H86" t="n">
-        <v>34.08</v>
-      </c>
-      <c r="I86" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.34</v>
+      </c>
+      <c r="I86" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J86" s="9" t="n">
-        <v>1.732</v>
+        <v>0.512</v>
       </c>
       <c r="K86" s="9" t="n">
-        <v>1.847</v>
+        <v>0.464</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="14" t="inlineStr"/>
@@ -4397,19 +4397,19 @@
         </is>
       </c>
       <c r="D87" s="9" t="n">
-        <v>2.63</v>
+        <v>2.66</v>
       </c>
       <c r="E87" s="17" t="n">
-        <v>-0.0259</v>
+        <v>-0.0148</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>2221900</v>
+        <v>2353500</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>0.41</v>
+        <v>0.43</v>
       </c>
       <c r="H87" t="n">
-        <v>72.69</v>
+        <v>76.54000000000001</v>
       </c>
       <c r="I87" s="13" t="inlineStr">
         <is>
@@ -4417,7 +4417,7 @@
         </is>
       </c>
       <c r="J87" s="9" t="n">
-        <v>2.454</v>
+        <v>2.457</v>
       </c>
       <c r="K87" s="9" t="n">
         <v>2.118</v>
@@ -4433,28 +4433,28 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D88" s="9" t="n">
-        <v>0.51</v>
+        <v>1.15</v>
       </c>
       <c r="E88" s="17" t="n">
-        <v>-0.0377</v>
+        <v>-0.0417</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>2207700</v>
+        <v>2342100</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>0.59</v>
+        <v>0.26</v>
       </c>
       <c r="H88" t="n">
-        <v>52.34</v>
+        <v>50.13</v>
       </c>
       <c r="I88" s="16" t="inlineStr">
         <is>
@@ -4462,10 +4462,10 @@
         </is>
       </c>
       <c r="J88" s="9" t="n">
-        <v>0.512</v>
+        <v>1.163</v>
       </c>
       <c r="K88" s="9" t="n">
-        <v>0.464</v>
+        <v>1.1</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="14" t="inlineStr"/>
@@ -4478,39 +4478,39 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>0393</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>TEAMSTR</t>
         </is>
       </c>
       <c r="D89" s="9" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="E89" s="17" t="n">
-        <v>-0.0268</v>
+        <v>0.23</v>
+      </c>
+      <c r="E89" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>2206500</v>
+        <v>2276900</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>0.46</v>
+        <v>0.75</v>
       </c>
       <c r="H89" t="n">
-        <v>76.75</v>
-      </c>
-      <c r="I89" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>31.51</v>
+      </c>
+      <c r="I89" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J89" s="9" t="n">
-        <v>0.973</v>
+        <v>0.244</v>
       </c>
       <c r="K89" s="9" t="n">
-        <v>0.8</v>
+        <v>0.243</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="14" t="inlineStr"/>
@@ -4538,10 +4538,10 @@
         <v>-0.0112</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>2176500</v>
+        <v>2194500</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="H90" t="n">
         <v>47.93</v>
@@ -4583,7 +4583,7 @@
         <v>0.018</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>2123100</v>
+        <v>2136100</v>
       </c>
       <c r="G91" s="12" t="n">
         <v>0.5600000000000001</v>
@@ -4628,10 +4628,10 @@
         <v>0</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>2002000</v>
+        <v>2108100</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="H92" t="n">
         <v>79.33</v>
@@ -4658,39 +4658,39 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0265</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>INFOM</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D93" s="9" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="E93" s="15" t="n">
-        <v>0.04969999999999999</v>
+        <v>4.79</v>
+      </c>
+      <c r="E93" s="17" t="n">
+        <v>-0.0021</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>1950100</v>
+        <v>2059100</v>
       </c>
       <c r="G93" s="12" t="n">
-        <v>5.68</v>
+        <v>0.11</v>
       </c>
       <c r="H93" t="n">
-        <v>73.53</v>
-      </c>
-      <c r="I93" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.75</v>
+      </c>
+      <c r="I93" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J93" s="9" t="n">
-        <v>1.59</v>
+        <v>4.845</v>
       </c>
       <c r="K93" s="9" t="n">
-        <v>1.536</v>
+        <v>4.96</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="14" t="inlineStr"/>
@@ -4703,28 +4703,28 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>5162</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>VSTECS</t>
         </is>
       </c>
       <c r="D94" s="9" t="n">
-        <v>0.55</v>
+        <v>1.65</v>
       </c>
       <c r="E94" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>1862600</v>
+        <v>2034300</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>1.04</v>
+        <v>1.37</v>
       </c>
       <c r="H94" t="n">
-        <v>63.26</v>
+        <v>50.17</v>
       </c>
       <c r="I94" s="16" t="inlineStr">
         <is>
@@ -4732,10 +4732,10 @@
         </is>
       </c>
       <c r="J94" s="9" t="n">
-        <v>0.498</v>
+        <v>1.636</v>
       </c>
       <c r="K94" s="9" t="n">
-        <v>0.401</v>
+        <v>1.692</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="14" t="inlineStr"/>
@@ -4748,28 +4748,28 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>5162</t>
+          <t>0265</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>VSTECS</t>
+          <t>INFOM</t>
         </is>
       </c>
       <c r="D95" s="9" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="E95" s="15" t="n">
-        <v>0.0061</v>
+        <v>0.04969999999999999</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>1846400</v>
+        <v>1954400</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>1.24</v>
+        <v>5.7</v>
       </c>
       <c r="H95" t="n">
-        <v>51.42</v>
+        <v>73.53</v>
       </c>
       <c r="I95" s="16" t="inlineStr">
         <is>
@@ -4777,10 +4777,10 @@
         </is>
       </c>
       <c r="J95" s="9" t="n">
-        <v>1.637</v>
+        <v>1.59</v>
       </c>
       <c r="K95" s="9" t="n">
-        <v>1.693</v>
+        <v>1.536</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="14" t="inlineStr"/>
@@ -4793,39 +4793,39 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D96" s="9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="E96" s="17" t="n">
-        <v>-0.0189</v>
+        <v>1.91</v>
+      </c>
+      <c r="E96" s="15" t="n">
+        <v>0.016</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>1838700</v>
+        <v>1915600</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>0.22</v>
+        <v>0.42</v>
       </c>
       <c r="H96" t="n">
-        <v>77.48999999999999</v>
-      </c>
-      <c r="I96" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.51</v>
+      </c>
+      <c r="I96" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J96" s="9" t="n">
-        <v>0.893</v>
+        <v>1.958</v>
       </c>
       <c r="K96" s="9" t="n">
-        <v>0.759</v>
+        <v>2.079</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="14" t="inlineStr"/>
@@ -4838,39 +4838,39 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D97" s="9" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="E97" s="15" t="n">
-        <v>0.016</v>
+        <v>1.04</v>
+      </c>
+      <c r="E97" s="17" t="n">
+        <v>-0.0189</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>1814400</v>
+        <v>1914200</v>
       </c>
       <c r="G97" s="12" t="n">
-        <v>0.4</v>
+        <v>0.23</v>
       </c>
       <c r="H97" t="n">
-        <v>39.51</v>
-      </c>
-      <c r="I97" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>77.48999999999999</v>
+      </c>
+      <c r="I97" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J97" s="9" t="n">
-        <v>1.958</v>
+        <v>0.893</v>
       </c>
       <c r="K97" s="9" t="n">
-        <v>2.079</v>
+        <v>0.759</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="14" t="inlineStr"/>
@@ -4883,39 +4883,39 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>4243</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>WTK</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D98" s="9" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="E98" s="17" t="n">
-        <v>-0.0204</v>
+        <v>0.555</v>
+      </c>
+      <c r="E98" s="15" t="n">
+        <v>0.0091</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>1724900</v>
+        <v>1909200</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.07</v>
       </c>
       <c r="H98" t="n">
-        <v>35.93</v>
-      </c>
-      <c r="I98" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.89</v>
+      </c>
+      <c r="I98" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J98" s="9" t="n">
-        <v>1.045</v>
+        <v>0.499</v>
       </c>
       <c r="K98" s="9" t="n">
-        <v>1.014</v>
+        <v>0.401</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="14" t="inlineStr"/>
@@ -4928,28 +4928,28 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>0272</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>TTVHB</t>
         </is>
       </c>
       <c r="D99" s="9" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="E99" s="10" t="n">
-        <v>0</v>
+        <v>0.24</v>
+      </c>
+      <c r="E99" s="17" t="n">
+        <v>-0.04</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>1671600</v>
+        <v>1897200</v>
       </c>
       <c r="G99" s="12" t="n">
-        <v>0.33</v>
+        <v>0.55</v>
       </c>
       <c r="H99" t="n">
-        <v>38.17</v>
+        <v>46.04</v>
       </c>
       <c r="I99" s="13" t="inlineStr">
         <is>
@@ -4957,10 +4957,10 @@
         </is>
       </c>
       <c r="J99" s="9" t="n">
-        <v>0.638</v>
+        <v>0.248</v>
       </c>
       <c r="K99" s="9" t="n">
-        <v>0.658</v>
+        <v>0.253</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="14" t="inlineStr"/>
@@ -4973,28 +4973,28 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0376</t>
+          <t>0223</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>IAB</t>
+          <t>SAMAIDEN</t>
         </is>
       </c>
       <c r="D100" s="9" t="n">
-        <v>1.3</v>
+        <v>2.88</v>
       </c>
       <c r="E100" s="15" t="n">
-        <v>0.0236</v>
+        <v>0.006999999999999999</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>1604500</v>
+        <v>1861200</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>1.07</v>
+        <v>0.75</v>
       </c>
       <c r="H100" t="n">
-        <v>50.37</v>
+        <v>89.38</v>
       </c>
       <c r="I100" s="16" t="inlineStr">
         <is>
@@ -5002,10 +5002,10 @@
         </is>
       </c>
       <c r="J100" s="9" t="n">
-        <v>1.284</v>
+        <v>2.186</v>
       </c>
       <c r="K100" s="9" t="n">
-        <v>1.345</v>
+        <v>1.768</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="14" t="inlineStr"/>
@@ -5018,28 +5018,28 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0358</t>
+          <t>0267</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>ICTZONE</t>
+          <t>ECA</t>
         </is>
       </c>
       <c r="D101" s="9" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E101" s="10" t="n">
-        <v>0</v>
+        <v>0.365</v>
+      </c>
+      <c r="E101" s="17" t="n">
+        <v>-0.0267</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>1602800</v>
+        <v>1845400</v>
       </c>
       <c r="G101" s="12" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="H101" t="n">
-        <v>50.51</v>
+        <v>42.31</v>
       </c>
       <c r="I101" s="13" t="inlineStr">
         <is>
@@ -5047,10 +5047,10 @@
         </is>
       </c>
       <c r="J101" s="9" t="n">
-        <v>0.262</v>
+        <v>0.394</v>
       </c>
       <c r="K101" s="9" t="n">
-        <v>0.251</v>
+        <v>0.372</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="14" t="inlineStr"/>
@@ -5063,28 +5063,28 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0272</t>
+          <t>5323</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>TTVHB</t>
+          <t>JPG</t>
         </is>
       </c>
       <c r="D102" s="9" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="E102" s="17" t="n">
-        <v>-0.04</v>
+        <v>1.8</v>
+      </c>
+      <c r="E102" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>1597000</v>
+        <v>1819100</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>0.47</v>
+        <v>0.26</v>
       </c>
       <c r="H102" t="n">
-        <v>46.04</v>
+        <v>35.54</v>
       </c>
       <c r="I102" s="13" t="inlineStr">
         <is>
@@ -5092,10 +5092,10 @@
         </is>
       </c>
       <c r="J102" s="9" t="n">
-        <v>0.248</v>
+        <v>1.902</v>
       </c>
       <c r="K102" s="9" t="n">
-        <v>0.253</v>
+        <v>1.966</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="14" t="inlineStr"/>
@@ -5108,39 +5108,39 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0233</t>
+          <t>4243</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>PEKAT</t>
+          <t>WTK</t>
         </is>
       </c>
       <c r="D103" s="9" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="E103" s="15" t="n">
-        <v>0.0213</v>
+        <v>0.955</v>
+      </c>
+      <c r="E103" s="17" t="n">
+        <v>-0.0255</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>1590300</v>
+        <v>1771800</v>
       </c>
       <c r="G103" s="12" t="n">
-        <v>0.73</v>
+        <v>0.71</v>
       </c>
       <c r="H103" t="n">
-        <v>89.54000000000001</v>
-      </c>
-      <c r="I103" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.37</v>
+      </c>
+      <c r="I103" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J103" s="9" t="n">
-        <v>2.253</v>
+        <v>1.045</v>
       </c>
       <c r="K103" s="9" t="n">
-        <v>1.952</v>
+        <v>1.014</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="14" t="inlineStr"/>
@@ -5153,39 +5153,39 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>0032</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>REDTONE</t>
+          <t>TENAGA</t>
         </is>
       </c>
       <c r="D104" s="9" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="E104" s="17" t="n">
-        <v>-0.0137</v>
+        <v>13.18</v>
+      </c>
+      <c r="E104" s="15" t="n">
+        <v>0.003</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>1561400</v>
+        <v>1752600</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>0.92</v>
+        <v>0.18</v>
       </c>
       <c r="H104" t="n">
-        <v>59.96</v>
-      </c>
-      <c r="I104" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>32.24</v>
+      </c>
+      <c r="I104" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J104" s="9" t="n">
-        <v>0.354</v>
+        <v>13.468</v>
       </c>
       <c r="K104" s="9" t="n">
-        <v>0.319</v>
+        <v>14.059</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="14" t="inlineStr"/>
@@ -5198,33 +5198,40 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>0470</t>
+          <t>0045</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>BFIELD</t>
+          <t>SSB8</t>
         </is>
       </c>
       <c r="D105" s="9" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="E105" s="10" t="n">
-        <v>0</v>
+        <v>0.64</v>
+      </c>
+      <c r="E105" s="17" t="n">
+        <v>-0.0303</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>1543100</v>
+        <v>1745500</v>
       </c>
       <c r="G105" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.46</v>
+      </c>
+      <c r="H105" t="n">
+        <v>57.65</v>
       </c>
       <c r="I105" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J105" s="9" t="n"/>
-      <c r="K105" s="9" t="n"/>
+      <c r="J105" s="9" t="n">
+        <v>0.619</v>
+      </c>
+      <c r="K105" s="9" t="n">
+        <v>0.581</v>
+      </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="14" t="inlineStr"/>
     </row>
@@ -5236,28 +5243,28 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>5212</t>
+          <t>0233</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>PAVREIT</t>
+          <t>PEKAT</t>
         </is>
       </c>
       <c r="D106" s="9" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="E106" s="10" t="n">
-        <v>0</v>
+        <v>2.86</v>
+      </c>
+      <c r="E106" s="15" t="n">
+        <v>0.0142</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>1534600</v>
+        <v>1734400</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>0.54</v>
+        <v>0.8</v>
       </c>
       <c r="H106" t="n">
-        <v>41.51</v>
+        <v>89.31999999999999</v>
       </c>
       <c r="I106" s="16" t="inlineStr">
         <is>
@@ -5265,10 +5272,10 @@
         </is>
       </c>
       <c r="J106" s="9" t="n">
-        <v>1.584</v>
+        <v>2.251</v>
       </c>
       <c r="K106" s="9" t="n">
-        <v>1.647</v>
+        <v>1.951</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="14" t="inlineStr"/>
@@ -5281,28 +5288,28 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D107" s="9" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="E107" s="10" t="n">
-        <v>0</v>
+        <v>0.61</v>
+      </c>
+      <c r="E107" s="17" t="n">
+        <v>-0.008100000000000001</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>1532400</v>
+        <v>1728400</v>
       </c>
       <c r="G107" s="12" t="n">
-        <v>0.35</v>
+        <v>0.58</v>
       </c>
       <c r="H107" t="n">
-        <v>42.29</v>
+        <v>57.09</v>
       </c>
       <c r="I107" s="13" t="inlineStr">
         <is>
@@ -5310,10 +5317,10 @@
         </is>
       </c>
       <c r="J107" s="9" t="n">
-        <v>0.377</v>
+        <v>0.608</v>
       </c>
       <c r="K107" s="9" t="n">
-        <v>0.391</v>
+        <v>0.588</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="14" t="inlineStr"/>
@@ -5326,39 +5333,39 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>0268</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>L&amp;PBHD</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D108" s="9" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="E108" s="15" t="n">
-        <v>0.0244</v>
+        <v>0.605</v>
+      </c>
+      <c r="E108" s="17" t="n">
+        <v>-0.008199999999999999</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>1528600</v>
+        <v>1692600</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.34</v>
       </c>
       <c r="H108" t="n">
-        <v>71.81999999999999</v>
-      </c>
-      <c r="I108" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.92</v>
+      </c>
+      <c r="I108" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J108" s="9" t="n">
-        <v>0.187</v>
+        <v>0.637</v>
       </c>
       <c r="K108" s="9" t="n">
-        <v>0.156</v>
+        <v>0.657</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="14" t="inlineStr"/>
@@ -5371,28 +5378,28 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>7161</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>TENAGA</t>
+          <t>KERJAYA</t>
         </is>
       </c>
       <c r="D109" s="9" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="E109" s="15" t="n">
-        <v>0.0046</v>
+        <v>3.6</v>
+      </c>
+      <c r="E109" s="17" t="n">
+        <v>-0.0083</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>1500500</v>
+        <v>1662400</v>
       </c>
       <c r="G109" s="12" t="n">
-        <v>0.15</v>
+        <v>0.52</v>
       </c>
       <c r="H109" t="n">
-        <v>33.3</v>
+        <v>73.84</v>
       </c>
       <c r="I109" s="16" t="inlineStr">
         <is>
@@ -5400,10 +5407,10 @@
         </is>
       </c>
       <c r="J109" s="9" t="n">
-        <v>13.47</v>
+        <v>3.311</v>
       </c>
       <c r="K109" s="9" t="n">
-        <v>14.059</v>
+        <v>2.885</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="14" t="inlineStr"/>
@@ -5416,39 +5423,39 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>0032</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>REDTONE</t>
         </is>
       </c>
       <c r="D110" s="9" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="E110" s="15" t="n">
-        <v>0.014</v>
+        <v>0.36</v>
+      </c>
+      <c r="E110" s="17" t="n">
+        <v>-0.0137</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>1491100</v>
+        <v>1631400</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>0.6</v>
+        <v>0.96</v>
       </c>
       <c r="H110" t="n">
-        <v>89.56999999999999</v>
-      </c>
-      <c r="I110" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>59.96</v>
+      </c>
+      <c r="I110" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J110" s="9" t="n">
-        <v>2.188</v>
+        <v>0.354</v>
       </c>
       <c r="K110" s="9" t="n">
-        <v>1.769</v>
+        <v>0.319</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="14" t="inlineStr"/>
@@ -5461,33 +5468,40 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>0468</t>
+          <t>0358</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>UNIPAC</t>
+          <t>ICTZONE</t>
         </is>
       </c>
       <c r="D111" s="9" t="n">
-        <v>0.245</v>
-      </c>
-      <c r="E111" s="17" t="n">
-        <v>-0.0392</v>
+        <v>0.26</v>
+      </c>
+      <c r="E111" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>1480600</v>
+        <v>1612800</v>
       </c>
       <c r="G111" s="12" t="n">
-        <v>0.09</v>
+        <v>0.58</v>
+      </c>
+      <c r="H111" t="n">
+        <v>50.51</v>
       </c>
       <c r="I111" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J111" s="9" t="n"/>
-      <c r="K111" s="9" t="n"/>
+      <c r="J111" s="9" t="n">
+        <v>0.262</v>
+      </c>
+      <c r="K111" s="9" t="n">
+        <v>0.251</v>
+      </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="14" t="inlineStr"/>
     </row>
@@ -5499,39 +5513,39 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>5212</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>PAVREIT</t>
         </is>
       </c>
       <c r="D112" s="9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="E112" s="10" t="n">
-        <v>0</v>
+        <v>1.55</v>
+      </c>
+      <c r="E112" s="17" t="n">
+        <v>-0.0064</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>1476100</v>
+        <v>1612000</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>0.08</v>
+        <v>0.57</v>
       </c>
       <c r="H112" t="n">
-        <v>40.81</v>
-      </c>
-      <c r="I112" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>39.82</v>
+      </c>
+      <c r="I112" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J112" s="9" t="n">
-        <v>4.846</v>
+        <v>1.584</v>
       </c>
       <c r="K112" s="9" t="n">
-        <v>4.96</v>
+        <v>1.647</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="14" t="inlineStr"/>
@@ -5544,28 +5558,28 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>0045</t>
+          <t>0376</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>SSB8</t>
+          <t>IAB</t>
         </is>
       </c>
       <c r="D113" s="9" t="n">
-        <v>0.645</v>
-      </c>
-      <c r="E113" s="17" t="n">
-        <v>-0.0227</v>
+        <v>1.3</v>
+      </c>
+      <c r="E113" s="15" t="n">
+        <v>0.0236</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>1435200</v>
+        <v>1609500</v>
       </c>
       <c r="G113" s="12" t="n">
-        <v>0.38</v>
+        <v>1.07</v>
       </c>
       <c r="H113" t="n">
-        <v>59.13</v>
+        <v>50.37</v>
       </c>
       <c r="I113" s="16" t="inlineStr">
         <is>
@@ -5573,10 +5587,10 @@
         </is>
       </c>
       <c r="J113" s="9" t="n">
-        <v>0.619</v>
+        <v>1.284</v>
       </c>
       <c r="K113" s="9" t="n">
-        <v>0.581</v>
+        <v>1.345</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="14" t="inlineStr"/>
@@ -5589,39 +5603,39 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>0128</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>JPG</t>
+          <t>FRONTKN</t>
         </is>
       </c>
       <c r="D114" s="9" t="n">
-        <v>1.79</v>
+        <v>4.96</v>
       </c>
       <c r="E114" s="17" t="n">
-        <v>-0.005600000000000001</v>
+        <v>-0.0178</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>1435200</v>
+        <v>1595400</v>
       </c>
       <c r="G114" s="12" t="n">
-        <v>0.2</v>
+        <v>0.29</v>
       </c>
       <c r="H114" t="n">
-        <v>34.72</v>
-      </c>
-      <c r="I114" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.52</v>
+      </c>
+      <c r="I114" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J114" s="9" t="n">
-        <v>1.901</v>
+        <v>4.98</v>
       </c>
       <c r="K114" s="9" t="n">
-        <v>1.966</v>
+        <v>5.04</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="14" t="inlineStr"/>
@@ -5634,40 +5648,33 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>0128</t>
+          <t>0470</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>FRONTKN</t>
+          <t>BFIELD</t>
         </is>
       </c>
       <c r="D115" s="9" t="n">
-        <v>4.96</v>
+        <v>0.475</v>
       </c>
       <c r="E115" s="17" t="n">
-        <v>-0.0178</v>
+        <v>-0.0104</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>1386900</v>
+        <v>1563100</v>
       </c>
       <c r="G115" s="12" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="H115" t="n">
-        <v>48.52</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I115" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J115" s="9" t="n">
-        <v>4.98</v>
-      </c>
-      <c r="K115" s="9" t="n">
-        <v>5.04</v>
-      </c>
+      <c r="J115" s="9" t="n"/>
+      <c r="K115" s="9" t="n"/>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="14" t="inlineStr"/>
     </row>
@@ -5679,39 +5686,39 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D116" s="9" t="n">
-        <v>0.65</v>
+        <v>0.37</v>
       </c>
       <c r="E116" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>1385100</v>
+        <v>1542400</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>0.41</v>
+        <v>0.35</v>
       </c>
       <c r="H116" t="n">
-        <v>70.55</v>
-      </c>
-      <c r="I116" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.29</v>
+      </c>
+      <c r="I116" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J116" s="9" t="n">
-        <v>0.634</v>
+        <v>0.377</v>
       </c>
       <c r="K116" s="9" t="n">
-        <v>0.591</v>
+        <v>0.391</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="14" t="inlineStr"/>
@@ -5724,28 +5731,28 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>0268</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>L&amp;PBHD</t>
         </is>
       </c>
       <c r="D117" s="9" t="n">
-        <v>0.425</v>
-      </c>
-      <c r="E117" s="17" t="n">
-        <v>-0.0449</v>
+        <v>0.21</v>
+      </c>
+      <c r="E117" s="15" t="n">
+        <v>0.0244</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>1325500</v>
+        <v>1528600</v>
       </c>
       <c r="G117" s="12" t="n">
-        <v>0.41</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H117" t="n">
-        <v>45.13</v>
+        <v>71.81999999999999</v>
       </c>
       <c r="I117" s="16" t="inlineStr">
         <is>
@@ -5753,10 +5760,10 @@
         </is>
       </c>
       <c r="J117" s="9" t="n">
-        <v>0.439</v>
+        <v>0.187</v>
       </c>
       <c r="K117" s="9" t="n">
-        <v>0.432</v>
+        <v>0.156</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="14" t="inlineStr"/>
@@ -5769,28 +5776,28 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D118" s="9" t="n">
-        <v>0.345</v>
-      </c>
-      <c r="E118" s="17" t="n">
-        <v>-0.0143</v>
+        <v>2.24</v>
+      </c>
+      <c r="E118" s="15" t="n">
+        <v>0.004500000000000001</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>1313500</v>
+        <v>1510300</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="H118" t="n">
-        <v>43.18</v>
+        <v>53.1</v>
       </c>
       <c r="I118" s="13" t="inlineStr">
         <is>
@@ -5798,10 +5805,10 @@
         </is>
       </c>
       <c r="J118" s="9" t="n">
-        <v>0.352</v>
+        <v>2.225</v>
       </c>
       <c r="K118" s="9" t="n">
-        <v>0.35</v>
+        <v>2.104</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="14" t="inlineStr"/>
@@ -5814,39 +5821,39 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>7161</t>
+          <t>0307</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>KERJAYA</t>
+          <t>KENERGY</t>
         </is>
       </c>
       <c r="D119" s="9" t="n">
-        <v>3.6</v>
+        <v>0.345</v>
       </c>
       <c r="E119" s="17" t="n">
-        <v>-0.0083</v>
+        <v>-0.0548</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>1312400</v>
+        <v>1485200</v>
       </c>
       <c r="G119" s="12" t="n">
-        <v>0.41</v>
+        <v>2.8</v>
       </c>
       <c r="H119" t="n">
-        <v>73.84</v>
-      </c>
-      <c r="I119" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>31.82</v>
+      </c>
+      <c r="I119" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J119" s="9" t="n">
-        <v>3.311</v>
+        <v>0.382</v>
       </c>
       <c r="K119" s="9" t="n">
-        <v>2.885</v>
+        <v>0.385</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="14" t="inlineStr"/>
@@ -5859,40 +5866,33 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>7225</t>
+          <t>0468</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>UNIPAC</t>
         </is>
       </c>
       <c r="D120" s="9" t="n">
-        <v>0.215</v>
+        <v>0.245</v>
       </c>
       <c r="E120" s="17" t="n">
-        <v>-0.0227</v>
+        <v>-0.0392</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>1297500</v>
+        <v>1484000</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="H120" t="n">
-        <v>51</v>
-      </c>
-      <c r="I120" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J120" s="9" t="n">
-        <v>0.214</v>
-      </c>
-      <c r="K120" s="9" t="n">
-        <v>0.212</v>
-      </c>
+        <v>0.09</v>
+      </c>
+      <c r="I120" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J120" s="9" t="n"/>
+      <c r="K120" s="9" t="n"/>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="14" t="inlineStr"/>
     </row>
@@ -5904,39 +5904,39 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>0172</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>OCK</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D121" s="9" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="E121" s="17" t="n">
-        <v>-0.0204</v>
+        <v>7.49</v>
+      </c>
+      <c r="E121" s="15" t="n">
+        <v>0.004</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>1292800</v>
+        <v>1447900</v>
       </c>
       <c r="G121" s="12" t="n">
-        <v>0.39</v>
+        <v>0.2</v>
       </c>
       <c r="H121" t="n">
-        <v>68.65000000000001</v>
-      </c>
-      <c r="I121" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.61</v>
+      </c>
+      <c r="I121" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J121" s="9" t="n">
-        <v>0.446</v>
+        <v>7.687</v>
       </c>
       <c r="K121" s="9" t="n">
-        <v>0.404</v>
+        <v>7.843</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="14" t="inlineStr"/>
@@ -5949,28 +5949,28 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D122" s="9" t="n">
-        <v>1.96</v>
+        <v>7.96</v>
       </c>
       <c r="E122" s="15" t="n">
-        <v>0.0051</v>
+        <v>0.0076</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>1284800</v>
+        <v>1438800</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>0.18</v>
+        <v>0.11</v>
       </c>
       <c r="H122" t="n">
-        <v>46.89</v>
+        <v>60.62</v>
       </c>
       <c r="I122" s="16" t="inlineStr">
         <is>
@@ -5978,10 +5978,10 @@
         </is>
       </c>
       <c r="J122" s="9" t="n">
-        <v>1.984</v>
+        <v>7.803</v>
       </c>
       <c r="K122" s="9" t="n">
-        <v>1.974</v>
+        <v>7.73</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="14" t="inlineStr"/>
@@ -5994,28 +5994,28 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>0104</t>
+          <t>7225</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>GENETEC</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="D123" s="9" t="n">
-        <v>0.315</v>
+        <v>0.215</v>
       </c>
       <c r="E123" s="17" t="n">
-        <v>-0.0156</v>
+        <v>-0.0227</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>1253200</v>
+        <v>1406700</v>
       </c>
       <c r="G123" s="12" t="n">
-        <v>0.2</v>
+        <v>0.24</v>
       </c>
       <c r="H123" t="n">
-        <v>44.97</v>
+        <v>51</v>
       </c>
       <c r="I123" s="16" t="inlineStr">
         <is>
@@ -6023,10 +6023,10 @@
         </is>
       </c>
       <c r="J123" s="9" t="n">
-        <v>0.321</v>
+        <v>0.214</v>
       </c>
       <c r="K123" s="9" t="n">
-        <v>0.339</v>
+        <v>0.212</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" s="14" t="inlineStr"/>
@@ -6039,39 +6039,39 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>3379</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>INSAS</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D124" s="9" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E124" s="15" t="n">
-        <v>0.0169</v>
+        <v>0.645</v>
+      </c>
+      <c r="E124" s="17" t="n">
+        <v>-0.0077</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>1246800</v>
+        <v>1394100</v>
       </c>
       <c r="G124" s="12" t="n">
-        <v>2.15</v>
+        <v>0.42</v>
       </c>
       <c r="H124" t="n">
-        <v>53.79</v>
-      </c>
-      <c r="I124" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>65.54000000000001</v>
+      </c>
+      <c r="I124" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J124" s="9" t="n">
-        <v>0.895</v>
+        <v>0.634</v>
       </c>
       <c r="K124" s="9" t="n">
-        <v>0.9</v>
+        <v>0.591</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="14" t="inlineStr"/>
@@ -6084,39 +6084,39 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>0172</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>OCK</t>
         </is>
       </c>
       <c r="D125" s="9" t="n">
-        <v>7.48</v>
-      </c>
-      <c r="E125" s="15" t="n">
-        <v>0.0027</v>
+        <v>0.48</v>
+      </c>
+      <c r="E125" s="17" t="n">
+        <v>-0.0204</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>1207600</v>
+        <v>1370100</v>
       </c>
       <c r="G125" s="12" t="n">
-        <v>0.16</v>
+        <v>0.41</v>
       </c>
       <c r="H125" t="n">
-        <v>38.06</v>
-      </c>
-      <c r="I125" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68.65000000000001</v>
+      </c>
+      <c r="I125" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J125" s="9" t="n">
-        <v>7.686</v>
+        <v>0.446</v>
       </c>
       <c r="K125" s="9" t="n">
-        <v>7.843</v>
+        <v>0.404</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="14" t="inlineStr"/>
@@ -6129,28 +6129,28 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>ALPHA</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D126" s="9" t="n">
-        <v>0.255</v>
-      </c>
-      <c r="E126" s="15" t="n">
-        <v>0.0408</v>
+        <v>1.95</v>
+      </c>
+      <c r="E126" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>1198300</v>
+        <v>1369300</v>
       </c>
       <c r="G126" s="12" t="n">
-        <v>0.58</v>
+        <v>0.19</v>
       </c>
       <c r="H126" t="n">
-        <v>53.99</v>
+        <v>45.43</v>
       </c>
       <c r="I126" s="16" t="inlineStr">
         <is>
@@ -6158,10 +6158,10 @@
         </is>
       </c>
       <c r="J126" s="9" t="n">
-        <v>0.248</v>
+        <v>1.983</v>
       </c>
       <c r="K126" s="9" t="n">
-        <v>0.261</v>
+        <v>1.974</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="14" t="inlineStr"/>
@@ -6174,39 +6174,39 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>0307</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>KENERGY</t>
+          <t>ALPHA</t>
         </is>
       </c>
       <c r="D127" s="9" t="n">
-        <v>0.355</v>
-      </c>
-      <c r="E127" s="17" t="n">
-        <v>-0.0274</v>
+        <v>0.245</v>
+      </c>
+      <c r="E127" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>1194800</v>
+        <v>1365000</v>
       </c>
       <c r="G127" s="12" t="n">
-        <v>2.25</v>
+        <v>0.66</v>
       </c>
       <c r="H127" t="n">
-        <v>34.74</v>
-      </c>
-      <c r="I127" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>44.33</v>
+      </c>
+      <c r="I127" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J127" s="9" t="n">
-        <v>0.383</v>
+        <v>0.247</v>
       </c>
       <c r="K127" s="9" t="n">
-        <v>0.385</v>
+        <v>0.261</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="14" t="inlineStr"/>
@@ -6219,28 +6219,28 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>5005</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>UNISEM</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D128" s="9" t="n">
-        <v>4.46</v>
-      </c>
-      <c r="E128" s="17" t="n">
-        <v>-0.0262</v>
+        <v>0.725</v>
+      </c>
+      <c r="E128" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>1182700</v>
+        <v>1361500</v>
       </c>
       <c r="G128" s="12" t="n">
-        <v>0.51</v>
+        <v>0.23</v>
       </c>
       <c r="H128" t="n">
-        <v>52.25</v>
+        <v>69.25</v>
       </c>
       <c r="I128" s="16" t="inlineStr">
         <is>
@@ -6248,10 +6248,10 @@
         </is>
       </c>
       <c r="J128" s="9" t="n">
-        <v>4.407</v>
+        <v>0.672</v>
       </c>
       <c r="K128" s="9" t="n">
-        <v>4.429</v>
+        <v>0.615</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="14" t="inlineStr"/>
@@ -6264,33 +6264,40 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>0471</t>
+          <t>5005</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>PIONEER</t>
+          <t>UNISEM</t>
         </is>
       </c>
       <c r="D129" s="9" t="n">
-        <v>0.285</v>
-      </c>
-      <c r="E129" s="10" t="n">
-        <v>0</v>
+        <v>4.48</v>
+      </c>
+      <c r="E129" s="17" t="n">
+        <v>-0.0218</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>1164200</v>
+        <v>1360100</v>
       </c>
       <c r="G129" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.59</v>
+      </c>
+      <c r="H129" t="n">
+        <v>52.97</v>
       </c>
       <c r="I129" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J129" s="9" t="n"/>
-      <c r="K129" s="9" t="n"/>
+      <c r="J129" s="9" t="n">
+        <v>4.408</v>
+      </c>
+      <c r="K129" s="9" t="n">
+        <v>4.429</v>
+      </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="14" t="inlineStr"/>
     </row>
@@ -6302,39 +6309,39 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D130" s="9" t="n">
-        <v>2.96</v>
+        <v>0.31</v>
       </c>
       <c r="E130" s="17" t="n">
-        <v>-0.0166</v>
+        <v>-0.0313</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>1156900</v>
+        <v>1355400</v>
       </c>
       <c r="G130" s="12" t="n">
-        <v>0.37</v>
+        <v>0.21</v>
       </c>
       <c r="H130" t="n">
-        <v>45.05</v>
-      </c>
-      <c r="I130" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>42.76</v>
+      </c>
+      <c r="I130" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J130" s="9" t="n">
-        <v>3.008</v>
+        <v>0.32</v>
       </c>
       <c r="K130" s="9" t="n">
-        <v>3.04</v>
+        <v>0.339</v>
       </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" s="14" t="inlineStr"/>
@@ -6347,39 +6354,39 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D131" s="9" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="E131" s="10" t="n">
-        <v>0</v>
+        <v>0.425</v>
+      </c>
+      <c r="E131" s="17" t="n">
+        <v>-0.0449</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>1155700</v>
+        <v>1350500</v>
       </c>
       <c r="G131" s="12" t="n">
-        <v>0.61</v>
+        <v>0.41</v>
       </c>
       <c r="H131" t="n">
-        <v>43.55</v>
-      </c>
-      <c r="I131" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>45.13</v>
+      </c>
+      <c r="I131" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J131" s="9" t="n">
-        <v>0.996</v>
+        <v>0.439</v>
       </c>
       <c r="K131" s="9" t="n">
-        <v>1.012</v>
+        <v>0.432</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="14" t="inlineStr"/>
@@ -6392,28 +6399,28 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>0217</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>PWRWELL</t>
         </is>
       </c>
       <c r="D132" s="9" t="n">
-        <v>7.95</v>
-      </c>
-      <c r="E132" s="15" t="n">
-        <v>0.0063</v>
+        <v>1.16</v>
+      </c>
+      <c r="E132" s="17" t="n">
+        <v>-0.0333</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>1153800</v>
+        <v>1330400</v>
       </c>
       <c r="G132" s="12" t="n">
-        <v>0.09</v>
+        <v>0.37</v>
       </c>
       <c r="H132" t="n">
-        <v>60.18</v>
+        <v>62.58</v>
       </c>
       <c r="I132" s="16" t="inlineStr">
         <is>
@@ -6421,10 +6428,10 @@
         </is>
       </c>
       <c r="J132" s="9" t="n">
-        <v>7.802</v>
+        <v>1.106</v>
       </c>
       <c r="K132" s="9" t="n">
-        <v>7.73</v>
+        <v>1.006</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="14" t="inlineStr"/>
@@ -6437,39 +6444,39 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>SPSETIA</t>
         </is>
       </c>
       <c r="D133" s="9" t="n">
-        <v>0.58</v>
+        <v>0.775</v>
       </c>
       <c r="E133" s="17" t="n">
-        <v>-0.0252</v>
+        <v>-0.0064</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>1127700</v>
+        <v>1325000</v>
       </c>
       <c r="G133" s="12" t="n">
-        <v>0.35</v>
+        <v>0.32</v>
       </c>
       <c r="H133" t="n">
-        <v>52.94</v>
-      </c>
-      <c r="I133" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.33</v>
+      </c>
+      <c r="I133" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J133" s="9" t="n">
-        <v>0.57</v>
+        <v>0.797</v>
       </c>
       <c r="K133" s="9" t="n">
-        <v>0.575</v>
+        <v>0.849</v>
       </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" s="14" t="inlineStr"/>
@@ -6482,39 +6489,39 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>7160</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>PENTA</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="D134" s="9" t="n">
-        <v>5.2</v>
+        <v>0.345</v>
       </c>
       <c r="E134" s="17" t="n">
-        <v>-0.0207</v>
+        <v>-0.0143</v>
       </c>
       <c r="F134" s="11" t="n">
-        <v>1117700</v>
+        <v>1314400</v>
       </c>
       <c r="G134" s="12" t="n">
-        <v>0.46</v>
+        <v>0.19</v>
       </c>
       <c r="H134" t="n">
-        <v>47.73</v>
-      </c>
-      <c r="I134" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.18</v>
+      </c>
+      <c r="I134" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J134" s="9" t="n">
-        <v>5.279</v>
+        <v>0.352</v>
       </c>
       <c r="K134" s="9" t="n">
-        <v>5.275</v>
+        <v>0.35</v>
       </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" s="14" t="inlineStr"/>
@@ -6527,28 +6534,28 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>IOICORP</t>
         </is>
       </c>
       <c r="D135" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="E135" s="17" t="n">
-        <v>-0.02</v>
+        <v>4.77</v>
+      </c>
+      <c r="E135" s="15" t="n">
+        <v>0.0021</v>
       </c>
       <c r="F135" s="11" t="n">
-        <v>1094700</v>
+        <v>1282200</v>
       </c>
       <c r="G135" s="12" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="H135" t="n">
-        <v>44.46</v>
+        <v>55.58</v>
       </c>
       <c r="I135" s="13" t="inlineStr">
         <is>
@@ -6556,10 +6563,10 @@
         </is>
       </c>
       <c r="J135" s="9" t="n">
-        <v>4.58</v>
+        <v>4.747</v>
       </c>
       <c r="K135" s="9" t="n">
-        <v>4.537</v>
+        <v>4.589</v>
       </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" s="14" t="inlineStr"/>
@@ -6572,39 +6579,39 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>7160</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>KPJ</t>
+          <t>PENTA</t>
         </is>
       </c>
       <c r="D136" s="9" t="n">
-        <v>2.63</v>
+        <v>5.2</v>
       </c>
       <c r="E136" s="17" t="n">
-        <v>-0.015</v>
+        <v>-0.0207</v>
       </c>
       <c r="F136" s="11" t="n">
-        <v>1094100</v>
+        <v>1275700</v>
       </c>
       <c r="G136" s="12" t="n">
-        <v>0.12</v>
+        <v>0.53</v>
       </c>
       <c r="H136" t="n">
-        <v>41.54</v>
-      </c>
-      <c r="I136" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.73</v>
+      </c>
+      <c r="I136" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J136" s="9" t="n">
-        <v>2.674</v>
+        <v>5.279</v>
       </c>
       <c r="K136" s="9" t="n">
-        <v>2.872</v>
+        <v>5.275</v>
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" s="14" t="inlineStr"/>
@@ -6617,39 +6624,39 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>8524</t>
+          <t>3379</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>TALIWRK</t>
+          <t>INSAS</t>
         </is>
       </c>
       <c r="D137" s="9" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="E137" s="10" t="n">
-        <v>0</v>
+        <v>0.905</v>
+      </c>
+      <c r="E137" s="15" t="n">
+        <v>0.0226</v>
       </c>
       <c r="F137" s="11" t="n">
-        <v>1093900</v>
+        <v>1259800</v>
       </c>
       <c r="G137" s="12" t="n">
-        <v>0.35</v>
+        <v>2.17</v>
       </c>
       <c r="H137" t="n">
-        <v>54.09</v>
-      </c>
-      <c r="I137" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>57.27</v>
+      </c>
+      <c r="I137" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J137" s="9" t="n">
-        <v>0.254</v>
+        <v>0.895</v>
       </c>
       <c r="K137" s="9" t="n">
-        <v>0.271</v>
+        <v>0.9</v>
       </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" s="14" t="inlineStr"/>
@@ -6662,28 +6669,28 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>KPJ</t>
         </is>
       </c>
       <c r="D138" s="9" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="E138" s="10" t="n">
-        <v>0</v>
+        <v>2.64</v>
+      </c>
+      <c r="E138" s="17" t="n">
+        <v>-0.0112</v>
       </c>
       <c r="F138" s="11" t="n">
-        <v>1085900</v>
+        <v>1233200</v>
       </c>
       <c r="G138" s="12" t="n">
-        <v>0.39</v>
+        <v>0.14</v>
       </c>
       <c r="H138" t="n">
-        <v>57.08</v>
+        <v>42.35</v>
       </c>
       <c r="I138" s="16" t="inlineStr">
         <is>
@@ -6691,10 +6698,10 @@
         </is>
       </c>
       <c r="J138" s="9" t="n">
-        <v>0.757</v>
+        <v>2.675</v>
       </c>
       <c r="K138" s="9" t="n">
-        <v>0.74</v>
+        <v>2.872</v>
       </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" s="14" t="inlineStr"/>
@@ -6722,10 +6729,10 @@
         <v>-0.031</v>
       </c>
       <c r="F139" s="11" t="n">
-        <v>1062900</v>
+        <v>1212100</v>
       </c>
       <c r="G139" s="12" t="n">
-        <v>0.34</v>
+        <v>0.39</v>
       </c>
       <c r="H139" t="n">
         <v>45.53</v>
@@ -6752,39 +6759,39 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>0395</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>OGX</t>
+          <t>SKYECHIP</t>
         </is>
       </c>
       <c r="D140" s="9" t="n">
-        <v>0.43</v>
+        <v>2.95</v>
       </c>
       <c r="E140" s="17" t="n">
-        <v>-0.0227</v>
+        <v>-0.0199</v>
       </c>
       <c r="F140" s="11" t="n">
-        <v>1055100</v>
+        <v>1206200</v>
       </c>
       <c r="G140" s="12" t="n">
-        <v>0.34</v>
+        <v>0.39</v>
       </c>
       <c r="H140" t="n">
-        <v>47.37</v>
-      </c>
-      <c r="I140" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.26</v>
+      </c>
+      <c r="I140" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J140" s="9" t="n">
-        <v>0.434</v>
+        <v>3.007</v>
       </c>
       <c r="K140" s="9" t="n">
-        <v>0.452</v>
+        <v>3.04</v>
       </c>
       <c r="L140" t="inlineStr"/>
       <c r="M140" s="14" t="inlineStr"/>
@@ -6797,39 +6804,39 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>0450</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>MFGROUP</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D141" s="9" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E141" s="10" t="n">
-        <v>0</v>
+        <v>0.84</v>
+      </c>
+      <c r="E141" s="17" t="n">
+        <v>-0.0059</v>
       </c>
       <c r="F141" s="11" t="n">
-        <v>1052600</v>
+        <v>1199900</v>
       </c>
       <c r="G141" s="12" t="n">
-        <v>1.33</v>
+        <v>0.4</v>
       </c>
       <c r="H141" t="n">
-        <v>45.51</v>
-      </c>
-      <c r="I141" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.11</v>
+      </c>
+      <c r="I141" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J141" s="9" t="n">
-        <v>0.261</v>
+        <v>0.801</v>
       </c>
       <c r="K141" s="9" t="n">
-        <v>0.266</v>
+        <v>0.72</v>
       </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" s="14" t="inlineStr"/>
@@ -6842,28 +6849,28 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D142" s="9" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="E142" s="15" t="n">
-        <v>0.004500000000000001</v>
+        <v>4.4</v>
+      </c>
+      <c r="E142" s="17" t="n">
+        <v>-0.02</v>
       </c>
       <c r="F142" s="11" t="n">
-        <v>1034700</v>
+        <v>1191800</v>
       </c>
       <c r="G142" s="12" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="H142" t="n">
-        <v>53.1</v>
+        <v>44.46</v>
       </c>
       <c r="I142" s="13" t="inlineStr">
         <is>
@@ -6871,10 +6878,10 @@
         </is>
       </c>
       <c r="J142" s="9" t="n">
-        <v>2.225</v>
+        <v>4.58</v>
       </c>
       <c r="K142" s="9" t="n">
-        <v>2.104</v>
+        <v>4.537</v>
       </c>
       <c r="L142" t="inlineStr"/>
       <c r="M142" s="14" t="inlineStr"/>
@@ -6887,39 +6894,39 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>5073</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>NAIM</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D143" s="9" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="E143" s="17" t="n">
-        <v>-0.0455</v>
+        <v>0.98</v>
+      </c>
+      <c r="E143" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F143" s="11" t="n">
-        <v>1030800</v>
+        <v>1169900</v>
       </c>
       <c r="G143" s="12" t="n">
-        <v>0.83</v>
+        <v>0.62</v>
       </c>
       <c r="H143" t="n">
-        <v>59.12</v>
-      </c>
-      <c r="I143" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.55</v>
+      </c>
+      <c r="I143" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J143" s="9" t="n">
-        <v>0.629</v>
+        <v>0.996</v>
       </c>
       <c r="K143" s="9" t="n">
-        <v>0.612</v>
+        <v>1.012</v>
       </c>
       <c r="L143" t="inlineStr"/>
       <c r="M143" s="14" t="inlineStr"/>
@@ -6932,40 +6939,33 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>0267</t>
+          <t>0471</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>ECA</t>
+          <t>PIONEER</t>
         </is>
       </c>
       <c r="D144" s="9" t="n">
-        <v>0.365</v>
-      </c>
-      <c r="E144" s="17" t="n">
-        <v>-0.0267</v>
+        <v>0.285</v>
+      </c>
+      <c r="E144" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F144" s="11" t="n">
-        <v>1016700</v>
+        <v>1168700</v>
       </c>
       <c r="G144" s="12" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="H144" t="n">
-        <v>42.31</v>
-      </c>
-      <c r="I144" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J144" s="9" t="n">
-        <v>0.394</v>
-      </c>
-      <c r="K144" s="9" t="n">
-        <v>0.372</v>
-      </c>
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I144" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J144" s="9" t="n"/>
+      <c r="K144" s="9" t="n"/>
       <c r="L144" t="inlineStr"/>
       <c r="M144" s="14" t="inlineStr"/>
     </row>
@@ -6977,28 +6977,28 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>IHH</t>
         </is>
       </c>
       <c r="D145" s="9" t="n">
-        <v>1.05</v>
+        <v>8</v>
       </c>
       <c r="E145" s="17" t="n">
-        <v>-0.0367</v>
+        <v>-0.0037</v>
       </c>
       <c r="F145" s="11" t="n">
-        <v>956800</v>
+        <v>1159200</v>
       </c>
       <c r="G145" s="12" t="n">
-        <v>0.38</v>
+        <v>0.28</v>
       </c>
       <c r="H145" t="n">
-        <v>39.35</v>
+        <v>50.63</v>
       </c>
       <c r="I145" s="16" t="inlineStr">
         <is>
@@ -7006,10 +7006,10 @@
         </is>
       </c>
       <c r="J145" s="9" t="n">
-        <v>1.098</v>
+        <v>7.949</v>
       </c>
       <c r="K145" s="9" t="n">
-        <v>1.119</v>
+        <v>8.151</v>
       </c>
       <c r="L145" t="inlineStr"/>
       <c r="M145" s="14" t="inlineStr"/>
@@ -7022,28 +7022,28 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>0372</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>CHEEDING</t>
+          <t>DUFU</t>
         </is>
       </c>
       <c r="D146" s="9" t="n">
-        <v>0.595</v>
+        <v>2.85</v>
       </c>
       <c r="E146" s="17" t="n">
-        <v>-0.0083</v>
+        <v>-0.024</v>
       </c>
       <c r="F146" s="11" t="n">
-        <v>954000</v>
+        <v>1138500</v>
       </c>
       <c r="G146" s="12" t="n">
-        <v>0.36</v>
+        <v>0.38</v>
       </c>
       <c r="H146" t="n">
-        <v>49.07</v>
+        <v>55.28</v>
       </c>
       <c r="I146" s="16" t="inlineStr">
         <is>
@@ -7051,10 +7051,10 @@
         </is>
       </c>
       <c r="J146" s="9" t="n">
-        <v>0.593</v>
+        <v>2.787</v>
       </c>
       <c r="K146" s="9" t="n">
-        <v>0.61</v>
+        <v>2.685</v>
       </c>
       <c r="L146" t="inlineStr"/>
       <c r="M146" s="14" t="inlineStr"/>
@@ -7067,28 +7067,28 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>0395</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>DUFU</t>
+          <t>OGX</t>
         </is>
       </c>
       <c r="D147" s="9" t="n">
-        <v>2.85</v>
+        <v>0.43</v>
       </c>
       <c r="E147" s="17" t="n">
-        <v>-0.024</v>
+        <v>-0.0227</v>
       </c>
       <c r="F147" s="11" t="n">
-        <v>947800</v>
+        <v>1133800</v>
       </c>
       <c r="G147" s="12" t="n">
-        <v>0.32</v>
+        <v>0.36</v>
       </c>
       <c r="H147" t="n">
-        <v>55.28</v>
+        <v>47.37</v>
       </c>
       <c r="I147" s="16" t="inlineStr">
         <is>
@@ -7096,10 +7096,10 @@
         </is>
       </c>
       <c r="J147" s="9" t="n">
-        <v>2.787</v>
+        <v>0.434</v>
       </c>
       <c r="K147" s="9" t="n">
-        <v>2.685</v>
+        <v>0.452</v>
       </c>
       <c r="L147" t="inlineStr"/>
       <c r="M147" s="14" t="inlineStr"/>
@@ -7112,28 +7112,28 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>IHH</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D148" s="9" t="n">
-        <v>8</v>
+        <v>0.58</v>
       </c>
       <c r="E148" s="17" t="n">
-        <v>-0.0037</v>
+        <v>-0.0252</v>
       </c>
       <c r="F148" s="11" t="n">
-        <v>947000</v>
+        <v>1127700</v>
       </c>
       <c r="G148" s="12" t="n">
-        <v>0.23</v>
+        <v>0.35</v>
       </c>
       <c r="H148" t="n">
-        <v>50.63</v>
+        <v>52.94</v>
       </c>
       <c r="I148" s="16" t="inlineStr">
         <is>
@@ -7141,10 +7141,10 @@
         </is>
       </c>
       <c r="J148" s="9" t="n">
-        <v>7.949</v>
+        <v>0.57</v>
       </c>
       <c r="K148" s="9" t="n">
-        <v>8.151</v>
+        <v>0.575</v>
       </c>
       <c r="L148" t="inlineStr"/>
       <c r="M148" s="14" t="inlineStr"/>
@@ -7157,28 +7157,28 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>8524</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>TALIWRK</t>
         </is>
       </c>
       <c r="D149" s="9" t="n">
-        <v>0.84</v>
+        <v>0.26</v>
       </c>
       <c r="E149" s="17" t="n">
-        <v>-0.0059</v>
+        <v>-0.0189</v>
       </c>
       <c r="F149" s="11" t="n">
-        <v>925100</v>
+        <v>1102000</v>
       </c>
       <c r="G149" s="12" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="H149" t="n">
-        <v>64.11</v>
+        <v>51.19</v>
       </c>
       <c r="I149" s="16" t="inlineStr">
         <is>
@@ -7186,10 +7186,10 @@
         </is>
       </c>
       <c r="J149" s="9" t="n">
-        <v>0.801</v>
+        <v>0.254</v>
       </c>
       <c r="K149" s="9" t="n">
-        <v>0.72</v>
+        <v>0.271</v>
       </c>
       <c r="L149" t="inlineStr"/>
       <c r="M149" s="14" t="inlineStr"/>
@@ -7202,39 +7202,39 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>SPSETIA</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D150" s="9" t="n">
-        <v>0.765</v>
+        <v>0.775</v>
       </c>
       <c r="E150" s="17" t="n">
-        <v>-0.0192</v>
+        <v>-0.0064</v>
       </c>
       <c r="F150" s="11" t="n">
-        <v>918800</v>
+        <v>1098500</v>
       </c>
       <c r="G150" s="12" t="n">
-        <v>0.22</v>
+        <v>0.39</v>
       </c>
       <c r="H150" t="n">
-        <v>37.15</v>
-      </c>
-      <c r="I150" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.68</v>
+      </c>
+      <c r="I150" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J150" s="9" t="n">
-        <v>0.796</v>
+        <v>0.757</v>
       </c>
       <c r="K150" s="9" t="n">
-        <v>0.849</v>
+        <v>0.74</v>
       </c>
       <c r="L150" t="inlineStr"/>
       <c r="M150" s="14" t="inlineStr"/>
@@ -7247,39 +7247,39 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>0398</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>IOICORP</t>
+          <t>GDGROUP</t>
         </is>
       </c>
       <c r="D151" s="9" t="n">
-        <v>4.77</v>
+        <v>0.38</v>
       </c>
       <c r="E151" s="15" t="n">
-        <v>0.0021</v>
+        <v>0.0133</v>
       </c>
       <c r="F151" s="11" t="n">
-        <v>916200</v>
+        <v>1096500</v>
       </c>
       <c r="G151" s="12" t="n">
-        <v>0.11</v>
+        <v>1.34</v>
       </c>
       <c r="H151" t="n">
-        <v>55.58</v>
-      </c>
-      <c r="I151" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.79</v>
+      </c>
+      <c r="I151" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J151" s="9" t="n">
-        <v>4.747</v>
+        <v>0.378</v>
       </c>
       <c r="K151" s="9" t="n">
-        <v>4.589</v>
+        <v>0.381</v>
       </c>
       <c r="L151" t="inlineStr"/>
       <c r="M151" s="14" t="inlineStr"/>
@@ -7292,39 +7292,39 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>0388</t>
+          <t>0240</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>SEMICO</t>
+          <t>CORAZA</t>
         </is>
       </c>
       <c r="D152" s="9" t="n">
-        <v>0.615</v>
-      </c>
-      <c r="E152" s="10" t="n">
-        <v>0</v>
+        <v>1.05</v>
+      </c>
+      <c r="E152" s="17" t="n">
+        <v>-0.0367</v>
       </c>
       <c r="F152" s="11" t="n">
-        <v>910200</v>
+        <v>1080700</v>
       </c>
       <c r="G152" s="12" t="n">
-        <v>0.3</v>
+        <v>0.43</v>
       </c>
       <c r="H152" t="n">
-        <v>65.06</v>
-      </c>
-      <c r="I152" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>39.35</v>
+      </c>
+      <c r="I152" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J152" s="9" t="n">
-        <v>0.609</v>
+        <v>1.098</v>
       </c>
       <c r="K152" s="9" t="n">
-        <v>0.589</v>
+        <v>1.119</v>
       </c>
       <c r="L152" t="inlineStr"/>
       <c r="M152" s="14" t="inlineStr"/>
@@ -7337,39 +7337,39 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>3069</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>MFCB</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D153" s="9" t="n">
-        <v>3.01</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E153" s="17" t="n">
-        <v>-0.0227</v>
+        <v>-0.0408</v>
       </c>
       <c r="F153" s="11" t="n">
-        <v>905700</v>
+        <v>1073500</v>
       </c>
       <c r="G153" s="12" t="n">
-        <v>1.01</v>
+        <v>0.35</v>
       </c>
       <c r="H153" t="n">
-        <v>57.2</v>
-      </c>
-      <c r="I153" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.04</v>
+      </c>
+      <c r="I153" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J153" s="9" t="n">
-        <v>2.944</v>
+        <v>0.895</v>
       </c>
       <c r="K153" s="9" t="n">
-        <v>2.902</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="L153" t="inlineStr"/>
       <c r="M153" s="14" t="inlineStr"/>
@@ -7382,39 +7382,39 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>5073</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>NAIM</t>
         </is>
       </c>
       <c r="D154" s="9" t="n">
-        <v>1.28</v>
+        <v>0.645</v>
       </c>
       <c r="E154" s="17" t="n">
-        <v>-0.007800000000000001</v>
+        <v>-0.0529</v>
       </c>
       <c r="F154" s="11" t="n">
-        <v>897100</v>
+        <v>1060400</v>
       </c>
       <c r="G154" s="12" t="n">
-        <v>0.23</v>
+        <v>0.86</v>
       </c>
       <c r="H154" t="n">
-        <v>57.33</v>
-      </c>
-      <c r="I154" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.44</v>
+      </c>
+      <c r="I154" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J154" s="9" t="n">
-        <v>1.24</v>
+        <v>0.628</v>
       </c>
       <c r="K154" s="9" t="n">
-        <v>1.138</v>
+        <v>0.612</v>
       </c>
       <c r="L154" t="inlineStr"/>
       <c r="M154" s="14" t="inlineStr"/>
@@ -7427,39 +7427,39 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>5211</t>
+          <t>0450</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>SUNWAY</t>
+          <t>MFGROUP</t>
         </is>
       </c>
       <c r="D155" s="9" t="n">
-        <v>4.57</v>
-      </c>
-      <c r="E155" s="17" t="n">
-        <v>-0.013</v>
+        <v>0.26</v>
+      </c>
+      <c r="E155" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F155" s="11" t="n">
-        <v>881700</v>
+        <v>1052600</v>
       </c>
       <c r="G155" s="12" t="n">
-        <v>0.17</v>
+        <v>1.33</v>
       </c>
       <c r="H155" t="n">
-        <v>35.27</v>
-      </c>
-      <c r="I155" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.51</v>
+      </c>
+      <c r="I155" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J155" s="9" t="n">
-        <v>4.724</v>
+        <v>0.261</v>
       </c>
       <c r="K155" s="9" t="n">
-        <v>4.993</v>
+        <v>0.266</v>
       </c>
       <c r="L155" t="inlineStr"/>
       <c r="M155" s="14" t="inlineStr"/>
@@ -7472,28 +7472,28 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>7241</t>
+          <t>0372</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>NGGB</t>
+          <t>CHEEDING</t>
         </is>
       </c>
       <c r="D156" s="9" t="n">
-        <v>0.715</v>
+        <v>0.595</v>
       </c>
       <c r="E156" s="17" t="n">
-        <v>-0.0069</v>
+        <v>-0.0083</v>
       </c>
       <c r="F156" s="11" t="n">
-        <v>879800</v>
+        <v>1041200</v>
       </c>
       <c r="G156" s="12" t="n">
-        <v>0.25</v>
+        <v>0.39</v>
       </c>
       <c r="H156" t="n">
-        <v>53.25</v>
+        <v>49.07</v>
       </c>
       <c r="I156" s="16" t="inlineStr">
         <is>
@@ -7501,10 +7501,10 @@
         </is>
       </c>
       <c r="J156" s="9" t="n">
-        <v>0.708</v>
+        <v>0.593</v>
       </c>
       <c r="K156" s="9" t="n">
-        <v>0.713</v>
+        <v>0.61</v>
       </c>
       <c r="L156" t="inlineStr"/>
       <c r="M156" s="14" t="inlineStr"/>
@@ -7517,28 +7517,28 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>5272</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>RANHILL</t>
         </is>
       </c>
       <c r="D157" s="9" t="n">
-        <v>1.18</v>
+        <v>3.25</v>
       </c>
       <c r="E157" s="17" t="n">
-        <v>-0.0167</v>
+        <v>-0.0181</v>
       </c>
       <c r="F157" s="11" t="n">
-        <v>877600</v>
+        <v>1030800</v>
       </c>
       <c r="G157" s="12" t="n">
-        <v>0.24</v>
+        <v>0.4</v>
       </c>
       <c r="H157" t="n">
-        <v>66.7</v>
+        <v>73.03</v>
       </c>
       <c r="I157" s="16" t="inlineStr">
         <is>
@@ -7546,10 +7546,10 @@
         </is>
       </c>
       <c r="J157" s="9" t="n">
-        <v>1.108</v>
+        <v>2.939</v>
       </c>
       <c r="K157" s="9" t="n">
-        <v>1.007</v>
+        <v>2.522</v>
       </c>
       <c r="L157" t="inlineStr"/>
       <c r="M157" s="14" t="inlineStr"/>
@@ -7562,39 +7562,39 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>0466</t>
+          <t>3069</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>SRKKAI</t>
+          <t>MFCB</t>
         </is>
       </c>
       <c r="D158" s="9" t="n">
-        <v>0.51</v>
+        <v>3.01</v>
       </c>
       <c r="E158" s="17" t="n">
-        <v>-0.0286</v>
+        <v>-0.0227</v>
       </c>
       <c r="F158" s="11" t="n">
-        <v>867800</v>
+        <v>1016600</v>
       </c>
       <c r="G158" s="12" t="n">
-        <v>0.71</v>
+        <v>1.13</v>
       </c>
       <c r="H158" t="n">
-        <v>42.12</v>
-      </c>
-      <c r="I158" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>57.2</v>
+      </c>
+      <c r="I158" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J158" s="9" t="n">
-        <v>0.524</v>
+        <v>2.944</v>
       </c>
       <c r="K158" s="9" t="n">
-        <v>0.532</v>
+        <v>2.902</v>
       </c>
       <c r="L158" t="inlineStr"/>
       <c r="M158" s="14" t="inlineStr"/>
@@ -7607,28 +7607,28 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>SUNWAY</t>
         </is>
       </c>
       <c r="D159" s="9" t="n">
-        <v>0.9399999999999999</v>
+        <v>4.58</v>
       </c>
       <c r="E159" s="17" t="n">
-        <v>-0.0408</v>
+        <v>-0.0108</v>
       </c>
       <c r="F159" s="11" t="n">
-        <v>865800</v>
+        <v>965800</v>
       </c>
       <c r="G159" s="12" t="n">
-        <v>0.29</v>
+        <v>0.19</v>
       </c>
       <c r="H159" t="n">
-        <v>60.04</v>
+        <v>35.73</v>
       </c>
       <c r="I159" s="16" t="inlineStr">
         <is>
@@ -7636,10 +7636,10 @@
         </is>
       </c>
       <c r="J159" s="9" t="n">
-        <v>0.895</v>
+        <v>4.725</v>
       </c>
       <c r="K159" s="9" t="n">
-        <v>0.8070000000000001</v>
+        <v>4.993</v>
       </c>
       <c r="L159" t="inlineStr"/>
       <c r="M159" s="14" t="inlineStr"/>
@@ -7652,28 +7652,28 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>CPETECH</t>
         </is>
       </c>
       <c r="D160" s="9" t="n">
-        <v>1</v>
+        <v>1.28</v>
       </c>
       <c r="E160" s="17" t="n">
-        <v>-0.0196</v>
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F160" s="11" t="n">
-        <v>860700</v>
+        <v>944500</v>
       </c>
       <c r="G160" s="12" t="n">
-        <v>0.18</v>
+        <v>0.24</v>
       </c>
       <c r="H160" t="n">
-        <v>34.67</v>
+        <v>57.33</v>
       </c>
       <c r="I160" s="13" t="inlineStr">
         <is>
@@ -7681,10 +7681,10 @@
         </is>
       </c>
       <c r="J160" s="9" t="n">
-        <v>1.049</v>
+        <v>1.24</v>
       </c>
       <c r="K160" s="9" t="n">
-        <v>1.074</v>
+        <v>1.138</v>
       </c>
       <c r="L160" t="inlineStr"/>
       <c r="M160" s="14" t="inlineStr"/>
@@ -7697,28 +7697,28 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D161" s="9" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="E161" s="17" t="n">
-        <v>-0.0135</v>
+        <v>7.83</v>
+      </c>
+      <c r="E161" s="15" t="n">
+        <v>0.0051</v>
       </c>
       <c r="F161" s="11" t="n">
-        <v>859700</v>
+        <v>925700</v>
       </c>
       <c r="G161" s="12" t="n">
-        <v>0.25</v>
+        <v>0.08</v>
       </c>
       <c r="H161" t="n">
-        <v>53.82</v>
+        <v>36.58</v>
       </c>
       <c r="I161" s="16" t="inlineStr">
         <is>
@@ -7726,9 +7726,11 @@
         </is>
       </c>
       <c r="J161" s="9" t="n">
-        <v>2.863</v>
-      </c>
-      <c r="K161" s="9" t="n"/>
+        <v>7.975</v>
+      </c>
+      <c r="K161" s="9" t="n">
+        <v>8.260999999999999</v>
+      </c>
       <c r="L161" t="inlineStr"/>
       <c r="M161" s="14" t="inlineStr"/>
     </row>
@@ -7740,39 +7742,39 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>4383</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>JTIASA</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D162" s="9" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="E162" s="10" t="n">
-        <v>0</v>
+        <v>1.26</v>
+      </c>
+      <c r="E162" s="15" t="n">
+        <v>0.0161</v>
       </c>
       <c r="F162" s="11" t="n">
-        <v>852900</v>
+        <v>921800</v>
       </c>
       <c r="G162" s="12" t="n">
-        <v>0.18</v>
+        <v>0.35</v>
       </c>
       <c r="H162" t="n">
-        <v>36.18</v>
-      </c>
-      <c r="I162" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>83.94</v>
+      </c>
+      <c r="I162" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J162" s="9" t="n">
-        <v>0.998</v>
+        <v>1.045</v>
       </c>
       <c r="K162" s="9" t="n">
-        <v>1.047</v>
+        <v>0.888</v>
       </c>
       <c r="L162" t="inlineStr"/>
       <c r="M162" s="14" t="inlineStr"/>
@@ -7785,28 +7787,28 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>5302</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>ATECH</t>
         </is>
       </c>
       <c r="D163" s="9" t="n">
-        <v>1.26</v>
+        <v>0.77</v>
       </c>
       <c r="E163" s="15" t="n">
-        <v>0.0161</v>
+        <v>0.006500000000000001</v>
       </c>
       <c r="F163" s="11" t="n">
-        <v>832100</v>
+        <v>909500</v>
       </c>
       <c r="G163" s="12" t="n">
-        <v>0.31</v>
+        <v>0.62</v>
       </c>
       <c r="H163" t="n">
-        <v>83.94</v>
+        <v>52.54</v>
       </c>
       <c r="I163" s="16" t="inlineStr">
         <is>
@@ -7814,10 +7816,10 @@
         </is>
       </c>
       <c r="J163" s="9" t="n">
-        <v>1.045</v>
+        <v>0.765</v>
       </c>
       <c r="K163" s="9" t="n">
-        <v>0.888</v>
+        <v>0.755</v>
       </c>
       <c r="L163" t="inlineStr"/>
       <c r="M163" s="14" t="inlineStr"/>
@@ -7830,28 +7832,28 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D164" s="9" t="n">
-        <v>0.72</v>
+        <v>2.91</v>
       </c>
       <c r="E164" s="17" t="n">
-        <v>-0.0069</v>
+        <v>-0.0169</v>
       </c>
       <c r="F164" s="11" t="n">
-        <v>825500</v>
+        <v>909500</v>
       </c>
       <c r="G164" s="12" t="n">
-        <v>0.14</v>
+        <v>0.27</v>
       </c>
       <c r="H164" t="n">
-        <v>67.44</v>
+        <v>53.29</v>
       </c>
       <c r="I164" s="16" t="inlineStr">
         <is>
@@ -7859,11 +7861,9 @@
         </is>
       </c>
       <c r="J164" s="9" t="n">
-        <v>0.671</v>
-      </c>
-      <c r="K164" s="9" t="n">
-        <v>0.614</v>
-      </c>
+        <v>2.862</v>
+      </c>
+      <c r="K164" s="9" t="n"/>
       <c r="L164" t="inlineStr"/>
       <c r="M164" s="14" t="inlineStr"/>
     </row>
@@ -7875,39 +7875,39 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>5271</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>PECCA</t>
+          <t>TAKAFUL</t>
         </is>
       </c>
       <c r="D165" s="9" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="E165" s="15" t="n">
-        <v>0.0072</v>
+        <v>2.97</v>
+      </c>
+      <c r="E165" s="17" t="n">
+        <v>-0.01</v>
       </c>
       <c r="F165" s="11" t="n">
-        <v>813400</v>
+        <v>900800</v>
       </c>
       <c r="G165" s="12" t="n">
-        <v>0.42</v>
+        <v>0.84</v>
       </c>
       <c r="H165" t="n">
-        <v>70.67</v>
-      </c>
-      <c r="I165" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>32.8</v>
+      </c>
+      <c r="I165" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J165" s="9" t="n">
-        <v>1.356</v>
+        <v>3.07</v>
       </c>
       <c r="K165" s="9" t="n">
-        <v>1.325</v>
+        <v>3.152</v>
       </c>
       <c r="L165" t="inlineStr"/>
       <c r="M165" s="14" t="inlineStr"/>
@@ -7920,28 +7920,28 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>TAKAFUL</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D166" s="9" t="n">
-        <v>2.97</v>
+        <v>1</v>
       </c>
       <c r="E166" s="17" t="n">
-        <v>-0.01</v>
+        <v>-0.0196</v>
       </c>
       <c r="F166" s="11" t="n">
-        <v>807900</v>
+        <v>895600</v>
       </c>
       <c r="G166" s="12" t="n">
-        <v>0.75</v>
+        <v>0.19</v>
       </c>
       <c r="H166" t="n">
-        <v>32.8</v>
+        <v>34.67</v>
       </c>
       <c r="I166" s="13" t="inlineStr">
         <is>
@@ -7949,10 +7949,10 @@
         </is>
       </c>
       <c r="J166" s="9" t="n">
-        <v>3.07</v>
+        <v>1.049</v>
       </c>
       <c r="K166" s="9" t="n">
-        <v>3.152</v>
+        <v>1.074</v>
       </c>
       <c r="L166" t="inlineStr"/>
       <c r="M166" s="14" t="inlineStr"/>
@@ -7965,39 +7965,39 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>4383</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>ATECH</t>
+          <t>JTIASA</t>
         </is>
       </c>
       <c r="D167" s="9" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="E167" s="15" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.96</v>
+      </c>
+      <c r="E167" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F167" s="11" t="n">
-        <v>795100</v>
+        <v>892700</v>
       </c>
       <c r="G167" s="12" t="n">
-        <v>0.54</v>
+        <v>0.19</v>
       </c>
       <c r="H167" t="n">
-        <v>52.54</v>
-      </c>
-      <c r="I167" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.18</v>
+      </c>
+      <c r="I167" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J167" s="9" t="n">
-        <v>0.765</v>
+        <v>0.998</v>
       </c>
       <c r="K167" s="9" t="n">
-        <v>0.755</v>
+        <v>1.047</v>
       </c>
       <c r="L167" t="inlineStr"/>
       <c r="M167" s="14" t="inlineStr"/>
@@ -8010,28 +8010,28 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>7241</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>NGGB</t>
         </is>
       </c>
       <c r="D168" s="9" t="n">
-        <v>7.82</v>
-      </c>
-      <c r="E168" s="15" t="n">
-        <v>0.0039</v>
+        <v>0.715</v>
+      </c>
+      <c r="E168" s="17" t="n">
+        <v>-0.0069</v>
       </c>
       <c r="F168" s="11" t="n">
-        <v>766000</v>
+        <v>880200</v>
       </c>
       <c r="G168" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.25</v>
       </c>
       <c r="H168" t="n">
-        <v>35.8</v>
+        <v>53.25</v>
       </c>
       <c r="I168" s="16" t="inlineStr">
         <is>
@@ -8039,10 +8039,10 @@
         </is>
       </c>
       <c r="J168" s="9" t="n">
-        <v>7.974</v>
+        <v>0.708</v>
       </c>
       <c r="K168" s="9" t="n">
-        <v>8.26</v>
+        <v>0.713</v>
       </c>
       <c r="L168" t="inlineStr"/>
       <c r="M168" s="14" t="inlineStr"/>
@@ -8055,28 +8055,28 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>0466</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>UWC</t>
+          <t>SRKKAI</t>
         </is>
       </c>
       <c r="D169" s="9" t="n">
-        <v>6.67</v>
+        <v>0.51</v>
       </c>
       <c r="E169" s="17" t="n">
-        <v>-0.0305</v>
+        <v>-0.0286</v>
       </c>
       <c r="F169" s="11" t="n">
-        <v>757700</v>
+        <v>867800</v>
       </c>
       <c r="G169" s="12" t="n">
-        <v>0.22</v>
+        <v>0.71</v>
       </c>
       <c r="H169" t="n">
-        <v>52.86</v>
+        <v>42.12</v>
       </c>
       <c r="I169" s="16" t="inlineStr">
         <is>
@@ -8084,10 +8084,10 @@
         </is>
       </c>
       <c r="J169" s="9" t="n">
-        <v>6.569</v>
+        <v>0.524</v>
       </c>
       <c r="K169" s="9" t="n">
-        <v>6.495</v>
+        <v>0.532</v>
       </c>
       <c r="L169" t="inlineStr"/>
       <c r="M169" s="14" t="inlineStr"/>
@@ -8100,39 +8100,39 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>0391</t>
+          <t>0097</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>AMBEST</t>
+          <t>VITROX</t>
         </is>
       </c>
       <c r="D170" s="9" t="n">
-        <v>1.38</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="E170" s="17" t="n">
-        <v>-0.0143</v>
+        <v>-0.005</v>
       </c>
       <c r="F170" s="11" t="n">
-        <v>743000</v>
+        <v>824900</v>
       </c>
       <c r="G170" s="12" t="n">
-        <v>0.23</v>
+        <v>0.25</v>
       </c>
       <c r="H170" t="n">
-        <v>58.09</v>
-      </c>
-      <c r="I170" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.77</v>
+      </c>
+      <c r="I170" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J170" s="9" t="n">
-        <v>1.345</v>
+        <v>9.532999999999999</v>
       </c>
       <c r="K170" s="9" t="n">
-        <v>1.148</v>
+        <v>9.061999999999999</v>
       </c>
       <c r="L170" t="inlineStr"/>
       <c r="M170" s="14" t="inlineStr"/>
@@ -8145,28 +8145,28 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>0097</t>
+          <t>5271</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>VITROX</t>
+          <t>PECCA</t>
         </is>
       </c>
       <c r="D171" s="9" t="n">
-        <v>9.82</v>
-      </c>
-      <c r="E171" s="17" t="n">
-        <v>-0.0091</v>
+        <v>1.4</v>
+      </c>
+      <c r="E171" s="15" t="n">
+        <v>0.0072</v>
       </c>
       <c r="F171" s="11" t="n">
-        <v>718700</v>
+        <v>813400</v>
       </c>
       <c r="G171" s="12" t="n">
-        <v>0.22</v>
+        <v>0.42</v>
       </c>
       <c r="H171" t="n">
-        <v>62.34</v>
+        <v>70.67</v>
       </c>
       <c r="I171" s="16" t="inlineStr">
         <is>
@@ -8174,10 +8174,10 @@
         </is>
       </c>
       <c r="J171" s="9" t="n">
-        <v>9.529999999999999</v>
+        <v>1.356</v>
       </c>
       <c r="K171" s="9" t="n">
-        <v>9.061</v>
+        <v>1.325</v>
       </c>
       <c r="L171" t="inlineStr"/>
       <c r="M171" s="14" t="inlineStr"/>
@@ -8190,39 +8190,39 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>0271</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>WELLS</t>
+          <t>UWC</t>
         </is>
       </c>
       <c r="D172" s="9" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E172" s="10" t="n">
-        <v>0</v>
+        <v>6.67</v>
+      </c>
+      <c r="E172" s="17" t="n">
+        <v>-0.0305</v>
       </c>
       <c r="F172" s="11" t="n">
-        <v>700000</v>
+        <v>788300</v>
       </c>
       <c r="G172" s="12" t="n">
-        <v>0.72</v>
+        <v>0.23</v>
       </c>
       <c r="H172" t="n">
-        <v>48.02</v>
-      </c>
-      <c r="I172" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.86</v>
+      </c>
+      <c r="I172" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J172" s="9" t="n">
-        <v>0.631</v>
+        <v>6.569</v>
       </c>
       <c r="K172" s="9" t="n">
-        <v>0.637</v>
+        <v>6.495</v>
       </c>
       <c r="L172" t="inlineStr"/>
       <c r="M172" s="14" t="inlineStr"/>
@@ -8235,39 +8235,39 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>5328</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>LWSABAH</t>
+          <t>DAYANG</t>
         </is>
       </c>
       <c r="D173" s="9" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="E173" s="17" t="n">
-        <v>-0.0173</v>
+        <v>1.5</v>
+      </c>
+      <c r="E173" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F173" s="11" t="n">
-        <v>692300</v>
+        <v>775900</v>
       </c>
       <c r="G173" s="12" t="n">
-        <v>0.53</v>
+        <v>0.3</v>
       </c>
       <c r="H173" t="n">
-        <v>52.1</v>
-      </c>
-      <c r="I173" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.85</v>
+      </c>
+      <c r="I173" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J173" s="9" t="n">
-        <v>1.703</v>
+        <v>1.48</v>
       </c>
       <c r="K173" s="9" t="n">
-        <v>1.614</v>
+        <v>1.532</v>
       </c>
       <c r="L173" t="inlineStr"/>
       <c r="M173" s="14" t="inlineStr"/>
@@ -8280,28 +8280,28 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>7197</t>
+          <t>5328</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>GESHEN</t>
+          <t>LWSABAH</t>
         </is>
       </c>
       <c r="D174" s="9" t="n">
-        <v>1.08</v>
+        <v>1.68</v>
       </c>
       <c r="E174" s="17" t="n">
-        <v>-0.0046</v>
+        <v>-0.0289</v>
       </c>
       <c r="F174" s="11" t="n">
-        <v>657200</v>
+        <v>754300</v>
       </c>
       <c r="G174" s="12" t="n">
-        <v>1.74</v>
+        <v>0.58</v>
       </c>
       <c r="H174" t="n">
-        <v>22.96</v>
+        <v>49.53</v>
       </c>
       <c r="I174" s="13" t="inlineStr">
         <is>
@@ -8309,10 +8309,10 @@
         </is>
       </c>
       <c r="J174" s="9" t="n">
-        <v>1.179</v>
+        <v>1.701</v>
       </c>
       <c r="K174" s="9" t="n">
-        <v>1.285</v>
+        <v>1.614</v>
       </c>
       <c r="L174" t="inlineStr"/>
       <c r="M174" s="14" t="inlineStr"/>
@@ -8325,39 +8325,39 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>5272</t>
+          <t>0391</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>RANHILL</t>
+          <t>AMBEST</t>
         </is>
       </c>
       <c r="D175" s="9" t="n">
-        <v>3.17</v>
+        <v>1.38</v>
       </c>
       <c r="E175" s="17" t="n">
-        <v>-0.0423</v>
+        <v>-0.0143</v>
       </c>
       <c r="F175" s="11" t="n">
-        <v>650000</v>
+        <v>743000</v>
       </c>
       <c r="G175" s="12" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="H175" t="n">
-        <v>67.34999999999999</v>
-      </c>
-      <c r="I175" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>58.09</v>
+      </c>
+      <c r="I175" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J175" s="9" t="n">
-        <v>2.931</v>
+        <v>1.345</v>
       </c>
       <c r="K175" s="9" t="n">
-        <v>2.521</v>
+        <v>1.148</v>
       </c>
       <c r="L175" t="inlineStr"/>
       <c r="M175" s="14" t="inlineStr"/>
@@ -8370,28 +8370,28 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>7498</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>RALCO</t>
         </is>
       </c>
       <c r="D176" s="9" t="n">
-        <v>6.21</v>
-      </c>
-      <c r="E176" s="17" t="n">
-        <v>-0.0048</v>
+        <v>0.985</v>
+      </c>
+      <c r="E176" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F176" s="11" t="n">
-        <v>644900</v>
+        <v>739900</v>
       </c>
       <c r="G176" s="12" t="n">
-        <v>0.04</v>
+        <v>1.46</v>
       </c>
       <c r="H176" t="n">
-        <v>40.13</v>
+        <v>53.67</v>
       </c>
       <c r="I176" s="16" t="inlineStr">
         <is>
@@ -8399,10 +8399,10 @@
         </is>
       </c>
       <c r="J176" s="9" t="n">
-        <v>6.308</v>
+        <v>0.98</v>
       </c>
       <c r="K176" s="9" t="n">
-        <v>6.496</v>
+        <v>0.974</v>
       </c>
       <c r="L176" t="inlineStr"/>
       <c r="M176" s="14" t="inlineStr"/>
@@ -8415,39 +8415,39 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>SIMEPROP</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D177" s="9" t="n">
-        <v>1.27</v>
+        <v>6.21</v>
       </c>
       <c r="E177" s="17" t="n">
-        <v>-0.007800000000000001</v>
+        <v>-0.0048</v>
       </c>
       <c r="F177" s="11" t="n">
-        <v>638800</v>
+        <v>739200</v>
       </c>
       <c r="G177" s="12" t="n">
-        <v>0.12</v>
+        <v>0.04</v>
       </c>
       <c r="H177" t="n">
-        <v>42.22</v>
-      </c>
-      <c r="I177" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>40.13</v>
+      </c>
+      <c r="I177" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J177" s="9" t="n">
-        <v>1.29</v>
+        <v>6.308</v>
       </c>
       <c r="K177" s="9" t="n">
-        <v>1.322</v>
+        <v>6.496</v>
       </c>
       <c r="L177" t="inlineStr"/>
       <c r="M177" s="14" t="inlineStr"/>
@@ -8460,39 +8460,39 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>0245</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>SEG</t>
+          <t>MNHLDG</t>
         </is>
       </c>
       <c r="D178" s="9" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E178" s="10" t="n">
-        <v>0</v>
+        <v>3.93</v>
+      </c>
+      <c r="E178" s="17" t="n">
+        <v>-0.0175</v>
       </c>
       <c r="F178" s="11" t="n">
-        <v>631100</v>
+        <v>716200</v>
       </c>
       <c r="G178" s="12" t="n">
-        <v>0.48</v>
+        <v>0.21</v>
       </c>
       <c r="H178" t="n">
-        <v>54.14</v>
-      </c>
-      <c r="I178" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.35</v>
+      </c>
+      <c r="I178" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J178" s="9" t="n">
-        <v>0.633</v>
+        <v>3.744</v>
       </c>
       <c r="K178" s="9" t="n">
-        <v>0.629</v>
+        <v>3.395</v>
       </c>
       <c r="L178" t="inlineStr"/>
       <c r="M178" s="14" t="inlineStr"/>
@@ -8505,39 +8505,39 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>5288</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>SIMEPROP</t>
         </is>
       </c>
       <c r="D179" s="9" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="E179" s="17" t="n">
-        <v>-0.02</v>
+        <v>1.28</v>
+      </c>
+      <c r="E179" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F179" s="11" t="n">
-        <v>622000</v>
+        <v>706700</v>
       </c>
       <c r="G179" s="12" t="n">
-        <v>0.18</v>
+        <v>0.14</v>
       </c>
       <c r="H179" t="n">
-        <v>62.75</v>
-      </c>
-      <c r="I179" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.52</v>
+      </c>
+      <c r="I179" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J179" s="9" t="n">
-        <v>3.743</v>
+        <v>1.291</v>
       </c>
       <c r="K179" s="9" t="n">
-        <v>3.395</v>
+        <v>1.322</v>
       </c>
       <c r="L179" t="inlineStr"/>
       <c r="M179" s="14" t="inlineStr"/>
@@ -8550,39 +8550,39 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>0326</t>
+          <t>0271</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>SORENTO</t>
+          <t>WELLS</t>
         </is>
       </c>
       <c r="D180" s="9" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="E180" s="17" t="n">
-        <v>-0.0074</v>
+        <v>0.63</v>
+      </c>
+      <c r="E180" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F180" s="11" t="n">
-        <v>617700</v>
+        <v>700000</v>
       </c>
       <c r="G180" s="12" t="n">
-        <v>1.48</v>
+        <v>0.72</v>
       </c>
       <c r="H180" t="n">
-        <v>57.6</v>
-      </c>
-      <c r="I180" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.02</v>
+      </c>
+      <c r="I180" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J180" s="9" t="n">
-        <v>0.655</v>
+        <v>0.631</v>
       </c>
       <c r="K180" s="9" t="n">
-        <v>0.647</v>
+        <v>0.637</v>
       </c>
       <c r="L180" t="inlineStr"/>
       <c r="M180" s="14" t="inlineStr"/>
@@ -8595,28 +8595,28 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>3794</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>DAYANG</t>
+          <t>MCEMENT</t>
         </is>
       </c>
       <c r="D181" s="9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="E181" s="10" t="n">
-        <v>0</v>
+        <v>5.48</v>
+      </c>
+      <c r="E181" s="17" t="n">
+        <v>-0.0072</v>
       </c>
       <c r="F181" s="11" t="n">
-        <v>593500</v>
+        <v>669100</v>
       </c>
       <c r="G181" s="12" t="n">
-        <v>0.23</v>
+        <v>0.38</v>
       </c>
       <c r="H181" t="n">
-        <v>52.85</v>
+        <v>36.18</v>
       </c>
       <c r="I181" s="16" t="inlineStr">
         <is>
@@ -8624,10 +8624,10 @@
         </is>
       </c>
       <c r="J181" s="9" t="n">
-        <v>1.48</v>
+        <v>5.696</v>
       </c>
       <c r="K181" s="9" t="n">
-        <v>1.532</v>
+        <v>6.083</v>
       </c>
       <c r="L181" t="inlineStr"/>
       <c r="M181" s="14" t="inlineStr"/>
@@ -8640,39 +8640,39 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>5916</t>
+          <t>5309</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>MSC</t>
+          <t>ITMAX</t>
         </is>
       </c>
       <c r="D182" s="9" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="E182" s="17" t="n">
-        <v>-0.0172</v>
+        <v>4.6</v>
+      </c>
+      <c r="E182" s="15" t="n">
+        <v>0.0155</v>
       </c>
       <c r="F182" s="11" t="n">
-        <v>588400</v>
+        <v>664400</v>
       </c>
       <c r="G182" s="12" t="n">
-        <v>0.34</v>
+        <v>0.33</v>
       </c>
       <c r="H182" t="n">
-        <v>40.98</v>
-      </c>
-      <c r="I182" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.65</v>
+      </c>
+      <c r="I182" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J182" s="9" t="n">
-        <v>1.757</v>
+        <v>4.441</v>
       </c>
       <c r="K182" s="9" t="n">
-        <v>1.857</v>
+        <v>4.489</v>
       </c>
       <c r="L182" t="inlineStr"/>
       <c r="M182" s="14" t="inlineStr"/>
@@ -8685,39 +8685,39 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>0056</t>
+          <t>7197</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>NCT</t>
+          <t>GESHEN</t>
         </is>
       </c>
       <c r="D183" s="9" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="E183" s="10" t="n">
-        <v>0</v>
+        <v>1.08</v>
+      </c>
+      <c r="E183" s="17" t="n">
+        <v>-0.0046</v>
       </c>
       <c r="F183" s="11" t="n">
-        <v>585500</v>
+        <v>657200</v>
       </c>
       <c r="G183" s="12" t="n">
-        <v>0.25</v>
+        <v>1.74</v>
       </c>
       <c r="H183" t="n">
-        <v>48.38</v>
-      </c>
-      <c r="I183" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>22.96</v>
+      </c>
+      <c r="I183" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J183" s="9" t="n">
-        <v>0.5629999999999999</v>
+        <v>1.179</v>
       </c>
       <c r="K183" s="9" t="n">
-        <v>0.5620000000000001</v>
+        <v>1.285</v>
       </c>
       <c r="L183" t="inlineStr"/>
       <c r="M183" s="14" t="inlineStr"/>
@@ -8730,39 +8730,39 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>5326</t>
+          <t>0359</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>99SMART</t>
+          <t>HKB</t>
         </is>
       </c>
       <c r="D184" s="9" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="E184" s="15" t="n">
-        <v>0.0031</v>
+        <v>0.625</v>
+      </c>
+      <c r="E184" s="17" t="n">
+        <v>-0.007900000000000001</v>
       </c>
       <c r="F184" s="11" t="n">
-        <v>575500</v>
+        <v>631100</v>
       </c>
       <c r="G184" s="12" t="n">
-        <v>0.17</v>
+        <v>0.49</v>
       </c>
       <c r="H184" t="n">
-        <v>36.09</v>
-      </c>
-      <c r="I184" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.12</v>
+      </c>
+      <c r="I184" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J184" s="9" t="n">
-        <v>3.301</v>
+        <v>0.627</v>
       </c>
       <c r="K184" s="9" t="n">
-        <v>3.487</v>
+        <v>0.604</v>
       </c>
       <c r="L184" t="inlineStr"/>
       <c r="M184" s="14" t="inlineStr"/>
@@ -8775,39 +8775,39 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>9792</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>SEG</t>
         </is>
       </c>
       <c r="D185" s="9" t="n">
-        <v>0.63</v>
+        <v>0.635</v>
       </c>
       <c r="E185" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F185" s="11" t="n">
-        <v>573500</v>
+        <v>631100</v>
       </c>
       <c r="G185" s="12" t="n">
-        <v>0.39</v>
+        <v>0.48</v>
       </c>
       <c r="H185" t="n">
-        <v>78.42</v>
-      </c>
-      <c r="I185" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>54.14</v>
+      </c>
+      <c r="I185" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J185" s="9" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.633</v>
       </c>
       <c r="K185" s="9" t="n">
-        <v>0.492</v>
+        <v>0.629</v>
       </c>
       <c r="L185" t="inlineStr"/>
       <c r="M185" s="14" t="inlineStr"/>
@@ -8820,39 +8820,39 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>3794</t>
+          <t>5326</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>MCEMENT</t>
+          <t>99SMART</t>
         </is>
       </c>
       <c r="D186" s="9" t="n">
-        <v>5.49</v>
-      </c>
-      <c r="E186" s="17" t="n">
-        <v>-0.0054</v>
+        <v>3.21</v>
+      </c>
+      <c r="E186" s="15" t="n">
+        <v>0.0031</v>
       </c>
       <c r="F186" s="11" t="n">
-        <v>570200</v>
+        <v>630000</v>
       </c>
       <c r="G186" s="12" t="n">
-        <v>0.32</v>
+        <v>0.19</v>
       </c>
       <c r="H186" t="n">
-        <v>36.48</v>
-      </c>
-      <c r="I186" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.09</v>
+      </c>
+      <c r="I186" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J186" s="9" t="n">
-        <v>5.697</v>
+        <v>3.301</v>
       </c>
       <c r="K186" s="9" t="n">
-        <v>6.083</v>
+        <v>3.487</v>
       </c>
       <c r="L186" t="inlineStr"/>
       <c r="M186" s="14" t="inlineStr"/>
@@ -8874,19 +8874,19 @@
         </is>
       </c>
       <c r="D187" s="9" t="n">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="E187" s="17" t="n">
-        <v>-0.0451</v>
+        <v>-0.0504</v>
       </c>
       <c r="F187" s="11" t="n">
-        <v>560400</v>
+        <v>621400</v>
       </c>
       <c r="G187" s="12" t="n">
-        <v>0.53</v>
+        <v>0.59</v>
       </c>
       <c r="H187" t="n">
-        <v>50.54</v>
+        <v>49.13</v>
       </c>
       <c r="I187" s="13" t="inlineStr">
         <is>
@@ -8894,10 +8894,10 @@
         </is>
       </c>
       <c r="J187" s="9" t="n">
-        <v>3.655</v>
+        <v>3.654</v>
       </c>
       <c r="K187" s="9" t="n">
-        <v>3.324</v>
+        <v>3.323</v>
       </c>
       <c r="L187" t="inlineStr"/>
       <c r="M187" s="14" t="inlineStr"/>
@@ -8910,39 +8910,39 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>5330</t>
+          <t>7084</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>TMK</t>
+          <t>QL</t>
         </is>
       </c>
       <c r="D188" s="9" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="E188" s="17" t="n">
-        <v>-0.0336</v>
+        <v>4.02</v>
+      </c>
+      <c r="E188" s="15" t="n">
+        <v>0.0025</v>
       </c>
       <c r="F188" s="11" t="n">
-        <v>550700</v>
+        <v>619800</v>
       </c>
       <c r="G188" s="12" t="n">
-        <v>0.41</v>
+        <v>0.36</v>
       </c>
       <c r="H188" t="n">
-        <v>45.7</v>
-      </c>
-      <c r="I188" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.04</v>
+      </c>
+      <c r="I188" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J188" s="9" t="n">
-        <v>2.974</v>
+        <v>3.934</v>
       </c>
       <c r="K188" s="9" t="n">
-        <v>2.798</v>
+        <v>3.93</v>
       </c>
       <c r="L188" t="inlineStr"/>
       <c r="M188" s="14" t="inlineStr"/>
@@ -8955,39 +8955,39 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>7174</t>
+          <t>0326</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>CAB</t>
+          <t>SORENTO</t>
         </is>
       </c>
       <c r="D189" s="9" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="E189" s="15" t="n">
-        <v>0.0189</v>
+        <v>0.67</v>
+      </c>
+      <c r="E189" s="17" t="n">
+        <v>-0.0074</v>
       </c>
       <c r="F189" s="11" t="n">
-        <v>549600</v>
+        <v>617700</v>
       </c>
       <c r="G189" s="12" t="n">
-        <v>0.98</v>
+        <v>1.48</v>
       </c>
       <c r="H189" t="n">
-        <v>60.7</v>
-      </c>
-      <c r="I189" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.6</v>
+      </c>
+      <c r="I189" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J189" s="9" t="n">
-        <v>0.53</v>
+        <v>0.655</v>
       </c>
       <c r="K189" s="9" t="n">
-        <v>0.527</v>
+        <v>0.647</v>
       </c>
       <c r="L189" t="inlineStr"/>
       <c r="M189" s="14" t="inlineStr"/>
@@ -9000,39 +9000,39 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>5180</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>CLMT</t>
+          <t>AWC</t>
         </is>
       </c>
       <c r="D190" s="9" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="E190" s="10" t="n">
-        <v>0</v>
+        <v>0.635</v>
+      </c>
+      <c r="E190" s="15" t="n">
+        <v>0.007900000000000001</v>
       </c>
       <c r="F190" s="11" t="n">
-        <v>541300</v>
+        <v>606300</v>
       </c>
       <c r="G190" s="12" t="n">
-        <v>0.14</v>
+        <v>0.41</v>
       </c>
       <c r="H190" t="n">
-        <v>43.06</v>
-      </c>
-      <c r="I190" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>79.06999999999999</v>
+      </c>
+      <c r="I190" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J190" s="9" t="n">
-        <v>0.587</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="K190" s="9" t="n">
-        <v>0.587</v>
+        <v>0.492</v>
       </c>
       <c r="L190" t="inlineStr"/>
       <c r="M190" s="14" t="inlineStr"/>
@@ -9045,39 +9045,39 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>7498</t>
+          <t>5180</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>RALCO</t>
+          <t>CLMT</t>
         </is>
       </c>
       <c r="D191" s="9" t="n">
-        <v>0.985</v>
+        <v>0.58</v>
       </c>
       <c r="E191" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F191" s="11" t="n">
-        <v>523900</v>
+        <v>606200</v>
       </c>
       <c r="G191" s="12" t="n">
-        <v>1.03</v>
+        <v>0.16</v>
       </c>
       <c r="H191" t="n">
-        <v>53.67</v>
-      </c>
-      <c r="I191" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.06</v>
+      </c>
+      <c r="I191" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J191" s="9" t="n">
-        <v>0.98</v>
+        <v>0.587</v>
       </c>
       <c r="K191" s="9" t="n">
-        <v>0.974</v>
+        <v>0.587</v>
       </c>
       <c r="L191" t="inlineStr"/>
       <c r="M191" s="14" t="inlineStr"/>
@@ -9090,45 +9090,630 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>5309</t>
+          <t>5916</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>ITMAX</t>
+          <t>MSC</t>
         </is>
       </c>
       <c r="D192" s="9" t="n">
-        <v>4.58</v>
-      </c>
-      <c r="E192" s="15" t="n">
-        <v>0.011</v>
+        <v>1.71</v>
+      </c>
+      <c r="E192" s="17" t="n">
+        <v>-0.0172</v>
       </c>
       <c r="F192" s="11" t="n">
-        <v>523800</v>
+        <v>599400</v>
       </c>
       <c r="G192" s="12" t="n">
-        <v>0.26</v>
+        <v>0.35</v>
       </c>
       <c r="H192" t="n">
-        <v>58.67</v>
-      </c>
-      <c r="I192" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.98</v>
+      </c>
+      <c r="I192" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J192" s="9" t="n">
-        <v>4.439</v>
+        <v>1.757</v>
       </c>
       <c r="K192" s="9" t="n">
-        <v>4.489</v>
+        <v>1.857</v>
       </c>
       <c r="L192" t="inlineStr"/>
       <c r="M192" s="14" t="inlineStr"/>
     </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>5330</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>TMK</t>
+        </is>
+      </c>
+      <c r="D193" s="9" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="E193" s="17" t="n">
+        <v>-0.0302</v>
+      </c>
+      <c r="F193" s="11" t="n">
+        <v>597000</v>
+      </c>
+      <c r="G193" s="12" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="H193" t="n">
+        <v>46.35</v>
+      </c>
+      <c r="I193" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J193" s="9" t="n">
+        <v>2.975</v>
+      </c>
+      <c r="K193" s="9" t="n">
+        <v>2.799</v>
+      </c>
+      <c r="L193" t="inlineStr"/>
+      <c r="M193" s="14" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>0056</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>NCT</t>
+        </is>
+      </c>
+      <c r="D194" s="9" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E194" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F194" s="11" t="n">
+        <v>585500</v>
+      </c>
+      <c r="G194" s="12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H194" t="n">
+        <v>48.38</v>
+      </c>
+      <c r="I194" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J194" s="9" t="n">
+        <v>0.5629999999999999</v>
+      </c>
+      <c r="K194" s="9" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="L194" t="inlineStr"/>
+      <c r="M194" s="14" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>6947</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>CDB</t>
+        </is>
+      </c>
+      <c r="D195" s="9" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="E195" s="17" t="n">
+        <v>-0.0039</v>
+      </c>
+      <c r="F195" s="11" t="n">
+        <v>572600</v>
+      </c>
+      <c r="G195" s="12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H195" t="n">
+        <v>30.14</v>
+      </c>
+      <c r="I195" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J195" s="9" t="n">
+        <v>2.668</v>
+      </c>
+      <c r="K195" s="9" t="n">
+        <v>2.788</v>
+      </c>
+      <c r="L195" t="inlineStr"/>
+      <c r="M195" s="14" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>7174</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>CAB</t>
+        </is>
+      </c>
+      <c r="D196" s="9" t="n">
+        <v>0.535</v>
+      </c>
+      <c r="E196" s="15" t="n">
+        <v>0.009399999999999999</v>
+      </c>
+      <c r="F196" s="11" t="n">
+        <v>565300</v>
+      </c>
+      <c r="G196" s="12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="H196" t="n">
+        <v>56.81</v>
+      </c>
+      <c r="I196" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J196" s="9" t="n">
+        <v>0.529</v>
+      </c>
+      <c r="K196" s="9" t="n">
+        <v>0.527</v>
+      </c>
+      <c r="L196" t="inlineStr"/>
+      <c r="M196" s="14" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>5337</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>ECOSHOP</t>
+        </is>
+      </c>
+      <c r="D197" s="9" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="E197" s="15" t="n">
+        <v>0.0068</v>
+      </c>
+      <c r="F197" s="11" t="n">
+        <v>553400</v>
+      </c>
+      <c r="G197" s="12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H197" t="n">
+        <v>56.14</v>
+      </c>
+      <c r="I197" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J197" s="9" t="n">
+        <v>1.474</v>
+      </c>
+      <c r="K197" s="9" t="n">
+        <v>1.473</v>
+      </c>
+      <c r="L197" t="inlineStr"/>
+      <c r="M197" s="14" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>5176</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>SUNREIT</t>
+        </is>
+      </c>
+      <c r="D198" s="9" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="E198" s="15" t="n">
+        <v>0.0049</v>
+      </c>
+      <c r="F198" s="11" t="n">
+        <v>546300</v>
+      </c>
+      <c r="G198" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H198" t="n">
+        <v>45.75</v>
+      </c>
+      <c r="I198" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J198" s="9" t="n">
+        <v>2.064</v>
+      </c>
+      <c r="K198" s="9" t="n">
+        <v>2.108</v>
+      </c>
+      <c r="L198" t="inlineStr"/>
+      <c r="M198" s="14" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>5263</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>SUNCON</t>
+        </is>
+      </c>
+      <c r="D199" s="9" t="n">
+        <v>7.77</v>
+      </c>
+      <c r="E199" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F199" s="11" t="n">
+        <v>538300</v>
+      </c>
+      <c r="G199" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H199" t="n">
+        <v>51.88</v>
+      </c>
+      <c r="I199" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J199" s="9" t="n">
+        <v>7.666</v>
+      </c>
+      <c r="K199" s="9" t="n">
+        <v>7.808</v>
+      </c>
+      <c r="L199" t="inlineStr"/>
+      <c r="M199" s="14" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>0246</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>CNERGEN</t>
+        </is>
+      </c>
+      <c r="D200" s="9" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="E200" s="17" t="n">
+        <v>-0.0213</v>
+      </c>
+      <c r="F200" s="11" t="n">
+        <v>527900</v>
+      </c>
+      <c r="G200" s="12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H200" t="n">
+        <v>56.09</v>
+      </c>
+      <c r="I200" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J200" s="9" t="n">
+        <v>0.907</v>
+      </c>
+      <c r="K200" s="9" t="n">
+        <v>0.782</v>
+      </c>
+      <c r="L200" t="inlineStr"/>
+      <c r="M200" s="14" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>0151</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>KGB</t>
+        </is>
+      </c>
+      <c r="D201" s="9" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="E201" s="17" t="n">
+        <v>-0.0267</v>
+      </c>
+      <c r="F201" s="11" t="n">
+        <v>517000</v>
+      </c>
+      <c r="G201" s="12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H201" t="n">
+        <v>51.9</v>
+      </c>
+      <c r="I201" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J201" s="9" t="n">
+        <v>8.709</v>
+      </c>
+      <c r="K201" s="9" t="n">
+        <v>8.571</v>
+      </c>
+      <c r="L201" t="inlineStr"/>
+      <c r="M201" s="14" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>4715</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>GENM</t>
+        </is>
+      </c>
+      <c r="D202" s="9" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="E202" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F202" s="11" t="n">
+        <v>513800</v>
+      </c>
+      <c r="G202" s="12" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H202" t="n">
+        <v>33.08</v>
+      </c>
+      <c r="I202" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J202" s="9" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="K202" s="9" t="n">
+        <v>1.675</v>
+      </c>
+      <c r="L202" t="inlineStr"/>
+      <c r="M202" s="14" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>7293</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>YINSON</t>
+        </is>
+      </c>
+      <c r="D203" s="9" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="E203" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F203" s="11" t="n">
+        <v>509000</v>
+      </c>
+      <c r="G203" s="12" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H203" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="I203" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J203" s="9" t="n">
+        <v>2.054</v>
+      </c>
+      <c r="K203" s="9" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="L203" t="inlineStr"/>
+      <c r="M203" s="14" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>5246</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>WPRTS</t>
+        </is>
+      </c>
+      <c r="D204" s="9" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="E204" s="15" t="n">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="F204" s="11" t="n">
+        <v>506400</v>
+      </c>
+      <c r="G204" s="12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H204" t="n">
+        <v>47.43</v>
+      </c>
+      <c r="I204" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J204" s="9" t="n">
+        <v>6.781</v>
+      </c>
+      <c r="K204" s="9" t="n">
+        <v>6.804</v>
+      </c>
+      <c r="L204" t="inlineStr"/>
+      <c r="M204" s="14" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>9075</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>THETA</t>
+        </is>
+      </c>
+      <c r="D205" s="9" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="E205" s="17" t="n">
+        <v>-0.031</v>
+      </c>
+      <c r="F205" s="11" t="n">
+        <v>503300</v>
+      </c>
+      <c r="G205" s="12" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H205" t="n">
+        <v>44.85</v>
+      </c>
+      <c r="I205" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J205" s="9" t="n">
+        <v>0.651</v>
+      </c>
+      <c r="K205" s="9" t="n">
+        <v>0.654</v>
+      </c>
+      <c r="L205" t="inlineStr"/>
+      <c r="M205" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M192"/>
+  <autoFilter ref="A1:M205"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>